--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -475,7 +475,7 @@
     <t>Real Madrid</t>
   </si>
   <si>
-    <t>2026-09-13 07:13:58</t>
+    <t>2026-09-13 09:38:58</t>
   </si>
 </sst>
 </file>
@@ -1072,10 +1072,10 @@
         <v>1.44</v>
       </c>
       <c r="G2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
         <v>18</v>
@@ -1084,7 +1084,7 @@
         <v>3.85</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L2">
         <v>1.49</v>
@@ -1096,7 +1096,7 @@
         <v>2.7</v>
       </c>
       <c r="O2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P2">
         <v>1.58</v>
@@ -1105,10 +1105,10 @@
         <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T2">
         <v>2.52</v>
@@ -1120,10 +1120,10 @@
         <v>1.09</v>
       </c>
       <c r="W2">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="X2">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="Y2">
         <v>1000</v>
@@ -1135,10 +1135,10 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="AC2">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -1147,10 +1147,10 @@
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="AG2">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="AH2">
         <v>1000</v>
@@ -1159,7 +1159,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="AK2">
         <v>1000</v>
@@ -1171,7 +1171,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1231,7 +1231,7 @@
         <v>1.94</v>
       </c>
       <c r="BH2">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="BI2">
         <v>2.54</v>
@@ -1249,7 +1249,7 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="BO2">
         <v>2.96</v>
@@ -1317,7 +1317,7 @@
         <v>2.84</v>
       </c>
       <c r="H3">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I3">
         <v>3.55</v>
@@ -1326,7 +1326,7 @@
         <v>2.94</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
         <v>1.52</v>
@@ -1335,13 +1335,13 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
         <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q3">
         <v>2.32</v>
@@ -1553,61 +1553,61 @@
         <v>131</v>
       </c>
       <c r="F4">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="G4">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="J4">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="K4">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
         <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S4">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V4">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W4">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4">
         <v>36</v>
@@ -1664,55 +1664,55 @@
         <v>1.87</v>
       </c>
       <c r="AQ4">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AR4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AS4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AT4">
         <v>5.7</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>2.08</v>
       </c>
       <c r="AV4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AW4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AX4">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AY4">
         <v>7.4</v>
       </c>
       <c r="AZ4">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="BA4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BB4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BC4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BD4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BE4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BF4">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="BG4">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1798,10 +1798,10 @@
         <v>1.87</v>
       </c>
       <c r="G5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H5">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I5">
         <v>4.7</v>
@@ -1828,13 +1828,13 @@
         <v>2.04</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R5">
         <v>1.39</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T5">
         <v>1.66</v>
@@ -1846,7 +1846,7 @@
         <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2040,7 +2040,7 @@
         <v>4.2</v>
       </c>
       <c r="G6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H6">
         <v>2.12</v>
@@ -2049,7 +2049,7 @@
         <v>2.44</v>
       </c>
       <c r="J6">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K6">
         <v>3.45</v>
@@ -2067,10 +2067,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Q6">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2279,16 +2279,16 @@
         <v>134</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G7">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H7">
         <v>3.6</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J7">
         <v>2.96</v>
@@ -2312,7 +2312,7 @@
         <v>1.4</v>
       </c>
       <c r="Q7">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2763,22 +2763,22 @@
         <v>136</v>
       </c>
       <c r="F9">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="G9">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="I9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>3.5</v>
       </c>
       <c r="K9">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3005,22 +3005,22 @@
         <v>137</v>
       </c>
       <c r="F10">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="G10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H10">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="I10">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="J10">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3035,10 +3035,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="Q10">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3247,7 +3247,7 @@
         <v>138</v>
       </c>
       <c r="F11">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -3259,10 +3259,10 @@
         <v>4.1</v>
       </c>
       <c r="J11">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3280,7 +3280,7 @@
         <v>2.58</v>
       </c>
       <c r="Q11">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3489,22 +3489,22 @@
         <v>139</v>
       </c>
       <c r="F12">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="G12">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H12">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>11</v>
       </c>
       <c r="J12">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K12">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3519,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3731,22 +3731,22 @@
         <v>140</v>
       </c>
       <c r="F13">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="G13">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H13">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I13">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K13">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3761,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q13">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3973,16 +3973,16 @@
         <v>141</v>
       </c>
       <c r="F14">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G14">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H14">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I14">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J14">
         <v>3.5</v>
@@ -4003,7 +4003,7 @@
         <v>1.35</v>
       </c>
       <c r="P14">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q14">
         <v>2.06</v>
@@ -4036,10 +4036,10 @@
         <v>29</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -4048,7 +4048,7 @@
         <v>16</v>
       </c>
       <c r="AE14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF14">
         <v>13</v>
@@ -4060,10 +4060,10 @@
         <v>19</v>
       </c>
       <c r="AI14">
-        <v>920</v>
+        <v>610</v>
       </c>
       <c r="AJ14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK14">
         <v>25</v>
@@ -4102,7 +4102,7 @@
         <v>14</v>
       </c>
       <c r="AW14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX14">
         <v>11.5</v>
@@ -4117,7 +4117,7 @@
         <v>46</v>
       </c>
       <c r="BB14">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC14">
         <v>20</v>
@@ -4215,22 +4215,22 @@
         <v>142</v>
       </c>
       <c r="F15">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="J15">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K15">
-        <v>920</v>
+        <v>4.9</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4245,10 +4245,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4457,22 +4457,22 @@
         <v>143</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H16">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="J16">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>920</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4487,10 +4487,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>2.52</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4729,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q17">
         <v>1.63</v>
@@ -4941,10 +4941,10 @@
         <v>145</v>
       </c>
       <c r="F18">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G18">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H18">
         <v>4.8</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q18">
         <v>2.64</v>
@@ -5186,19 +5186,19 @@
         <v>1.67</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="H19">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I19">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J19">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5213,10 +5213,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q19">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5434,7 +5434,7 @@
         <v>13.5</v>
       </c>
       <c r="I20">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="J20">
         <v>8.6</v>
@@ -5667,37 +5667,37 @@
         <v>148</v>
       </c>
       <c r="F21">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G21">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H21">
+        <v>5</v>
+      </c>
+      <c r="I21">
         <v>5.1</v>
       </c>
-      <c r="I21">
-        <v>5.3</v>
-      </c>
       <c r="J21">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K21">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O21">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P21">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q21">
         <v>2.38</v>
@@ -5706,13 +5706,13 @@
         <v>1.25</v>
       </c>
       <c r="S21">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T21">
         <v>2.08</v>
       </c>
       <c r="U21">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -5745,7 +5745,7 @@
         <v>1000</v>
       </c>
       <c r="AF21">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG21">
         <v>11</v>
@@ -5763,13 +5763,13 @@
         <v>25</v>
       </c>
       <c r="AL21">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AM21">
         <v>1000</v>
       </c>
       <c r="AN21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO21">
         <v>1000</v>
@@ -5790,22 +5790,22 @@
         <v>6.6</v>
       </c>
       <c r="AU21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV21">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW21">
         <v>34</v>
       </c>
       <c r="AX21">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY21">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ21">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA21">
         <v>38</v>
@@ -5909,19 +5909,19 @@
         <v>149</v>
       </c>
       <c r="F22">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G22">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H22">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="I22">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K22">
         <v>4.1</v>
@@ -5942,7 +5942,7 @@
         <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6151,13 +6151,13 @@
         <v>150</v>
       </c>
       <c r="F23">
+        <v>1.61</v>
+      </c>
+      <c r="G23">
         <v>1.62</v>
       </c>
-      <c r="G23">
-        <v>1.65</v>
-      </c>
       <c r="H23">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I23">
         <v>6.2</v>
@@ -6393,13 +6393,13 @@
         <v>151</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G24">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H24">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I24">
         <v>4.2</v>
@@ -6408,7 +6408,7 @@
         <v>3.65</v>
       </c>
       <c r="K24">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6635,22 +6635,22 @@
         <v>152</v>
       </c>
       <c r="F25">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="G25">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="H25">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="I25">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="J25">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="K25">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6659,28 +6659,28 @@
         <v>1.02</v>
       </c>
       <c r="N25">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O25">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P25">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q25">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R25">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="S25">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="T25">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U25">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -6689,25 +6689,25 @@
         <v>0</v>
       </c>
       <c r="X25">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Y25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z25">
         <v>10.5</v>
       </c>
       <c r="AA25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB25">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AC25">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD25">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE25">
         <v>12</v>
@@ -6716,13 +6716,13 @@
         <v>1000</v>
       </c>
       <c r="AG25">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AH25">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI25">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ25">
         <v>470</v>
@@ -6734,28 +6734,28 @@
         <v>110</v>
       </c>
       <c r="AM25">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AN25">
         <v>1000</v>
       </c>
       <c r="AO25">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AP25">
         <v>32</v>
       </c>
       <c r="AQ25">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR25">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT25">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AU25">
         <v>13.5</v>
@@ -6773,7 +6773,7 @@
         <v>29</v>
       </c>
       <c r="AZ25">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA25">
         <v>21</v>
@@ -6785,7 +6785,7 @@
         <v>42</v>
       </c>
       <c r="BD25">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE25">
         <v>55</v>
@@ -6794,7 +6794,7 @@
         <v>40</v>
       </c>
       <c r="BG25">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BH25">
         <v>970</v>
@@ -6839,7 +6839,7 @@
         <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BW25">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="145">
   <si>
     <t>League</t>
   </si>
@@ -271,9 +271,6 @@
     <t>Egyptian Premier</t>
   </si>
   <si>
-    <t>Latvian Virsliga</t>
-  </si>
-  <si>
     <t>Polish Ekstraklasa</t>
   </si>
   <si>
@@ -295,9 +292,6 @@
     <t>Dutch Eredivisie</t>
   </si>
   <si>
-    <t>English Sky Bet Championship</t>
-  </si>
-  <si>
     <t>2026-09-15</t>
   </si>
   <si>
@@ -325,9 +319,6 @@
     <t>18:30:00</t>
   </si>
   <si>
-    <t>18:45:00</t>
-  </si>
-  <si>
     <t>19:30:00</t>
   </si>
   <si>
@@ -349,9 +340,6 @@
     <t>Wadi Degla</t>
   </si>
   <si>
-    <t>SK Super Nova</t>
-  </si>
-  <si>
     <t>Rakow Czestochowa</t>
   </si>
   <si>
@@ -394,12 +382,6 @@
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>Middlesbrough</t>
-  </si>
-  <si>
-    <t>Bristol City</t>
-  </si>
-  <si>
     <t>Elche</t>
   </si>
   <si>
@@ -421,9 +403,6 @@
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>FK Riga</t>
-  </si>
-  <si>
     <t>Zaglebie Lubin</t>
   </si>
   <si>
@@ -466,16 +445,10 @@
     <t>Gornik Zabrze</t>
   </si>
   <si>
-    <t>Millwall</t>
-  </si>
-  <si>
-    <t>Lincoln</t>
-  </si>
-  <si>
     <t>Real Madrid</t>
   </si>
   <si>
-    <t>2026-09-13 09:38:58</t>
+    <t>2026-09-13 11:58:09</t>
   </si>
 </sst>
 </file>
@@ -807,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1057,16 +1030,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F2">
         <v>1.44</v>
@@ -1075,7 +1048,7 @@
         <v>1.53</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
         <v>18</v>
@@ -1084,7 +1057,7 @@
         <v>3.85</v>
       </c>
       <c r="K2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>1.49</v>
@@ -1096,16 +1069,16 @@
         <v>2.7</v>
       </c>
       <c r="O2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q2">
         <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
         <v>4.3</v>
@@ -1120,10 +1093,10 @@
         <v>1.09</v>
       </c>
       <c r="W2">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="X2">
-        <v>570</v>
+        <v>970</v>
       </c>
       <c r="Y2">
         <v>1000</v>
@@ -1135,10 +1108,10 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>570</v>
+        <v>460</v>
       </c>
       <c r="AC2">
-        <v>570</v>
+        <v>460</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -1147,10 +1120,10 @@
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>570</v>
+        <v>970</v>
       </c>
       <c r="AG2">
-        <v>570</v>
+        <v>460</v>
       </c>
       <c r="AH2">
         <v>1000</v>
@@ -1159,7 +1132,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>570</v>
+        <v>460</v>
       </c>
       <c r="AK2">
         <v>1000</v>
@@ -1171,7 +1144,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>570</v>
+        <v>970</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1231,10 +1204,10 @@
         <v>1.94</v>
       </c>
       <c r="BH2">
-        <v>570</v>
+        <v>970</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>1.35</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
@@ -1249,16 +1222,16 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>570</v>
+        <v>970</v>
       </c>
       <c r="BO2">
-        <v>2.96</v>
+        <v>1.46</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1270,7 +1243,7 @@
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1291,7 +1264,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1299,16 +1272,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
         <v>94</v>
       </c>
-      <c r="C3" t="s">
-        <v>96</v>
-      </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F3">
         <v>2.48</v>
@@ -1317,22 +1290,22 @@
         <v>2.84</v>
       </c>
       <c r="H3">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J3">
         <v>2.94</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
         <v>1.52</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
         <v>2.96</v>
@@ -1350,7 +1323,7 @@
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T3">
         <v>1.91</v>
@@ -1359,7 +1332,7 @@
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
         <v>1.54</v>
@@ -1533,7 +1506,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1541,178 +1514,178 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="H4">
         <v>10</v>
       </c>
       <c r="I4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="V4">
         <v>1.09</v>
       </c>
       <c r="W4">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="X4">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Y4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF4">
         <v>8.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN4">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AP4">
-        <v>1.87</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
-        <v>1.98</v>
+        <v>6.8</v>
       </c>
       <c r="AR4">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="AS4">
-        <v>2.08</v>
+        <v>7.8</v>
       </c>
       <c r="AT4">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="AV4">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="AW4">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="AX4">
-        <v>1.66</v>
+        <v>7</v>
       </c>
       <c r="AY4">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>1.99</v>
+        <v>6.6</v>
       </c>
       <c r="BA4">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="BB4">
-        <v>2.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4">
-        <v>2.08</v>
+        <v>14.5</v>
       </c>
       <c r="BD4">
-        <v>2.08</v>
+        <v>7.2</v>
       </c>
       <c r="BE4">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="BF4">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG4">
-        <v>2.08</v>
+        <v>7.8</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1775,7 +1748,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1783,70 +1756,70 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F5">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="G5">
         <v>2.08</v>
       </c>
       <c r="H5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J5">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q5">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S5">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1855,106 +1828,106 @@
         <v>90</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB5">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>90</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF5">
         <v>29</v>
       </c>
       <c r="AG5">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM5">
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP5">
         <v>11</v>
       </c>
       <c r="AQ5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR5">
-        <v>1.37</v>
+        <v>2.38</v>
       </c>
       <c r="AS5">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="AT5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW5">
-        <v>1.37</v>
+        <v>2.38</v>
       </c>
       <c r="AX5">
-        <v>1.31</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY5">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="BB5">
-        <v>1.37</v>
+        <v>18</v>
       </c>
       <c r="BC5">
-        <v>1.37</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>1.37</v>
+        <v>2.32</v>
       </c>
       <c r="BE5">
-        <v>1.37</v>
+        <v>2.48</v>
       </c>
       <c r="BF5">
         <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>1.37</v>
+        <v>6.6</v>
       </c>
       <c r="BH5">
         <v>4.2</v>
@@ -2017,7 +1990,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2025,46 +1998,46 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F6">
         <v>4.2</v>
       </c>
       <c r="G6">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H6">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I6">
         <v>2.44</v>
       </c>
       <c r="J6">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="K6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6">
         <v>1.37</v>
@@ -2073,184 +2046,184 @@
         <v>2.96</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2259,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2267,241 +2240,241 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="H7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I7">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <v>3.55</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P7">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Q7">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2509,34 +2482,34 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>900</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2551,10 +2524,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.07</v>
+        <v>1.99</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2743,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2751,34 +2724,34 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F9">
-        <v>1.82</v>
+        <v>3.95</v>
       </c>
       <c r="G9">
-        <v>1.98</v>
+        <v>5.7</v>
       </c>
       <c r="H9">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>2.14</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2793,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="Q9">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2985,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2993,34 +2966,34 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F10">
+        <v>1.88</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>3.45</v>
+      </c>
+      <c r="I10">
+        <v>4.1</v>
+      </c>
+      <c r="J10">
         <v>3.95</v>
       </c>
-      <c r="G10">
-        <v>5.6</v>
-      </c>
-      <c r="H10">
-        <v>1.8</v>
-      </c>
-      <c r="I10">
-        <v>2.12</v>
-      </c>
-      <c r="J10">
-        <v>3.6</v>
-      </c>
       <c r="K10">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3038,7 +3011,7 @@
         <v>2.58</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3227,42 +3200,42 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F11">
-        <v>1.88</v>
+        <v>1.46</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="H11">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="K11">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3277,10 +3250,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="Q11">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3469,42 +3442,42 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F12">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="G12">
-        <v>1.67</v>
+        <v>3.35</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>2.26</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="J12">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3519,10 +3492,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q12">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3711,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3719,64 +3692,64 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F13">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="G13">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="H13">
-        <v>2.46</v>
+        <v>3.8</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="J13">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P13">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="Q13">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3785,175 +3758,175 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3961,64 +3934,64 @@
         <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F14">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="G14">
+        <v>3.6</v>
+      </c>
+      <c r="H14">
         <v>2.22</v>
       </c>
-      <c r="H14">
-        <v>3.8</v>
-      </c>
       <c r="I14">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="J14">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K14">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="Q14">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="R14">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4027,210 +4000,210 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BH14">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN14">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F15">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="H15">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="I15">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="J15">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4245,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="Q15">
         <v>1.49</v>
@@ -4437,42 +4410,42 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F16">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="G16">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H16">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="I16">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="J16">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>910</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4487,10 +4460,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="Q16">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4679,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4687,282 +4660,282 @@
         <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17">
+        <v>1.97</v>
+      </c>
+      <c r="G17">
+        <v>2.16</v>
+      </c>
+      <c r="H17">
+        <v>4.8</v>
+      </c>
+      <c r="I17">
+        <v>6.2</v>
+      </c>
+      <c r="J17">
+        <v>2.92</v>
+      </c>
+      <c r="K17">
+        <v>3.35</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1.1</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1.47</v>
+      </c>
+      <c r="Q17">
+        <v>2.66</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>2.14</v>
+      </c>
+      <c r="U17">
+        <v>1.64</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>970</v>
+      </c>
+      <c r="Y17">
+        <v>970</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>970</v>
+      </c>
+      <c r="AC17">
+        <v>970</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>970</v>
+      </c>
+      <c r="AG17">
+        <v>970</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.52</v>
+      </c>
+      <c r="AQ17">
+        <v>1.64</v>
+      </c>
+      <c r="AR17">
+        <v>1.74</v>
+      </c>
+      <c r="AS17">
+        <v>1.74</v>
+      </c>
+      <c r="AT17">
+        <v>1.46</v>
+      </c>
+      <c r="AU17">
+        <v>1.47</v>
+      </c>
+      <c r="AV17">
+        <v>1.74</v>
+      </c>
+      <c r="AW17">
+        <v>1.74</v>
+      </c>
+      <c r="AX17">
+        <v>1.59</v>
+      </c>
+      <c r="AY17">
+        <v>1.62</v>
+      </c>
+      <c r="AZ17">
+        <v>1.74</v>
+      </c>
+      <c r="BA17">
+        <v>1.74</v>
+      </c>
+      <c r="BB17">
+        <v>1.74</v>
+      </c>
+      <c r="BC17">
+        <v>1.74</v>
+      </c>
+      <c r="BD17">
+        <v>1.74</v>
+      </c>
+      <c r="BE17">
+        <v>1.74</v>
+      </c>
+      <c r="BF17">
+        <v>1.74</v>
+      </c>
+      <c r="BG17">
+        <v>1.74</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
         <v>144</v>
-      </c>
-      <c r="F17">
-        <v>1.04</v>
-      </c>
-      <c r="G17">
-        <v>1000</v>
-      </c>
-      <c r="H17">
-        <v>1.04</v>
-      </c>
-      <c r="I17">
-        <v>1000</v>
-      </c>
-      <c r="J17">
-        <v>5.7</v>
-      </c>
-      <c r="K17">
-        <v>910</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>2.2</v>
-      </c>
-      <c r="Q17">
-        <v>1.63</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>0</v>
-      </c>
-      <c r="BC17">
-        <v>0</v>
-      </c>
-      <c r="BD17">
-        <v>0</v>
-      </c>
-      <c r="BE17">
-        <v>0</v>
-      </c>
-      <c r="BF17">
-        <v>0</v>
-      </c>
-      <c r="BG17">
-        <v>0</v>
-      </c>
-      <c r="BH17">
-        <v>0</v>
-      </c>
-      <c r="BI17">
-        <v>0</v>
-      </c>
-      <c r="BJ17">
-        <v>0</v>
-      </c>
-      <c r="BK17">
-        <v>0</v>
-      </c>
-      <c r="BL17">
-        <v>0</v>
-      </c>
-      <c r="BM17">
-        <v>0</v>
-      </c>
-      <c r="BN17">
-        <v>0</v>
-      </c>
-      <c r="BO17">
-        <v>0</v>
-      </c>
-      <c r="BP17">
-        <v>0</v>
-      </c>
-      <c r="BQ17">
-        <v>0</v>
-      </c>
-      <c r="BR17">
-        <v>0</v>
-      </c>
-      <c r="BS17">
-        <v>0</v>
-      </c>
-      <c r="BT17">
-        <v>0</v>
-      </c>
-      <c r="BU17">
-        <v>0</v>
-      </c>
-      <c r="BV17">
-        <v>0</v>
-      </c>
-      <c r="BW17">
-        <v>0</v>
-      </c>
-      <c r="BX17">
-        <v>0</v>
-      </c>
-      <c r="BY17">
-        <v>0</v>
-      </c>
-      <c r="BZ17">
-        <v>0</v>
-      </c>
-      <c r="CA17">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F18">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="G18">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="H18">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I18">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>2.92</v>
+        <v>3.95</v>
       </c>
       <c r="K18">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4971,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="Q18">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -4983,10 +4956,10 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -4995,112 +4968,112 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ18">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AU18">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AV18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AW18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX18">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY18">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AZ18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BC18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BE18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BG18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BH18">
         <v>0</v>
@@ -5163,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5171,34 +5144,34 @@
         <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F19">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="G19">
-        <v>1.87</v>
+        <v>1.24</v>
       </c>
       <c r="H19">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="I19">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="J19">
-        <v>3.95</v>
+        <v>8.6</v>
       </c>
       <c r="K19">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5213,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>1.71</v>
+        <v>1.26</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5405,314 +5378,314 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" t="s">
         <v>92</v>
       </c>
-      <c r="B20" t="s">
-        <v>94</v>
-      </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F20">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="G20">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="H20">
-        <v>13.5</v>
+        <v>4.9</v>
       </c>
       <c r="I20">
-        <v>17.5</v>
+        <v>5.1</v>
       </c>
       <c r="J20">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="K20">
+        <v>3.45</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1.1</v>
+      </c>
+      <c r="N20">
+        <v>3.05</v>
+      </c>
+      <c r="O20">
+        <v>1.46</v>
+      </c>
+      <c r="P20">
+        <v>1.67</v>
+      </c>
+      <c r="Q20">
+        <v>2.38</v>
+      </c>
+      <c r="R20">
+        <v>1.25</v>
+      </c>
+      <c r="S20">
+        <v>4.6</v>
+      </c>
+      <c r="T20">
+        <v>2.08</v>
+      </c>
+      <c r="U20">
+        <v>1.85</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>10.5</v>
+      </c>
+      <c r="Y20">
+        <v>14.5</v>
+      </c>
+      <c r="Z20">
+        <v>40</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>7.2</v>
+      </c>
+      <c r="AC20">
+        <v>7.8</v>
+      </c>
+      <c r="AD20">
+        <v>21</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>10.5</v>
+      </c>
+      <c r="AG20">
+        <v>11</v>
+      </c>
+      <c r="AH20">
+        <v>23</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>24</v>
+      </c>
+      <c r="AK20">
+        <v>25</v>
+      </c>
+      <c r="AL20">
+        <v>300</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>19</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ20">
+        <v>12.5</v>
+      </c>
+      <c r="AR20">
+        <v>30</v>
+      </c>
+      <c r="AS20">
+        <v>40</v>
+      </c>
+      <c r="AT20">
+        <v>6.6</v>
+      </c>
+      <c r="AU20">
+        <v>7</v>
+      </c>
+      <c r="AV20">
+        <v>18</v>
+      </c>
+      <c r="AW20">
+        <v>34</v>
+      </c>
+      <c r="AX20">
+        <v>9.6</v>
+      </c>
+      <c r="AY20">
         <v>9.800000000000001</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>4</v>
-      </c>
-      <c r="Q20">
-        <v>1.01</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20">
-        <v>0</v>
-      </c>
-      <c r="AI20">
-        <v>0</v>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>0</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F21">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="G21">
-        <v>1.96</v>
+        <v>3.05</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="I21">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K21">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>1.66</v>
       </c>
       <c r="R21">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -5721,240 +5694,240 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ21">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AS21">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AU21">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AW21">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AX21">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AY21">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ21">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA21">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BB21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE21">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF21">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BG21">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BH21">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN21">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F22">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="G22">
-        <v>3.05</v>
+        <v>12.5</v>
       </c>
       <c r="H22">
-        <v>2.58</v>
+        <v>1.29</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>1.31</v>
       </c>
       <c r="J22">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="K22">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P22">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="Q22">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -5963,901 +5936,175 @@
         <v>0</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:80">
-      <c r="A23" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" t="s">
-        <v>150</v>
-      </c>
-      <c r="F23">
-        <v>1.61</v>
-      </c>
-      <c r="G23">
-        <v>1.62</v>
-      </c>
-      <c r="H23">
-        <v>5.8</v>
-      </c>
-      <c r="I23">
-        <v>6.2</v>
-      </c>
-      <c r="J23">
-        <v>4.5</v>
-      </c>
-      <c r="K23">
-        <v>4.7</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>2.32</v>
-      </c>
-      <c r="Q23">
-        <v>1.68</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <v>0</v>
-      </c>
-      <c r="AI23">
-        <v>0</v>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>0</v>
-      </c>
-      <c r="AO23">
-        <v>0</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
-      <c r="AV23">
-        <v>0</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>0</v>
-      </c>
-      <c r="BC23">
-        <v>0</v>
-      </c>
-      <c r="BD23">
-        <v>0</v>
-      </c>
-      <c r="BE23">
-        <v>0</v>
-      </c>
-      <c r="BF23">
-        <v>0</v>
-      </c>
-      <c r="BG23">
-        <v>0</v>
-      </c>
-      <c r="BH23">
-        <v>0</v>
-      </c>
-      <c r="BI23">
-        <v>0</v>
-      </c>
-      <c r="BJ23">
-        <v>0</v>
-      </c>
-      <c r="BK23">
-        <v>0</v>
-      </c>
-      <c r="BL23">
-        <v>0</v>
-      </c>
-      <c r="BM23">
-        <v>0</v>
-      </c>
-      <c r="BN23">
-        <v>0</v>
-      </c>
-      <c r="BO23">
-        <v>0</v>
-      </c>
-      <c r="BP23">
-        <v>0</v>
-      </c>
-      <c r="BQ23">
-        <v>0</v>
-      </c>
-      <c r="BR23">
-        <v>0</v>
-      </c>
-      <c r="BS23">
-        <v>0</v>
-      </c>
-      <c r="BT23">
-        <v>0</v>
-      </c>
-      <c r="BU23">
-        <v>0</v>
-      </c>
-      <c r="BV23">
-        <v>0</v>
-      </c>
-      <c r="BW23">
-        <v>0</v>
-      </c>
-      <c r="BX23">
-        <v>0</v>
-      </c>
-      <c r="BY23">
-        <v>0</v>
-      </c>
-      <c r="BZ23">
-        <v>0</v>
-      </c>
-      <c r="CA23">
-        <v>0</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="24" spans="1:80">
-      <c r="A24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" t="s">
-        <v>151</v>
-      </c>
-      <c r="F24">
-        <v>2.02</v>
-      </c>
-      <c r="G24">
-        <v>2.06</v>
-      </c>
-      <c r="H24">
-        <v>3.95</v>
-      </c>
-      <c r="I24">
-        <v>4.2</v>
-      </c>
-      <c r="J24">
-        <v>3.65</v>
-      </c>
-      <c r="K24">
-        <v>3.8</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>1.99</v>
-      </c>
-      <c r="Q24">
-        <v>1.91</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AI24">
-        <v>0</v>
-      </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>0</v>
-      </c>
-      <c r="AO24">
-        <v>0</v>
-      </c>
-      <c r="AP24">
-        <v>0</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
-      </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>0</v>
-      </c>
-      <c r="BC24">
-        <v>0</v>
-      </c>
-      <c r="BD24">
-        <v>0</v>
-      </c>
-      <c r="BE24">
-        <v>0</v>
-      </c>
-      <c r="BF24">
-        <v>0</v>
-      </c>
-      <c r="BG24">
-        <v>0</v>
-      </c>
-      <c r="BH24">
-        <v>0</v>
-      </c>
-      <c r="BI24">
-        <v>0</v>
-      </c>
-      <c r="BJ24">
-        <v>0</v>
-      </c>
-      <c r="BK24">
-        <v>0</v>
-      </c>
-      <c r="BL24">
-        <v>0</v>
-      </c>
-      <c r="BM24">
-        <v>0</v>
-      </c>
-      <c r="BN24">
-        <v>0</v>
-      </c>
-      <c r="BO24">
-        <v>0</v>
-      </c>
-      <c r="BP24">
-        <v>0</v>
-      </c>
-      <c r="BQ24">
-        <v>0</v>
-      </c>
-      <c r="BR24">
-        <v>0</v>
-      </c>
-      <c r="BS24">
-        <v>0</v>
-      </c>
-      <c r="BT24">
-        <v>0</v>
-      </c>
-      <c r="BU24">
-        <v>0</v>
-      </c>
-      <c r="BV24">
-        <v>0</v>
-      </c>
-      <c r="BW24">
-        <v>0</v>
-      </c>
-      <c r="BX24">
-        <v>0</v>
-      </c>
-      <c r="BY24">
-        <v>0</v>
-      </c>
-      <c r="BZ24">
-        <v>0</v>
-      </c>
-      <c r="CA24">
-        <v>0</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="25" spans="1:80">
-      <c r="A25" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" t="s">
-        <v>152</v>
-      </c>
-      <c r="F25">
-        <v>12</v>
-      </c>
-      <c r="G25">
-        <v>12.5</v>
-      </c>
-      <c r="H25">
-        <v>1.29</v>
-      </c>
-      <c r="I25">
-        <v>1.31</v>
-      </c>
-      <c r="J25">
-        <v>6.6</v>
-      </c>
-      <c r="K25">
-        <v>7</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>1.02</v>
-      </c>
-      <c r="N25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O25">
-        <v>1.12</v>
-      </c>
-      <c r="P25">
-        <v>3.25</v>
-      </c>
-      <c r="Q25">
-        <v>1.39</v>
-      </c>
-      <c r="R25">
-        <v>1.96</v>
-      </c>
-      <c r="S25">
-        <v>1.95</v>
-      </c>
-      <c r="T25">
-        <v>1.69</v>
-      </c>
-      <c r="U25">
-        <v>2.36</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>48</v>
-      </c>
-      <c r="Y25">
-        <v>14.5</v>
-      </c>
-      <c r="Z25">
-        <v>10.5</v>
-      </c>
-      <c r="AA25">
-        <v>13</v>
-      </c>
-      <c r="AB25">
-        <v>70</v>
-      </c>
-      <c r="AC25">
-        <v>16.5</v>
-      </c>
-      <c r="AD25">
-        <v>11.5</v>
-      </c>
-      <c r="AE25">
-        <v>12</v>
-      </c>
-      <c r="AF25">
-        <v>1000</v>
-      </c>
-      <c r="AG25">
-        <v>50</v>
-      </c>
-      <c r="AH25">
-        <v>26</v>
-      </c>
-      <c r="AI25">
-        <v>26</v>
-      </c>
-      <c r="AJ25">
-        <v>470</v>
-      </c>
-      <c r="AK25">
-        <v>1000</v>
-      </c>
-      <c r="AL25">
-        <v>110</v>
-      </c>
-      <c r="AM25">
-        <v>110</v>
-      </c>
-      <c r="AN25">
-        <v>1000</v>
-      </c>
-      <c r="AO25">
-        <v>3.6</v>
-      </c>
-      <c r="AP25">
-        <v>32</v>
-      </c>
-      <c r="AQ25">
-        <v>13</v>
-      </c>
-      <c r="AR25">
-        <v>9</v>
-      </c>
-      <c r="AS25">
-        <v>11.5</v>
-      </c>
-      <c r="AT25">
-        <v>30</v>
-      </c>
-      <c r="AU25">
-        <v>13.5</v>
-      </c>
-      <c r="AV25">
-        <v>9.4</v>
-      </c>
-      <c r="AW25">
-        <v>10.5</v>
-      </c>
-      <c r="AX25">
-        <v>40</v>
-      </c>
-      <c r="AY25">
-        <v>29</v>
-      </c>
-      <c r="AZ25">
-        <v>21</v>
-      </c>
-      <c r="BA25">
-        <v>21</v>
-      </c>
-      <c r="BB25">
-        <v>95</v>
-      </c>
-      <c r="BC25">
-        <v>42</v>
-      </c>
-      <c r="BD25">
-        <v>38</v>
-      </c>
-      <c r="BE25">
-        <v>55</v>
-      </c>
-      <c r="BF25">
-        <v>40</v>
-      </c>
-      <c r="BG25">
-        <v>3.4</v>
-      </c>
-      <c r="BH25">
-        <v>970</v>
-      </c>
-      <c r="BI25">
-        <v>1.01</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.01</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.01</v>
-      </c>
-      <c r="BN25">
-        <v>1000</v>
-      </c>
-      <c r="BO25">
-        <v>1.01</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>1.01</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
-        <v>1.01</v>
-      </c>
-      <c r="BT25">
-        <v>970</v>
-      </c>
-      <c r="BU25">
-        <v>1.01</v>
-      </c>
-      <c r="BV25">
-        <v>970</v>
-      </c>
-      <c r="BW25">
-        <v>1.01</v>
-      </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
-      <c r="BY25">
-        <v>1.01</v>
-      </c>
-      <c r="BZ25">
-        <v>1000</v>
-      </c>
-      <c r="CA25">
-        <v>1.01</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="148">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Egyptian Premier</t>
   </si>
   <si>
+    <t>Latvian Virsliga</t>
+  </si>
+  <si>
     <t>Polish Ekstraklasa</t>
   </si>
   <si>
@@ -340,6 +343,9 @@
     <t>Wadi Degla</t>
   </si>
   <si>
+    <t>SK Super Nova</t>
+  </si>
+  <si>
     <t>Rakow Czestochowa</t>
   </si>
   <si>
@@ -358,12 +364,12 @@
     <t>Rayo Vallecano</t>
   </si>
   <si>
+    <t>SV Meppen</t>
+  </si>
+  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
-    <t>SV Meppen</t>
-  </si>
-  <si>
     <t>Al Ahly Cairo</t>
   </si>
   <si>
@@ -403,6 +409,9 @@
     <t>Al Mokawloon</t>
   </si>
   <si>
+    <t>FK Riga</t>
+  </si>
+  <si>
     <t>Zaglebie Lubin</t>
   </si>
   <si>
@@ -421,12 +430,12 @@
     <t>Espanyol</t>
   </si>
   <si>
+    <t>Viktoria Koln</t>
+  </si>
+  <si>
     <t>Fortuna Dusseldorf</t>
   </si>
   <si>
-    <t>Viktoria Koln</t>
-  </si>
-  <si>
     <t>Abo Qair Semads</t>
   </si>
   <si>
@@ -448,7 +457,7 @@
     <t>Real Madrid</t>
   </si>
   <si>
-    <t>2026-09-13 11:58:09</t>
+    <t>2026-09-13 14:14:59</t>
   </si>
 </sst>
 </file>
@@ -780,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1030,34 +1039,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F2">
         <v>1.44</v>
       </c>
       <c r="G2">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L2">
         <v>1.49</v>
@@ -1066,7 +1075,7 @@
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O2">
         <v>1.44</v>
@@ -1081,19 +1090,19 @@
         <v>1.22</v>
       </c>
       <c r="S2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T2">
         <v>2.52</v>
       </c>
       <c r="U2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V2">
         <v>1.09</v>
       </c>
       <c r="W2">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="X2">
         <v>970</v>
@@ -1108,10 +1117,10 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>460</v>
+        <v>330</v>
       </c>
       <c r="AC2">
-        <v>460</v>
+        <v>330</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -1123,7 +1132,7 @@
         <v>970</v>
       </c>
       <c r="AG2">
-        <v>460</v>
+        <v>330</v>
       </c>
       <c r="AH2">
         <v>1000</v>
@@ -1132,7 +1141,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>460</v>
+        <v>330</v>
       </c>
       <c r="AK2">
         <v>1000</v>
@@ -1153,13 +1162,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AR2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AS2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AT2">
         <v>4.5</v>
@@ -1168,10 +1177,10 @@
         <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AW2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AX2">
         <v>5.2</v>
@@ -1180,28 +1189,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BA2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BB2">
         <v>8</v>
       </c>
       <c r="BC2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BD2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BE2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BF2">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BG2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BH2">
         <v>970</v>
@@ -1264,7 +1273,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1272,178 +1281,178 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F3">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="G3">
         <v>2.84</v>
       </c>
       <c r="H3">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
         <v>1.52</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
         <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
         <v>1.54</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG3">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP3">
-        <v>1.42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>1.41</v>
+        <v>8.6</v>
       </c>
       <c r="AR3">
-        <v>1.55</v>
+        <v>16</v>
       </c>
       <c r="AS3">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
-        <v>1.39</v>
+        <v>8</v>
       </c>
       <c r="AU3">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>1.55</v>
+        <v>30</v>
       </c>
       <c r="AX3">
-        <v>1.55</v>
+        <v>14</v>
       </c>
       <c r="AY3">
-        <v>1.49</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>1.55</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BB3">
-        <v>1.55</v>
+        <v>32</v>
       </c>
       <c r="BC3">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BD3">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BF3">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BG3">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BH3">
         <v>970</v>
@@ -1506,7 +1515,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1514,28 +1523,28 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H4">
         <v>10</v>
       </c>
       <c r="I4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J4">
         <v>4.7</v>
@@ -1547,25 +1556,25 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
         <v>3.85</v>
       </c>
       <c r="O4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P4">
         <v>2</v>
       </c>
       <c r="Q4">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R4">
         <v>1.37</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T4">
         <v>2.28</v>
@@ -1577,7 +1586,7 @@
         <v>1.09</v>
       </c>
       <c r="W4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X4">
         <v>17.5</v>
@@ -1595,7 +1604,7 @@
         <v>7.6</v>
       </c>
       <c r="AC4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD4">
         <v>44</v>
@@ -1628,22 +1637,22 @@
         <v>230</v>
       </c>
       <c r="AN4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO4">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AP4">
         <v>13</v>
       </c>
       <c r="AQ4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
@@ -1652,10 +1661,10 @@
         <v>10</v>
       </c>
       <c r="AV4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AW4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX4">
         <v>7</v>
@@ -1664,10 +1673,10 @@
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
         <v>9.800000000000001</v>
@@ -1676,16 +1685,16 @@
         <v>14.5</v>
       </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF4">
         <v>6.6</v>
       </c>
       <c r="BG4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1694,61 +1703,61 @@
         <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1756,31 +1765,31 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F5">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
         <v>4.1</v>
@@ -1789,145 +1798,145 @@
         <v>1.34</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
         <v>4.4</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="R5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U5">
         <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y5">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="Z5">
+        <v>36</v>
+      </c>
+      <c r="AA5">
+        <v>95</v>
+      </c>
+      <c r="AB5">
+        <v>10.5</v>
+      </c>
+      <c r="AC5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD5">
+        <v>17</v>
+      </c>
+      <c r="AE5">
         <v>55</v>
       </c>
-      <c r="AA5">
+      <c r="AF5">
+        <v>15.5</v>
+      </c>
+      <c r="AG5">
+        <v>11</v>
+      </c>
+      <c r="AH5">
+        <v>17.5</v>
+      </c>
+      <c r="AI5">
+        <v>60</v>
+      </c>
+      <c r="AJ5">
+        <v>25</v>
+      </c>
+      <c r="AK5">
+        <v>21</v>
+      </c>
+      <c r="AL5">
+        <v>38</v>
+      </c>
+      <c r="AM5">
         <v>100</v>
       </c>
-      <c r="AB5">
+      <c r="AN5">
         <v>14.5</v>
       </c>
-      <c r="AC5">
-        <v>10</v>
-      </c>
-      <c r="AD5">
-        <v>90</v>
-      </c>
-      <c r="AE5">
-        <v>65</v>
-      </c>
-      <c r="AF5">
-        <v>29</v>
-      </c>
-      <c r="AG5">
-        <v>13.5</v>
-      </c>
-      <c r="AH5">
-        <v>26</v>
-      </c>
-      <c r="AI5">
-        <v>70</v>
-      </c>
-      <c r="AJ5">
-        <v>38</v>
-      </c>
-      <c r="AK5">
-        <v>29</v>
-      </c>
-      <c r="AL5">
-        <v>40</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>24</v>
-      </c>
       <c r="AO5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP5">
+        <v>15</v>
+      </c>
+      <c r="AQ5">
+        <v>14.5</v>
+      </c>
+      <c r="AR5">
+        <v>7.2</v>
+      </c>
+      <c r="AS5">
+        <v>8.4</v>
+      </c>
+      <c r="AT5">
+        <v>9.4</v>
+      </c>
+      <c r="AU5">
+        <v>7.8</v>
+      </c>
+      <c r="AV5">
+        <v>14.5</v>
+      </c>
+      <c r="AW5">
+        <v>7.8</v>
+      </c>
+      <c r="AX5">
+        <v>11.5</v>
+      </c>
+      <c r="AY5">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5">
+        <v>15</v>
+      </c>
+      <c r="BA5">
+        <v>8</v>
+      </c>
+      <c r="BB5">
+        <v>20</v>
+      </c>
+      <c r="BC5">
+        <v>17.5</v>
+      </c>
+      <c r="BD5">
+        <v>7.2</v>
+      </c>
+      <c r="BE5">
+        <v>8.4</v>
+      </c>
+      <c r="BF5">
         <v>11</v>
       </c>
-      <c r="AQ5">
-        <v>12</v>
-      </c>
-      <c r="AR5">
-        <v>2.38</v>
-      </c>
-      <c r="AS5">
-        <v>2.42</v>
-      </c>
-      <c r="AT5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU5">
-        <v>6.6</v>
-      </c>
-      <c r="AV5">
-        <v>11</v>
-      </c>
-      <c r="AW5">
-        <v>2.38</v>
-      </c>
-      <c r="AX5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ5">
-        <v>12.5</v>
-      </c>
-      <c r="BA5">
-        <v>2.4</v>
-      </c>
-      <c r="BB5">
-        <v>18</v>
-      </c>
-      <c r="BC5">
-        <v>15.5</v>
-      </c>
-      <c r="BD5">
-        <v>2.32</v>
-      </c>
-      <c r="BE5">
-        <v>2.48</v>
-      </c>
-      <c r="BF5">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
         <v>4.2</v>
@@ -1990,7 +1999,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1998,16 +2007,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F6">
         <v>4.2</v>
@@ -2016,7 +2025,7 @@
         <v>5.4</v>
       </c>
       <c r="H6">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I6">
         <v>2.44</v>
@@ -2025,7 +2034,7 @@
         <v>2.74</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2061,7 +2070,7 @@
         <v>1.7</v>
       </c>
       <c r="W6">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2232,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2240,16 +2249,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F7">
         <v>2.12</v>
@@ -2276,13 +2285,13 @@
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q7">
         <v>2.48</v>
@@ -2306,7 +2315,7 @@
         <v>1.73</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y7">
         <v>22</v>
@@ -2363,7 +2372,7 @@
         <v>5.9</v>
       </c>
       <c r="AQ7">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
         <v>1.01</v>
@@ -2378,16 +2387,16 @@
         <v>5.4</v>
       </c>
       <c r="AV7">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
         <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
         <v>1.01</v>
@@ -2414,7 +2423,7 @@
         <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>2.82</v>
+        <v>970</v>
       </c>
       <c r="BI7">
         <v>2.18</v>
@@ -2474,7 +2483,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2482,241 +2491,241 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F8">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="G8">
-        <v>1.98</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>900</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P8">
-        <v>1.99</v>
+        <v>1.07</v>
       </c>
       <c r="Q8">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2724,241 +2733,241 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
         <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F9">
-        <v>3.95</v>
+        <v>1.84</v>
       </c>
       <c r="G9">
-        <v>5.7</v>
+        <v>1.98</v>
       </c>
       <c r="H9">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="I9">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2966,725 +2975,725 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="H10">
-        <v>3.45</v>
+        <v>1.82</v>
       </c>
       <c r="I10">
+        <v>1.93</v>
+      </c>
+      <c r="J10">
         <v>4.1</v>
       </c>
-      <c r="J10">
-        <v>3.95</v>
-      </c>
       <c r="K10">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q10">
+        <v>1.5</v>
+      </c>
+      <c r="R10">
+        <v>1.69</v>
+      </c>
+      <c r="S10">
+        <v>2.12</v>
+      </c>
+      <c r="T10">
         <v>1.46</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F11">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="G11">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>7.2</v>
+        <v>3.45</v>
       </c>
       <c r="I11">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="J11">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="K11">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="Q11">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>2.5</v>
+        <v>1.47</v>
       </c>
       <c r="G12">
-        <v>3.35</v>
+        <v>1.53</v>
       </c>
       <c r="H12">
-        <v>2.26</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="K12">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P12">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB12" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3692,181 +3701,181 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F13">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="G13">
+        <v>3.35</v>
+      </c>
+      <c r="H13">
+        <v>2.26</v>
+      </c>
+      <c r="I13">
+        <v>3.2</v>
+      </c>
+      <c r="J13">
+        <v>3.35</v>
+      </c>
+      <c r="K13">
+        <v>6.4</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>4.1</v>
+      </c>
+      <c r="O13">
+        <v>1.18</v>
+      </c>
+      <c r="P13">
         <v>2.22</v>
       </c>
-      <c r="H13">
-        <v>3.8</v>
-      </c>
-      <c r="I13">
-        <v>3.85</v>
-      </c>
-      <c r="J13">
-        <v>3.5</v>
-      </c>
-      <c r="K13">
-        <v>3.6</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>1.08</v>
-      </c>
-      <c r="N13">
-        <v>3.7</v>
-      </c>
-      <c r="O13">
-        <v>1.35</v>
-      </c>
-      <c r="P13">
-        <v>1.91</v>
-      </c>
       <c r="Q13">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="R13">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S13">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="T13">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
         <v>1.01</v>
@@ -3884,7 +3893,7 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
         <v>1.01</v>
@@ -3926,7 +3935,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3934,258 +3943,258 @@
         <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>2.96</v>
+        <v>2.16</v>
       </c>
       <c r="G14">
+        <v>2.2</v>
+      </c>
+      <c r="H14">
+        <v>3.9</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <v>3.5</v>
+      </c>
+      <c r="K14">
         <v>3.6</v>
       </c>
-      <c r="H14">
-        <v>2.22</v>
-      </c>
-      <c r="I14">
-        <v>2.78</v>
-      </c>
-      <c r="J14">
-        <v>3.2</v>
-      </c>
-      <c r="K14">
-        <v>4.2</v>
-      </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P14">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="Q14">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CB14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F15">
         <v>2.58</v>
@@ -4194,7 +4203,7 @@
         <v>3.05</v>
       </c>
       <c r="H15">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="I15">
         <v>2.66</v>
@@ -4206,16 +4215,16 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
         <v>2.56</v>
@@ -4224,435 +4233,435 @@
         <v>1.49</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H16">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J16">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>910</v>
+        <v>4.6</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P16">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q16">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4660,232 +4669,232 @@
         <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F17">
-        <v>1.97</v>
+        <v>1.23</v>
       </c>
       <c r="G17">
-        <v>2.16</v>
+        <v>1.3</v>
       </c>
       <c r="H17">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="I17">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="J17">
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>2.22</v>
+      </c>
+      <c r="O17">
+        <v>1.22</v>
+      </c>
+      <c r="P17">
+        <v>2.22</v>
+      </c>
+      <c r="Q17">
+        <v>1.67</v>
+      </c>
+      <c r="R17">
+        <v>1.42</v>
+      </c>
+      <c r="S17">
+        <v>2.68</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
+        <v>1.05</v>
+      </c>
+      <c r="W17">
+        <v>4.3</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>19.5</v>
+      </c>
+      <c r="AD17">
+        <v>85</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17">
+        <v>1.01</v>
+      </c>
+      <c r="AR17">
+        <v>1.01</v>
+      </c>
+      <c r="AS17">
+        <v>1.01</v>
+      </c>
+      <c r="AT17">
+        <v>1.01</v>
+      </c>
+      <c r="AU17">
+        <v>1.01</v>
+      </c>
+      <c r="AV17">
+        <v>10</v>
+      </c>
+      <c r="AW17">
+        <v>1.01</v>
+      </c>
+      <c r="AX17">
+        <v>1.01</v>
+      </c>
+      <c r="AY17">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17">
+        <v>1.01</v>
+      </c>
+      <c r="BA17">
+        <v>1.01</v>
+      </c>
+      <c r="BB17">
+        <v>1.01</v>
+      </c>
+      <c r="BC17">
+        <v>1.01</v>
+      </c>
+      <c r="BD17">
+        <v>1.01</v>
+      </c>
+      <c r="BE17">
+        <v>1.01</v>
+      </c>
+      <c r="BF17">
+        <v>3.65</v>
+      </c>
+      <c r="BG17">
+        <v>95</v>
+      </c>
+      <c r="BH17">
+        <v>5.3</v>
+      </c>
+      <c r="BI17">
         <v>2.92</v>
       </c>
-      <c r="K17">
-        <v>3.35</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>1.1</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>1.47</v>
-      </c>
-      <c r="Q17">
-        <v>2.66</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>2.14</v>
-      </c>
-      <c r="U17">
-        <v>1.64</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>970</v>
-      </c>
-      <c r="Y17">
-        <v>970</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>970</v>
-      </c>
-      <c r="AC17">
-        <v>970</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>970</v>
-      </c>
-      <c r="AG17">
-        <v>970</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.52</v>
-      </c>
-      <c r="AQ17">
-        <v>1.64</v>
-      </c>
-      <c r="AR17">
-        <v>1.74</v>
-      </c>
-      <c r="AS17">
-        <v>1.74</v>
-      </c>
-      <c r="AT17">
-        <v>1.46</v>
-      </c>
-      <c r="AU17">
-        <v>1.47</v>
-      </c>
-      <c r="AV17">
-        <v>1.74</v>
-      </c>
-      <c r="AW17">
-        <v>1.74</v>
-      </c>
-      <c r="AX17">
-        <v>1.59</v>
-      </c>
-      <c r="AY17">
-        <v>1.62</v>
-      </c>
-      <c r="AZ17">
-        <v>1.74</v>
-      </c>
-      <c r="BA17">
-        <v>1.74</v>
-      </c>
-      <c r="BB17">
-        <v>1.74</v>
-      </c>
-      <c r="BC17">
-        <v>1.74</v>
-      </c>
-      <c r="BD17">
-        <v>1.74</v>
-      </c>
-      <c r="BE17">
-        <v>1.74</v>
-      </c>
-      <c r="BF17">
-        <v>1.74</v>
-      </c>
-      <c r="BG17">
-        <v>1.74</v>
-      </c>
-      <c r="BH17">
-        <v>0</v>
-      </c>
-      <c r="BI17">
-        <v>0</v>
-      </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -4894,249 +4903,249 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F18">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="G18">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="H18">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I18">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="J18">
-        <v>3.95</v>
+        <v>2.92</v>
       </c>
       <c r="K18">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P18">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="Q18">
-        <v>1.8</v>
+        <v>2.66</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5144,306 +5153,306 @@
         <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
         <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F19">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="G19">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="H19">
-        <v>13.5</v>
+        <v>4.9</v>
       </c>
       <c r="I19">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J19">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>1.97</v>
       </c>
       <c r="Q19">
-        <v>1.26</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F20">
-        <v>1.96</v>
+        <v>1.19</v>
       </c>
       <c r="G20">
-        <v>1.97</v>
+        <v>1.23</v>
       </c>
       <c r="H20">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="I20">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="J20">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="K20">
-        <v>3.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>1.67</v>
+        <v>4.3</v>
       </c>
       <c r="Q20">
-        <v>2.38</v>
+        <v>1.26</v>
       </c>
       <c r="R20">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -5452,240 +5461,240 @@
         <v>0</v>
       </c>
       <c r="X20">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH20">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL20">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN20">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ20">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR20">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV20">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AW20">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AX20">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AY20">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ20">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA20">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BB20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD20">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE20">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF20">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BG20">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BH20">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN20">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
         <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F21">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G21">
+        <v>1.96</v>
+      </c>
+      <c r="H21">
+        <v>4.9</v>
+      </c>
+      <c r="I21">
+        <v>5.1</v>
+      </c>
+      <c r="J21">
+        <v>3.4</v>
+      </c>
+      <c r="K21">
+        <v>3.5</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1.1</v>
+      </c>
+      <c r="N21">
         <v>3.05</v>
       </c>
-      <c r="H21">
-        <v>2.58</v>
-      </c>
-      <c r="I21">
-        <v>3</v>
-      </c>
-      <c r="J21">
-        <v>3.2</v>
-      </c>
-      <c r="K21">
-        <v>4.4</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P21">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="Q21">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -5694,417 +5703,659 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
         <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F22">
+        <v>1.04</v>
+      </c>
+      <c r="G22">
+        <v>3.05</v>
+      </c>
+      <c r="H22">
+        <v>2.58</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>3.2</v>
+      </c>
+      <c r="K22">
+        <v>4.4</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.04</v>
+      </c>
+      <c r="Q22">
+        <v>1.67</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23">
+        <v>11.5</v>
+      </c>
+      <c r="G23">
+        <v>12.5</v>
+      </c>
+      <c r="H23">
+        <v>1.28</v>
+      </c>
+      <c r="I23">
+        <v>1.3</v>
+      </c>
+      <c r="J23">
+        <v>6.6</v>
+      </c>
+      <c r="K23">
+        <v>7</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1.02</v>
+      </c>
+      <c r="N23">
+        <v>8.6</v>
+      </c>
+      <c r="O23">
+        <v>1.11</v>
+      </c>
+      <c r="P23">
+        <v>3.3</v>
+      </c>
+      <c r="Q23">
+        <v>1.39</v>
+      </c>
+      <c r="R23">
+        <v>2</v>
+      </c>
+      <c r="S23">
+        <v>1.9</v>
+      </c>
+      <c r="T23">
+        <v>1.73</v>
+      </c>
+      <c r="U23">
+        <v>2.28</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>46</v>
+      </c>
+      <c r="Y23">
+        <v>16</v>
+      </c>
+      <c r="Z23">
+        <v>10.5</v>
+      </c>
+      <c r="AA23">
+        <v>12.5</v>
+      </c>
+      <c r="AB23">
+        <v>65</v>
+      </c>
+      <c r="AC23">
+        <v>17</v>
+      </c>
+      <c r="AD23">
         <v>12</v>
       </c>
-      <c r="G22">
-        <v>12.5</v>
-      </c>
-      <c r="H22">
-        <v>1.29</v>
-      </c>
-      <c r="I22">
-        <v>1.31</v>
-      </c>
-      <c r="J22">
-        <v>6.6</v>
-      </c>
-      <c r="K22">
-        <v>7</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>1.02</v>
-      </c>
-      <c r="N22">
-        <v>8.4</v>
-      </c>
-      <c r="O22">
-        <v>1.11</v>
-      </c>
-      <c r="P22">
-        <v>3.3</v>
-      </c>
-      <c r="Q22">
-        <v>1.39</v>
-      </c>
-      <c r="R22">
-        <v>1.99</v>
-      </c>
-      <c r="S22">
-        <v>1.9</v>
-      </c>
-      <c r="T22">
-        <v>1.73</v>
-      </c>
-      <c r="U22">
-        <v>2.28</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
+      <c r="AE23">
+        <v>11.5</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
         <v>46</v>
       </c>
-      <c r="Y22">
-        <v>15.5</v>
-      </c>
-      <c r="Z22">
-        <v>10.5</v>
-      </c>
-      <c r="AA22">
-        <v>12</v>
-      </c>
-      <c r="AB22">
-        <v>65</v>
-      </c>
-      <c r="AC22">
-        <v>16.5</v>
-      </c>
-      <c r="AD22">
-        <v>12</v>
-      </c>
-      <c r="AE22">
-        <v>11.5</v>
-      </c>
-      <c r="AF22">
-        <v>1000</v>
-      </c>
-      <c r="AG22">
-        <v>46</v>
-      </c>
-      <c r="AH22">
+      <c r="AH23">
         <v>26</v>
       </c>
-      <c r="AI22">
-        <v>28</v>
-      </c>
-      <c r="AJ22">
+      <c r="AI23">
+        <v>29</v>
+      </c>
+      <c r="AJ23">
         <v>540</v>
       </c>
-      <c r="AK22">
-        <v>1000</v>
-      </c>
-      <c r="AL22">
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
         <v>130</v>
       </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>1000</v>
-      </c>
-      <c r="AO22">
+      <c r="AM23">
+        <v>95</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
         <v>3.45</v>
       </c>
-      <c r="AP22">
+      <c r="AP23">
         <v>34</v>
       </c>
-      <c r="AQ22">
-        <v>13.5</v>
-      </c>
-      <c r="AR22">
+      <c r="AQ23">
+        <v>14</v>
+      </c>
+      <c r="AR23">
         <v>9</v>
       </c>
-      <c r="AS22">
+      <c r="AS23">
         <v>11</v>
       </c>
-      <c r="AT22">
-        <v>46</v>
-      </c>
-      <c r="AU22">
+      <c r="AT23">
+        <v>48</v>
+      </c>
+      <c r="AU23">
         <v>14.5</v>
       </c>
-      <c r="AV22">
+      <c r="AV23">
         <v>11</v>
       </c>
-      <c r="AW22">
+      <c r="AW23">
         <v>10</v>
       </c>
-      <c r="AX22">
+      <c r="AX23">
         <v>42</v>
       </c>
-      <c r="AY22">
-        <v>36</v>
-      </c>
-      <c r="AZ22">
+      <c r="AY23">
+        <v>34</v>
+      </c>
+      <c r="AZ23">
         <v>22</v>
       </c>
-      <c r="BA22">
-        <v>24</v>
-      </c>
-      <c r="BB22">
-        <v>90</v>
-      </c>
-      <c r="BC22">
+      <c r="BA23">
+        <v>23</v>
+      </c>
+      <c r="BB23">
+        <v>95</v>
+      </c>
+      <c r="BC23">
+        <v>44</v>
+      </c>
+      <c r="BD23">
+        <v>38</v>
+      </c>
+      <c r="BE23">
+        <v>55</v>
+      </c>
+      <c r="BF23">
         <v>42</v>
       </c>
-      <c r="BD22">
-        <v>38</v>
-      </c>
-      <c r="BE22">
-        <v>55</v>
-      </c>
-      <c r="BF22">
-        <v>42</v>
-      </c>
-      <c r="BG22">
+      <c r="BG23">
         <v>3.25</v>
       </c>
-      <c r="BH22">
+      <c r="BH23">
         <v>970</v>
       </c>
-      <c r="BI22">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>1.01</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.01</v>
-      </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
-      <c r="BO22">
-        <v>1.01</v>
-      </c>
-      <c r="BP22">
-        <v>1000</v>
-      </c>
-      <c r="BQ22">
-        <v>1.01</v>
-      </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>1.01</v>
-      </c>
-      <c r="BT22">
+      <c r="BI23">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.01</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.01</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.01</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.01</v>
+      </c>
+      <c r="BT23">
         <v>970</v>
       </c>
-      <c r="BU22">
-        <v>1.01</v>
-      </c>
-      <c r="BV22">
+      <c r="BU23">
+        <v>1.01</v>
+      </c>
+      <c r="BV23">
         <v>970</v>
       </c>
-      <c r="BW22">
-        <v>1.01</v>
-      </c>
-      <c r="BX22">
-        <v>1000</v>
-      </c>
-      <c r="BY22">
-        <v>1.01</v>
-      </c>
-      <c r="BZ22">
-        <v>1000</v>
-      </c>
-      <c r="CA22">
-        <v>1.01</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>144</v>
+      <c r="BW23">
+        <v>1.01</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="188">
   <si>
     <t>League</t>
   </si>
@@ -277,24 +277,39 @@
     <t>Polish Ekstraklasa</t>
   </si>
   <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>Israeli Premier League</t>
+  </si>
+  <si>
+    <t>German 3 Liga</t>
+  </si>
+  <si>
     <t>Swiss Super League</t>
   </si>
   <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
-    <t>Spanish La Liga</t>
-  </si>
-  <si>
-    <t>German 3 Liga</t>
-  </si>
-  <si>
-    <t>Israeli Premier League</t>
-  </si>
-  <si>
     <t>Dutch Eredivisie</t>
   </si>
   <si>
+    <t>Welsh Premiership</t>
+  </si>
+  <si>
+    <t>Scottish League One</t>
+  </si>
+  <si>
+    <t>Scottish Championship</t>
+  </si>
+  <si>
+    <t>English Sky Bet Championship</t>
+  </si>
+  <si>
+    <t>English National League</t>
+  </si>
+  <si>
     <t>2026-09-15</t>
   </si>
   <si>
@@ -322,6 +337,9 @@
     <t>18:30:00</t>
   </si>
   <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
     <t>19:30:00</t>
   </si>
   <si>
@@ -349,45 +367,96 @@
     <t>Rakow Czestochowa</t>
   </si>
   <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>IK Brage</t>
+  </si>
+  <si>
+    <t>Rayo Vallecano</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Al-Masry</t>
+  </si>
+  <si>
+    <t>SV Meppen</t>
+  </si>
+  <si>
+    <t>Al Ahly Cairo</t>
+  </si>
+  <si>
+    <t>Varnamo</t>
+  </si>
+  <si>
+    <t>Jahn Regensburg</t>
+  </si>
+  <si>
     <t>Grasshoppers Zurich</t>
   </si>
   <si>
-    <t>Varnamo</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>IK Brage</t>
-  </si>
-  <si>
-    <t>Rayo Vallecano</t>
-  </si>
-  <si>
-    <t>SV Meppen</t>
-  </si>
-  <si>
-    <t>Jahn Regensburg</t>
-  </si>
-  <si>
-    <t>Al Ahly Cairo</t>
-  </si>
-  <si>
-    <t>Al-Masry</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
+    <t>Alaves</t>
   </si>
   <si>
     <t>Ajax</t>
   </si>
   <si>
-    <t>Alaves</t>
-  </si>
-  <si>
     <t>Korona Kielce</t>
   </si>
   <si>
+    <t>Connahs Quay</t>
+  </si>
+  <si>
+    <t>Barry Town Utd</t>
+  </si>
+  <si>
+    <t>Penybont FC</t>
+  </si>
+  <si>
+    <t>The New Saints</t>
+  </si>
+  <si>
+    <t>Ross Co</t>
+  </si>
+  <si>
+    <t>Stenhousemuir</t>
+  </si>
+  <si>
+    <t>Middlesbrough</t>
+  </si>
+  <si>
+    <t>Bristol City</t>
+  </si>
+  <si>
+    <t>Aldershot</t>
+  </si>
+  <si>
+    <t>Carlisle</t>
+  </si>
+  <si>
+    <t>Sutton Utd</t>
+  </si>
+  <si>
+    <t>Worthing</t>
+  </si>
+  <si>
+    <t>Solihull Moors</t>
+  </si>
+  <si>
+    <t>Wealdstone</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
+    <t>Southend</t>
+  </si>
+  <si>
+    <t>Boston Utd</t>
+  </si>
+  <si>
     <t>Elche</t>
   </si>
   <si>
@@ -415,49 +484,100 @@
     <t>Zaglebie Lubin</t>
   </si>
   <si>
+    <t>Sundsvall</t>
+  </si>
+  <si>
+    <t>Sandvikens IF</t>
+  </si>
+  <si>
+    <t>Espanyol</t>
+  </si>
+  <si>
+    <t>Maccabi Petach Tikva</t>
+  </si>
+  <si>
+    <t>Al Ittihad (EGY)</t>
+  </si>
+  <si>
+    <t>Viktoria Koln</t>
+  </si>
+  <si>
+    <t>Abo Qair Semads</t>
+  </si>
+  <si>
+    <t>Osters</t>
+  </si>
+  <si>
+    <t>Fortuna Dusseldorf</t>
+  </si>
+  <si>
     <t>Sion</t>
   </si>
   <si>
-    <t>Osters</t>
-  </si>
-  <si>
-    <t>Sundsvall</t>
-  </si>
-  <si>
-    <t>Sandvikens IF</t>
-  </si>
-  <si>
-    <t>Espanyol</t>
-  </si>
-  <si>
-    <t>Viktoria Koln</t>
-  </si>
-  <si>
-    <t>Fortuna Dusseldorf</t>
-  </si>
-  <si>
-    <t>Abo Qair Semads</t>
-  </si>
-  <si>
-    <t>Al Ittihad (EGY)</t>
-  </si>
-  <si>
-    <t>Maccabi Petach Tikva</t>
+    <t>Valencia</t>
   </si>
   <si>
     <t>Willem II</t>
   </si>
   <si>
-    <t>Valencia</t>
-  </si>
-  <si>
     <t>Gornik Zabrze</t>
   </si>
   <si>
+    <t>Airbus UK Broughton</t>
+  </si>
+  <si>
+    <t>Ammanford AFC</t>
+  </si>
+  <si>
+    <t>Briton Ferry Llansawel</t>
+  </si>
+  <si>
+    <t>Flint Town United</t>
+  </si>
+  <si>
+    <t>Queen of South</t>
+  </si>
+  <si>
+    <t>Partick</t>
+  </si>
+  <si>
+    <t>Millwall</t>
+  </si>
+  <si>
+    <t>Lincoln</t>
+  </si>
+  <si>
+    <t>Yeovil</t>
+  </si>
+  <si>
+    <t>Forest Green</t>
+  </si>
+  <si>
+    <t>Eastleigh</t>
+  </si>
+  <si>
+    <t>Hornchurch</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>FC Halifax Town</t>
+  </si>
+  <si>
+    <t>AFC Fylde</t>
+  </si>
+  <si>
+    <t>Tamworth FC</t>
+  </si>
+  <si>
+    <t>Woking</t>
+  </si>
+  <si>
     <t>Real Madrid</t>
   </si>
   <si>
-    <t>2026-09-13 14:14:59</t>
+    <t>2026-09-13 16:32:48</t>
   </si>
 </sst>
 </file>
@@ -789,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1039,31 +1159,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F2">
         <v>1.44</v>
       </c>
       <c r="G2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
         <v>5.1</v>
@@ -1072,7 +1192,7 @@
         <v>1.49</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
         <v>2.68</v>
@@ -1081,7 +1201,7 @@
         <v>1.44</v>
       </c>
       <c r="P2">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q2">
         <v>2.28</v>
@@ -1093,7 +1213,7 @@
         <v>4.2</v>
       </c>
       <c r="T2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
         <v>1.48</v>
@@ -1117,10 +1237,10 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>330</v>
+        <v>190</v>
       </c>
       <c r="AC2">
-        <v>330</v>
+        <v>970</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -1132,7 +1252,7 @@
         <v>970</v>
       </c>
       <c r="AG2">
-        <v>330</v>
+        <v>190</v>
       </c>
       <c r="AH2">
         <v>1000</v>
@@ -1141,7 +1261,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>330</v>
+        <v>190</v>
       </c>
       <c r="AK2">
         <v>1000</v>
@@ -1213,7 +1333,7 @@
         <v>1.98</v>
       </c>
       <c r="BH2">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
         <v>1.35</v>
@@ -1231,7 +1351,7 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
         <v>1.46</v>
@@ -1273,7 +1393,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1281,16 +1401,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="F3">
         <v>2.64</v>
@@ -1377,7 +1497,7 @@
         <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI3">
         <v>75</v>
@@ -1410,7 +1530,7 @@
         <v>16</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1422,7 +1542,7 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1434,28 +1554,28 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB3">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="BC3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE3">
+        <v>7.2</v>
+      </c>
+      <c r="BF3">
         <v>6.2</v>
       </c>
-      <c r="BF3">
-        <v>6</v>
-      </c>
       <c r="BG3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH3">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
         <v>1.01</v>
@@ -1464,13 +1584,13 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BN3">
         <v>1000</v>
@@ -1482,13 +1602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BT3">
         <v>1000</v>
@@ -1500,22 +1620,22 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="CB3" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1523,16 +1643,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="F4">
         <v>1.4</v>
@@ -1550,7 +1670,7 @@
         <v>4.7</v>
       </c>
       <c r="K4">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1592,7 +1712,7 @@
         <v>17.5</v>
       </c>
       <c r="Y4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z4">
         <v>120</v>
@@ -1652,7 +1772,7 @@
         <v>7.2</v>
       </c>
       <c r="AS4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
@@ -1673,7 +1793,7 @@
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA4">
         <v>7.4</v>
@@ -1694,70 +1814,70 @@
         <v>6.6</v>
       </c>
       <c r="BG4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BJ4">
         <v>18</v>
       </c>
       <c r="BK4">
-        <v>8.4</v>
+        <v>1.71</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>21</v>
+        <v>1.89</v>
       </c>
       <c r="BN4">
         <v>4.8</v>
       </c>
       <c r="BO4">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BP4">
         <v>11.5</v>
       </c>
       <c r="BQ4">
-        <v>5.6</v>
+        <v>1.63</v>
       </c>
       <c r="BR4">
         <v>40</v>
       </c>
       <c r="BS4">
-        <v>18.5</v>
+        <v>1.81</v>
       </c>
       <c r="BT4">
         <v>19</v>
       </c>
       <c r="BU4">
-        <v>8.800000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>21</v>
+        <v>1.89</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>21</v>
+        <v>1.89</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>1.76</v>
       </c>
       <c r="CB4" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1765,25 +1885,25 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="F5">
         <v>1.98</v>
       </c>
       <c r="G5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I5">
         <v>4.2</v>
@@ -1807,7 +1927,7 @@
         <v>1.28</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q5">
         <v>1.82</v>
@@ -1816,16 +1936,16 @@
         <v>1.45</v>
       </c>
       <c r="S5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
         <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
         <v>1.96</v>
@@ -1897,7 +2017,7 @@
         <v>8.4</v>
       </c>
       <c r="AT5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
         <v>7.8</v>
@@ -1912,7 +2032,7 @@
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5">
         <v>15</v>
@@ -1939,7 +2059,7 @@
         <v>7.6</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
         <v>3.1</v>
@@ -1957,7 +2077,7 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
         <v>3.95</v>
@@ -1975,7 +2095,7 @@
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
         <v>5.7</v>
@@ -1999,7 +2119,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2007,145 +2127,145 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="F6">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="G6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H6">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I6">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="J6">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="K6">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N6">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="O6">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="P6">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Q6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S6">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V6">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="W6">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6">
         <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
         <v>1.01</v>
@@ -2154,10 +2274,10 @@
         <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA6">
         <v>1.01</v>
@@ -2190,49 +2310,49 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2241,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2249,157 +2369,157 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G7">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H7">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I7">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
+        <v>2.54</v>
+      </c>
+      <c r="O7">
+        <v>1.54</v>
+      </c>
+      <c r="P7">
+        <v>1.51</v>
+      </c>
+      <c r="Q7">
         <v>2.62</v>
       </c>
-      <c r="O7">
-        <v>1.48</v>
-      </c>
-      <c r="P7">
-        <v>1.48</v>
-      </c>
-      <c r="Q7">
-        <v>2.48</v>
-      </c>
       <c r="R7">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="S7">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="T7">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U7">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V7">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X7">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y7">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AC7">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF7">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AG7">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP7">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS7">
         <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU7">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW7">
         <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
         <v>1.01</v>
@@ -2408,7 +2528,7 @@
         <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD7">
         <v>1.01</v>
@@ -2423,7 +2543,7 @@
         <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
         <v>2.18</v>
@@ -2432,13 +2552,13 @@
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BN7">
         <v>1000</v>
@@ -2450,40 +2570,40 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="CB7" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2491,16 +2611,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="F8">
         <v>1.04</v>
@@ -2527,22 +2647,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O8">
         <v>1.15</v>
       </c>
       <c r="P8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q8">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S8">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2725,7 +2845,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2733,22 +2853,22 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="F9">
         <v>1.84</v>
       </c>
       <c r="G9">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H9">
         <v>4.1</v>
@@ -2757,7 +2877,7 @@
         <v>4.9</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
         <v>4.4</v>
@@ -2769,7 +2889,7 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O9">
         <v>1.28</v>
@@ -2811,10 +2931,10 @@
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AC9">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD9">
         <v>1000</v>
@@ -2826,7 +2946,7 @@
         <v>22</v>
       </c>
       <c r="AG9">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH9">
         <v>1000</v>
@@ -2916,58 +3036,58 @@
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN9">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="CB9" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2975,276 +3095,276 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="F10">
-        <v>4.2</v>
+        <v>1.42</v>
       </c>
       <c r="G10">
+        <v>1.54</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>9.4</v>
+      </c>
+      <c r="J10">
+        <v>4.7</v>
+      </c>
+      <c r="K10">
+        <v>6.4</v>
+      </c>
+      <c r="L10">
+        <v>1.26</v>
+      </c>
+      <c r="M10">
+        <v>1.05</v>
+      </c>
+      <c r="N10">
+        <v>4.8</v>
+      </c>
+      <c r="O10">
+        <v>1.23</v>
+      </c>
+      <c r="P10">
+        <v>2.3</v>
+      </c>
+      <c r="Q10">
+        <v>1.68</v>
+      </c>
+      <c r="R10">
+        <v>1.51</v>
+      </c>
+      <c r="S10">
+        <v>2.7</v>
+      </c>
+      <c r="T10">
+        <v>1.87</v>
+      </c>
+      <c r="U10">
+        <v>2.02</v>
+      </c>
+      <c r="V10">
+        <v>1.12</v>
+      </c>
+      <c r="W10">
+        <v>2.84</v>
+      </c>
+      <c r="X10">
+        <v>26</v>
+      </c>
+      <c r="Y10">
+        <v>32</v>
+      </c>
+      <c r="Z10">
+        <v>80</v>
+      </c>
+      <c r="AA10">
+        <v>260</v>
+      </c>
+      <c r="AB10">
+        <v>12</v>
+      </c>
+      <c r="AC10">
+        <v>13.5</v>
+      </c>
+      <c r="AD10">
+        <v>34</v>
+      </c>
+      <c r="AE10">
+        <v>130</v>
+      </c>
+      <c r="AF10">
+        <v>12</v>
+      </c>
+      <c r="AG10">
+        <v>12.5</v>
+      </c>
+      <c r="AH10">
+        <v>28</v>
+      </c>
+      <c r="AI10">
+        <v>110</v>
+      </c>
+      <c r="AJ10">
+        <v>16.5</v>
+      </c>
+      <c r="AK10">
+        <v>18.5</v>
+      </c>
+      <c r="AL10">
+        <v>40</v>
+      </c>
+      <c r="AM10">
+        <v>140</v>
+      </c>
+      <c r="AN10">
+        <v>6.6</v>
+      </c>
+      <c r="AO10">
+        <v>140</v>
+      </c>
+      <c r="AP10">
+        <v>15.5</v>
+      </c>
+      <c r="AQ10">
+        <v>19</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>8.6</v>
+      </c>
+      <c r="AU10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV10">
+        <v>19.5</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>8.6</v>
+      </c>
+      <c r="AY10">
+        <v>9</v>
+      </c>
+      <c r="AZ10">
+        <v>19.5</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>11.5</v>
+      </c>
+      <c r="BC10">
+        <v>13.5</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>5.8</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>4.8</v>
+      </c>
+      <c r="BI10">
+        <v>3.2</v>
+      </c>
+      <c r="BJ10">
+        <v>13</v>
+      </c>
+      <c r="BK10">
+        <v>3.5</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>4.6</v>
+      </c>
+      <c r="BN10">
+        <v>4.8</v>
+      </c>
+      <c r="BO10">
+        <v>3.2</v>
+      </c>
+      <c r="BP10">
+        <v>11</v>
+      </c>
+      <c r="BQ10">
+        <v>3.3</v>
+      </c>
+      <c r="BR10">
+        <v>27</v>
+      </c>
+      <c r="BS10">
+        <v>4</v>
+      </c>
+      <c r="BT10">
+        <v>13</v>
+      </c>
+      <c r="BU10">
+        <v>3.5</v>
+      </c>
+      <c r="BV10">
+        <v>75</v>
+      </c>
+      <c r="BW10">
         <v>4.5</v>
       </c>
-      <c r="H10">
-        <v>1.82</v>
-      </c>
-      <c r="I10">
-        <v>1.93</v>
-      </c>
-      <c r="J10">
-        <v>4.1</v>
-      </c>
-      <c r="K10">
-        <v>4.5</v>
-      </c>
-      <c r="L10">
-        <v>1.23</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>5.2</v>
-      </c>
-      <c r="O10">
-        <v>1.16</v>
-      </c>
-      <c r="P10">
-        <v>2.62</v>
-      </c>
-      <c r="Q10">
-        <v>1.5</v>
-      </c>
-      <c r="R10">
-        <v>1.69</v>
-      </c>
-      <c r="S10">
-        <v>2.12</v>
-      </c>
-      <c r="T10">
-        <v>1.46</v>
-      </c>
-      <c r="U10">
-        <v>2.54</v>
-      </c>
-      <c r="V10">
-        <v>2.06</v>
-      </c>
-      <c r="W10">
-        <v>1.28</v>
-      </c>
-      <c r="X10">
-        <v>1000</v>
-      </c>
-      <c r="Y10">
-        <v>1000</v>
-      </c>
-      <c r="Z10">
+      <c r="BX10">
+        <v>70</v>
+      </c>
+      <c r="BY10">
+        <v>4.4</v>
+      </c>
+      <c r="BZ10">
         <v>17</v>
       </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>1000</v>
-      </c>
-      <c r="AC10">
-        <v>11.5</v>
-      </c>
-      <c r="AD10">
-        <v>22</v>
-      </c>
-      <c r="AE10">
-        <v>18.5</v>
-      </c>
-      <c r="AF10">
-        <v>48</v>
-      </c>
-      <c r="AG10">
-        <v>20</v>
-      </c>
-      <c r="AH10">
-        <v>17</v>
-      </c>
-      <c r="AI10">
-        <v>1000</v>
-      </c>
-      <c r="AJ10">
-        <v>100</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>7.8</v>
-      </c>
-      <c r="AP10">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS10">
-        <v>17</v>
-      </c>
-      <c r="AT10">
-        <v>17</v>
-      </c>
-      <c r="AU10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW10">
-        <v>10</v>
-      </c>
-      <c r="AX10">
-        <v>1.01</v>
-      </c>
-      <c r="AY10">
-        <v>11</v>
-      </c>
-      <c r="AZ10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA10">
-        <v>16.5</v>
-      </c>
-      <c r="BB10">
-        <v>1.01</v>
-      </c>
-      <c r="BC10">
-        <v>1.01</v>
-      </c>
-      <c r="BD10">
-        <v>1.01</v>
-      </c>
-      <c r="BE10">
-        <v>36</v>
-      </c>
-      <c r="BF10">
-        <v>1.01</v>
-      </c>
-      <c r="BG10">
-        <v>5.6</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.01</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.01</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.01</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
-        <v>1.01</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
-        <v>1.01</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>1.01</v>
-      </c>
-      <c r="BT10">
-        <v>1000</v>
-      </c>
-      <c r="BU10">
-        <v>1.01</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>1.01</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>1.01</v>
-      </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="CB10" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="F11">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="H11">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="I11">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="J11">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3253,22 +3373,22 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="O11">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="Q11">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="R11">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="S11">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3277,10 +3397,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3451,7 +3571,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3459,300 +3579,300 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="F12">
-        <v>1.47</v>
+        <v>2.22</v>
       </c>
       <c r="G12">
-        <v>1.53</v>
+        <v>2.26</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="I12">
+        <v>3.8</v>
+      </c>
+      <c r="J12">
+        <v>3.5</v>
+      </c>
+      <c r="K12">
+        <v>3.55</v>
+      </c>
+      <c r="L12">
+        <v>1.4</v>
+      </c>
+      <c r="M12">
+        <v>1.08</v>
+      </c>
+      <c r="N12">
+        <v>3.65</v>
+      </c>
+      <c r="O12">
+        <v>1.35</v>
+      </c>
+      <c r="P12">
+        <v>1.89</v>
+      </c>
+      <c r="Q12">
+        <v>2.04</v>
+      </c>
+      <c r="R12">
+        <v>1.34</v>
+      </c>
+      <c r="S12">
+        <v>3.7</v>
+      </c>
+      <c r="T12">
+        <v>1.84</v>
+      </c>
+      <c r="U12">
+        <v>2.12</v>
+      </c>
+      <c r="V12">
+        <v>1.36</v>
+      </c>
+      <c r="W12">
+        <v>1.79</v>
+      </c>
+      <c r="X12">
+        <v>13.5</v>
+      </c>
+      <c r="Y12">
+        <v>14</v>
+      </c>
+      <c r="Z12">
+        <v>26</v>
+      </c>
+      <c r="AA12">
+        <v>75</v>
+      </c>
+      <c r="AB12">
         <v>9.800000000000001</v>
       </c>
-      <c r="J12">
-        <v>4.7</v>
-      </c>
-      <c r="K12">
-        <v>5.1</v>
-      </c>
-      <c r="L12">
-        <v>1.27</v>
-      </c>
-      <c r="M12">
-        <v>1.05</v>
-      </c>
-      <c r="N12">
-        <v>4.4</v>
-      </c>
-      <c r="O12">
-        <v>1.21</v>
-      </c>
-      <c r="P12">
-        <v>2.1</v>
-      </c>
-      <c r="Q12">
-        <v>1.57</v>
-      </c>
-      <c r="R12">
-        <v>1.46</v>
-      </c>
-      <c r="S12">
-        <v>2.54</v>
-      </c>
-      <c r="T12">
-        <v>1.8</v>
-      </c>
-      <c r="U12">
-        <v>1.93</v>
-      </c>
-      <c r="V12">
+      <c r="AC12">
+        <v>7.8</v>
+      </c>
+      <c r="AD12">
+        <v>15</v>
+      </c>
+      <c r="AE12">
+        <v>48</v>
+      </c>
+      <c r="AF12">
+        <v>14</v>
+      </c>
+      <c r="AG12">
+        <v>11</v>
+      </c>
+      <c r="AH12">
+        <v>18.5</v>
+      </c>
+      <c r="AI12">
+        <v>60</v>
+      </c>
+      <c r="AJ12">
+        <v>27</v>
+      </c>
+      <c r="AK12">
+        <v>24</v>
+      </c>
+      <c r="AL12">
+        <v>40</v>
+      </c>
+      <c r="AM12">
+        <v>100</v>
+      </c>
+      <c r="AN12">
+        <v>18.5</v>
+      </c>
+      <c r="AO12">
+        <v>50</v>
+      </c>
+      <c r="AP12">
+        <v>12</v>
+      </c>
+      <c r="AQ12">
+        <v>12.5</v>
+      </c>
+      <c r="AR12">
+        <v>23</v>
+      </c>
+      <c r="AS12">
+        <v>60</v>
+      </c>
+      <c r="AT12">
+        <v>9</v>
+      </c>
+      <c r="AU12">
+        <v>7.2</v>
+      </c>
+      <c r="AV12">
+        <v>13.5</v>
+      </c>
+      <c r="AW12">
+        <v>40</v>
+      </c>
+      <c r="AX12">
+        <v>12.5</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
+        <v>16</v>
+      </c>
+      <c r="BA12">
+        <v>48</v>
+      </c>
+      <c r="BB12">
+        <v>25</v>
+      </c>
+      <c r="BC12">
+        <v>21</v>
+      </c>
+      <c r="BD12">
+        <v>34</v>
+      </c>
+      <c r="BE12">
+        <v>40</v>
+      </c>
+      <c r="BF12">
+        <v>16</v>
+      </c>
+      <c r="BG12">
+        <v>38</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.38</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
         <v>1.11</v>
       </c>
-      <c r="W12">
-        <v>2.88</v>
-      </c>
-      <c r="X12">
-        <v>1000</v>
-      </c>
-      <c r="Y12">
-        <v>1000</v>
-      </c>
-      <c r="Z12">
-        <v>1000</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>1000</v>
-      </c>
-      <c r="AC12">
-        <v>1000</v>
-      </c>
-      <c r="AD12">
-        <v>1000</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>1000</v>
-      </c>
-      <c r="AG12">
-        <v>1000</v>
-      </c>
-      <c r="AH12">
-        <v>1000</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>1.01</v>
-      </c>
-      <c r="AQ12">
-        <v>1.01</v>
-      </c>
-      <c r="AR12">
-        <v>1.01</v>
-      </c>
-      <c r="AS12">
-        <v>1.01</v>
-      </c>
-      <c r="AT12">
-        <v>1.01</v>
-      </c>
-      <c r="AU12">
-        <v>1.01</v>
-      </c>
-      <c r="AV12">
-        <v>1.01</v>
-      </c>
-      <c r="AW12">
-        <v>1.01</v>
-      </c>
-      <c r="AX12">
-        <v>1.01</v>
-      </c>
-      <c r="AY12">
-        <v>1.01</v>
-      </c>
-      <c r="AZ12">
-        <v>1.01</v>
-      </c>
-      <c r="BA12">
-        <v>1.01</v>
-      </c>
-      <c r="BB12">
-        <v>1.01</v>
-      </c>
-      <c r="BC12">
-        <v>1.01</v>
-      </c>
-      <c r="BD12">
-        <v>1.01</v>
-      </c>
-      <c r="BE12">
-        <v>1.01</v>
-      </c>
-      <c r="BF12">
-        <v>1.01</v>
-      </c>
-      <c r="BG12">
-        <v>1.01</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.01</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>6.6</v>
-      </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>21</v>
+        <v>1.11</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="BP12">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>5.6</v>
+        <v>1.11</v>
       </c>
       <c r="BR12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BT12">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
         <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>21</v>
+        <v>1.11</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>21</v>
+        <v>1.11</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>8.4</v>
+        <v>1.11</v>
       </c>
       <c r="CB12" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="F13">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="G13">
-        <v>3.35</v>
+        <v>1.74</v>
       </c>
       <c r="H13">
-        <v>2.26</v>
+        <v>4.9</v>
       </c>
       <c r="I13">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J13">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K13">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O13">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="P13">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="Q13">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="R13">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S13">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3761,10 +3881,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.12</v>
       </c>
       <c r="W13">
-        <v>1.42</v>
+        <v>2.36</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3878,7 +3998,7 @@
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
@@ -3935,249 +4055,249 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="F14">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="G14">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H14">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="J14">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="K14">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N14">
-        <v>3.7</v>
+        <v>2.58</v>
       </c>
       <c r="O14">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="P14">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="Q14">
-        <v>2.04</v>
+        <v>2.66</v>
       </c>
       <c r="R14">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="S14">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="T14">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="U14">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="W14">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="X14">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y14">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z14">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AC14">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AD14">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG14">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
         <v>1000</v>
       </c>
       <c r="AN14">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>11.5</v>
+        <v>1.52</v>
       </c>
       <c r="AQ14">
-        <v>12.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR14">
-        <v>24</v>
+        <v>1.74</v>
       </c>
       <c r="AS14">
-        <v>46</v>
+        <v>1.74</v>
       </c>
       <c r="AT14">
-        <v>8.800000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="AU14">
-        <v>7.2</v>
+        <v>1.47</v>
       </c>
       <c r="AV14">
-        <v>14</v>
+        <v>1.74</v>
       </c>
       <c r="AW14">
-        <v>40</v>
+        <v>1.74</v>
       </c>
       <c r="AX14">
-        <v>11.5</v>
+        <v>1.59</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>1.62</v>
       </c>
       <c r="AZ14">
-        <v>16</v>
+        <v>1.74</v>
       </c>
       <c r="BA14">
-        <v>50</v>
+        <v>1.74</v>
       </c>
       <c r="BB14">
-        <v>24</v>
+        <v>1.74</v>
       </c>
       <c r="BC14">
-        <v>21</v>
+        <v>1.74</v>
       </c>
       <c r="BD14">
-        <v>34</v>
+        <v>1.74</v>
       </c>
       <c r="BE14">
-        <v>65</v>
+        <v>1.74</v>
       </c>
       <c r="BF14">
-        <v>15</v>
+        <v>1.74</v>
       </c>
       <c r="BG14">
-        <v>28</v>
+        <v>1.74</v>
       </c>
       <c r="BH14">
-        <v>970</v>
+        <v>3.1</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>29</v>
+        <v>1.49</v>
       </c>
       <c r="BN14">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>7.8</v>
+        <v>1.49</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>12.5</v>
+        <v>1.49</v>
       </c>
       <c r="BT14">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>12.5</v>
+        <v>1.49</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>15.5</v>
+        <v>1.49</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>11</v>
+        <v>1.49</v>
       </c>
       <c r="CB14" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4185,16 +4305,16 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="F15">
         <v>2.58</v>
@@ -4203,16 +4323,16 @@
         <v>3.05</v>
       </c>
       <c r="H15">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="I15">
         <v>2.66</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="K15">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4224,7 +4344,7 @@
         <v>2.56</v>
       </c>
       <c r="O15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P15">
         <v>2.56</v>
@@ -4233,10 +4353,10 @@
         <v>1.49</v>
       </c>
       <c r="R15">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="S15">
-        <v>1.57</v>
+        <v>2.22</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4419,135 +4539,135 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="F16">
-        <v>2.96</v>
+        <v>1.23</v>
       </c>
       <c r="G16">
-        <v>3.6</v>
+        <v>1.28</v>
       </c>
       <c r="H16">
-        <v>2.24</v>
+        <v>16</v>
       </c>
       <c r="I16">
-        <v>2.76</v>
+        <v>24</v>
       </c>
       <c r="J16">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="O16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="P16">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q16">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="R16">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S16">
-        <v>2.02</v>
+        <v>2.72</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="W16">
-        <v>1.39</v>
+        <v>4.5</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA16">
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16">
         <v>1.01</v>
@@ -4559,10 +4679,10 @@
         <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV16">
         <v>1.01</v>
@@ -4571,10 +4691,10 @@
         <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16">
         <v>1.01</v>
@@ -4583,10 +4703,10 @@
         <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD16">
         <v>1.01</v>
@@ -4595,7 +4715,7 @@
         <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG16">
         <v>1.01</v>
@@ -4655,48 +4775,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="F17">
-        <v>1.23</v>
+        <v>1.95</v>
       </c>
       <c r="G17">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="I17">
-        <v>20</v>
+        <v>3.95</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4705,22 +4825,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.22</v>
+        <v>2.88</v>
       </c>
       <c r="O17">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="Q17">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="R17">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S17">
-        <v>2.68</v>
+        <v>2.12</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4729,10 +4849,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4750,10 +4870,10 @@
         <v>1000</v>
       </c>
       <c r="AC17">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
         <v>1000</v>
@@ -4807,7 +4927,7 @@
         <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
         <v>1.01</v>
@@ -4837,16 +4957,16 @@
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
@@ -4897,90 +5017,90 @@
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="F18">
-        <v>1.97</v>
+        <v>2.96</v>
       </c>
       <c r="G18">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="H18">
-        <v>4.8</v>
+        <v>2.24</v>
       </c>
       <c r="I18">
-        <v>6.2</v>
+        <v>2.76</v>
       </c>
       <c r="J18">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="K18">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="O18">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="P18">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="Q18">
-        <v>2.66</v>
+        <v>1.5</v>
       </c>
       <c r="R18">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="S18">
-        <v>5.1</v>
+        <v>2.02</v>
       </c>
       <c r="T18">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="W18">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="X18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
         <v>1000</v>
@@ -4989,10 +5109,10 @@
         <v>1000</v>
       </c>
       <c r="AB18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
         <v>1000</v>
@@ -5001,10 +5121,10 @@
         <v>1000</v>
       </c>
       <c r="AF18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
         <v>1000</v>
@@ -5031,64 +5151,64 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
@@ -5106,7 +5226,7 @@
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
         <v>1000</v>
@@ -5145,7 +5265,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5153,683 +5273,683 @@
         <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="F19">
-        <v>1.56</v>
+        <v>4.2</v>
       </c>
       <c r="G19">
-        <v>1.74</v>
+        <v>4.5</v>
       </c>
       <c r="H19">
-        <v>4.9</v>
+        <v>1.82</v>
       </c>
       <c r="I19">
+        <v>1.93</v>
+      </c>
+      <c r="J19">
+        <v>4.1</v>
+      </c>
+      <c r="K19">
+        <v>4.5</v>
+      </c>
+      <c r="L19">
+        <v>1.23</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>6</v>
+      </c>
+      <c r="O19">
+        <v>1.17</v>
+      </c>
+      <c r="P19">
+        <v>2.68</v>
+      </c>
+      <c r="Q19">
+        <v>1.5</v>
+      </c>
+      <c r="R19">
+        <v>1.69</v>
+      </c>
+      <c r="S19">
+        <v>2.2</v>
+      </c>
+      <c r="T19">
+        <v>1.5</v>
+      </c>
+      <c r="U19">
+        <v>2.54</v>
+      </c>
+      <c r="V19">
+        <v>2.06</v>
+      </c>
+      <c r="W19">
+        <v>1.28</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>50</v>
+      </c>
+      <c r="Z19">
+        <v>17</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>11.5</v>
+      </c>
+      <c r="AD19">
+        <v>22</v>
+      </c>
+      <c r="AE19">
+        <v>18.5</v>
+      </c>
+      <c r="AF19">
+        <v>48</v>
+      </c>
+      <c r="AG19">
+        <v>20</v>
+      </c>
+      <c r="AH19">
+        <v>17</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>100</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>7.8</v>
+      </c>
+      <c r="AP19">
+        <v>2.2</v>
+      </c>
+      <c r="AQ19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS19">
+        <v>17</v>
+      </c>
+      <c r="AT19">
+        <v>17</v>
+      </c>
+      <c r="AU19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV19">
         <v>9.199999999999999</v>
       </c>
-      <c r="J19">
-        <v>4</v>
-      </c>
-      <c r="K19">
-        <v>6.8</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>3.8</v>
-      </c>
-      <c r="O19">
-        <v>1.28</v>
-      </c>
-      <c r="P19">
-        <v>1.97</v>
-      </c>
-      <c r="Q19">
-        <v>1.78</v>
-      </c>
-      <c r="R19">
+      <c r="AW19">
+        <v>10</v>
+      </c>
+      <c r="AX19">
+        <v>2.08</v>
+      </c>
+      <c r="AY19">
+        <v>1.98</v>
+      </c>
+      <c r="AZ19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA19">
+        <v>16.5</v>
+      </c>
+      <c r="BB19">
+        <v>2.16</v>
+      </c>
+      <c r="BC19">
+        <v>2.2</v>
+      </c>
+      <c r="BD19">
+        <v>2.2</v>
+      </c>
+      <c r="BE19">
+        <v>2.2</v>
+      </c>
+      <c r="BF19">
+        <v>19</v>
+      </c>
+      <c r="BG19">
+        <v>5.6</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.31</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.54</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.72</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.72</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.72</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.72</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
         <v>1.35</v>
       </c>
-      <c r="S19">
-        <v>2.78</v>
-      </c>
-      <c r="T19">
-        <v>1.01</v>
-      </c>
-      <c r="U19">
-        <v>1.01</v>
-      </c>
-      <c r="V19">
-        <v>1.12</v>
-      </c>
-      <c r="W19">
-        <v>2.3</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>1000</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>1000</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>1.01</v>
-      </c>
-      <c r="AQ19">
-        <v>1.01</v>
-      </c>
-      <c r="AR19">
-        <v>1.01</v>
-      </c>
-      <c r="AS19">
-        <v>1.01</v>
-      </c>
-      <c r="AT19">
-        <v>1.01</v>
-      </c>
-      <c r="AU19">
-        <v>1.01</v>
-      </c>
-      <c r="AV19">
-        <v>1.01</v>
-      </c>
-      <c r="AW19">
-        <v>1.01</v>
-      </c>
-      <c r="AX19">
-        <v>1.01</v>
-      </c>
-      <c r="AY19">
-        <v>1.01</v>
-      </c>
-      <c r="AZ19">
-        <v>1.01</v>
-      </c>
-      <c r="BA19">
-        <v>1.01</v>
-      </c>
-      <c r="BB19">
-        <v>1.01</v>
-      </c>
-      <c r="BC19">
-        <v>1.01</v>
-      </c>
-      <c r="BD19">
-        <v>1.01</v>
-      </c>
-      <c r="BE19">
-        <v>1.01</v>
-      </c>
-      <c r="BF19">
-        <v>1.01</v>
-      </c>
-      <c r="BG19">
-        <v>1.01</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>2.88</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.01</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.01</v>
-      </c>
-      <c r="BN19">
-        <v>1000</v>
-      </c>
-      <c r="BO19">
-        <v>1.01</v>
-      </c>
-      <c r="BP19">
-        <v>1000</v>
-      </c>
-      <c r="BQ19">
-        <v>1.01</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>1.01</v>
-      </c>
-      <c r="BT19">
-        <v>1000</v>
-      </c>
-      <c r="BU19">
-        <v>1.01</v>
-      </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="CB19" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="F20">
-        <v>1.19</v>
+        <v>1.98</v>
       </c>
       <c r="G20">
-        <v>1.23</v>
+        <v>1.99</v>
       </c>
       <c r="H20">
+        <v>4.9</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>3.4</v>
+      </c>
+      <c r="K20">
+        <v>3.45</v>
+      </c>
+      <c r="L20">
+        <v>1.51</v>
+      </c>
+      <c r="M20">
+        <v>1.1</v>
+      </c>
+      <c r="N20">
+        <v>3.1</v>
+      </c>
+      <c r="O20">
+        <v>1.44</v>
+      </c>
+      <c r="P20">
+        <v>1.7</v>
+      </c>
+      <c r="Q20">
+        <v>2.34</v>
+      </c>
+      <c r="R20">
+        <v>1.26</v>
+      </c>
+      <c r="S20">
+        <v>4.6</v>
+      </c>
+      <c r="T20">
+        <v>2.08</v>
+      </c>
+      <c r="U20">
+        <v>1.88</v>
+      </c>
+      <c r="V20">
+        <v>1.25</v>
+      </c>
+      <c r="W20">
+        <v>2</v>
+      </c>
+      <c r="X20">
+        <v>10.5</v>
+      </c>
+      <c r="Y20">
+        <v>14</v>
+      </c>
+      <c r="Z20">
+        <v>36</v>
+      </c>
+      <c r="AA20">
+        <v>130</v>
+      </c>
+      <c r="AB20">
+        <v>7.4</v>
+      </c>
+      <c r="AC20">
+        <v>7.6</v>
+      </c>
+      <c r="AD20">
+        <v>20</v>
+      </c>
+      <c r="AE20">
+        <v>80</v>
+      </c>
+      <c r="AF20">
+        <v>11</v>
+      </c>
+      <c r="AG20">
+        <v>10.5</v>
+      </c>
+      <c r="AH20">
+        <v>22</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>23</v>
+      </c>
+      <c r="AK20">
+        <v>24</v>
+      </c>
+      <c r="AL20">
+        <v>230</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>19</v>
+      </c>
+      <c r="AO20">
+        <v>110</v>
+      </c>
+      <c r="AP20">
+        <v>9.6</v>
+      </c>
+      <c r="AQ20">
+        <v>13</v>
+      </c>
+      <c r="AR20">
+        <v>30</v>
+      </c>
+      <c r="AS20">
+        <v>40</v>
+      </c>
+      <c r="AT20">
+        <v>6.8</v>
+      </c>
+      <c r="AU20">
+        <v>7.2</v>
+      </c>
+      <c r="AV20">
+        <v>17.5</v>
+      </c>
+      <c r="AW20">
+        <v>65</v>
+      </c>
+      <c r="AX20">
+        <v>9.6</v>
+      </c>
+      <c r="AY20">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20">
+        <v>21</v>
+      </c>
+      <c r="BA20">
+        <v>70</v>
+      </c>
+      <c r="BB20">
+        <v>20</v>
+      </c>
+      <c r="BC20">
+        <v>21</v>
+      </c>
+      <c r="BD20">
+        <v>42</v>
+      </c>
+      <c r="BE20">
+        <v>44</v>
+      </c>
+      <c r="BF20">
+        <v>16.5</v>
+      </c>
+      <c r="BG20">
+        <v>38</v>
+      </c>
+      <c r="BH20">
+        <v>2.98</v>
+      </c>
+      <c r="BI20">
+        <v>2.74</v>
+      </c>
+      <c r="BJ20">
+        <v>11</v>
+      </c>
+      <c r="BK20">
+        <v>6.6</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>16</v>
+      </c>
+      <c r="BN20">
+        <v>4.5</v>
+      </c>
+      <c r="BO20">
+        <v>4</v>
+      </c>
+      <c r="BP20">
+        <v>15</v>
+      </c>
+      <c r="BQ20">
+        <v>8</v>
+      </c>
+      <c r="BR20">
+        <v>34</v>
+      </c>
+      <c r="BS20">
+        <v>11.5</v>
+      </c>
+      <c r="BT20">
+        <v>8</v>
+      </c>
+      <c r="BU20">
+        <v>7</v>
+      </c>
+      <c r="BV20">
+        <v>46</v>
+      </c>
+      <c r="BW20">
+        <v>12.5</v>
+      </c>
+      <c r="BX20">
+        <v>60</v>
+      </c>
+      <c r="BY20">
         <v>13.5</v>
       </c>
-      <c r="I20">
-        <v>20</v>
-      </c>
-      <c r="J20">
-        <v>8.6</v>
-      </c>
-      <c r="K20">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>4.3</v>
-      </c>
-      <c r="Q20">
-        <v>1.26</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20">
-        <v>0</v>
-      </c>
-      <c r="AI20">
-        <v>0</v>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>0</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>0</v>
-      </c>
-      <c r="BC20">
-        <v>0</v>
-      </c>
-      <c r="BD20">
-        <v>0</v>
-      </c>
-      <c r="BE20">
-        <v>0</v>
-      </c>
-      <c r="BF20">
-        <v>0</v>
-      </c>
-      <c r="BG20">
-        <v>0</v>
-      </c>
-      <c r="BH20">
-        <v>0</v>
-      </c>
-      <c r="BI20">
-        <v>0</v>
-      </c>
-      <c r="BJ20">
-        <v>0</v>
-      </c>
-      <c r="BK20">
-        <v>0</v>
-      </c>
-      <c r="BL20">
-        <v>0</v>
-      </c>
-      <c r="BM20">
-        <v>0</v>
-      </c>
-      <c r="BN20">
-        <v>0</v>
-      </c>
-      <c r="BO20">
-        <v>0</v>
-      </c>
-      <c r="BP20">
-        <v>0</v>
-      </c>
-      <c r="BQ20">
-        <v>0</v>
-      </c>
-      <c r="BR20">
-        <v>0</v>
-      </c>
-      <c r="BS20">
-        <v>0</v>
-      </c>
-      <c r="BT20">
-        <v>0</v>
-      </c>
-      <c r="BU20">
-        <v>0</v>
-      </c>
-      <c r="BV20">
-        <v>0</v>
-      </c>
-      <c r="BW20">
-        <v>0</v>
-      </c>
-      <c r="BX20">
-        <v>0</v>
-      </c>
-      <c r="BY20">
-        <v>0</v>
-      </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CB20" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" t="s">
+        <v>167</v>
+      </c>
+      <c r="F21">
+        <v>1.2</v>
+      </c>
+      <c r="G21">
+        <v>1.22</v>
+      </c>
+      <c r="H21">
+        <v>13.5</v>
+      </c>
+      <c r="I21">
+        <v>18</v>
+      </c>
+      <c r="J21">
+        <v>8.6</v>
+      </c>
+      <c r="K21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L21">
+        <v>1.15</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>9</v>
+      </c>
+      <c r="O21">
+        <v>1.08</v>
+      </c>
+      <c r="P21">
+        <v>4.3</v>
+      </c>
+      <c r="Q21">
+        <v>1.27</v>
+      </c>
+      <c r="R21">
+        <v>2.34</v>
+      </c>
+      <c r="S21">
+        <v>1.67</v>
+      </c>
+      <c r="T21">
+        <v>1.77</v>
+      </c>
+      <c r="U21">
+        <v>2.04</v>
+      </c>
+      <c r="V21">
+        <v>1.06</v>
+      </c>
+      <c r="W21">
+        <v>5.5</v>
+      </c>
+      <c r="X21">
+        <v>85</v>
+      </c>
+      <c r="Y21">
         <v>100</v>
       </c>
-      <c r="D21" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F21">
-        <v>1.94</v>
-      </c>
-      <c r="G21">
-        <v>1.96</v>
-      </c>
-      <c r="H21">
-        <v>4.9</v>
-      </c>
-      <c r="I21">
-        <v>5.1</v>
-      </c>
-      <c r="J21">
-        <v>3.4</v>
-      </c>
-      <c r="K21">
-        <v>3.5</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>1.1</v>
-      </c>
-      <c r="N21">
-        <v>3.05</v>
-      </c>
-      <c r="O21">
-        <v>1.45</v>
-      </c>
-      <c r="P21">
-        <v>1.67</v>
-      </c>
-      <c r="Q21">
-        <v>2.38</v>
-      </c>
-      <c r="R21">
-        <v>1.25</v>
-      </c>
-      <c r="S21">
-        <v>4.6</v>
-      </c>
-      <c r="T21">
-        <v>2.1</v>
-      </c>
-      <c r="U21">
-        <v>1.84</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>10.5</v>
-      </c>
-      <c r="Y21">
-        <v>14.5</v>
-      </c>
       <c r="Z21">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AB21">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AC21">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="AD21">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF21">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG21">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH21">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ21">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AK21">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AL21">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN21">
-        <v>19</v>
+        <v>2.6</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP21">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ21">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR21">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AS21">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21">
         <v>6.6</v>
       </c>
       <c r="AU21">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV21">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AW21">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX21">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY21">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AZ21">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA21">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="BB21">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC21">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BD21">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="BE21">
-        <v>46</v>
+        <v>7.8</v>
       </c>
       <c r="BF21">
-        <v>16.5</v>
+        <v>2.42</v>
       </c>
       <c r="BG21">
-        <v>40</v>
+        <v>8.6</v>
       </c>
       <c r="BH21">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BN21">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
         <v>1.01</v>
@@ -5838,40 +5958,40 @@
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="CB21" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5879,28 +5999,28 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="F22">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="G22">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="J22">
         <v>3.2</v>
@@ -5909,453 +6029,4567 @@
         <v>4.4</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P22">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q22">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="CB22" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" t="s">
+        <v>169</v>
+      </c>
+      <c r="F23">
+        <v>1.02</v>
+      </c>
+      <c r="G23">
+        <v>110</v>
+      </c>
+      <c r="H23">
+        <v>1.02</v>
+      </c>
+      <c r="I23">
+        <v>1000</v>
+      </c>
+      <c r="J23">
+        <v>1.01</v>
+      </c>
+      <c r="K23">
+        <v>880</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>1.25</v>
+      </c>
+      <c r="O23">
+        <v>1.21</v>
+      </c>
+      <c r="P23">
+        <v>1.24</v>
+      </c>
+      <c r="Q23">
+        <v>1.21</v>
+      </c>
+      <c r="R23">
+        <v>1.18</v>
+      </c>
+      <c r="S23">
+        <v>1.21</v>
+      </c>
+      <c r="T23">
+        <v>1.01</v>
+      </c>
+      <c r="U23">
+        <v>1.01</v>
+      </c>
+      <c r="V23">
+        <v>1.01</v>
+      </c>
+      <c r="W23">
+        <v>1.01</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>1000</v>
+      </c>
+      <c r="AC23">
+        <v>1000</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
+        <v>1000</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23">
+        <v>1.01</v>
+      </c>
+      <c r="AR23">
+        <v>1.01</v>
+      </c>
+      <c r="AS23">
+        <v>1.01</v>
+      </c>
+      <c r="AT23">
+        <v>1.01</v>
+      </c>
+      <c r="AU23">
+        <v>1.01</v>
+      </c>
+      <c r="AV23">
+        <v>1.01</v>
+      </c>
+      <c r="AW23">
+        <v>1.01</v>
+      </c>
+      <c r="AX23">
+        <v>1.01</v>
+      </c>
+      <c r="AY23">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23">
+        <v>1.01</v>
+      </c>
+      <c r="BA23">
+        <v>1.01</v>
+      </c>
+      <c r="BB23">
+        <v>1.01</v>
+      </c>
+      <c r="BC23">
+        <v>1.01</v>
+      </c>
+      <c r="BD23">
+        <v>1.01</v>
+      </c>
+      <c r="BE23">
+        <v>1.01</v>
+      </c>
+      <c r="BF23">
+        <v>1.01</v>
+      </c>
+      <c r="BG23">
+        <v>1.01</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.01</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.01</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.01</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.01</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.01</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.01</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
         <v>93</v>
       </c>
-      <c r="C23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F24">
+        <v>1.02</v>
+      </c>
+      <c r="G24">
+        <v>110</v>
+      </c>
+      <c r="H24">
+        <v>1.02</v>
+      </c>
+      <c r="I24">
+        <v>1000</v>
+      </c>
+      <c r="J24">
+        <v>1.01</v>
+      </c>
+      <c r="K24">
+        <v>870</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>1.25</v>
+      </c>
+      <c r="O24">
+        <v>1.2</v>
+      </c>
+      <c r="P24">
+        <v>1.24</v>
+      </c>
+      <c r="Q24">
+        <v>1.2</v>
+      </c>
+      <c r="R24">
+        <v>1.18</v>
+      </c>
+      <c r="S24">
+        <v>1.2</v>
+      </c>
+      <c r="T24">
+        <v>1.01</v>
+      </c>
+      <c r="U24">
+        <v>1.01</v>
+      </c>
+      <c r="V24">
+        <v>1.01</v>
+      </c>
+      <c r="W24">
+        <v>1.01</v>
+      </c>
+      <c r="X24">
+        <v>1000</v>
+      </c>
+      <c r="Y24">
+        <v>1000</v>
+      </c>
+      <c r="Z24">
+        <v>1000</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>1000</v>
+      </c>
+      <c r="AC24">
+        <v>1000</v>
+      </c>
+      <c r="AD24">
+        <v>1000</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>1000</v>
+      </c>
+      <c r="AG24">
+        <v>1000</v>
+      </c>
+      <c r="AH24">
+        <v>1000</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>1000</v>
+      </c>
+      <c r="AK24">
+        <v>1000</v>
+      </c>
+      <c r="AL24">
+        <v>1000</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>1000</v>
+      </c>
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24">
+        <v>1.01</v>
+      </c>
+      <c r="AR24">
+        <v>1.01</v>
+      </c>
+      <c r="AS24">
+        <v>1.01</v>
+      </c>
+      <c r="AT24">
+        <v>1.01</v>
+      </c>
+      <c r="AU24">
+        <v>1.01</v>
+      </c>
+      <c r="AV24">
+        <v>1.01</v>
+      </c>
+      <c r="AW24">
+        <v>1.01</v>
+      </c>
+      <c r="AX24">
+        <v>1.01</v>
+      </c>
+      <c r="AY24">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24">
+        <v>1.01</v>
+      </c>
+      <c r="BA24">
+        <v>1.01</v>
+      </c>
+      <c r="BB24">
+        <v>1.01</v>
+      </c>
+      <c r="BC24">
+        <v>1.01</v>
+      </c>
+      <c r="BD24">
+        <v>1.01</v>
+      </c>
+      <c r="BE24">
+        <v>1.01</v>
+      </c>
+      <c r="BF24">
+        <v>1.01</v>
+      </c>
+      <c r="BG24">
+        <v>1.01</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.01</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.01</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.01</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.01</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.01</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.01</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25">
+        <v>1.03</v>
+      </c>
+      <c r="G25">
+        <v>110</v>
+      </c>
+      <c r="H25">
+        <v>1.02</v>
+      </c>
+      <c r="I25">
+        <v>1000</v>
+      </c>
+      <c r="J25">
+        <v>1.01</v>
+      </c>
+      <c r="K25">
+        <v>880</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>1.24</v>
+      </c>
+      <c r="O25">
+        <v>1.01</v>
+      </c>
+      <c r="P25">
+        <v>1.24</v>
+      </c>
+      <c r="Q25">
+        <v>1.02</v>
+      </c>
+      <c r="R25">
+        <v>1.18</v>
+      </c>
+      <c r="S25">
+        <v>1.32</v>
+      </c>
+      <c r="T25">
+        <v>1.01</v>
+      </c>
+      <c r="U25">
+        <v>1.01</v>
+      </c>
+      <c r="V25">
+        <v>1.01</v>
+      </c>
+      <c r="W25">
+        <v>1.01</v>
+      </c>
+      <c r="X25">
+        <v>1000</v>
+      </c>
+      <c r="Y25">
+        <v>1000</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>1000</v>
+      </c>
+      <c r="AC25">
+        <v>1000</v>
+      </c>
+      <c r="AD25">
+        <v>1000</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>1000</v>
+      </c>
+      <c r="AG25">
+        <v>1000</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25">
+        <v>1.01</v>
+      </c>
+      <c r="AR25">
+        <v>1.01</v>
+      </c>
+      <c r="AS25">
+        <v>1.01</v>
+      </c>
+      <c r="AT25">
+        <v>1.01</v>
+      </c>
+      <c r="AU25">
+        <v>1.01</v>
+      </c>
+      <c r="AV25">
+        <v>1.01</v>
+      </c>
+      <c r="AW25">
+        <v>1.01</v>
+      </c>
+      <c r="AX25">
+        <v>1.01</v>
+      </c>
+      <c r="AY25">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25">
+        <v>1.01</v>
+      </c>
+      <c r="BA25">
+        <v>1.01</v>
+      </c>
+      <c r="BB25">
+        <v>1.01</v>
+      </c>
+      <c r="BC25">
+        <v>1.01</v>
+      </c>
+      <c r="BD25">
+        <v>1.01</v>
+      </c>
+      <c r="BE25">
+        <v>1.01</v>
+      </c>
+      <c r="BF25">
+        <v>1.01</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.01</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.01</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26">
+        <v>1.02</v>
+      </c>
+      <c r="G26">
+        <v>110</v>
+      </c>
+      <c r="H26">
+        <v>1.16</v>
+      </c>
+      <c r="I26">
+        <v>1000</v>
+      </c>
+      <c r="J26">
+        <v>4.1</v>
+      </c>
+      <c r="K26">
+        <v>890</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>1.24</v>
+      </c>
+      <c r="O26">
+        <v>1.09</v>
+      </c>
+      <c r="P26">
+        <v>1.24</v>
+      </c>
+      <c r="Q26">
+        <v>1.09</v>
+      </c>
+      <c r="R26">
+        <v>1.18</v>
+      </c>
+      <c r="S26">
+        <v>1.09</v>
+      </c>
+      <c r="T26">
+        <v>1.01</v>
+      </c>
+      <c r="U26">
+        <v>1.01</v>
+      </c>
+      <c r="V26">
+        <v>1.01</v>
+      </c>
+      <c r="W26">
+        <v>1.14</v>
+      </c>
+      <c r="X26">
+        <v>1000</v>
+      </c>
+      <c r="Y26">
+        <v>1000</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>1000</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>1000</v>
+      </c>
+      <c r="AG26">
+        <v>1000</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26">
+        <v>1.01</v>
+      </c>
+      <c r="AR26">
+        <v>1.01</v>
+      </c>
+      <c r="AS26">
+        <v>1.01</v>
+      </c>
+      <c r="AT26">
+        <v>1.01</v>
+      </c>
+      <c r="AU26">
+        <v>1.01</v>
+      </c>
+      <c r="AV26">
+        <v>1.01</v>
+      </c>
+      <c r="AW26">
+        <v>1.01</v>
+      </c>
+      <c r="AX26">
+        <v>1.01</v>
+      </c>
+      <c r="AY26">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26">
+        <v>1.01</v>
+      </c>
+      <c r="BA26">
+        <v>1.01</v>
+      </c>
+      <c r="BB26">
+        <v>1.01</v>
+      </c>
+      <c r="BC26">
+        <v>1.01</v>
+      </c>
+      <c r="BD26">
+        <v>1.01</v>
+      </c>
+      <c r="BE26">
+        <v>1.01</v>
+      </c>
+      <c r="BF26">
+        <v>1.01</v>
+      </c>
+      <c r="BG26">
+        <v>1.01</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>1.01</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
+        <v>1.01</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>1.01</v>
+      </c>
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
+        <v>1.01</v>
+      </c>
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
+        <v>1.01</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>1.01</v>
+      </c>
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
+        <v>1.01</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>1.01</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
+        <v>1.01</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" t="s">
+        <v>173</v>
+      </c>
+      <c r="F27">
+        <v>1.31</v>
+      </c>
+      <c r="G27">
+        <v>2.2</v>
+      </c>
+      <c r="H27">
+        <v>1.87</v>
+      </c>
+      <c r="I27">
+        <v>1000</v>
+      </c>
+      <c r="J27">
+        <v>1.84</v>
+      </c>
+      <c r="K27">
+        <v>930</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
+        <v>2.52</v>
+      </c>
+      <c r="O27">
+        <v>1.01</v>
+      </c>
+      <c r="P27">
+        <v>2.52</v>
+      </c>
+      <c r="Q27">
+        <v>1.34</v>
+      </c>
+      <c r="R27">
+        <v>1.57</v>
+      </c>
+      <c r="S27">
+        <v>2.22</v>
+      </c>
+      <c r="T27">
+        <v>1.01</v>
+      </c>
+      <c r="U27">
+        <v>1.01</v>
+      </c>
+      <c r="V27">
+        <v>1.01</v>
+      </c>
+      <c r="W27">
+        <v>1.84</v>
+      </c>
+      <c r="X27">
+        <v>1000</v>
+      </c>
+      <c r="Y27">
+        <v>1000</v>
+      </c>
+      <c r="Z27">
+        <v>1000</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>1000</v>
+      </c>
+      <c r="AC27">
+        <v>1000</v>
+      </c>
+      <c r="AD27">
+        <v>1000</v>
+      </c>
+      <c r="AE27">
+        <v>1000</v>
+      </c>
+      <c r="AF27">
+        <v>1000</v>
+      </c>
+      <c r="AG27">
+        <v>1000</v>
+      </c>
+      <c r="AH27">
+        <v>1000</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>1000</v>
+      </c>
+      <c r="AK27">
+        <v>1000</v>
+      </c>
+      <c r="AL27">
+        <v>1000</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>1000</v>
+      </c>
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27">
+        <v>1.01</v>
+      </c>
+      <c r="AR27">
+        <v>1.01</v>
+      </c>
+      <c r="AS27">
+        <v>1.01</v>
+      </c>
+      <c r="AT27">
+        <v>1.01</v>
+      </c>
+      <c r="AU27">
+        <v>1.01</v>
+      </c>
+      <c r="AV27">
+        <v>1.01</v>
+      </c>
+      <c r="AW27">
+        <v>1.01</v>
+      </c>
+      <c r="AX27">
+        <v>1.01</v>
+      </c>
+      <c r="AY27">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27">
+        <v>1.01</v>
+      </c>
+      <c r="BA27">
+        <v>1.01</v>
+      </c>
+      <c r="BB27">
+        <v>1.01</v>
+      </c>
+      <c r="BC27">
+        <v>1.01</v>
+      </c>
+      <c r="BD27">
+        <v>1.01</v>
+      </c>
+      <c r="BE27">
+        <v>1.01</v>
+      </c>
+      <c r="BF27">
+        <v>1.01</v>
+      </c>
+      <c r="BG27">
+        <v>1.01</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.01</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.01</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.01</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.01</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F28">
+        <v>5.9</v>
+      </c>
+      <c r="G28">
+        <v>7.8</v>
+      </c>
+      <c r="H28">
+        <v>1.6</v>
+      </c>
+      <c r="I28">
+        <v>1.69</v>
+      </c>
+      <c r="J28">
+        <v>4.1</v>
+      </c>
+      <c r="K28">
+        <v>4.4</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.02</v>
+      </c>
+      <c r="N28">
+        <v>3.6</v>
+      </c>
+      <c r="O28">
+        <v>1.3</v>
+      </c>
+      <c r="P28">
+        <v>1.99</v>
+      </c>
+      <c r="Q28">
+        <v>1.85</v>
+      </c>
+      <c r="R28">
+        <v>1.34</v>
+      </c>
+      <c r="S28">
+        <v>3</v>
+      </c>
+      <c r="T28">
+        <v>1.82</v>
+      </c>
+      <c r="U28">
+        <v>1.88</v>
+      </c>
+      <c r="V28">
+        <v>2.44</v>
+      </c>
+      <c r="W28">
+        <v>1.16</v>
+      </c>
+      <c r="X28">
+        <v>1000</v>
+      </c>
+      <c r="Y28">
+        <v>13</v>
+      </c>
+      <c r="Z28">
+        <v>1000</v>
+      </c>
+      <c r="AA28">
+        <v>17.5</v>
+      </c>
+      <c r="AB28">
+        <v>1000</v>
+      </c>
+      <c r="AC28">
+        <v>1000</v>
+      </c>
+      <c r="AD28">
+        <v>1000</v>
+      </c>
+      <c r="AE28">
+        <v>19</v>
+      </c>
+      <c r="AF28">
+        <v>1000</v>
+      </c>
+      <c r="AG28">
+        <v>1000</v>
+      </c>
+      <c r="AH28">
+        <v>1000</v>
+      </c>
+      <c r="AI28">
+        <v>44</v>
+      </c>
+      <c r="AJ28">
+        <v>1000</v>
+      </c>
+      <c r="AK28">
+        <v>1000</v>
+      </c>
+      <c r="AL28">
+        <v>1000</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>1000</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>10</v>
+      </c>
+      <c r="AQ28">
+        <v>6.2</v>
+      </c>
+      <c r="AR28">
+        <v>7</v>
+      </c>
+      <c r="AS28">
+        <v>10</v>
+      </c>
+      <c r="AT28">
+        <v>16.5</v>
+      </c>
+      <c r="AU28">
+        <v>6.8</v>
+      </c>
+      <c r="AV28">
+        <v>7.2</v>
+      </c>
+      <c r="AW28">
+        <v>10.5</v>
+      </c>
+      <c r="AX28">
+        <v>36</v>
+      </c>
+      <c r="AY28">
+        <v>17</v>
+      </c>
+      <c r="AZ28">
+        <v>1.01</v>
+      </c>
+      <c r="BA28">
+        <v>1.01</v>
+      </c>
+      <c r="BB28">
+        <v>95</v>
+      </c>
+      <c r="BC28">
+        <v>1.01</v>
+      </c>
+      <c r="BD28">
+        <v>1.01</v>
+      </c>
+      <c r="BE28">
+        <v>85</v>
+      </c>
+      <c r="BF28">
+        <v>75</v>
+      </c>
+      <c r="BG28">
+        <v>6.8</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.01</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.01</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.01</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.01</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.01</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.01</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.01</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.01</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" t="s">
+        <v>175</v>
+      </c>
+      <c r="F29">
+        <v>1.63</v>
+      </c>
+      <c r="G29">
+        <v>1.64</v>
+      </c>
+      <c r="H29">
+        <v>5.8</v>
+      </c>
+      <c r="I29">
+        <v>5.9</v>
+      </c>
+      <c r="J29">
+        <v>4.5</v>
+      </c>
+      <c r="K29">
+        <v>4.6</v>
+      </c>
+      <c r="L29">
+        <v>1.32</v>
+      </c>
+      <c r="M29">
+        <v>1.05</v>
+      </c>
+      <c r="N29">
+        <v>4.9</v>
+      </c>
+      <c r="O29">
+        <v>1.22</v>
+      </c>
+      <c r="P29">
+        <v>2.32</v>
+      </c>
+      <c r="Q29">
+        <v>1.68</v>
+      </c>
+      <c r="R29">
+        <v>1.53</v>
+      </c>
+      <c r="S29">
+        <v>2.68</v>
+      </c>
+      <c r="T29">
+        <v>1.76</v>
+      </c>
+      <c r="U29">
+        <v>2.2</v>
+      </c>
+      <c r="V29">
+        <v>1.2</v>
+      </c>
+      <c r="W29">
+        <v>2.56</v>
+      </c>
+      <c r="X29">
+        <v>21</v>
+      </c>
+      <c r="Y29">
+        <v>25</v>
+      </c>
+      <c r="Z29">
+        <v>50</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>10.5</v>
+      </c>
+      <c r="AC29">
+        <v>10.5</v>
+      </c>
+      <c r="AD29">
+        <v>23</v>
+      </c>
+      <c r="AE29">
+        <v>1000</v>
+      </c>
+      <c r="AF29">
+        <v>11</v>
+      </c>
+      <c r="AG29">
+        <v>10</v>
+      </c>
+      <c r="AH29">
+        <v>19.5</v>
+      </c>
+      <c r="AI29">
+        <v>70</v>
+      </c>
+      <c r="AJ29">
+        <v>16.5</v>
+      </c>
+      <c r="AK29">
+        <v>16</v>
+      </c>
+      <c r="AL29">
+        <v>30</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>7.4</v>
+      </c>
+      <c r="AO29">
+        <v>75</v>
+      </c>
+      <c r="AP29">
+        <v>19</v>
+      </c>
+      <c r="AQ29">
+        <v>21</v>
+      </c>
+      <c r="AR29">
+        <v>42</v>
+      </c>
+      <c r="AS29">
+        <v>42</v>
+      </c>
+      <c r="AT29">
+        <v>9.4</v>
+      </c>
+      <c r="AU29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV29">
+        <v>20</v>
+      </c>
+      <c r="AW29">
+        <v>60</v>
+      </c>
+      <c r="AX29">
+        <v>9.6</v>
+      </c>
+      <c r="AY29">
+        <v>9</v>
+      </c>
+      <c r="AZ29">
+        <v>17.5</v>
+      </c>
+      <c r="BA29">
+        <v>55</v>
+      </c>
+      <c r="BB29">
+        <v>14.5</v>
+      </c>
+      <c r="BC29">
+        <v>14</v>
+      </c>
+      <c r="BD29">
+        <v>26</v>
+      </c>
+      <c r="BE29">
+        <v>36</v>
+      </c>
+      <c r="BF29">
+        <v>6.8</v>
+      </c>
+      <c r="BG29">
+        <v>32</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>3.35</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>7</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.01</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>3.55</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>7.2</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.01</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>6.6</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.01</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.01</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.01</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F30">
+        <v>2.02</v>
+      </c>
+      <c r="G30">
+        <v>2.1</v>
+      </c>
+      <c r="H30">
+        <v>3.9</v>
+      </c>
+      <c r="I30">
+        <v>4.1</v>
+      </c>
+      <c r="J30">
+        <v>3.65</v>
+      </c>
+      <c r="K30">
+        <v>3.9</v>
+      </c>
+      <c r="L30">
+        <v>1.38</v>
+      </c>
+      <c r="M30">
+        <v>1.06</v>
+      </c>
+      <c r="N30">
+        <v>4</v>
+      </c>
+      <c r="O30">
+        <v>1.3</v>
+      </c>
+      <c r="P30">
+        <v>2.02</v>
+      </c>
+      <c r="Q30">
+        <v>1.92</v>
+      </c>
+      <c r="R30">
+        <v>1.39</v>
+      </c>
+      <c r="S30">
+        <v>3.3</v>
+      </c>
+      <c r="T30">
+        <v>1.76</v>
+      </c>
+      <c r="U30">
+        <v>2.18</v>
+      </c>
+      <c r="V30">
+        <v>1.32</v>
+      </c>
+      <c r="W30">
+        <v>1.91</v>
+      </c>
+      <c r="X30">
+        <v>16</v>
+      </c>
+      <c r="Y30">
+        <v>15.5</v>
+      </c>
+      <c r="Z30">
+        <v>32</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>10</v>
+      </c>
+      <c r="AC30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD30">
+        <v>17</v>
+      </c>
+      <c r="AE30">
+        <v>150</v>
+      </c>
+      <c r="AF30">
+        <v>13</v>
+      </c>
+      <c r="AG30">
+        <v>11</v>
+      </c>
+      <c r="AH30">
+        <v>19.5</v>
+      </c>
+      <c r="AI30">
+        <v>420</v>
+      </c>
+      <c r="AJ30">
+        <v>26</v>
+      </c>
+      <c r="AK30">
+        <v>22</v>
+      </c>
+      <c r="AL30">
+        <v>42</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>14.5</v>
+      </c>
+      <c r="AO30">
+        <v>190</v>
+      </c>
+      <c r="AP30">
+        <v>13.5</v>
+      </c>
+      <c r="AQ30">
+        <v>13.5</v>
+      </c>
+      <c r="AR30">
+        <v>19</v>
+      </c>
+      <c r="AS30">
+        <v>48</v>
+      </c>
+      <c r="AT30">
+        <v>9</v>
+      </c>
+      <c r="AU30">
+        <v>7.6</v>
+      </c>
+      <c r="AV30">
+        <v>13.5</v>
+      </c>
+      <c r="AW30">
+        <v>26</v>
+      </c>
+      <c r="AX30">
+        <v>11.5</v>
+      </c>
+      <c r="AY30">
+        <v>9.6</v>
+      </c>
+      <c r="AZ30">
+        <v>16</v>
+      </c>
+      <c r="BA30">
+        <v>38</v>
+      </c>
+      <c r="BB30">
+        <v>21</v>
+      </c>
+      <c r="BC30">
+        <v>17.5</v>
+      </c>
+      <c r="BD30">
+        <v>23</v>
+      </c>
+      <c r="BE30">
+        <v>38</v>
+      </c>
+      <c r="BF30">
+        <v>12.5</v>
+      </c>
+      <c r="BG30">
+        <v>36</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>2.98</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>6.8</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.01</v>
+      </c>
+      <c r="BN30">
+        <v>5.8</v>
+      </c>
+      <c r="BO30">
+        <v>3.9</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.01</v>
+      </c>
+      <c r="BT30">
+        <v>1000</v>
+      </c>
+      <c r="BU30">
+        <v>5.5</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.01</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>1.01</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31">
+        <v>2.36</v>
+      </c>
+      <c r="G31">
+        <v>2.52</v>
+      </c>
+      <c r="H31">
+        <v>3.05</v>
+      </c>
+      <c r="I31">
+        <v>3.25</v>
+      </c>
+      <c r="J31">
+        <v>3.6</v>
+      </c>
+      <c r="K31">
+        <v>3.85</v>
+      </c>
+      <c r="L31">
+        <v>1.33</v>
+      </c>
+      <c r="M31">
+        <v>1.06</v>
+      </c>
+      <c r="N31">
+        <v>3.55</v>
+      </c>
+      <c r="O31">
+        <v>1.28</v>
+      </c>
+      <c r="P31">
+        <v>2.04</v>
+      </c>
+      <c r="Q31">
+        <v>1.81</v>
+      </c>
+      <c r="R31">
+        <v>1.38</v>
+      </c>
+      <c r="S31">
+        <v>3</v>
+      </c>
+      <c r="T31">
+        <v>1.69</v>
+      </c>
+      <c r="U31">
+        <v>2.24</v>
+      </c>
+      <c r="V31">
+        <v>1.44</v>
+      </c>
+      <c r="W31">
+        <v>1.66</v>
+      </c>
+      <c r="X31">
+        <v>21</v>
+      </c>
+      <c r="Y31">
+        <v>14.5</v>
+      </c>
+      <c r="Z31">
+        <v>25</v>
+      </c>
+      <c r="AA31">
+        <v>65</v>
+      </c>
+      <c r="AB31">
+        <v>12</v>
+      </c>
+      <c r="AC31">
+        <v>10.5</v>
+      </c>
+      <c r="AD31">
+        <v>14.5</v>
+      </c>
+      <c r="AE31">
+        <v>38</v>
+      </c>
+      <c r="AF31">
+        <v>17</v>
+      </c>
+      <c r="AG31">
+        <v>12</v>
+      </c>
+      <c r="AH31">
+        <v>17</v>
+      </c>
+      <c r="AI31">
+        <v>55</v>
+      </c>
+      <c r="AJ31">
+        <v>34</v>
+      </c>
+      <c r="AK31">
+        <v>26</v>
+      </c>
+      <c r="AL31">
+        <v>38</v>
+      </c>
+      <c r="AM31">
+        <v>95</v>
+      </c>
+      <c r="AN31">
+        <v>18</v>
+      </c>
+      <c r="AO31">
+        <v>32</v>
+      </c>
+      <c r="AP31">
+        <v>14</v>
+      </c>
+      <c r="AQ31">
+        <v>12</v>
+      </c>
+      <c r="AR31">
+        <v>19.5</v>
+      </c>
+      <c r="AS31">
+        <v>44</v>
+      </c>
+      <c r="AT31">
+        <v>10</v>
+      </c>
+      <c r="AU31">
+        <v>7.4</v>
+      </c>
+      <c r="AV31">
+        <v>12</v>
+      </c>
+      <c r="AW31">
+        <v>29</v>
+      </c>
+      <c r="AX31">
+        <v>13.5</v>
+      </c>
+      <c r="AY31">
+        <v>10</v>
+      </c>
+      <c r="AZ31">
+        <v>13.5</v>
+      </c>
+      <c r="BA31">
+        <v>34</v>
+      </c>
+      <c r="BB31">
+        <v>26</v>
+      </c>
+      <c r="BC31">
+        <v>20</v>
+      </c>
+      <c r="BD31">
+        <v>29</v>
+      </c>
+      <c r="BE31">
+        <v>65</v>
+      </c>
+      <c r="BF31">
+        <v>14.5</v>
+      </c>
+      <c r="BG31">
+        <v>24</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.01</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.01</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.01</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.01</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.01</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.01</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.01</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.01</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.01</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>1.01</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" t="s">
+        <v>178</v>
+      </c>
+      <c r="F32">
+        <v>2.1</v>
+      </c>
+      <c r="G32">
+        <v>2.24</v>
+      </c>
+      <c r="H32">
+        <v>3.2</v>
+      </c>
+      <c r="I32">
+        <v>3.45</v>
+      </c>
+      <c r="J32">
+        <v>3.95</v>
+      </c>
+      <c r="K32">
+        <v>4.4</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>5.2</v>
+      </c>
+      <c r="O32">
+        <v>1.17</v>
+      </c>
+      <c r="P32">
+        <v>2.48</v>
+      </c>
+      <c r="Q32">
+        <v>1.57</v>
+      </c>
+      <c r="R32">
+        <v>1.59</v>
+      </c>
+      <c r="S32">
+        <v>2.4</v>
+      </c>
+      <c r="T32">
+        <v>1.48</v>
+      </c>
+      <c r="U32">
+        <v>2.46</v>
+      </c>
+      <c r="V32">
+        <v>1.4</v>
+      </c>
+      <c r="W32">
+        <v>1.8</v>
+      </c>
+      <c r="X32">
+        <v>1000</v>
+      </c>
+      <c r="Y32">
+        <v>19.5</v>
+      </c>
+      <c r="Z32">
+        <v>1000</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>1000</v>
+      </c>
+      <c r="AC32">
+        <v>10.5</v>
+      </c>
+      <c r="AD32">
+        <v>1000</v>
+      </c>
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>21</v>
+      </c>
+      <c r="AG32">
+        <v>1000</v>
+      </c>
+      <c r="AH32">
+        <v>1000</v>
+      </c>
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>1000</v>
+      </c>
+      <c r="AK32">
+        <v>1000</v>
+      </c>
+      <c r="AL32">
+        <v>1000</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>1000</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>18</v>
+      </c>
+      <c r="AQ32">
+        <v>15.5</v>
+      </c>
+      <c r="AR32">
+        <v>20</v>
+      </c>
+      <c r="AS32">
+        <v>38</v>
+      </c>
+      <c r="AT32">
+        <v>12</v>
+      </c>
+      <c r="AU32">
+        <v>8.6</v>
+      </c>
+      <c r="AV32">
+        <v>12.5</v>
+      </c>
+      <c r="AW32">
+        <v>23</v>
+      </c>
+      <c r="AX32">
+        <v>14</v>
+      </c>
+      <c r="AY32">
+        <v>10</v>
+      </c>
+      <c r="AZ32">
+        <v>12.5</v>
+      </c>
+      <c r="BA32">
+        <v>25</v>
+      </c>
+      <c r="BB32">
+        <v>19.5</v>
+      </c>
+      <c r="BC32">
+        <v>17</v>
+      </c>
+      <c r="BD32">
+        <v>19.5</v>
+      </c>
+      <c r="BE32">
+        <v>40</v>
+      </c>
+      <c r="BF32">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG32">
+        <v>16</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>3.15</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.01</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.01</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.01</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.01</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.01</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.01</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.01</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.01</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.01</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" t="s">
+        <v>179</v>
+      </c>
+      <c r="F33">
+        <v>2.1</v>
+      </c>
+      <c r="G33">
+        <v>2.3</v>
+      </c>
+      <c r="H33">
+        <v>3.65</v>
+      </c>
+      <c r="I33">
+        <v>4</v>
+      </c>
+      <c r="J33">
+        <v>3.45</v>
+      </c>
+      <c r="K33">
+        <v>3.65</v>
+      </c>
+      <c r="L33">
+        <v>1.36</v>
+      </c>
+      <c r="M33">
+        <v>1.01</v>
+      </c>
+      <c r="N33">
+        <v>3.5</v>
+      </c>
+      <c r="O33">
+        <v>1.28</v>
+      </c>
+      <c r="P33">
+        <v>1.86</v>
+      </c>
+      <c r="Q33">
+        <v>1.86</v>
+      </c>
+      <c r="R33">
+        <v>1.38</v>
+      </c>
+      <c r="S33">
+        <v>3</v>
+      </c>
+      <c r="T33">
+        <v>1.7</v>
+      </c>
+      <c r="U33">
+        <v>2.04</v>
+      </c>
+      <c r="V33">
+        <v>1.33</v>
+      </c>
+      <c r="W33">
+        <v>1.78</v>
+      </c>
+      <c r="X33">
+        <v>1000</v>
+      </c>
+      <c r="Y33">
+        <v>1000</v>
+      </c>
+      <c r="Z33">
+        <v>1000</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>20</v>
+      </c>
+      <c r="AC33">
+        <v>11.5</v>
+      </c>
+      <c r="AD33">
+        <v>1000</v>
+      </c>
+      <c r="AE33">
+        <v>1000</v>
+      </c>
+      <c r="AF33">
+        <v>1000</v>
+      </c>
+      <c r="AG33">
+        <v>22</v>
+      </c>
+      <c r="AH33">
+        <v>1000</v>
+      </c>
+      <c r="AI33">
+        <v>1000</v>
+      </c>
+      <c r="AJ33">
+        <v>1000</v>
+      </c>
+      <c r="AK33">
+        <v>1000</v>
+      </c>
+      <c r="AL33">
+        <v>1000</v>
+      </c>
+      <c r="AM33">
+        <v>1000</v>
+      </c>
+      <c r="AN33">
+        <v>1000</v>
+      </c>
+      <c r="AO33">
+        <v>1000</v>
+      </c>
+      <c r="AP33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ33">
+        <v>9.4</v>
+      </c>
+      <c r="AR33">
+        <v>1.01</v>
+      </c>
+      <c r="AS33">
+        <v>1.01</v>
+      </c>
+      <c r="AT33">
+        <v>7.4</v>
+      </c>
+      <c r="AU33">
+        <v>5.9</v>
+      </c>
+      <c r="AV33">
+        <v>10</v>
+      </c>
+      <c r="AW33">
+        <v>1.01</v>
+      </c>
+      <c r="AX33">
+        <v>8.6</v>
+      </c>
+      <c r="AY33">
+        <v>7.8</v>
+      </c>
+      <c r="AZ33">
+        <v>11</v>
+      </c>
+      <c r="BA33">
+        <v>1.01</v>
+      </c>
+      <c r="BB33">
+        <v>1.01</v>
+      </c>
+      <c r="BC33">
+        <v>12</v>
+      </c>
+      <c r="BD33">
+        <v>1.01</v>
+      </c>
+      <c r="BE33">
+        <v>1.01</v>
+      </c>
+      <c r="BF33">
+        <v>9.6</v>
+      </c>
+      <c r="BG33">
+        <v>1.01</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.01</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.01</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.01</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.01</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.01</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.01</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.01</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.01</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34">
+        <v>2.22</v>
+      </c>
+      <c r="G34">
+        <v>2.6</v>
+      </c>
+      <c r="H34">
+        <v>2.84</v>
+      </c>
+      <c r="I34">
+        <v>3.35</v>
+      </c>
+      <c r="J34">
+        <v>3.4</v>
+      </c>
+      <c r="K34">
+        <v>5.1</v>
+      </c>
+      <c r="L34">
+        <v>1.27</v>
+      </c>
+      <c r="M34">
+        <v>1.01</v>
+      </c>
+      <c r="N34">
+        <v>2.28</v>
+      </c>
+      <c r="O34">
+        <v>1.2</v>
+      </c>
+      <c r="P34">
+        <v>2.28</v>
+      </c>
+      <c r="Q34">
+        <v>1.55</v>
+      </c>
+      <c r="R34">
+        <v>1.51</v>
+      </c>
+      <c r="S34">
+        <v>2.38</v>
+      </c>
+      <c r="T34">
+        <v>1.48</v>
+      </c>
+      <c r="U34">
+        <v>1.01</v>
+      </c>
+      <c r="V34">
+        <v>1.43</v>
+      </c>
+      <c r="W34">
+        <v>1.62</v>
+      </c>
+      <c r="X34">
+        <v>1000</v>
+      </c>
+      <c r="Y34">
+        <v>1000</v>
+      </c>
+      <c r="Z34">
+        <v>1000</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>1000</v>
+      </c>
+      <c r="AC34">
+        <v>16</v>
+      </c>
+      <c r="AD34">
+        <v>1000</v>
+      </c>
+      <c r="AE34">
+        <v>1000</v>
+      </c>
+      <c r="AF34">
+        <v>1000</v>
+      </c>
+      <c r="AG34">
+        <v>1000</v>
+      </c>
+      <c r="AH34">
+        <v>1000</v>
+      </c>
+      <c r="AI34">
+        <v>1000</v>
+      </c>
+      <c r="AJ34">
+        <v>1000</v>
+      </c>
+      <c r="AK34">
+        <v>1000</v>
+      </c>
+      <c r="AL34">
+        <v>1000</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>1000</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34">
+        <v>11</v>
+      </c>
+      <c r="AR34">
+        <v>1.01</v>
+      </c>
+      <c r="AS34">
+        <v>1.01</v>
+      </c>
+      <c r="AT34">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU34">
+        <v>6.4</v>
+      </c>
+      <c r="AV34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW34">
+        <v>1.01</v>
+      </c>
+      <c r="AX34">
+        <v>11</v>
+      </c>
+      <c r="AY34">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ34">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA34">
+        <v>1.01</v>
+      </c>
+      <c r="BB34">
+        <v>1.01</v>
+      </c>
+      <c r="BC34">
+        <v>12</v>
+      </c>
+      <c r="BD34">
+        <v>1.01</v>
+      </c>
+      <c r="BE34">
+        <v>1.01</v>
+      </c>
+      <c r="BF34">
+        <v>9</v>
+      </c>
+      <c r="BG34">
+        <v>12</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>1.01</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.01</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.01</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.01</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.01</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.01</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.01</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.01</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.01</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.01</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" t="s">
+        <v>181</v>
+      </c>
+      <c r="F35">
+        <v>2.8</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>2.52</v>
+      </c>
+      <c r="I35">
+        <v>2.66</v>
+      </c>
+      <c r="J35">
+        <v>3.6</v>
+      </c>
+      <c r="K35">
+        <v>3.9</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.01</v>
+      </c>
+      <c r="N35">
+        <v>3.9</v>
+      </c>
+      <c r="O35">
+        <v>1.26</v>
+      </c>
+      <c r="P35">
+        <v>2.1</v>
+      </c>
+      <c r="Q35">
+        <v>1.73</v>
+      </c>
+      <c r="R35">
+        <v>1.41</v>
+      </c>
+      <c r="S35">
+        <v>2.68</v>
+      </c>
+      <c r="T35">
+        <v>1.58</v>
+      </c>
+      <c r="U35">
+        <v>2.24</v>
+      </c>
+      <c r="V35">
+        <v>1.6</v>
+      </c>
+      <c r="W35">
+        <v>1.51</v>
+      </c>
+      <c r="X35">
+        <v>26</v>
+      </c>
+      <c r="Y35">
+        <v>18.5</v>
+      </c>
+      <c r="Z35">
+        <v>28</v>
+      </c>
+      <c r="AA35">
+        <v>55</v>
+      </c>
+      <c r="AB35">
+        <v>1000</v>
+      </c>
+      <c r="AC35">
+        <v>10.5</v>
+      </c>
+      <c r="AD35">
+        <v>17.5</v>
+      </c>
+      <c r="AE35">
+        <v>38</v>
+      </c>
+      <c r="AF35">
+        <v>30</v>
+      </c>
+      <c r="AG35">
+        <v>18</v>
+      </c>
+      <c r="AH35">
+        <v>22</v>
+      </c>
+      <c r="AI35">
+        <v>50</v>
+      </c>
+      <c r="AJ35">
+        <v>65</v>
+      </c>
+      <c r="AK35">
+        <v>44</v>
+      </c>
+      <c r="AL35">
+        <v>55</v>
+      </c>
+      <c r="AM35">
+        <v>100</v>
+      </c>
+      <c r="AN35">
+        <v>30</v>
+      </c>
+      <c r="AO35">
+        <v>28</v>
+      </c>
+      <c r="AP35">
+        <v>12.5</v>
+      </c>
+      <c r="AQ35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR35">
+        <v>13</v>
+      </c>
+      <c r="AS35">
+        <v>22</v>
+      </c>
+      <c r="AT35">
+        <v>10</v>
+      </c>
+      <c r="AU35">
+        <v>6.2</v>
+      </c>
+      <c r="AV35">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW35">
+        <v>16</v>
+      </c>
+      <c r="AX35">
+        <v>14.5</v>
+      </c>
+      <c r="AY35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ35">
+        <v>11.5</v>
+      </c>
+      <c r="BA35">
+        <v>21</v>
+      </c>
+      <c r="BB35">
+        <v>25</v>
+      </c>
+      <c r="BC35">
+        <v>17.5</v>
+      </c>
+      <c r="BD35">
+        <v>22</v>
+      </c>
+      <c r="BE35">
+        <v>42</v>
+      </c>
+      <c r="BF35">
+        <v>15</v>
+      </c>
+      <c r="BG35">
+        <v>13</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>1.01</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>1.01</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.01</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>1.01</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.01</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.01</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>1.01</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.01</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.01</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.01</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" t="s">
+        <v>182</v>
+      </c>
+      <c r="F36">
+        <v>2.24</v>
+      </c>
+      <c r="G36">
+        <v>2.6</v>
+      </c>
+      <c r="H36">
+        <v>2.88</v>
+      </c>
+      <c r="I36">
+        <v>3.5</v>
+      </c>
+      <c r="J36">
+        <v>3.55</v>
+      </c>
+      <c r="K36">
+        <v>4.2</v>
+      </c>
+      <c r="L36">
+        <v>1.23</v>
+      </c>
+      <c r="M36">
+        <v>1.01</v>
+      </c>
+      <c r="N36">
+        <v>2.9</v>
+      </c>
+      <c r="O36">
+        <v>1.22</v>
+      </c>
+      <c r="P36">
+        <v>2.22</v>
+      </c>
+      <c r="Q36">
+        <v>1.63</v>
+      </c>
+      <c r="R36">
+        <v>1.47</v>
+      </c>
+      <c r="S36">
+        <v>2.5</v>
+      </c>
+      <c r="T36">
+        <v>1.53</v>
+      </c>
+      <c r="U36">
+        <v>1.01</v>
+      </c>
+      <c r="V36">
+        <v>1.4</v>
+      </c>
+      <c r="W36">
+        <v>1.63</v>
+      </c>
+      <c r="X36">
+        <v>1000</v>
+      </c>
+      <c r="Y36">
+        <v>1000</v>
+      </c>
+      <c r="Z36">
+        <v>1000</v>
+      </c>
+      <c r="AA36">
+        <v>1000</v>
+      </c>
+      <c r="AB36">
+        <v>1000</v>
+      </c>
+      <c r="AC36">
+        <v>1000</v>
+      </c>
+      <c r="AD36">
+        <v>1000</v>
+      </c>
+      <c r="AE36">
+        <v>1000</v>
+      </c>
+      <c r="AF36">
+        <v>1000</v>
+      </c>
+      <c r="AG36">
+        <v>1000</v>
+      </c>
+      <c r="AH36">
+        <v>1000</v>
+      </c>
+      <c r="AI36">
+        <v>1000</v>
+      </c>
+      <c r="AJ36">
+        <v>1000</v>
+      </c>
+      <c r="AK36">
+        <v>1000</v>
+      </c>
+      <c r="AL36">
+        <v>1000</v>
+      </c>
+      <c r="AM36">
+        <v>1000</v>
+      </c>
+      <c r="AN36">
+        <v>1000</v>
+      </c>
+      <c r="AO36">
+        <v>1000</v>
+      </c>
+      <c r="AP36">
+        <v>12</v>
+      </c>
+      <c r="AQ36">
+        <v>10.5</v>
+      </c>
+      <c r="AR36">
+        <v>1.01</v>
+      </c>
+      <c r="AS36">
+        <v>1.01</v>
+      </c>
+      <c r="AT36">
+        <v>9.4</v>
+      </c>
+      <c r="AU36">
+        <v>6.4</v>
+      </c>
+      <c r="AV36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW36">
+        <v>1.01</v>
+      </c>
+      <c r="AX36">
+        <v>10.5</v>
+      </c>
+      <c r="AY36">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ36">
+        <v>10</v>
+      </c>
+      <c r="BA36">
+        <v>1.01</v>
+      </c>
+      <c r="BB36">
+        <v>1.01</v>
+      </c>
+      <c r="BC36">
+        <v>1.01</v>
+      </c>
+      <c r="BD36">
+        <v>1.01</v>
+      </c>
+      <c r="BE36">
+        <v>1.01</v>
+      </c>
+      <c r="BF36">
+        <v>9.4</v>
+      </c>
+      <c r="BG36">
+        <v>1.01</v>
+      </c>
+      <c r="BH36">
+        <v>1000</v>
+      </c>
+      <c r="BI36">
+        <v>1.01</v>
+      </c>
+      <c r="BJ36">
+        <v>1000</v>
+      </c>
+      <c r="BK36">
+        <v>1.01</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>1.01</v>
+      </c>
+      <c r="BN36">
+        <v>1000</v>
+      </c>
+      <c r="BO36">
+        <v>1.01</v>
+      </c>
+      <c r="BP36">
+        <v>1000</v>
+      </c>
+      <c r="BQ36">
+        <v>1.01</v>
+      </c>
+      <c r="BR36">
+        <v>1000</v>
+      </c>
+      <c r="BS36">
+        <v>1.01</v>
+      </c>
+      <c r="BT36">
+        <v>1000</v>
+      </c>
+      <c r="BU36">
+        <v>1.01</v>
+      </c>
+      <c r="BV36">
+        <v>1000</v>
+      </c>
+      <c r="BW36">
+        <v>1.01</v>
+      </c>
+      <c r="BX36">
+        <v>1000</v>
+      </c>
+      <c r="BY36">
+        <v>1.01</v>
+      </c>
+      <c r="BZ36">
+        <v>1000</v>
+      </c>
+      <c r="CA36">
+        <v>1.01</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" t="s">
+        <v>183</v>
+      </c>
+      <c r="F37">
+        <v>2.02</v>
+      </c>
+      <c r="G37">
+        <v>2.24</v>
+      </c>
+      <c r="H37">
+        <v>3.15</v>
+      </c>
+      <c r="I37">
+        <v>3.65</v>
+      </c>
+      <c r="J37">
+        <v>3.9</v>
+      </c>
+      <c r="K37">
+        <v>4.6</v>
+      </c>
+      <c r="L37">
+        <v>1.01</v>
+      </c>
+      <c r="M37">
+        <v>1.01</v>
+      </c>
+      <c r="N37">
+        <v>5.5</v>
+      </c>
+      <c r="O37">
+        <v>1.17</v>
+      </c>
+      <c r="P37">
+        <v>2.54</v>
+      </c>
+      <c r="Q37">
+        <v>1.52</v>
+      </c>
+      <c r="R37">
+        <v>1.62</v>
+      </c>
+      <c r="S37">
+        <v>2.1</v>
+      </c>
+      <c r="T37">
+        <v>1.44</v>
+      </c>
+      <c r="U37">
+        <v>2.34</v>
+      </c>
+      <c r="V37">
+        <v>1.37</v>
+      </c>
+      <c r="W37">
+        <v>1.8</v>
+      </c>
+      <c r="X37">
+        <v>38</v>
+      </c>
+      <c r="Y37">
+        <v>21</v>
+      </c>
+      <c r="Z37">
+        <v>44</v>
+      </c>
+      <c r="AA37">
+        <v>70</v>
+      </c>
+      <c r="AB37">
+        <v>18</v>
+      </c>
+      <c r="AC37">
+        <v>11</v>
+      </c>
+      <c r="AD37">
+        <v>16</v>
+      </c>
+      <c r="AE37">
+        <v>40</v>
+      </c>
+      <c r="AF37">
+        <v>21</v>
+      </c>
+      <c r="AG37">
+        <v>14</v>
+      </c>
+      <c r="AH37">
+        <v>18.5</v>
+      </c>
+      <c r="AI37">
+        <v>36</v>
+      </c>
+      <c r="AJ37">
+        <v>34</v>
+      </c>
+      <c r="AK37">
+        <v>21</v>
+      </c>
+      <c r="AL37">
+        <v>38</v>
+      </c>
+      <c r="AM37">
+        <v>65</v>
+      </c>
+      <c r="AN37">
+        <v>12</v>
+      </c>
+      <c r="AO37">
+        <v>25</v>
+      </c>
+      <c r="AP37">
+        <v>19</v>
+      </c>
+      <c r="AQ37">
+        <v>14.5</v>
+      </c>
+      <c r="AR37">
+        <v>20</v>
+      </c>
+      <c r="AS37">
+        <v>40</v>
+      </c>
+      <c r="AT37">
+        <v>11</v>
+      </c>
+      <c r="AU37">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV37">
+        <v>11</v>
+      </c>
+      <c r="AW37">
+        <v>23</v>
+      </c>
+      <c r="AX37">
+        <v>12.5</v>
+      </c>
+      <c r="AY37">
+        <v>8.4</v>
+      </c>
+      <c r="AZ37">
+        <v>11</v>
+      </c>
+      <c r="BA37">
+        <v>25</v>
+      </c>
+      <c r="BB37">
+        <v>19</v>
+      </c>
+      <c r="BC37">
+        <v>14</v>
+      </c>
+      <c r="BD37">
+        <v>19</v>
+      </c>
+      <c r="BE37">
+        <v>38</v>
+      </c>
+      <c r="BF37">
+        <v>7.4</v>
+      </c>
+      <c r="BG37">
+        <v>17.5</v>
+      </c>
+      <c r="BH37">
+        <v>1000</v>
+      </c>
+      <c r="BI37">
+        <v>1.01</v>
+      </c>
+      <c r="BJ37">
+        <v>1000</v>
+      </c>
+      <c r="BK37">
+        <v>1.01</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>1.01</v>
+      </c>
+      <c r="BN37">
+        <v>1000</v>
+      </c>
+      <c r="BO37">
+        <v>1.01</v>
+      </c>
+      <c r="BP37">
+        <v>1000</v>
+      </c>
+      <c r="BQ37">
+        <v>1.01</v>
+      </c>
+      <c r="BR37">
+        <v>1000</v>
+      </c>
+      <c r="BS37">
+        <v>1.01</v>
+      </c>
+      <c r="BT37">
+        <v>1000</v>
+      </c>
+      <c r="BU37">
+        <v>1.01</v>
+      </c>
+      <c r="BV37">
+        <v>1000</v>
+      </c>
+      <c r="BW37">
+        <v>1.01</v>
+      </c>
+      <c r="BX37">
+        <v>1000</v>
+      </c>
+      <c r="BY37">
+        <v>1.01</v>
+      </c>
+      <c r="BZ37">
+        <v>1000</v>
+      </c>
+      <c r="CA37">
+        <v>1.01</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" t="s">
+        <v>184</v>
+      </c>
+      <c r="F38">
+        <v>1.51</v>
+      </c>
+      <c r="G38">
+        <v>1.68</v>
+      </c>
+      <c r="H38">
+        <v>5</v>
+      </c>
+      <c r="I38">
+        <v>7.8</v>
+      </c>
+      <c r="J38">
+        <v>4.5</v>
+      </c>
+      <c r="K38">
+        <v>7.4</v>
+      </c>
+      <c r="L38">
+        <v>1.01</v>
+      </c>
+      <c r="M38">
+        <v>1.01</v>
+      </c>
+      <c r="N38">
+        <v>5.1</v>
+      </c>
+      <c r="O38">
+        <v>1.15</v>
+      </c>
+      <c r="P38">
+        <v>2.56</v>
+      </c>
+      <c r="Q38">
+        <v>1.45</v>
+      </c>
+      <c r="R38">
+        <v>1.64</v>
+      </c>
+      <c r="S38">
+        <v>2.1</v>
+      </c>
+      <c r="T38">
+        <v>1.58</v>
+      </c>
+      <c r="U38">
+        <v>1.01</v>
+      </c>
+      <c r="V38">
+        <v>1.16</v>
+      </c>
+      <c r="W38">
+        <v>2.46</v>
+      </c>
+      <c r="X38">
+        <v>1000</v>
+      </c>
+      <c r="Y38">
+        <v>1000</v>
+      </c>
+      <c r="Z38">
+        <v>1000</v>
+      </c>
+      <c r="AA38">
+        <v>1000</v>
+      </c>
+      <c r="AB38">
+        <v>1000</v>
+      </c>
+      <c r="AC38">
+        <v>1000</v>
+      </c>
+      <c r="AD38">
+        <v>1000</v>
+      </c>
+      <c r="AE38">
+        <v>1000</v>
+      </c>
+      <c r="AF38">
+        <v>1000</v>
+      </c>
+      <c r="AG38">
+        <v>1000</v>
+      </c>
+      <c r="AH38">
+        <v>1000</v>
+      </c>
+      <c r="AI38">
+        <v>1000</v>
+      </c>
+      <c r="AJ38">
+        <v>1000</v>
+      </c>
+      <c r="AK38">
+        <v>1000</v>
+      </c>
+      <c r="AL38">
+        <v>1000</v>
+      </c>
+      <c r="AM38">
+        <v>1000</v>
+      </c>
+      <c r="AN38">
+        <v>6.8</v>
+      </c>
+      <c r="AO38">
+        <v>1000</v>
+      </c>
+      <c r="AP38">
+        <v>1.01</v>
+      </c>
+      <c r="AQ38">
+        <v>1.01</v>
+      </c>
+      <c r="AR38">
+        <v>1.01</v>
+      </c>
+      <c r="AS38">
+        <v>1.01</v>
+      </c>
+      <c r="AT38">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU38">
+        <v>8</v>
+      </c>
+      <c r="AV38">
+        <v>1.01</v>
+      </c>
+      <c r="AW38">
+        <v>1.01</v>
+      </c>
+      <c r="AX38">
+        <v>8.4</v>
+      </c>
+      <c r="AY38">
+        <v>7.8</v>
+      </c>
+      <c r="AZ38">
+        <v>11.5</v>
+      </c>
+      <c r="BA38">
+        <v>1.01</v>
+      </c>
+      <c r="BB38">
+        <v>10</v>
+      </c>
+      <c r="BC38">
+        <v>9.6</v>
+      </c>
+      <c r="BD38">
+        <v>1.01</v>
+      </c>
+      <c r="BE38">
+        <v>1.01</v>
+      </c>
+      <c r="BF38">
+        <v>4.3</v>
+      </c>
+      <c r="BG38">
+        <v>1.01</v>
+      </c>
+      <c r="BH38">
+        <v>1000</v>
+      </c>
+      <c r="BI38">
+        <v>1.01</v>
+      </c>
+      <c r="BJ38">
+        <v>1000</v>
+      </c>
+      <c r="BK38">
+        <v>1.01</v>
+      </c>
+      <c r="BL38">
+        <v>1000</v>
+      </c>
+      <c r="BM38">
+        <v>1.01</v>
+      </c>
+      <c r="BN38">
+        <v>1000</v>
+      </c>
+      <c r="BO38">
+        <v>1.01</v>
+      </c>
+      <c r="BP38">
+        <v>1000</v>
+      </c>
+      <c r="BQ38">
+        <v>1.01</v>
+      </c>
+      <c r="BR38">
+        <v>1000</v>
+      </c>
+      <c r="BS38">
+        <v>1.01</v>
+      </c>
+      <c r="BT38">
+        <v>1000</v>
+      </c>
+      <c r="BU38">
+        <v>1.01</v>
+      </c>
+      <c r="BV38">
+        <v>1000</v>
+      </c>
+      <c r="BW38">
+        <v>1.01</v>
+      </c>
+      <c r="BX38">
+        <v>1000</v>
+      </c>
+      <c r="BY38">
+        <v>1.01</v>
+      </c>
+      <c r="BZ38">
+        <v>1000</v>
+      </c>
+      <c r="CA38">
+        <v>1.01</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:80">
+      <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" t="s">
         <v>146</v>
       </c>
-      <c r="F23">
+      <c r="E39" t="s">
+        <v>185</v>
+      </c>
+      <c r="F39">
+        <v>2.3</v>
+      </c>
+      <c r="G39">
+        <v>2.52</v>
+      </c>
+      <c r="H39">
+        <v>3.1</v>
+      </c>
+      <c r="I39">
+        <v>3.45</v>
+      </c>
+      <c r="J39">
+        <v>3.4</v>
+      </c>
+      <c r="K39">
+        <v>3.8</v>
+      </c>
+      <c r="L39">
+        <v>1.01</v>
+      </c>
+      <c r="M39">
+        <v>1.01</v>
+      </c>
+      <c r="N39">
+        <v>2.72</v>
+      </c>
+      <c r="O39">
+        <v>1.01</v>
+      </c>
+      <c r="P39">
+        <v>1.8</v>
+      </c>
+      <c r="Q39">
+        <v>1.73</v>
+      </c>
+      <c r="R39">
+        <v>1.29</v>
+      </c>
+      <c r="S39">
+        <v>2.26</v>
+      </c>
+      <c r="T39">
+        <v>1.01</v>
+      </c>
+      <c r="U39">
+        <v>1.01</v>
+      </c>
+      <c r="V39">
+        <v>1.4</v>
+      </c>
+      <c r="W39">
+        <v>1.65</v>
+      </c>
+      <c r="X39">
+        <v>1000</v>
+      </c>
+      <c r="Y39">
+        <v>1000</v>
+      </c>
+      <c r="Z39">
+        <v>1000</v>
+      </c>
+      <c r="AA39">
+        <v>1000</v>
+      </c>
+      <c r="AB39">
+        <v>1000</v>
+      </c>
+      <c r="AC39">
+        <v>1000</v>
+      </c>
+      <c r="AD39">
+        <v>1000</v>
+      </c>
+      <c r="AE39">
+        <v>1000</v>
+      </c>
+      <c r="AF39">
+        <v>1000</v>
+      </c>
+      <c r="AG39">
+        <v>1000</v>
+      </c>
+      <c r="AH39">
+        <v>1000</v>
+      </c>
+      <c r="AI39">
+        <v>1000</v>
+      </c>
+      <c r="AJ39">
+        <v>1000</v>
+      </c>
+      <c r="AK39">
+        <v>1000</v>
+      </c>
+      <c r="AL39">
+        <v>1000</v>
+      </c>
+      <c r="AM39">
+        <v>1000</v>
+      </c>
+      <c r="AN39">
+        <v>1000</v>
+      </c>
+      <c r="AO39">
+        <v>1000</v>
+      </c>
+      <c r="AP39">
+        <v>1.01</v>
+      </c>
+      <c r="AQ39">
+        <v>1.01</v>
+      </c>
+      <c r="AR39">
+        <v>1.01</v>
+      </c>
+      <c r="AS39">
+        <v>1.01</v>
+      </c>
+      <c r="AT39">
+        <v>1.01</v>
+      </c>
+      <c r="AU39">
+        <v>1.01</v>
+      </c>
+      <c r="AV39">
+        <v>1.01</v>
+      </c>
+      <c r="AW39">
+        <v>1.01</v>
+      </c>
+      <c r="AX39">
+        <v>1.01</v>
+      </c>
+      <c r="AY39">
+        <v>1.01</v>
+      </c>
+      <c r="AZ39">
+        <v>1.01</v>
+      </c>
+      <c r="BA39">
+        <v>1.01</v>
+      </c>
+      <c r="BB39">
+        <v>1.01</v>
+      </c>
+      <c r="BC39">
+        <v>1.01</v>
+      </c>
+      <c r="BD39">
+        <v>1.01</v>
+      </c>
+      <c r="BE39">
+        <v>1.01</v>
+      </c>
+      <c r="BF39">
+        <v>1.01</v>
+      </c>
+      <c r="BG39">
+        <v>1.01</v>
+      </c>
+      <c r="BH39">
+        <v>4.4</v>
+      </c>
+      <c r="BI39">
+        <v>2.78</v>
+      </c>
+      <c r="BJ39">
+        <v>1000</v>
+      </c>
+      <c r="BK39">
+        <v>1.01</v>
+      </c>
+      <c r="BL39">
+        <v>1000</v>
+      </c>
+      <c r="BM39">
+        <v>1.01</v>
+      </c>
+      <c r="BN39">
+        <v>1000</v>
+      </c>
+      <c r="BO39">
+        <v>1.01</v>
+      </c>
+      <c r="BP39">
+        <v>1000</v>
+      </c>
+      <c r="BQ39">
+        <v>1.01</v>
+      </c>
+      <c r="BR39">
+        <v>1000</v>
+      </c>
+      <c r="BS39">
+        <v>1.01</v>
+      </c>
+      <c r="BT39">
+        <v>1000</v>
+      </c>
+      <c r="BU39">
+        <v>1.01</v>
+      </c>
+      <c r="BV39">
+        <v>1000</v>
+      </c>
+      <c r="BW39">
+        <v>1.01</v>
+      </c>
+      <c r="BX39">
+        <v>1000</v>
+      </c>
+      <c r="BY39">
+        <v>1.01</v>
+      </c>
+      <c r="BZ39">
+        <v>1000</v>
+      </c>
+      <c r="CA39">
+        <v>1.01</v>
+      </c>
+      <c r="CB39" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:80">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" t="s">
+        <v>186</v>
+      </c>
+      <c r="F40">
         <v>11.5</v>
       </c>
-      <c r="G23">
+      <c r="G40">
+        <v>12</v>
+      </c>
+      <c r="H40">
+        <v>1.29</v>
+      </c>
+      <c r="I40">
+        <v>1.3</v>
+      </c>
+      <c r="J40">
+        <v>6.8</v>
+      </c>
+      <c r="K40">
+        <v>7.2</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>1.02</v>
+      </c>
+      <c r="N40">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O40">
+        <v>1.11</v>
+      </c>
+      <c r="P40">
+        <v>3.45</v>
+      </c>
+      <c r="Q40">
+        <v>1.37</v>
+      </c>
+      <c r="R40">
+        <v>2.02</v>
+      </c>
+      <c r="S40">
+        <v>1.9</v>
+      </c>
+      <c r="T40">
+        <v>1.71</v>
+      </c>
+      <c r="U40">
+        <v>2.3</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>48</v>
+      </c>
+      <c r="Y40">
+        <v>16</v>
+      </c>
+      <c r="Z40">
+        <v>10.5</v>
+      </c>
+      <c r="AA40">
         <v>12.5</v>
       </c>
-      <c r="H23">
-        <v>1.28</v>
-      </c>
-      <c r="I23">
-        <v>1.3</v>
-      </c>
-      <c r="J23">
-        <v>6.6</v>
-      </c>
-      <c r="K23">
-        <v>7</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>1.02</v>
-      </c>
-      <c r="N23">
-        <v>8.6</v>
-      </c>
-      <c r="O23">
-        <v>1.11</v>
-      </c>
-      <c r="P23">
-        <v>3.3</v>
-      </c>
-      <c r="Q23">
-        <v>1.39</v>
-      </c>
-      <c r="R23">
-        <v>2</v>
-      </c>
-      <c r="S23">
-        <v>1.9</v>
-      </c>
-      <c r="T23">
-        <v>1.73</v>
-      </c>
-      <c r="U23">
-        <v>2.28</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
+      <c r="AB40">
+        <v>60</v>
+      </c>
+      <c r="AC40">
+        <v>17</v>
+      </c>
+      <c r="AD40">
+        <v>12</v>
+      </c>
+      <c r="AE40">
+        <v>11.5</v>
+      </c>
+      <c r="AF40">
+        <v>140</v>
+      </c>
+      <c r="AG40">
+        <v>42</v>
+      </c>
+      <c r="AH40">
+        <v>26</v>
+      </c>
+      <c r="AI40">
+        <v>28</v>
+      </c>
+      <c r="AJ40">
+        <v>450</v>
+      </c>
+      <c r="AK40">
+        <v>150</v>
+      </c>
+      <c r="AL40">
+        <v>100</v>
+      </c>
+      <c r="AM40">
+        <v>120</v>
+      </c>
+      <c r="AN40">
+        <v>1000</v>
+      </c>
+      <c r="AO40">
+        <v>3.35</v>
+      </c>
+      <c r="AP40">
+        <v>34</v>
+      </c>
+      <c r="AQ40">
+        <v>13.5</v>
+      </c>
+      <c r="AR40">
+        <v>9.6</v>
+      </c>
+      <c r="AS40">
+        <v>11</v>
+      </c>
+      <c r="AT40">
         <v>46</v>
       </c>
-      <c r="Y23">
-        <v>16</v>
-      </c>
-      <c r="Z23">
-        <v>10.5</v>
-      </c>
-      <c r="AA23">
-        <v>12.5</v>
-      </c>
-      <c r="AB23">
+      <c r="AU40">
+        <v>15</v>
+      </c>
+      <c r="AV40">
+        <v>11</v>
+      </c>
+      <c r="AW40">
+        <v>10</v>
+      </c>
+      <c r="AX40">
+        <v>42</v>
+      </c>
+      <c r="AY40">
+        <v>30</v>
+      </c>
+      <c r="AZ40">
+        <v>22</v>
+      </c>
+      <c r="BA40">
+        <v>23</v>
+      </c>
+      <c r="BB40">
+        <v>90</v>
+      </c>
+      <c r="BC40">
+        <v>44</v>
+      </c>
+      <c r="BD40">
         <v>65</v>
       </c>
-      <c r="AC23">
+      <c r="BE40">
+        <v>55</v>
+      </c>
+      <c r="BF40">
+        <v>42</v>
+      </c>
+      <c r="BG40">
+        <v>3.2</v>
+      </c>
+      <c r="BH40">
+        <v>6.8</v>
+      </c>
+      <c r="BI40">
+        <v>4.9</v>
+      </c>
+      <c r="BJ40">
+        <v>13</v>
+      </c>
+      <c r="BK40">
+        <v>3.6</v>
+      </c>
+      <c r="BL40">
+        <v>110</v>
+      </c>
+      <c r="BM40">
+        <v>4.6</v>
+      </c>
+      <c r="BN40">
         <v>17</v>
       </c>
-      <c r="AD23">
-        <v>12</v>
-      </c>
-      <c r="AE23">
-        <v>11.5</v>
-      </c>
-      <c r="AF23">
-        <v>1000</v>
-      </c>
-      <c r="AG23">
-        <v>46</v>
-      </c>
-      <c r="AH23">
-        <v>26</v>
-      </c>
-      <c r="AI23">
-        <v>29</v>
-      </c>
-      <c r="AJ23">
-        <v>540</v>
-      </c>
-      <c r="AK23">
-        <v>1000</v>
-      </c>
-      <c r="AL23">
-        <v>130</v>
-      </c>
-      <c r="AM23">
-        <v>95</v>
-      </c>
-      <c r="AN23">
-        <v>1000</v>
-      </c>
-      <c r="AO23">
-        <v>3.45</v>
-      </c>
-      <c r="AP23">
-        <v>34</v>
-      </c>
-      <c r="AQ23">
-        <v>14</v>
-      </c>
-      <c r="AR23">
+      <c r="BO40">
+        <v>3.7</v>
+      </c>
+      <c r="BP40">
+        <v>85</v>
+      </c>
+      <c r="BQ40">
+        <v>4.5</v>
+      </c>
+      <c r="BR40">
+        <v>70</v>
+      </c>
+      <c r="BS40">
+        <v>4.4</v>
+      </c>
+      <c r="BT40">
+        <v>5.1</v>
+      </c>
+      <c r="BU40">
+        <v>3.9</v>
+      </c>
+      <c r="BV40">
+        <v>8.4</v>
+      </c>
+      <c r="BW40">
+        <v>6.2</v>
+      </c>
+      <c r="BX40">
+        <v>21</v>
+      </c>
+      <c r="BY40">
+        <v>3.9</v>
+      </c>
+      <c r="BZ40">
         <v>9</v>
       </c>
-      <c r="AS23">
-        <v>11</v>
-      </c>
-      <c r="AT23">
-        <v>48</v>
-      </c>
-      <c r="AU23">
-        <v>14.5</v>
-      </c>
-      <c r="AV23">
-        <v>11</v>
-      </c>
-      <c r="AW23">
-        <v>10</v>
-      </c>
-      <c r="AX23">
-        <v>42</v>
-      </c>
-      <c r="AY23">
-        <v>34</v>
-      </c>
-      <c r="AZ23">
-        <v>22</v>
-      </c>
-      <c r="BA23">
-        <v>23</v>
-      </c>
-      <c r="BB23">
-        <v>95</v>
-      </c>
-      <c r="BC23">
-        <v>44</v>
-      </c>
-      <c r="BD23">
-        <v>38</v>
-      </c>
-      <c r="BE23">
-        <v>55</v>
-      </c>
-      <c r="BF23">
-        <v>42</v>
-      </c>
-      <c r="BG23">
-        <v>3.25</v>
-      </c>
-      <c r="BH23">
-        <v>970</v>
-      </c>
-      <c r="BI23">
-        <v>1.01</v>
-      </c>
-      <c r="BJ23">
-        <v>1000</v>
-      </c>
-      <c r="BK23">
-        <v>1.01</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.01</v>
-      </c>
-      <c r="BN23">
-        <v>1000</v>
-      </c>
-      <c r="BO23">
-        <v>1.01</v>
-      </c>
-      <c r="BP23">
-        <v>1000</v>
-      </c>
-      <c r="BQ23">
-        <v>1.01</v>
-      </c>
-      <c r="BR23">
-        <v>1000</v>
-      </c>
-      <c r="BS23">
-        <v>1.01</v>
-      </c>
-      <c r="BT23">
-        <v>970</v>
-      </c>
-      <c r="BU23">
-        <v>1.01</v>
-      </c>
-      <c r="BV23">
-        <v>970</v>
-      </c>
-      <c r="BW23">
-        <v>1.01</v>
-      </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>1.01</v>
-      </c>
-      <c r="BZ23">
-        <v>1000</v>
-      </c>
-      <c r="CA23">
-        <v>1.01</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>147</v>
+      <c r="CA40">
+        <v>5.7</v>
+      </c>
+      <c r="CB40" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -577,7 +577,7 @@
     <t>Real Madrid</t>
   </si>
   <si>
-    <t>2026-09-13 16:32:48</t>
+    <t>2026-09-13 18:48:25</t>
   </si>
 </sst>
 </file>
@@ -1174,163 +1174,163 @@
         <v>1.44</v>
       </c>
       <c r="G2">
+        <v>1.47</v>
+      </c>
+      <c r="H2">
+        <v>10.5</v>
+      </c>
+      <c r="I2">
+        <v>12.5</v>
+      </c>
+      <c r="J2">
+        <v>4.3</v>
+      </c>
+      <c r="K2">
+        <v>4.7</v>
+      </c>
+      <c r="L2">
+        <v>1.46</v>
+      </c>
+      <c r="M2">
+        <v>1.1</v>
+      </c>
+      <c r="N2">
+        <v>2.92</v>
+      </c>
+      <c r="O2">
         <v>1.48</v>
       </c>
-      <c r="H2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I2">
-        <v>16.5</v>
-      </c>
-      <c r="J2">
-        <v>3.95</v>
-      </c>
-      <c r="K2">
-        <v>5.1</v>
-      </c>
-      <c r="L2">
-        <v>1.49</v>
-      </c>
-      <c r="M2">
-        <v>1.09</v>
-      </c>
-      <c r="N2">
-        <v>2.68</v>
-      </c>
-      <c r="O2">
-        <v>1.44</v>
-      </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="R2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="U2">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V2">
         <v>1.09</v>
       </c>
       <c r="W2">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X2">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>190</v>
+        <v>5.5</v>
       </c>
       <c r="AC2">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AF2">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AG2">
-        <v>190</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AJ2">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AN2">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
+        <v>9.6</v>
+      </c>
+      <c r="AQ2">
+        <v>20</v>
+      </c>
+      <c r="AR2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT2">
+        <v>5.1</v>
+      </c>
+      <c r="AU2">
+        <v>9.6</v>
+      </c>
+      <c r="AV2">
+        <v>7.6</v>
+      </c>
+      <c r="AW2">
+        <v>8.6</v>
+      </c>
+      <c r="AX2">
+        <v>6</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
         <v>7.4</v>
       </c>
-      <c r="AQ2">
-        <v>1.98</v>
-      </c>
-      <c r="AR2">
-        <v>1.98</v>
-      </c>
-      <c r="AS2">
-        <v>1.98</v>
-      </c>
-      <c r="AT2">
-        <v>4.5</v>
-      </c>
-      <c r="AU2">
-        <v>7.8</v>
-      </c>
-      <c r="AV2">
-        <v>1.98</v>
-      </c>
-      <c r="AW2">
-        <v>1.98</v>
-      </c>
-      <c r="AX2">
-        <v>5.2</v>
-      </c>
-      <c r="AY2">
+      <c r="BA2">
+        <v>8.6</v>
+      </c>
+      <c r="BB2">
+        <v>10.5</v>
+      </c>
+      <c r="BC2">
+        <v>18.5</v>
+      </c>
+      <c r="BD2">
+        <v>8</v>
+      </c>
+      <c r="BE2">
+        <v>8.6</v>
+      </c>
+      <c r="BF2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG2">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2">
-        <v>1.98</v>
-      </c>
-      <c r="BA2">
-        <v>1.98</v>
-      </c>
-      <c r="BB2">
-        <v>8</v>
-      </c>
-      <c r="BC2">
-        <v>1.98</v>
-      </c>
-      <c r="BD2">
-        <v>1.98</v>
-      </c>
-      <c r="BE2">
-        <v>1.98</v>
-      </c>
-      <c r="BF2">
-        <v>1.78</v>
-      </c>
-      <c r="BG2">
-        <v>1.98</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1372,7 +1372,7 @@
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1440,7 +1440,7 @@
         <v>2.92</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
         <v>1.65</v>
@@ -1458,7 +1458,7 @@
         <v>1.96</v>
       </c>
       <c r="U3">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V3">
         <v>1.45</v>
@@ -1530,7 +1530,7 @@
         <v>16</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1542,7 +1542,7 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1554,19 +1554,19 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC3">
         <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF3">
         <v>6.2</v>
@@ -1584,13 +1584,13 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
         <v>1000</v>
@@ -1602,13 +1602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
         <v>1000</v>
@@ -1620,19 +1620,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>187</v>
@@ -1658,43 +1658,43 @@
         <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H4">
         <v>10</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J4">
         <v>4.7</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
         <v>1.32</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q4">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
         <v>2.28</v>
@@ -1790,7 +1790,7 @@
         <v>7</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
         <v>6.6</v>
@@ -1817,64 +1817,64 @@
         <v>7.6</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>1.89</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4">
+        <v>14</v>
+      </c>
+      <c r="BK4">
+        <v>5.3</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>8.4</v>
+      </c>
+      <c r="BN4">
+        <v>3.75</v>
+      </c>
+      <c r="BO4">
+        <v>3.2</v>
+      </c>
+      <c r="BP4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ4">
+        <v>5.6</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>6.6</v>
+      </c>
+      <c r="BT4">
+        <v>14.5</v>
+      </c>
+      <c r="BU4">
+        <v>5.4</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>8</v>
+      </c>
+      <c r="BZ4">
         <v>18</v>
       </c>
-      <c r="BK4">
-        <v>1.71</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.89</v>
-      </c>
-      <c r="BN4">
-        <v>4.8</v>
-      </c>
-      <c r="BO4">
-        <v>2.64</v>
-      </c>
-      <c r="BP4">
-        <v>11.5</v>
-      </c>
-      <c r="BQ4">
-        <v>1.63</v>
-      </c>
-      <c r="BR4">
-        <v>40</v>
-      </c>
-      <c r="BS4">
-        <v>1.81</v>
-      </c>
-      <c r="BT4">
-        <v>19</v>
-      </c>
-      <c r="BU4">
-        <v>1.72</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>1.89</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>1.89</v>
-      </c>
-      <c r="BZ4">
-        <v>24</v>
-      </c>
       <c r="CA4">
-        <v>1.76</v>
+        <v>5.8</v>
       </c>
       <c r="CB4" t="s">
         <v>187</v>
@@ -1915,7 +1915,7 @@
         <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.06</v>
@@ -1939,7 +1939,7 @@
         <v>3.05</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U5">
         <v>2.28</v>
@@ -1954,7 +1954,7 @@
         <v>17.5</v>
       </c>
       <c r="Y5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z5">
         <v>36</v>
@@ -1987,13 +1987,13 @@
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK5">
         <v>21</v>
       </c>
       <c r="AL5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM5">
         <v>100</v>
@@ -2011,10 +2011,10 @@
         <v>14.5</v>
       </c>
       <c r="AR5">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5">
         <v>9.6</v>
@@ -2026,7 +2026,7 @@
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
@@ -2038,7 +2038,7 @@
         <v>15</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5">
         <v>20</v>
@@ -2047,16 +2047,16 @@
         <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5">
         <v>11</v>
       </c>
       <c r="BG5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2065,58 +2065,58 @@
         <v>3.1</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2151,7 +2151,7 @@
         <v>2.2</v>
       </c>
       <c r="J6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K6">
         <v>3.25</v>
@@ -2256,7 +2256,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT6">
         <v>9.800000000000001</v>
@@ -2268,10 +2268,10 @@
         <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY6">
         <v>17.5</v>
@@ -2280,25 +2280,25 @@
         <v>21</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH6">
         <v>2.82</v>
@@ -2384,7 +2384,7 @@
         <v>2.16</v>
       </c>
       <c r="G7">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H7">
         <v>3.9</v>
@@ -2405,7 +2405,7 @@
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
         <v>1.54</v>
@@ -2432,7 +2432,7 @@
         <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X7">
         <v>8.800000000000001</v>
@@ -2495,10 +2495,10 @@
         <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
@@ -2510,7 +2510,7 @@
         <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2522,25 +2522,25 @@
         <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC7">
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2552,13 +2552,13 @@
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
         <v>1000</v>
@@ -2570,37 +2570,37 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>187</v>
@@ -2626,16 +2626,16 @@
         <v>1.04</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8">
         <v>1.04</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K8">
         <v>900</v>
@@ -2671,10 +2671,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2889,16 +2889,16 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P9">
         <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="R9">
         <v>1.35</v>
@@ -3107,7 +3107,7 @@
         <v>156</v>
       </c>
       <c r="F10">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="G10">
         <v>1.54</v>
@@ -3116,13 +3116,13 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="L10">
         <v>1.26</v>
@@ -3137,7 +3137,7 @@
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q10">
         <v>1.68</v>
@@ -3146,7 +3146,7 @@
         <v>1.51</v>
       </c>
       <c r="S10">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T10">
         <v>1.87</v>
@@ -3155,7 +3155,7 @@
         <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W10">
         <v>2.84</v>
@@ -3164,7 +3164,7 @@
         <v>26</v>
       </c>
       <c r="Y10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z10">
         <v>80</v>
@@ -3209,7 +3209,7 @@
         <v>140</v>
       </c>
       <c r="AN10">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO10">
         <v>140</v>
@@ -3221,10 +3221,10 @@
         <v>19</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT10">
         <v>8.6</v>
@@ -3236,7 +3236,7 @@
         <v>19.5</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX10">
         <v>8.6</v>
@@ -3245,10 +3245,10 @@
         <v>9</v>
       </c>
       <c r="AZ10">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB10">
         <v>11.5</v>
@@ -3257,16 +3257,16 @@
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF10">
         <v>5.8</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH10">
         <v>4.8</v>
@@ -3373,7 +3373,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O11">
         <v>1.18</v>
@@ -3591,16 +3591,16 @@
         <v>158</v>
       </c>
       <c r="F12">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G12">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H12">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I12">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -3609,19 +3609,19 @@
         <v>3.55</v>
       </c>
       <c r="L12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M12">
         <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O12">
         <v>1.35</v>
       </c>
       <c r="P12">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q12">
         <v>2.04</v>
@@ -3630,7 +3630,7 @@
         <v>1.34</v>
       </c>
       <c r="S12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T12">
         <v>1.84</v>
@@ -3639,22 +3639,22 @@
         <v>2.12</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X12">
+        <v>13</v>
+      </c>
+      <c r="Y12">
         <v>13.5</v>
-      </c>
-      <c r="Y12">
-        <v>14</v>
       </c>
       <c r="Z12">
         <v>26</v>
       </c>
       <c r="AA12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB12">
         <v>9.800000000000001</v>
@@ -3666,10 +3666,10 @@
         <v>15</v>
       </c>
       <c r="AE12">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG12">
         <v>11</v>
@@ -3678,13 +3678,13 @@
         <v>18.5</v>
       </c>
       <c r="AI12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ12">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL12">
         <v>40</v>
@@ -3693,22 +3693,22 @@
         <v>100</v>
       </c>
       <c r="AN12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO12">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP12">
         <v>12</v>
       </c>
       <c r="AQ12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT12">
         <v>9</v>
@@ -3720,7 +3720,7 @@
         <v>13.5</v>
       </c>
       <c r="AW12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX12">
         <v>12.5</v>
@@ -3732,7 +3732,7 @@
         <v>16</v>
       </c>
       <c r="BA12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB12">
         <v>25</v>
@@ -3747,70 +3747,70 @@
         <v>40</v>
       </c>
       <c r="BF12">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="CB12" t="s">
         <v>187</v>
@@ -3833,28 +3833,28 @@
         <v>159</v>
       </c>
       <c r="F13">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G13">
         <v>1.74</v>
       </c>
       <c r="H13">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>3.95</v>
       </c>
       <c r="K13">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L13">
         <v>1.27</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
         <v>3.8</v>
@@ -3869,19 +3869,19 @@
         <v>1.78</v>
       </c>
       <c r="R13">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S13">
         <v>2.78</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V13">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
         <v>2.36</v>
@@ -4320,61 +4320,61 @@
         <v>2.58</v>
       </c>
       <c r="G15">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H15">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I15">
         <v>2.66</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15">
-        <v>2.56</v>
+        <v>5.6</v>
       </c>
       <c r="O15">
         <v>1.15</v>
       </c>
       <c r="P15">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q15">
         <v>1.49</v>
       </c>
       <c r="R15">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S15">
         <v>2.22</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V15">
         <v>1.6</v>
       </c>
       <c r="W15">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X15">
         <v>1000</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z15">
         <v>1000</v>
@@ -4398,28 +4398,28 @@
         <v>1000</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ15">
         <v>1000</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM15">
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO15">
         <v>1000</v>
@@ -4440,13 +4440,13 @@
         <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX15">
         <v>1.01</v>
@@ -4455,16 +4455,16 @@
         <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BB15">
         <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD15">
         <v>1.01</v>
@@ -4473,10 +4473,10 @@
         <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4559,22 +4559,22 @@
         <v>162</v>
       </c>
       <c r="F16">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H16">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="I16">
         <v>24</v>
       </c>
       <c r="J16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K16">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4583,34 +4583,34 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O16">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P16">
         <v>2.22</v>
       </c>
       <c r="Q16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R16">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S16">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T16">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="U16">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="V16">
         <v>1.04</v>
       </c>
       <c r="W16">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X16">
         <v>26</v>
@@ -4625,10 +4625,10 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD16">
         <v>80</v>
@@ -4637,10 +4637,10 @@
         <v>470</v>
       </c>
       <c r="AF16">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AG16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH16">
         <v>55</v>
@@ -4649,7 +4649,7 @@
         <v>330</v>
       </c>
       <c r="AJ16">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AK16">
         <v>16.5</v>
@@ -4661,7 +4661,7 @@
         <v>350</v>
       </c>
       <c r="AN16">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AO16">
         <v>1000</v>
@@ -4670,55 +4670,55 @@
         <v>15.5</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU16">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX16">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY16">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB16">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC16">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF16">
         <v>4.2</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4801,118 +4801,118 @@
         <v>163</v>
       </c>
       <c r="F17">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H17">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I17">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J17">
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="O17">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P17">
         <v>2.58</v>
       </c>
       <c r="Q17">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="R17">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="S17">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR17">
         <v>1.01</v>
@@ -4921,46 +4921,46 @@
         <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW17">
         <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA17">
         <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC17">
         <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE17">
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5082,7 +5082,7 @@
         <v>1.25</v>
       </c>
       <c r="S18">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5291,7 +5291,7 @@
         <v>4.5</v>
       </c>
       <c r="H19">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I19">
         <v>1.93</v>
@@ -5315,10 +5315,10 @@
         <v>1.17</v>
       </c>
       <c r="P19">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="Q19">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R19">
         <v>1.69</v>
@@ -5327,124 +5327,124 @@
         <v>2.2</v>
       </c>
       <c r="T19">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="U19">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V19">
         <v>2.06</v>
       </c>
       <c r="W19">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y19">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="Z19">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC19">
+        <v>11</v>
+      </c>
+      <c r="AD19">
         <v>11.5</v>
       </c>
-      <c r="AD19">
-        <v>22</v>
-      </c>
       <c r="AE19">
+        <v>17.5</v>
+      </c>
+      <c r="AF19">
+        <v>40</v>
+      </c>
+      <c r="AG19">
         <v>18.5</v>
       </c>
-      <c r="AF19">
-        <v>48</v>
-      </c>
-      <c r="AG19">
-        <v>20</v>
-      </c>
       <c r="AH19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ19">
         <v>100</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO19">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP19">
-        <v>2.2</v>
+        <v>20</v>
       </c>
       <c r="AQ19">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AR19">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AS19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AU19">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV19">
+        <v>9.6</v>
+      </c>
+      <c r="AW19">
+        <v>14.5</v>
+      </c>
+      <c r="AX19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY19">
+        <v>15</v>
+      </c>
+      <c r="AZ19">
+        <v>13.5</v>
+      </c>
+      <c r="BA19">
+        <v>21</v>
+      </c>
+      <c r="BB19">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW19">
-        <v>10</v>
-      </c>
-      <c r="AX19">
-        <v>2.08</v>
-      </c>
-      <c r="AY19">
-        <v>1.98</v>
-      </c>
-      <c r="AZ19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA19">
-        <v>16.5</v>
-      </c>
-      <c r="BB19">
-        <v>2.16</v>
-      </c>
       <c r="BC19">
-        <v>2.2</v>
+        <v>8.6</v>
       </c>
       <c r="BD19">
-        <v>2.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE19">
-        <v>2.2</v>
+        <v>9</v>
       </c>
       <c r="BF19">
-        <v>19</v>
+        <v>7.6</v>
       </c>
       <c r="BG19">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5527,16 +5527,16 @@
         <v>166</v>
       </c>
       <c r="F20">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="G20">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H20">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J20">
         <v>3.4</v>
@@ -5551,7 +5551,7 @@
         <v>1.1</v>
       </c>
       <c r="N20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O20">
         <v>1.44</v>
@@ -5560,7 +5560,7 @@
         <v>1.7</v>
       </c>
       <c r="Q20">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R20">
         <v>1.26</v>
@@ -5575,10 +5575,10 @@
         <v>1.88</v>
       </c>
       <c r="V20">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W20">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X20">
         <v>10.5</v>
@@ -5605,25 +5605,25 @@
         <v>80</v>
       </c>
       <c r="AF20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG20">
         <v>10.5</v>
       </c>
       <c r="AH20">
+        <v>23</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
         <v>22</v>
-      </c>
-      <c r="AI20">
-        <v>1000</v>
-      </c>
-      <c r="AJ20">
-        <v>23</v>
       </c>
       <c r="AK20">
         <v>24</v>
       </c>
       <c r="AL20">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="AM20">
         <v>1000</v>
@@ -5653,13 +5653,13 @@
         <v>7.2</v>
       </c>
       <c r="AV20">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW20">
         <v>65</v>
       </c>
       <c r="AX20">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY20">
         <v>9.6</v>
@@ -5686,67 +5686,67 @@
         <v>16.5</v>
       </c>
       <c r="BG20">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="BH20">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BI20">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="BJ20">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>6.6</v>
+        <v>2.48</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>16</v>
+        <v>2.8</v>
       </c>
       <c r="BN20">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="BP20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="BR20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>11.5</v>
+        <v>2.8</v>
       </c>
       <c r="BT20">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>7</v>
+        <v>2.26</v>
       </c>
       <c r="BV20">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>12.5</v>
+        <v>2.8</v>
       </c>
       <c r="BX20">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>13.5</v>
+        <v>2.8</v>
       </c>
       <c r="BZ20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>11.5</v>
+        <v>2.8</v>
       </c>
       <c r="CB20" t="s">
         <v>187</v>
@@ -5778,13 +5778,13 @@
         <v>13.5</v>
       </c>
       <c r="I21">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J21">
         <v>8.6</v>
       </c>
       <c r="K21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>1.15</v>
@@ -5793,28 +5793,28 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O21">
         <v>1.08</v>
       </c>
       <c r="P21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q21">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R21">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S21">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T21">
         <v>1.77</v>
       </c>
       <c r="U21">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V21">
         <v>1.06</v>
@@ -5823,7 +5823,7 @@
         <v>5.5</v>
       </c>
       <c r="X21">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Y21">
         <v>100</v>
@@ -5847,7 +5847,7 @@
         <v>210</v>
       </c>
       <c r="AF21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG21">
         <v>14</v>
@@ -5862,7 +5862,7 @@
         <v>11.5</v>
       </c>
       <c r="AK21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL21">
         <v>36</v>
@@ -5883,13 +5883,13 @@
         <v>8.4</v>
       </c>
       <c r="AR21">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS21">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT21">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="AU21">
         <v>6.6</v>
@@ -5919,16 +5919,16 @@
         <v>11.5</v>
       </c>
       <c r="BD21">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE21">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF21">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BG21">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6032,16 +6032,16 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O22">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q22">
         <v>1.78</v>
@@ -6056,7 +6056,7 @@
         <v>1.57</v>
       </c>
       <c r="U22">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V22">
         <v>1.53</v>
@@ -6065,7 +6065,7 @@
         <v>1.5</v>
       </c>
       <c r="X22">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
         <v>44</v>
@@ -6080,7 +6080,7 @@
         <v>40</v>
       </c>
       <c r="AC22">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD22">
         <v>34</v>
@@ -6253,19 +6253,19 @@
         <v>169</v>
       </c>
       <c r="F23">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="G23">
         <v>110</v>
       </c>
       <c r="H23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J23">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="K23">
         <v>880</v>
@@ -6283,16 +6283,16 @@
         <v>1.21</v>
       </c>
       <c r="P23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q23">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R23">
         <v>1.18</v>
       </c>
       <c r="S23">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6301,7 +6301,7 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23">
         <v>1.01</v>
@@ -6495,16 +6495,16 @@
         <v>170</v>
       </c>
       <c r="F24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G24">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H24">
         <v>1.02</v>
       </c>
       <c r="I24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J24">
         <v>1.01</v>
@@ -6534,7 +6534,7 @@
         <v>1.18</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6543,7 +6543,7 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W24">
         <v>1.01</v>
@@ -6737,19 +6737,19 @@
         <v>171</v>
       </c>
       <c r="F25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="G25">
         <v>110</v>
       </c>
       <c r="H25">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="I25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J25">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="K25">
         <v>880</v>
@@ -6770,7 +6770,7 @@
         <v>1.24</v>
       </c>
       <c r="Q25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R25">
         <v>1.18</v>
@@ -6785,7 +6785,7 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25">
         <v>1.01</v>
@@ -6979,16 +6979,16 @@
         <v>172</v>
       </c>
       <c r="F26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G26">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H26">
         <v>1.16</v>
       </c>
       <c r="I26">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J26">
         <v>4.1</v>
@@ -7003,7 +7003,7 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O26">
         <v>1.09</v>
@@ -7027,7 +7027,7 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W26">
         <v>1.14</v>
@@ -7224,16 +7224,16 @@
         <v>1.31</v>
       </c>
       <c r="G27">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="H27">
-        <v>1.87</v>
+        <v>3.15</v>
       </c>
       <c r="I27">
         <v>1000</v>
       </c>
       <c r="J27">
-        <v>1.84</v>
+        <v>3.15</v>
       </c>
       <c r="K27">
         <v>930</v>
@@ -7269,10 +7269,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7472,7 +7472,7 @@
         <v>1.6</v>
       </c>
       <c r="I28">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J28">
         <v>4.1</v>
@@ -7487,16 +7487,16 @@
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O28">
         <v>1.3</v>
       </c>
       <c r="P28">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q28">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R28">
         <v>1.34</v>
@@ -7511,16 +7511,16 @@
         <v>1.88</v>
       </c>
       <c r="V28">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="W28">
         <v>1.16</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y28">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z28">
         <v>1000</v>
@@ -7535,7 +7535,7 @@
         <v>1000</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE28">
         <v>19</v>
@@ -7571,31 +7571,31 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
         <v>16.5</v>
       </c>
       <c r="AU28">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
         <v>17</v>
@@ -7607,7 +7607,7 @@
         <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
         <v>1.01</v>
@@ -7616,13 +7616,13 @@
         <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7705,46 +7705,46 @@
         <v>175</v>
       </c>
       <c r="F29">
+        <v>1.62</v>
+      </c>
+      <c r="G29">
         <v>1.63</v>
-      </c>
-      <c r="G29">
-        <v>1.64</v>
       </c>
       <c r="H29">
         <v>5.8</v>
       </c>
       <c r="I29">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K29">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L29">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M29">
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P29">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q29">
         <v>1.68</v>
       </c>
       <c r="R29">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S29">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T29">
         <v>1.76</v>
@@ -7756,7 +7756,7 @@
         <v>1.2</v>
       </c>
       <c r="W29">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X29">
         <v>21</v>
@@ -7768,7 +7768,7 @@
         <v>50</v>
       </c>
       <c r="AA29">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB29">
         <v>10.5</v>
@@ -7780,7 +7780,7 @@
         <v>23</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF29">
         <v>11</v>
@@ -7804,13 +7804,13 @@
         <v>30</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN29">
         <v>7.4</v>
       </c>
       <c r="AO29">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP29">
         <v>19</v>
@@ -7837,10 +7837,10 @@
         <v>60</v>
       </c>
       <c r="AX29">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY29">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29">
         <v>17.5</v>
@@ -7864,67 +7864,67 @@
         <v>6.8</v>
       </c>
       <c r="BG29">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BH29">
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>3.35</v>
+        <v>1.58</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>7</v>
+        <v>2.12</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>3.55</v>
+        <v>1.62</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>7.2</v>
+        <v>2.12</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>6.6</v>
+        <v>2.08</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="CB29" t="s">
         <v>187</v>
@@ -7950,16 +7950,16 @@
         <v>2.02</v>
       </c>
       <c r="G30">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H30">
         <v>3.9</v>
       </c>
       <c r="I30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J30">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K30">
         <v>3.9</v>
@@ -7974,7 +7974,7 @@
         <v>4</v>
       </c>
       <c r="O30">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P30">
         <v>2.02</v>
@@ -7989,7 +7989,7 @@
         <v>3.3</v>
       </c>
       <c r="T30">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U30">
         <v>2.18</v>
@@ -7998,7 +7998,7 @@
         <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="X30">
         <v>16</v>
@@ -8013,49 +8013,49 @@
         <v>1000</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC30">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD30">
         <v>17</v>
       </c>
       <c r="AE30">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF30">
         <v>13</v>
       </c>
       <c r="AG30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH30">
         <v>19.5</v>
       </c>
       <c r="AI30">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="AJ30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK30">
         <v>22</v>
       </c>
       <c r="AL30">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AM30">
         <v>1000</v>
       </c>
       <c r="AN30">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO30">
         <v>190</v>
       </c>
       <c r="AP30">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ30">
         <v>13.5</v>
@@ -8064,7 +8064,7 @@
         <v>19</v>
       </c>
       <c r="AS30">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AT30">
         <v>9</v>
@@ -8073,7 +8073,7 @@
         <v>7.6</v>
       </c>
       <c r="AV30">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW30">
         <v>26</v>
@@ -8088,7 +8088,7 @@
         <v>16</v>
       </c>
       <c r="BA30">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BB30">
         <v>21</v>
@@ -8106,67 +8106,67 @@
         <v>12.5</v>
       </c>
       <c r="BG30">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BH30">
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>2.98</v>
+        <v>1.49</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BN30">
         <v>5.8</v>
       </c>
       <c r="BO30">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>9.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BT30">
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>5.5</v>
+        <v>1.96</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="CB30" t="s">
         <v>187</v>
@@ -8189,10 +8189,10 @@
         <v>177</v>
       </c>
       <c r="F31">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G31">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H31">
         <v>3.05</v>
@@ -8204,31 +8204,31 @@
         <v>3.6</v>
       </c>
       <c r="K31">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L31">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M31">
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>1.28</v>
       </c>
       <c r="P31">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q31">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="R31">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T31">
         <v>1.69</v>
@@ -8306,7 +8306,7 @@
         <v>19.5</v>
       </c>
       <c r="AS31">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
         <v>10</v>
@@ -8318,7 +8318,7 @@
         <v>12</v>
       </c>
       <c r="AW31">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
         <v>13.5</v>
@@ -8330,25 +8330,25 @@
         <v>13.5</v>
       </c>
       <c r="BA31">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
         <v>20</v>
       </c>
       <c r="BD31">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
         <v>14.5</v>
       </c>
       <c r="BG31">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8431,16 +8431,16 @@
         <v>178</v>
       </c>
       <c r="F32">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G32">
         <v>2.24</v>
       </c>
       <c r="H32">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I32">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J32">
         <v>3.95</v>
@@ -8455,13 +8455,13 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O32">
         <v>1.17</v>
       </c>
       <c r="P32">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
         <v>1.57</v>
@@ -8470,88 +8470,88 @@
         <v>1.59</v>
       </c>
       <c r="S32">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T32">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="U32">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
         <v>1.8</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y32">
         <v>19.5</v>
       </c>
       <c r="Z32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB32">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC32">
         <v>10.5</v>
       </c>
       <c r="AD32">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE32">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF32">
         <v>21</v>
       </c>
       <c r="AG32">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH32">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI32">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK32">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM32">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN32">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO32">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP32">
         <v>18</v>
       </c>
       <c r="AQ32">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR32">
         <v>20</v>
       </c>
       <c r="AS32">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU32">
         <v>8.6</v>
@@ -8560,19 +8560,19 @@
         <v>12.5</v>
       </c>
       <c r="AW32">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY32">
         <v>10</v>
       </c>
       <c r="AZ32">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA32">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
         <v>19.5</v>
@@ -8584,7 +8584,7 @@
         <v>19.5</v>
       </c>
       <c r="BE32">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
         <v>9.199999999999999</v>
@@ -8596,61 +8596,61 @@
         <v>1000</v>
       </c>
       <c r="BI32">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK32">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ32">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU32">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW32">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA32">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="CB32" t="s">
         <v>187</v>
@@ -8676,7 +8676,7 @@
         <v>2.1</v>
       </c>
       <c r="G33">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="H33">
         <v>3.65</v>
@@ -8691,61 +8691,61 @@
         <v>3.65</v>
       </c>
       <c r="L33">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N33">
         <v>3.5</v>
       </c>
       <c r="O33">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="P33">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q33">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S33">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
         <v>1.7</v>
       </c>
       <c r="U33">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V33">
         <v>1.33</v>
       </c>
       <c r="W33">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X33">
         <v>1000</v>
       </c>
       <c r="Y33">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z33">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB33">
         <v>20</v>
       </c>
       <c r="AC33">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD33">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE33">
         <v>1000</v>
@@ -8754,16 +8754,16 @@
         <v>1000</v>
       </c>
       <c r="AG33">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH33">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI33">
         <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK33">
         <v>1000</v>
@@ -8775,16 +8775,16 @@
         <v>1000</v>
       </c>
       <c r="AN33">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO33">
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR33">
         <v>1.01</v>
@@ -8793,34 +8793,34 @@
         <v>1.01</v>
       </c>
       <c r="AT33">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU33">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV33">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW33">
         <v>1.01</v>
       </c>
       <c r="AX33">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY33">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA33">
         <v>1.01</v>
       </c>
       <c r="BB33">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC33">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BD33">
         <v>1.01</v>
@@ -8829,7 +8829,7 @@
         <v>1.01</v>
       </c>
       <c r="BF33">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG33">
         <v>1.01</v>
@@ -8915,118 +8915,118 @@
         <v>180</v>
       </c>
       <c r="F34">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G34">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="H34">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="I34">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J34">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K34">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L34">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N34">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="O34">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P34">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q34">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R34">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S34">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T34">
         <v>1.48</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V34">
         <v>1.43</v>
       </c>
       <c r="W34">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="X34">
         <v>1000</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC34">
+        <v>970</v>
+      </c>
+      <c r="AD34">
+        <v>18.5</v>
+      </c>
+      <c r="AE34">
+        <v>44</v>
+      </c>
+      <c r="AF34">
+        <v>25</v>
+      </c>
+      <c r="AG34">
         <v>16</v>
       </c>
-      <c r="AD34">
-        <v>1000</v>
-      </c>
-      <c r="AE34">
-        <v>1000</v>
-      </c>
-      <c r="AF34">
-        <v>1000</v>
-      </c>
-      <c r="AG34">
-        <v>1000</v>
-      </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK34">
         <v>1000</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP34">
         <v>1.01</v>
       </c>
       <c r="AQ34">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR34">
         <v>1.01</v>
@@ -9035,46 +9035,46 @@
         <v>1.01</v>
       </c>
       <c r="AT34">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU34">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV34">
+        <v>10</v>
+      </c>
+      <c r="AW34">
+        <v>18.5</v>
+      </c>
+      <c r="AX34">
+        <v>12</v>
+      </c>
+      <c r="AY34">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW34">
-        <v>1.01</v>
-      </c>
-      <c r="AX34">
-        <v>11</v>
-      </c>
-      <c r="AY34">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ34">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BA34">
         <v>1.01</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC34">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BD34">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE34">
         <v>1.01</v>
       </c>
       <c r="BF34">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG34">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9157,31 +9157,31 @@
         <v>181</v>
       </c>
       <c r="F35">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H35">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="I35">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="J35">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K35">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L35">
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N35">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O35">
         <v>1.26</v>
@@ -9190,25 +9190,25 @@
         <v>2.1</v>
       </c>
       <c r="Q35">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R35">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S35">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="T35">
+        <v>1.61</v>
+      </c>
+      <c r="U35">
+        <v>2.22</v>
+      </c>
+      <c r="V35">
         <v>1.58</v>
       </c>
-      <c r="U35">
-        <v>2.24</v>
-      </c>
-      <c r="V35">
-        <v>1.6</v>
-      </c>
       <c r="W35">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X35">
         <v>26</v>
@@ -9223,7 +9223,7 @@
         <v>55</v>
       </c>
       <c r="AB35">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC35">
         <v>10.5</v>
@@ -9274,7 +9274,7 @@
         <v>13</v>
       </c>
       <c r="AS35">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AT35">
         <v>10</v>
@@ -9298,19 +9298,19 @@
         <v>11.5</v>
       </c>
       <c r="BA35">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BB35">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BC35">
         <v>17.5</v>
       </c>
       <c r="BD35">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BE35">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF35">
         <v>15</v>
@@ -9399,16 +9399,16 @@
         <v>182</v>
       </c>
       <c r="F36">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G36">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H36">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I36">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J36">
         <v>3.55</v>
@@ -9417,40 +9417,40 @@
         <v>4.2</v>
       </c>
       <c r="L36">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M36">
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="O36">
         <v>1.22</v>
       </c>
       <c r="P36">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q36">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R36">
         <v>1.47</v>
       </c>
       <c r="S36">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T36">
         <v>1.53</v>
       </c>
       <c r="U36">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W36">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9507,10 +9507,10 @@
         <v>1000</v>
       </c>
       <c r="AP36">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR36">
         <v>1.01</v>
@@ -9519,25 +9519,25 @@
         <v>1.01</v>
       </c>
       <c r="AT36">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU36">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV36">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW36">
         <v>1.01</v>
       </c>
       <c r="AX36">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY36">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BA36">
         <v>1.01</v>
@@ -9555,7 +9555,7 @@
         <v>1.01</v>
       </c>
       <c r="BF36">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG36">
         <v>1.01</v>
@@ -9680,10 +9680,10 @@
         <v>1.62</v>
       </c>
       <c r="S37">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="T37">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U37">
         <v>2.34</v>
@@ -9758,7 +9758,7 @@
         <v>20</v>
       </c>
       <c r="AS37">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT37">
         <v>11</v>
@@ -9770,7 +9770,7 @@
         <v>11</v>
       </c>
       <c r="AW37">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX37">
         <v>12.5</v>
@@ -9782,7 +9782,7 @@
         <v>11</v>
       </c>
       <c r="BA37">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB37">
         <v>19</v>
@@ -9794,7 +9794,7 @@
         <v>19</v>
       </c>
       <c r="BE37">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BF37">
         <v>7.4</v>
@@ -9883,22 +9883,22 @@
         <v>184</v>
       </c>
       <c r="F38">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G38">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="H38">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I38">
+        <v>7.4</v>
+      </c>
+      <c r="J38">
+        <v>4.3</v>
+      </c>
+      <c r="K38">
         <v>7.8</v>
-      </c>
-      <c r="J38">
-        <v>4.5</v>
-      </c>
-      <c r="K38">
-        <v>7.4</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -9919,22 +9919,22 @@
         <v>1.45</v>
       </c>
       <c r="R38">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="S38">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T38">
         <v>1.58</v>
       </c>
       <c r="U38">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V38">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W38">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -9985,7 +9985,7 @@
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="AO38">
         <v>1000</v>
@@ -10003,10 +10003,10 @@
         <v>1.01</v>
       </c>
       <c r="AT38">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU38">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV38">
         <v>1.01</v>
@@ -10015,22 +10015,22 @@
         <v>1.01</v>
       </c>
       <c r="AX38">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY38">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA38">
         <v>1.01</v>
       </c>
       <c r="BB38">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC38">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD38">
         <v>1.01</v>
@@ -10149,10 +10149,10 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>2.72</v>
+        <v>3.75</v>
       </c>
       <c r="O39">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="P39">
         <v>1.8</v>
@@ -10161,10 +10161,10 @@
         <v>1.73</v>
       </c>
       <c r="R39">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S39">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="T39">
         <v>1.01</v>
@@ -10296,55 +10296,55 @@
         <v>1000</v>
       </c>
       <c r="BK39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BN39">
         <v>1000</v>
       </c>
       <c r="BO39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BP39">
         <v>1000</v>
       </c>
       <c r="BQ39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BT39">
         <v>1000</v>
       </c>
       <c r="BU39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BV39">
         <v>1000</v>
       </c>
       <c r="BW39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BZ39">
         <v>1000</v>
       </c>
       <c r="CA39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="CB39" t="s">
         <v>187</v>
@@ -10367,61 +10367,61 @@
         <v>186</v>
       </c>
       <c r="F40">
+        <v>10.5</v>
+      </c>
+      <c r="G40">
         <v>11.5</v>
       </c>
-      <c r="G40">
-        <v>12</v>
-      </c>
       <c r="H40">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I40">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="J40">
         <v>6.8</v>
       </c>
       <c r="K40">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M40">
         <v>1.02</v>
       </c>
       <c r="N40">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O40">
         <v>1.11</v>
       </c>
       <c r="P40">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q40">
         <v>1.37</v>
       </c>
       <c r="R40">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S40">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="T40">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U40">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X40">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y40">
         <v>16</v>
@@ -10430,13 +10430,13 @@
         <v>10.5</v>
       </c>
       <c r="AA40">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AB40">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AC40">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD40">
         <v>12</v>
@@ -10445,148 +10445,148 @@
         <v>11.5</v>
       </c>
       <c r="AF40">
+        <v>130</v>
+      </c>
+      <c r="AG40">
+        <v>40</v>
+      </c>
+      <c r="AH40">
+        <v>25</v>
+      </c>
+      <c r="AI40">
+        <v>27</v>
+      </c>
+      <c r="AJ40">
+        <v>430</v>
+      </c>
+      <c r="AK40">
         <v>140</v>
       </c>
-      <c r="AG40">
-        <v>42</v>
-      </c>
-      <c r="AH40">
-        <v>26</v>
-      </c>
-      <c r="AI40">
-        <v>28</v>
-      </c>
-      <c r="AJ40">
-        <v>450</v>
-      </c>
-      <c r="AK40">
-        <v>150</v>
-      </c>
       <c r="AL40">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM40">
         <v>120</v>
       </c>
       <c r="AN40">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO40">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AP40">
         <v>34</v>
       </c>
       <c r="AQ40">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR40">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS40">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT40">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AU40">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AV40">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW40">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX40">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AY40">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AZ40">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA40">
         <v>23</v>
       </c>
       <c r="BB40">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BC40">
         <v>44</v>
       </c>
       <c r="BD40">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BE40">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF40">
         <v>42</v>
       </c>
       <c r="BG40">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BH40">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BI40">
-        <v>4.9</v>
+        <v>1.47</v>
       </c>
       <c r="BJ40">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK40">
-        <v>3.6</v>
+        <v>1.88</v>
       </c>
       <c r="BL40">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM40">
-        <v>4.6</v>
+        <v>1.88</v>
       </c>
       <c r="BN40">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BO40">
-        <v>3.7</v>
+        <v>1.88</v>
       </c>
       <c r="BP40">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR40">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS40">
-        <v>4.4</v>
+        <v>1.88</v>
       </c>
       <c r="BT40">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU40">
-        <v>3.9</v>
+        <v>1.36</v>
       </c>
       <c r="BV40">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BW40">
-        <v>6.2</v>
+        <v>1.56</v>
       </c>
       <c r="BX40">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY40">
-        <v>3.9</v>
+        <v>1.88</v>
       </c>
       <c r="BZ40">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="CA40">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="CB40" t="s">
         <v>187</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -577,7 +577,7 @@
     <t>Real Madrid</t>
   </si>
   <si>
-    <t>2026-09-13 18:48:25</t>
+    <t>2026-09-13 21:16:22</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1180,7 @@
         <v>10.5</v>
       </c>
       <c r="I2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J2">
         <v>4.3</v>
@@ -1195,13 +1195,13 @@
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O2">
         <v>1.48</v>
       </c>
       <c r="P2">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q2">
         <v>2.42</v>
@@ -1231,7 +1231,7 @@
         <v>27</v>
       </c>
       <c r="Z2">
-        <v>960</v>
+        <v>840</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1246,7 +1246,7 @@
         <v>55</v>
       </c>
       <c r="AE2">
-        <v>960</v>
+        <v>840</v>
       </c>
       <c r="AF2">
         <v>6.8</v>
@@ -1258,7 +1258,7 @@
         <v>50</v>
       </c>
       <c r="AI2">
-        <v>960</v>
+        <v>830</v>
       </c>
       <c r="AJ2">
         <v>14</v>
@@ -1270,7 +1270,7 @@
         <v>85</v>
       </c>
       <c r="AM2">
-        <v>960</v>
+        <v>830</v>
       </c>
       <c r="AN2">
         <v>13</v>
@@ -1330,7 +1330,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1413,40 +1413,40 @@
         <v>149</v>
       </c>
       <c r="F3">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H3">
+        <v>2.92</v>
+      </c>
+      <c r="I3">
         <v>3</v>
       </c>
-      <c r="I3">
-        <v>3.2</v>
-      </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
         <v>2.92</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
         <v>1.65</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1455,28 +1455,28 @@
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
         <v>1.92</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="Z3">
         <v>24</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB3">
         <v>9.199999999999999</v>
@@ -1488,7 +1488,7 @@
         <v>17</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF3">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI3">
         <v>75</v>
@@ -1518,19 +1518,19 @@
         <v>46</v>
       </c>
       <c r="AO3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP3">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS3">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1542,10 +1542,10 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY3">
         <v>11</v>
@@ -1554,37 +1554,37 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BB3">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC3">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BD3">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE3">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BF3">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BG3">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1614,7 +1614,7 @@
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1667,7 +1667,7 @@
         <v>11.5</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K4">
         <v>5.2</v>
@@ -1688,7 +1688,7 @@
         <v>2.02</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R4">
         <v>1.38</v>
@@ -1706,7 +1706,7 @@
         <v>1.09</v>
       </c>
       <c r="W4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X4">
         <v>17.5</v>
@@ -1763,7 +1763,7 @@
         <v>410</v>
       </c>
       <c r="AP4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4">
         <v>6.6</v>
@@ -1936,7 +1936,7 @@
         <v>1.45</v>
       </c>
       <c r="S5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T5">
         <v>1.74</v>
@@ -1945,7 +1945,7 @@
         <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
         <v>1.96</v>
@@ -2020,7 +2020,7 @@
         <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV5">
         <v>14.5</v>
@@ -2139,7 +2139,7 @@
         <v>152</v>
       </c>
       <c r="F6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G6">
         <v>5.3</v>
@@ -2154,7 +2154,7 @@
         <v>2.94</v>
       </c>
       <c r="K6">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2163,13 +2163,13 @@
         <v>1.16</v>
       </c>
       <c r="N6">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O6">
         <v>1.67</v>
       </c>
       <c r="P6">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -2193,10 +2193,10 @@
         <v>1.23</v>
       </c>
       <c r="X6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="Z6">
         <v>13.5</v>
@@ -2247,7 +2247,7 @@
         <v>44</v>
       </c>
       <c r="AP6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6">
         <v>5.2</v>
@@ -2256,7 +2256,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT6">
         <v>9.800000000000001</v>
@@ -2268,10 +2268,10 @@
         <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX6">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AY6">
         <v>17.5</v>
@@ -2280,25 +2280,25 @@
         <v>21</v>
       </c>
       <c r="BA6">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB6">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BC6">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BD6">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE6">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF6">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG6">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH6">
         <v>2.82</v>
@@ -2537,7 +2537,7 @@
         <v>8.6</v>
       </c>
       <c r="BF7">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BG7">
         <v>8.199999999999999</v>
@@ -2623,19 +2623,19 @@
         <v>154</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G8">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>870</v>
       </c>
       <c r="J8">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K8">
         <v>900</v>
@@ -2671,10 +2671,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2871,7 +2871,7 @@
         <v>1.97</v>
       </c>
       <c r="H9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I9">
         <v>4.9</v>
@@ -2889,31 +2889,31 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
         <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="R9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U9">
         <v>2.04</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W9">
         <v>2.02</v>
@@ -3107,7 +3107,7 @@
         <v>156</v>
       </c>
       <c r="F10">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G10">
         <v>1.54</v>
@@ -3116,7 +3116,7 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J10">
         <v>4.7</v>
@@ -3137,7 +3137,7 @@
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
         <v>1.68</v>
@@ -3146,7 +3146,7 @@
         <v>1.51</v>
       </c>
       <c r="S10">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T10">
         <v>1.87</v>
@@ -3155,7 +3155,7 @@
         <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W10">
         <v>2.84</v>
@@ -3209,7 +3209,7 @@
         <v>140</v>
       </c>
       <c r="AN10">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO10">
         <v>140</v>
@@ -3221,10 +3221,10 @@
         <v>19</v>
       </c>
       <c r="AR10">
+        <v>4.5</v>
+      </c>
+      <c r="AS10">
         <v>4.4</v>
-      </c>
-      <c r="AS10">
-        <v>4.3</v>
       </c>
       <c r="AT10">
         <v>8.6</v>
@@ -3236,7 +3236,7 @@
         <v>19.5</v>
       </c>
       <c r="AW10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX10">
         <v>8.6</v>
@@ -3248,7 +3248,7 @@
         <v>16</v>
       </c>
       <c r="BA10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB10">
         <v>11.5</v>
@@ -3257,16 +3257,16 @@
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF10">
         <v>5.8</v>
       </c>
       <c r="BG10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH10">
         <v>4.8</v>
@@ -3349,22 +3349,22 @@
         <v>157</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G11">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H11">
         <v>2.26</v>
       </c>
       <c r="I11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J11">
         <v>3.35</v>
       </c>
       <c r="K11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3373,13 +3373,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O11">
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q11">
         <v>1.52</v>
@@ -3400,7 +3400,7 @@
         <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3591,16 +3591,16 @@
         <v>158</v>
       </c>
       <c r="F12">
+        <v>2.26</v>
+      </c>
+      <c r="G12">
         <v>2.3</v>
-      </c>
-      <c r="G12">
-        <v>2.34</v>
       </c>
       <c r="H12">
         <v>3.5</v>
       </c>
       <c r="I12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -3615,7 +3615,7 @@
         <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
         <v>1.35</v>
@@ -3627,28 +3627,28 @@
         <v>2.04</v>
       </c>
       <c r="R12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S12">
         <v>3.75</v>
       </c>
       <c r="T12">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X12">
         <v>13</v>
       </c>
       <c r="Y12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z12">
         <v>26</v>
@@ -3663,7 +3663,7 @@
         <v>7.8</v>
       </c>
       <c r="AD12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE12">
         <v>42</v>
@@ -3744,7 +3744,7 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF12">
         <v>17.5</v>
@@ -3753,64 +3753,64 @@
         <v>36</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI12">
-        <v>1.42</v>
+        <v>2.84</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.39</v>
+        <v>2.08</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="CB12" t="s">
         <v>187</v>
@@ -3839,16 +3839,16 @@
         <v>1.74</v>
       </c>
       <c r="H13">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J13">
         <v>3.95</v>
       </c>
       <c r="K13">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="L13">
         <v>1.27</v>
@@ -3860,19 +3860,19 @@
         <v>3.8</v>
       </c>
       <c r="O13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P13">
         <v>1.97</v>
       </c>
       <c r="Q13">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R13">
         <v>1.37</v>
       </c>
       <c r="S13">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T13">
         <v>1.81</v>
@@ -3935,7 +3935,7 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO13">
         <v>1000</v>
@@ -4323,13 +4323,13 @@
         <v>2.94</v>
       </c>
       <c r="H15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I15">
         <v>2.66</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4338,37 +4338,37 @@
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O15">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q15">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R15">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S15">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T15">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="U15">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="V15">
         <v>1.6</v>
       </c>
       <c r="W15">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4428,7 +4428,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR15">
         <v>1.01</v>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU15">
         <v>7.2</v>
@@ -4452,7 +4452,7 @@
         <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ15">
         <v>10</v>
@@ -4583,22 +4583,22 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O16">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P16">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q16">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R16">
         <v>1.48</v>
       </c>
       <c r="S16">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T16">
         <v>2.48</v>
@@ -4625,10 +4625,10 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD16">
         <v>80</v>
@@ -4667,16 +4667,16 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AQ16">
         <v>6.8</v>
       </c>
       <c r="AR16">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT16">
         <v>7</v>
@@ -4685,10 +4685,10 @@
         <v>13</v>
       </c>
       <c r="AV16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX16">
         <v>6.2</v>
@@ -4700,7 +4700,7 @@
         <v>6.8</v>
       </c>
       <c r="BA16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB16">
         <v>7.6</v>
@@ -4709,16 +4709,16 @@
         <v>13.5</v>
       </c>
       <c r="BD16">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4801,7 +4801,7 @@
         <v>163</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G17">
         <v>2.1</v>
@@ -4810,13 +4810,13 @@
         <v>3.55</v>
       </c>
       <c r="I17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J17">
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4828,19 +4828,19 @@
         <v>5.4</v>
       </c>
       <c r="O17">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P17">
         <v>2.58</v>
       </c>
       <c r="Q17">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R17">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="S17">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T17">
         <v>1.58</v>
@@ -4849,7 +4849,7 @@
         <v>2.56</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
         <v>1.9</v>
@@ -4879,7 +4879,7 @@
         <v>38</v>
       </c>
       <c r="AF17">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG17">
         <v>11.5</v>
@@ -4903,7 +4903,7 @@
         <v>70</v>
       </c>
       <c r="AN17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO17">
         <v>27</v>
@@ -4957,7 +4957,7 @@
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG17">
         <v>19</v>
@@ -5043,31 +5043,31 @@
         <v>164</v>
       </c>
       <c r="F18">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G18">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H18">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I18">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K18">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
         <v>1.18</v>
@@ -5076,13 +5076,13 @@
         <v>2.14</v>
       </c>
       <c r="Q18">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R18">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S18">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5091,10 +5091,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5112,7 +5112,7 @@
         <v>1000</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD18">
         <v>1000</v>
@@ -5154,22 +5154,22 @@
         <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS18">
         <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW18">
         <v>1.01</v>
@@ -5178,10 +5178,10 @@
         <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BA18">
         <v>1.01</v>
@@ -5199,10 +5199,10 @@
         <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5288,7 +5288,7 @@
         <v>4.2</v>
       </c>
       <c r="G19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H19">
         <v>1.83</v>
@@ -5315,10 +5315,10 @@
         <v>1.17</v>
       </c>
       <c r="P19">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q19">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R19">
         <v>1.69</v>
@@ -5339,7 +5339,7 @@
         <v>1.29</v>
       </c>
       <c r="X19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y19">
         <v>15</v>
@@ -5381,7 +5381,7 @@
         <v>50</v>
       </c>
       <c r="AL19">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM19">
         <v>65</v>
@@ -5429,19 +5429,19 @@
         <v>21</v>
       </c>
       <c r="BB19">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD19">
         <v>8.4</v>
       </c>
       <c r="BE19">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG19">
         <v>6.8</v>
@@ -5527,10 +5527,10 @@
         <v>166</v>
       </c>
       <c r="F20">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G20">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -5542,7 +5542,7 @@
         <v>3.4</v>
       </c>
       <c r="K20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L20">
         <v>1.51</v>
@@ -5578,7 +5578,7 @@
         <v>1.24</v>
       </c>
       <c r="W20">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X20">
         <v>10.5</v>
@@ -5626,10 +5626,10 @@
         <v>50</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO20">
         <v>110</v>
@@ -5641,7 +5641,7 @@
         <v>13</v>
       </c>
       <c r="AR20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS20">
         <v>40</v>
@@ -5698,31 +5698,31 @@
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>2.48</v>
+        <v>8</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.83</v>
+        <v>3.7</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BT20">
         <v>1000</v>
@@ -5734,19 +5734,19 @@
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CB20" t="s">
         <v>187</v>
@@ -5775,16 +5775,16 @@
         <v>1.22</v>
       </c>
       <c r="H21">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="I21">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="J21">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L21">
         <v>1.15</v>
@@ -5811,7 +5811,7 @@
         <v>1.66</v>
       </c>
       <c r="T21">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U21">
         <v>2.16</v>
@@ -5820,7 +5820,7 @@
         <v>1.06</v>
       </c>
       <c r="W21">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X21">
         <v>80</v>
@@ -5832,7 +5832,7 @@
         <v>200</v>
       </c>
       <c r="AA21">
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="AB21">
         <v>23</v>
@@ -5853,7 +5853,7 @@
         <v>14</v>
       </c>
       <c r="AH21">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI21">
         <v>140</v>
@@ -5871,34 +5871,34 @@
         <v>130</v>
       </c>
       <c r="AN21">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AO21">
         <v>170</v>
       </c>
       <c r="AP21">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR21">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS21">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT21">
         <v>17</v>
       </c>
       <c r="AU21">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV21">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW21">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX21">
         <v>11</v>
@@ -5910,7 +5910,7 @@
         <v>18.5</v>
       </c>
       <c r="BA21">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21">
         <v>9.800000000000001</v>
@@ -5922,13 +5922,13 @@
         <v>7.4</v>
       </c>
       <c r="BE21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF21">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BG21">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6011,7 +6011,7 @@
         <v>168</v>
       </c>
       <c r="F22">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -6023,10 +6023,10 @@
         <v>2.88</v>
       </c>
       <c r="J22">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6038,7 +6038,7 @@
         <v>4</v>
       </c>
       <c r="O22">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P22">
         <v>2.04</v>
@@ -6056,7 +6056,7 @@
         <v>1.57</v>
       </c>
       <c r="U22">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
         <v>1.53</v>
@@ -6253,7 +6253,7 @@
         <v>169</v>
       </c>
       <c r="F23">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="G23">
         <v>110</v>
@@ -6262,10 +6262,10 @@
         <v>1.03</v>
       </c>
       <c r="I23">
-        <v>110</v>
+        <v>870</v>
       </c>
       <c r="J23">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="K23">
         <v>880</v>
@@ -6277,7 +6277,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O23">
         <v>1.21</v>
@@ -6286,7 +6286,7 @@
         <v>1.25</v>
       </c>
       <c r="Q23">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R23">
         <v>1.18</v>
@@ -6301,7 +6301,7 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W23">
         <v>1.01</v>
@@ -6418,61 +6418,61 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
         <v>187</v>
@@ -6495,19 +6495,19 @@
         <v>170</v>
       </c>
       <c r="F24">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="G24">
-        <v>970</v>
+        <v>1.5</v>
       </c>
       <c r="H24">
         <v>1.02</v>
       </c>
       <c r="I24">
-        <v>110</v>
+        <v>870</v>
       </c>
       <c r="J24">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K24">
         <v>870</v>
@@ -6519,13 +6519,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O24">
         <v>1.2</v>
       </c>
       <c r="P24">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q24">
         <v>1.2</v>
@@ -6543,7 +6543,7 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24">
         <v>1.01</v>
@@ -6660,61 +6660,61 @@
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
         <v>1000</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
         <v>187</v>
@@ -6737,7 +6737,7 @@
         <v>171</v>
       </c>
       <c r="F25">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="G25">
         <v>110</v>
@@ -6749,7 +6749,7 @@
         <v>110</v>
       </c>
       <c r="J25">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="K25">
         <v>880</v>
@@ -6761,7 +6761,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O25">
         <v>1.01</v>
@@ -6770,7 +6770,7 @@
         <v>1.24</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R25">
         <v>1.18</v>
@@ -6785,7 +6785,7 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W25">
         <v>1.01</v>
@@ -6979,19 +6979,19 @@
         <v>172</v>
       </c>
       <c r="F26">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="G26">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="H26">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="I26">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J26">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K26">
         <v>890</v>
@@ -7003,13 +7003,13 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O26">
         <v>1.09</v>
       </c>
       <c r="P26">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q26">
         <v>1.09</v>
@@ -7018,19 +7018,19 @@
         <v>1.18</v>
       </c>
       <c r="S26">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V26">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7144,61 +7144,61 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
         <v>187</v>
@@ -7248,7 +7248,7 @@
         <v>2.52</v>
       </c>
       <c r="O27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P27">
         <v>2.52</v>
@@ -7466,7 +7466,7 @@
         <v>5.9</v>
       </c>
       <c r="G28">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="H28">
         <v>1.6</v>
@@ -7478,7 +7478,7 @@
         <v>4.1</v>
       </c>
       <c r="K28">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7487,7 +7487,7 @@
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O28">
         <v>1.3</v>
@@ -7496,7 +7496,7 @@
         <v>2</v>
       </c>
       <c r="Q28">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R28">
         <v>1.34</v>
@@ -7511,7 +7511,7 @@
         <v>1.88</v>
       </c>
       <c r="V28">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="W28">
         <v>1.16</v>
@@ -7535,7 +7535,7 @@
         <v>1000</v>
       </c>
       <c r="AD28">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
         <v>19</v>
@@ -7571,58 +7571,58 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AT28">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AY28">
         <v>17</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7705,7 +7705,7 @@
         <v>175</v>
       </c>
       <c r="F29">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G29">
         <v>1.63</v>
@@ -7717,7 +7717,7 @@
         <v>6</v>
       </c>
       <c r="J29">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K29">
         <v>4.7</v>
@@ -7735,19 +7735,19 @@
         <v>1.23</v>
       </c>
       <c r="P29">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q29">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R29">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S29">
         <v>2.7</v>
       </c>
       <c r="T29">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U29">
         <v>2.2</v>
@@ -7807,13 +7807,13 @@
         <v>95</v>
       </c>
       <c r="AN29">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO29">
         <v>70</v>
       </c>
       <c r="AP29">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ29">
         <v>21</v>
@@ -7953,7 +7953,7 @@
         <v>2.06</v>
       </c>
       <c r="H30">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I30">
         <v>4.2</v>
@@ -7962,16 +7962,16 @@
         <v>3.75</v>
       </c>
       <c r="K30">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L30">
         <v>1.38</v>
       </c>
       <c r="M30">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O30">
         <v>1.31</v>
@@ -7980,7 +7980,7 @@
         <v>2.02</v>
       </c>
       <c r="Q30">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R30">
         <v>1.39</v>
@@ -8034,7 +8034,7 @@
         <v>19.5</v>
       </c>
       <c r="AI30">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="AJ30">
         <v>25</v>
@@ -8189,19 +8189,19 @@
         <v>177</v>
       </c>
       <c r="F31">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G31">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H31">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J31">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K31">
         <v>3.8</v>
@@ -8222,7 +8222,7 @@
         <v>2.06</v>
       </c>
       <c r="Q31">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R31">
         <v>1.37</v>
@@ -8240,7 +8240,7 @@
         <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X31">
         <v>21</v>
@@ -8303,7 +8303,7 @@
         <v>12</v>
       </c>
       <c r="AR31">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS31">
         <v>1.01</v>
@@ -8336,7 +8336,7 @@
         <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BD31">
         <v>1.01</v>
@@ -8348,7 +8348,7 @@
         <v>14.5</v>
       </c>
       <c r="BG31">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8431,19 +8431,19 @@
         <v>178</v>
       </c>
       <c r="F32">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G32">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H32">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I32">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J32">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K32">
         <v>4.4</v>
@@ -8458,16 +8458,16 @@
         <v>5.3</v>
       </c>
       <c r="O32">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P32">
         <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R32">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S32">
         <v>2.38</v>
@@ -8479,10 +8479,10 @@
         <v>2.56</v>
       </c>
       <c r="V32">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X32">
         <v>30</v>
@@ -8509,13 +8509,13 @@
         <v>40</v>
       </c>
       <c r="AF32">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AG32">
         <v>12</v>
       </c>
       <c r="AH32">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI32">
         <v>44</v>
@@ -8539,10 +8539,10 @@
         <v>27</v>
       </c>
       <c r="AP32">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ32">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR32">
         <v>20</v>
@@ -8551,31 +8551,31 @@
         <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU32">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV32">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW32">
         <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY32">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA32">
         <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC32">
         <v>17</v>
@@ -8587,16 +8587,16 @@
         <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG32">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH32">
         <v>1000</v>
       </c>
       <c r="BI32">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BJ32">
         <v>12.5</v>
@@ -8611,10 +8611,10 @@
         <v>1.95</v>
       </c>
       <c r="BN32">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP32">
         <v>20</v>
@@ -8626,7 +8626,7 @@
         <v>32</v>
       </c>
       <c r="BS32">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BT32">
         <v>10</v>
@@ -8644,13 +8644,13 @@
         <v>44</v>
       </c>
       <c r="BY32">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="BZ32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA32">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CB32" t="s">
         <v>187</v>
@@ -8685,7 +8685,7 @@
         <v>4</v>
       </c>
       <c r="J33">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K33">
         <v>3.65</v>
@@ -8697,10 +8697,10 @@
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O33">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P33">
         <v>1.91</v>
@@ -8712,7 +8712,7 @@
         <v>1.36</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T33">
         <v>1.7</v>
@@ -8730,13 +8730,13 @@
         <v>1000</v>
       </c>
       <c r="Y33">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z33">
         <v>34</v>
       </c>
       <c r="AA33">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB33">
         <v>20</v>
@@ -8769,7 +8769,7 @@
         <v>1000</v>
       </c>
       <c r="AL33">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM33">
         <v>1000</v>
@@ -8781,40 +8781,40 @@
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AQ33">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AR33">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="AS33">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AT33">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="AU33">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AV33">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="AW33">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AX33">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AY33">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AZ33">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BA33">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BB33">
         <v>19</v>
@@ -8823,76 +8823,76 @@
         <v>16.5</v>
       </c>
       <c r="BD33">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BE33">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BF33">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BG33">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BH33">
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="s">
         <v>187</v>
@@ -8915,19 +8915,19 @@
         <v>180</v>
       </c>
       <c r="F34">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G34">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="H34">
         <v>2.92</v>
       </c>
       <c r="I34">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J34">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K34">
         <v>4.4</v>
@@ -8939,22 +8939,22 @@
         <v>1.04</v>
       </c>
       <c r="N34">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O34">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P34">
         <v>2.36</v>
       </c>
       <c r="Q34">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R34">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S34">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="T34">
         <v>1.48</v>
@@ -8966,7 +8966,7 @@
         <v>1.43</v>
       </c>
       <c r="W34">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -8990,7 +8990,7 @@
         <v>18.5</v>
       </c>
       <c r="AE34">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF34">
         <v>25</v>
@@ -9008,7 +9008,7 @@
         <v>44</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL34">
         <v>40</v>
@@ -9026,19 +9026,19 @@
         <v>1.01</v>
       </c>
       <c r="AQ34">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR34">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS34">
         <v>1.01</v>
       </c>
       <c r="AT34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU34">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV34">
         <v>10</v>
@@ -9047,10 +9047,10 @@
         <v>18.5</v>
       </c>
       <c r="AX34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY34">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ34">
         <v>10.5</v>
@@ -9062,7 +9062,7 @@
         <v>19</v>
       </c>
       <c r="BC34">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BD34">
         <v>18.5</v>
@@ -9071,70 +9071,70 @@
         <v>1.01</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG34">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH34">
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB34" t="s">
         <v>187</v>
@@ -9157,22 +9157,22 @@
         <v>181</v>
       </c>
       <c r="F35">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="G35">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H35">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I35">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J35">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K35">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9187,7 +9187,7 @@
         <v>1.26</v>
       </c>
       <c r="P35">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q35">
         <v>1.76</v>
@@ -9196,22 +9196,22 @@
         <v>1.4</v>
       </c>
       <c r="S35">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="T35">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="U35">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V35">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X35">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y35">
         <v>18.5</v>
@@ -9229,7 +9229,7 @@
         <v>10.5</v>
       </c>
       <c r="AD35">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE35">
         <v>38</v>
@@ -9262,13 +9262,13 @@
         <v>30</v>
       </c>
       <c r="AO35">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP35">
         <v>12.5</v>
       </c>
       <c r="AQ35">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR35">
         <v>13</v>
@@ -9277,13 +9277,13 @@
         <v>1.01</v>
       </c>
       <c r="AT35">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU35">
         <v>6.2</v>
       </c>
       <c r="AV35">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW35">
         <v>16</v>
@@ -9292,10 +9292,10 @@
         <v>14.5</v>
       </c>
       <c r="AY35">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ35">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA35">
         <v>1.01</v>
@@ -9313,7 +9313,7 @@
         <v>1.01</v>
       </c>
       <c r="BF35">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BG35">
         <v>13</v>
@@ -9426,7 +9426,7 @@
         <v>4.8</v>
       </c>
       <c r="O36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P36">
         <v>2.24</v>
@@ -9438,13 +9438,13 @@
         <v>1.47</v>
       </c>
       <c r="S36">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="T36">
         <v>1.53</v>
       </c>
       <c r="U36">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V36">
         <v>1.43</v>
@@ -9731,7 +9731,7 @@
         <v>36</v>
       </c>
       <c r="AJ37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK37">
         <v>21</v>
@@ -9895,10 +9895,10 @@
         <v>7.4</v>
       </c>
       <c r="J38">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K38">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -9907,7 +9907,7 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="O38">
         <v>1.15</v>
@@ -10128,19 +10128,19 @@
         <v>2.3</v>
       </c>
       <c r="G39">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="H39">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I39">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J39">
         <v>3.4</v>
       </c>
       <c r="K39">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L39">
         <v>1.01</v>
@@ -10152,7 +10152,7 @@
         <v>3.75</v>
       </c>
       <c r="O39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="P39">
         <v>1.8</v>
@@ -10161,10 +10161,10 @@
         <v>1.73</v>
       </c>
       <c r="R39">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="S39">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="T39">
         <v>1.01</v>
@@ -10173,10 +10173,10 @@
         <v>1.01</v>
       </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W39">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10367,16 +10367,16 @@
         <v>186</v>
       </c>
       <c r="F40">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G40">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="H40">
         <v>1.3</v>
       </c>
       <c r="I40">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="J40">
         <v>6.8</v>
@@ -10385,19 +10385,19 @@
         <v>7</v>
       </c>
       <c r="L40">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M40">
         <v>1.02</v>
       </c>
       <c r="N40">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O40">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P40">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q40">
         <v>1.37</v>
@@ -10406,16 +10406,16 @@
         <v>2.04</v>
       </c>
       <c r="S40">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="T40">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U40">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V40">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="W40">
         <v>1.09</v>
@@ -10457,7 +10457,7 @@
         <v>27</v>
       </c>
       <c r="AJ40">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="AK40">
         <v>140</v>
@@ -10466,16 +10466,16 @@
         <v>95</v>
       </c>
       <c r="AM40">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AN40">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AO40">
         <v>3.4</v>
       </c>
       <c r="AP40">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ40">
         <v>14</v>
@@ -10493,7 +10493,7 @@
         <v>14.5</v>
       </c>
       <c r="AV40">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW40">
         <v>10.5</v>
@@ -10517,10 +10517,10 @@
         <v>44</v>
       </c>
       <c r="BD40">
+        <v>65</v>
+      </c>
+      <c r="BE40">
         <v>75</v>
-      </c>
-      <c r="BE40">
-        <v>60</v>
       </c>
       <c r="BF40">
         <v>42</v>
@@ -10532,25 +10532,25 @@
         <v>1000</v>
       </c>
       <c r="BI40">
-        <v>1.47</v>
+        <v>4.3</v>
       </c>
       <c r="BJ40">
         <v>1000</v>
       </c>
       <c r="BK40">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="BN40">
         <v>1000</v>
       </c>
       <c r="BO40">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="BP40">
         <v>1000</v>
@@ -10562,25 +10562,25 @@
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="BT40">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU40">
-        <v>1.36</v>
+        <v>3.5</v>
       </c>
       <c r="BV40">
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>1.56</v>
+        <v>5.3</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.88</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ40">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -577,7 +577,7 @@
     <t>Real Madrid</t>
   </si>
   <si>
-    <t>2026-09-13 21:16:22</t>
+    <t>2026-09-13 23:30:02</t>
   </si>
 </sst>
 </file>
@@ -1186,10 +1186,10 @@
         <v>4.3</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M2">
         <v>1.1</v>
@@ -1198,13 +1198,13 @@
         <v>2.88</v>
       </c>
       <c r="O2">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P2">
         <v>1.64</v>
       </c>
       <c r="Q2">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R2">
         <v>1.23</v>
@@ -1231,7 +1231,7 @@
         <v>27</v>
       </c>
       <c r="Z2">
-        <v>840</v>
+        <v>730</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1246,19 +1246,19 @@
         <v>55</v>
       </c>
       <c r="AE2">
-        <v>840</v>
+        <v>730</v>
       </c>
       <c r="AF2">
         <v>6.8</v>
       </c>
       <c r="AG2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
         <v>50</v>
       </c>
       <c r="AI2">
-        <v>830</v>
+        <v>720</v>
       </c>
       <c r="AJ2">
         <v>14</v>
@@ -1270,7 +1270,7 @@
         <v>85</v>
       </c>
       <c r="AM2">
-        <v>830</v>
+        <v>720</v>
       </c>
       <c r="AN2">
         <v>13</v>
@@ -1291,7 +1291,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AU2">
         <v>9.6</v>
@@ -1437,40 +1437,40 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O3">
         <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
         <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V3">
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Z3">
         <v>24</v>
@@ -1530,10 +1530,10 @@
         <v>16.5</v>
       </c>
       <c r="AS3">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
@@ -1542,7 +1542,7 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
         <v>15</v>
@@ -1551,28 +1551,28 @@
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA3">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC3">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE3">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG3">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1664,19 +1664,19 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J4">
         <v>4.8</v>
       </c>
       <c r="K4">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L4">
         <v>1.38</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
         <v>3.9</v>
@@ -1718,13 +1718,13 @@
         <v>120</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD4">
         <v>44</v>
@@ -1748,7 +1748,7 @@
         <v>11.5</v>
       </c>
       <c r="AK4">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL4">
         <v>50</v>
@@ -1766,13 +1766,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR4">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
@@ -1781,10 +1781,10 @@
         <v>10</v>
       </c>
       <c r="AV4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX4">
         <v>7</v>
@@ -1793,10 +1793,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB4">
         <v>9.800000000000001</v>
@@ -1805,16 +1805,16 @@
         <v>14.5</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BE4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
         <v>6.6</v>
       </c>
       <c r="BG4">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH4">
         <v>3.9</v>
@@ -1897,7 +1897,7 @@
         <v>151</v>
       </c>
       <c r="F5">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G5">
         <v>2.04</v>
@@ -1930,10 +1930,10 @@
         <v>2.14</v>
       </c>
       <c r="Q5">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S5">
         <v>3.1</v>
@@ -1948,7 +1948,7 @@
         <v>1.31</v>
       </c>
       <c r="W5">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X5">
         <v>17.5</v>
@@ -1975,16 +1975,16 @@
         <v>55</v>
       </c>
       <c r="AF5">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
         <v>17.5</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>24</v>
@@ -1993,13 +1993,13 @@
         <v>21</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM5">
         <v>100</v>
       </c>
       <c r="AN5">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO5">
         <v>55</v>
@@ -2011,10 +2011,10 @@
         <v>14.5</v>
       </c>
       <c r="AR5">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT5">
         <v>9.6</v>
@@ -2026,19 +2026,19 @@
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB5">
         <v>20</v>
@@ -2047,16 +2047,16 @@
         <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF5">
         <v>11</v>
       </c>
       <c r="BG5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2098,7 +2098,7 @@
         <v>10</v>
       </c>
       <c r="BU5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV5">
         <v>44</v>
@@ -2142,7 +2142,7 @@
         <v>4.7</v>
       </c>
       <c r="G6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H6">
         <v>2.08</v>
@@ -2163,7 +2163,7 @@
         <v>1.16</v>
       </c>
       <c r="N6">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O6">
         <v>1.67</v>
@@ -2181,16 +2181,16 @@
         <v>6.8</v>
       </c>
       <c r="T6">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U6">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V6">
         <v>1.83</v>
       </c>
       <c r="W6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X6">
         <v>8.800000000000001</v>
@@ -2214,16 +2214,16 @@
         <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF6">
         <v>36</v>
       </c>
       <c r="AG6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI6">
         <v>95</v>
@@ -2244,19 +2244,19 @@
         <v>210</v>
       </c>
       <c r="AO6">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP6">
         <v>6.4</v>
       </c>
       <c r="AQ6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR6">
         <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT6">
         <v>9.800000000000001</v>
@@ -2268,10 +2268,10 @@
         <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX6">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AY6">
         <v>17.5</v>
@@ -2280,25 +2280,25 @@
         <v>21</v>
       </c>
       <c r="BA6">
+        <v>5.3</v>
+      </c>
+      <c r="BB6">
+        <v>5.3</v>
+      </c>
+      <c r="BC6">
+        <v>5.4</v>
+      </c>
+      <c r="BD6">
+        <v>5.4</v>
+      </c>
+      <c r="BE6">
+        <v>5.4</v>
+      </c>
+      <c r="BF6">
+        <v>5.3</v>
+      </c>
+      <c r="BG6">
         <v>5</v>
-      </c>
-      <c r="BB6">
-        <v>5.1</v>
-      </c>
-      <c r="BC6">
-        <v>5.1</v>
-      </c>
-      <c r="BD6">
-        <v>5.1</v>
-      </c>
-      <c r="BE6">
-        <v>5.1</v>
-      </c>
-      <c r="BF6">
-        <v>5.1</v>
-      </c>
-      <c r="BG6">
-        <v>4.9</v>
       </c>
       <c r="BH6">
         <v>2.82</v>
@@ -2396,7 +2396,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2408,13 +2408,13 @@
         <v>2.6</v>
       </c>
       <c r="O7">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P7">
         <v>1.51</v>
       </c>
       <c r="Q7">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R7">
         <v>1.19</v>
@@ -2489,7 +2489,7 @@
         <v>130</v>
       </c>
       <c r="AP7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ7">
         <v>9.4</v>
@@ -2498,19 +2498,19 @@
         <v>22</v>
       </c>
       <c r="AS7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
       </c>
       <c r="AU7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
         <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2519,13 +2519,13 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA7">
         <v>8.199999999999999</v>
       </c>
       <c r="BB7">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BC7">
         <v>21</v>
@@ -2540,7 +2540,7 @@
         <v>25</v>
       </c>
       <c r="BG7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2623,19 +2623,19 @@
         <v>154</v>
       </c>
       <c r="F8">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H8">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>900</v>
@@ -2647,7 +2647,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
         <v>1.15</v>
@@ -2656,7 +2656,7 @@
         <v>1.09</v>
       </c>
       <c r="Q8">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="R8">
         <v>1.09</v>
@@ -2665,16 +2665,16 @@
         <v>1.16</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2865,7 +2865,7 @@
         <v>155</v>
       </c>
       <c r="F9">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G9">
         <v>1.97</v>
@@ -2874,10 +2874,10 @@
         <v>4.2</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
         <v>4.4</v>
@@ -2898,7 +2898,7 @@
         <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="R9">
         <v>1.36</v>
@@ -2907,13 +2907,13 @@
         <v>3</v>
       </c>
       <c r="T9">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U9">
         <v>2.04</v>
       </c>
       <c r="V9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
         <v>2.02</v>
@@ -3107,91 +3107,91 @@
         <v>156</v>
       </c>
       <c r="F10">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="G10">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I10">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K10">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L10">
+        <v>1.28</v>
+      </c>
+      <c r="M10">
+        <v>1.06</v>
+      </c>
+      <c r="N10">
+        <v>4.3</v>
+      </c>
+      <c r="O10">
         <v>1.26</v>
       </c>
-      <c r="M10">
-        <v>1.05</v>
-      </c>
-      <c r="N10">
-        <v>4.8</v>
-      </c>
-      <c r="O10">
-        <v>1.23</v>
-      </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q10">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="R10">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S10">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T10">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="U10">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V10">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="X10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Y10">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Z10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA10">
         <v>260</v>
       </c>
       <c r="AB10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC10">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AE10">
         <v>130</v>
       </c>
       <c r="AF10">
+        <v>11.5</v>
+      </c>
+      <c r="AG10">
         <v>12</v>
       </c>
-      <c r="AG10">
-        <v>12.5</v>
-      </c>
       <c r="AH10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI10">
         <v>110</v>
@@ -3209,76 +3209,76 @@
         <v>140</v>
       </c>
       <c r="AN10">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AO10">
         <v>140</v>
       </c>
       <c r="AP10">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ10">
         <v>19</v>
       </c>
       <c r="AR10">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS10">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT10">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU10">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV10">
         <v>19.5</v>
       </c>
       <c r="AW10">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX10">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
         <v>16</v>
       </c>
       <c r="BA10">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC10">
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE10">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF10">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG10">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH10">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BI10">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ10">
         <v>13</v>
       </c>
       <c r="BK10">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3290,7 +3290,7 @@
         <v>4.8</v>
       </c>
       <c r="BO10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP10">
         <v>11</v>
@@ -3299,34 +3299,34 @@
         <v>3.3</v>
       </c>
       <c r="BR10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BS10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BT10">
         <v>13</v>
       </c>
       <c r="BU10">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV10">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BW10">
         <v>4.5</v>
       </c>
       <c r="BX10">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY10">
         <v>4.4</v>
       </c>
       <c r="BZ10">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="CA10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="CB10" t="s">
         <v>187</v>
@@ -3373,7 +3373,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O11">
         <v>1.18</v>
@@ -3388,7 +3388,7 @@
         <v>1.52</v>
       </c>
       <c r="S11">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3633,7 +3633,7 @@
         <v>3.75</v>
       </c>
       <c r="T12">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U12">
         <v>2.14</v>
@@ -3651,7 +3651,7 @@
         <v>13</v>
       </c>
       <c r="Z12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA12">
         <v>70</v>
@@ -3666,10 +3666,10 @@
         <v>14.5</v>
       </c>
       <c r="AE12">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG12">
         <v>11</v>
@@ -3732,7 +3732,7 @@
         <v>16</v>
       </c>
       <c r="BA12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB12">
         <v>25</v>
@@ -3744,13 +3744,13 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BF12">
         <v>17.5</v>
       </c>
       <c r="BG12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH12">
         <v>3.65</v>
@@ -3881,7 +3881,7 @@
         <v>1.89</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W13">
         <v>2.36</v>
@@ -4078,7 +4078,7 @@
         <v>1.97</v>
       </c>
       <c r="G14">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H14">
         <v>4.8</v>
@@ -4087,7 +4087,7 @@
         <v>6.2</v>
       </c>
       <c r="J14">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K14">
         <v>3.35</v>
@@ -4126,7 +4126,7 @@
         <v>1.2</v>
       </c>
       <c r="W14">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X14">
         <v>970</v>
@@ -4317,19 +4317,19 @@
         <v>161</v>
       </c>
       <c r="F15">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G15">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H15">
         <v>2.4</v>
       </c>
       <c r="I15">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J15">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4347,7 +4347,7 @@
         <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q15">
         <v>1.51</v>
@@ -4359,10 +4359,10 @@
         <v>2.26</v>
       </c>
       <c r="T15">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="U15">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V15">
         <v>1.6</v>
@@ -4383,10 +4383,10 @@
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD15">
         <v>1000</v>
@@ -4428,16 +4428,16 @@
         <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS15">
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
         <v>7.2</v>
@@ -4452,7 +4452,7 @@
         <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
         <v>10</v>
@@ -4580,7 +4580,7 @@
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16">
         <v>4.6</v>
@@ -4598,7 +4598,7 @@
         <v>1.48</v>
       </c>
       <c r="S16">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T16">
         <v>2.48</v>
@@ -4834,7 +4834,7 @@
         <v>2.58</v>
       </c>
       <c r="Q17">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="R17">
         <v>1.61</v>
@@ -4879,7 +4879,7 @@
         <v>38</v>
       </c>
       <c r="AF17">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG17">
         <v>11.5</v>
@@ -4903,7 +4903,7 @@
         <v>70</v>
       </c>
       <c r="AN17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO17">
         <v>27</v>
@@ -5046,13 +5046,13 @@
         <v>2.98</v>
       </c>
       <c r="G18">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H18">
         <v>2.26</v>
       </c>
       <c r="I18">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="J18">
         <v>3.3</v>
@@ -5067,34 +5067,34 @@
         <v>1.02</v>
       </c>
       <c r="N18">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P18">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="Q18">
         <v>1.56</v>
       </c>
       <c r="R18">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S18">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W18">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5112,7 +5112,7 @@
         <v>1000</v>
       </c>
       <c r="AC18">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AD18">
         <v>1000</v>
@@ -5154,22 +5154,22 @@
         <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
         <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
         <v>1.01</v>
@@ -5178,10 +5178,10 @@
         <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
         <v>1.01</v>
@@ -5199,10 +5199,10 @@
         <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5288,7 +5288,7 @@
         <v>4.2</v>
       </c>
       <c r="G19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H19">
         <v>1.83</v>
@@ -5315,7 +5315,7 @@
         <v>1.17</v>
       </c>
       <c r="P19">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q19">
         <v>1.5</v>
@@ -5324,7 +5324,7 @@
         <v>1.69</v>
       </c>
       <c r="S19">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T19">
         <v>1.54</v>
@@ -5336,10 +5336,10 @@
         <v>2.06</v>
       </c>
       <c r="W19">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X19">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y19">
         <v>15</v>
@@ -5372,7 +5372,7 @@
         <v>16</v>
       </c>
       <c r="AI19">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ19">
         <v>100</v>
@@ -5387,7 +5387,7 @@
         <v>65</v>
       </c>
       <c r="AN19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO19">
         <v>7.6</v>
@@ -5417,7 +5417,7 @@
         <v>14.5</v>
       </c>
       <c r="AX19">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY19">
         <v>15</v>
@@ -5429,19 +5429,19 @@
         <v>21</v>
       </c>
       <c r="BB19">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC19">
         <v>8.800000000000001</v>
       </c>
       <c r="BD19">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE19">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG19">
         <v>6.8</v>
@@ -5533,7 +5533,7 @@
         <v>1.96</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I20">
         <v>5.2</v>
@@ -5575,7 +5575,7 @@
         <v>1.88</v>
       </c>
       <c r="V20">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W20">
         <v>2.04</v>
@@ -5775,10 +5775,10 @@
         <v>1.22</v>
       </c>
       <c r="H21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I21">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="J21">
         <v>8.800000000000001</v>
@@ -5910,7 +5910,7 @@
         <v>18.5</v>
       </c>
       <c r="BA21">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB21">
         <v>9.800000000000001</v>
@@ -6011,7 +6011,7 @@
         <v>168</v>
       </c>
       <c r="F22">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -6035,7 +6035,7 @@
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O22">
         <v>1.27</v>
@@ -6044,13 +6044,13 @@
         <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R22">
         <v>1.37</v>
       </c>
       <c r="S22">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T22">
         <v>1.57</v>
@@ -6256,16 +6256,16 @@
         <v>1.07</v>
       </c>
       <c r="G23">
-        <v>110</v>
+        <v>1.7</v>
       </c>
       <c r="H23">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="I23">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J23">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K23">
         <v>880</v>
@@ -6277,13 +6277,13 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O23">
         <v>1.21</v>
       </c>
       <c r="P23">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q23">
         <v>1.21</v>
@@ -6295,10 +6295,10 @@
         <v>1.22</v>
       </c>
       <c r="T23">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
         <v>1.04</v>
@@ -6504,7 +6504,7 @@
         <v>1.02</v>
       </c>
       <c r="I24">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J24">
         <v>1.1</v>
@@ -6519,13 +6519,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O24">
         <v>1.2</v>
       </c>
       <c r="P24">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q24">
         <v>1.2</v>
@@ -6537,10 +6537,10 @@
         <v>1.21</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V24">
         <v>1.03</v>
@@ -6737,13 +6737,13 @@
         <v>171</v>
       </c>
       <c r="F25">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="G25">
         <v>110</v>
       </c>
       <c r="H25">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I25">
         <v>110</v>
@@ -6761,13 +6761,13 @@
         <v>1.01</v>
       </c>
       <c r="N25">
+        <v>1.26</v>
+      </c>
+      <c r="O25">
+        <v>1.3</v>
+      </c>
+      <c r="P25">
         <v>1.25</v>
-      </c>
-      <c r="O25">
-        <v>1.01</v>
-      </c>
-      <c r="P25">
-        <v>1.24</v>
       </c>
       <c r="Q25">
         <v>1.32</v>
@@ -6982,16 +6982,16 @@
         <v>1.06</v>
       </c>
       <c r="G26">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H26">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="I26">
         <v>990</v>
       </c>
       <c r="J26">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K26">
         <v>890</v>
@@ -7475,7 +7475,7 @@
         <v>1.7</v>
       </c>
       <c r="J28">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K28">
         <v>4.6</v>
@@ -7487,7 +7487,7 @@
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O28">
         <v>1.3</v>
@@ -7726,7 +7726,7 @@
         <v>1.31</v>
       </c>
       <c r="M29">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N29">
         <v>5</v>
@@ -7744,10 +7744,10 @@
         <v>1.53</v>
       </c>
       <c r="S29">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T29">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U29">
         <v>2.2</v>
@@ -7947,10 +7947,10 @@
         <v>176</v>
       </c>
       <c r="F30">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G30">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H30">
         <v>3.95</v>
@@ -7968,7 +7968,7 @@
         <v>1.38</v>
       </c>
       <c r="M30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N30">
         <v>3.95</v>
@@ -7998,7 +7998,7 @@
         <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X30">
         <v>16</v>
@@ -8022,7 +8022,7 @@
         <v>17</v>
       </c>
       <c r="AE30">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF30">
         <v>13</v>
@@ -8034,7 +8034,7 @@
         <v>19.5</v>
       </c>
       <c r="AI30">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AJ30">
         <v>25</v>
@@ -8189,19 +8189,19 @@
         <v>177</v>
       </c>
       <c r="F31">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G31">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H31">
         <v>3</v>
       </c>
       <c r="I31">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K31">
         <v>3.8</v>
@@ -8222,10 +8222,10 @@
         <v>2.06</v>
       </c>
       <c r="Q31">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R31">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S31">
         <v>3.05</v>
@@ -8234,7 +8234,7 @@
         <v>1.69</v>
       </c>
       <c r="U31">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V31">
         <v>1.44</v>
@@ -8455,22 +8455,22 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="O32">
         <v>1.19</v>
       </c>
       <c r="P32">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q32">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R32">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="S32">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T32">
         <v>1.54</v>
@@ -8685,7 +8685,7 @@
         <v>4</v>
       </c>
       <c r="J33">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K33">
         <v>3.65</v>
@@ -8697,7 +8697,7 @@
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O33">
         <v>1.32</v>
@@ -8781,40 +8781,40 @@
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AQ33">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AR33">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AS33">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AT33">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AU33">
         <v>1.41</v>
       </c>
       <c r="AV33">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AW33">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AX33">
-        <v>1.61</v>
+        <v>11</v>
       </c>
       <c r="AY33">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AZ33">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="BA33">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="BB33">
         <v>19</v>
@@ -8823,16 +8823,16 @@
         <v>16.5</v>
       </c>
       <c r="BD33">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BE33">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="BF33">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="BG33">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8915,22 +8915,22 @@
         <v>180</v>
       </c>
       <c r="F34">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G34">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="H34">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I34">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J34">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K34">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -8939,7 +8939,7 @@
         <v>1.04</v>
       </c>
       <c r="N34">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="O34">
         <v>1.2</v>
@@ -8948,13 +8948,13 @@
         <v>2.36</v>
       </c>
       <c r="Q34">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R34">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S34">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T34">
         <v>1.48</v>
@@ -8963,10 +8963,10 @@
         <v>2.44</v>
       </c>
       <c r="V34">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9026,7 +9026,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR34">
         <v>15.5</v>
@@ -9041,7 +9041,7 @@
         <v>7</v>
       </c>
       <c r="AV34">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW34">
         <v>18.5</v>
@@ -9071,10 +9071,10 @@
         <v>1.01</v>
       </c>
       <c r="BF34">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG34">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9157,7 +9157,7 @@
         <v>181</v>
       </c>
       <c r="F35">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G35">
         <v>3.05</v>
@@ -9181,13 +9181,13 @@
         <v>1.02</v>
       </c>
       <c r="N35">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O35">
         <v>1.26</v>
       </c>
       <c r="P35">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q35">
         <v>1.76</v>
@@ -9196,7 +9196,7 @@
         <v>1.4</v>
       </c>
       <c r="S35">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T35">
         <v>1.58</v>
@@ -9205,16 +9205,16 @@
         <v>2.24</v>
       </c>
       <c r="V35">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W35">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X35">
         <v>25</v>
       </c>
       <c r="Y35">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z35">
         <v>28</v>
@@ -9402,7 +9402,7 @@
         <v>2.26</v>
       </c>
       <c r="G36">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H36">
         <v>2.9</v>
@@ -9438,7 +9438,7 @@
         <v>1.47</v>
       </c>
       <c r="S36">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T36">
         <v>1.53</v>
@@ -9450,7 +9450,7 @@
         <v>1.43</v>
       </c>
       <c r="W36">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9895,10 +9895,10 @@
         <v>7.4</v>
       </c>
       <c r="J38">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K38">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -9907,7 +9907,7 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="O38">
         <v>1.15</v>
@@ -9931,7 +9931,7 @@
         <v>2.2</v>
       </c>
       <c r="V38">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W38">
         <v>2.56</v>
@@ -10039,7 +10039,7 @@
         <v>1.01</v>
       </c>
       <c r="BF38">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG38">
         <v>1.01</v>
@@ -10367,19 +10367,19 @@
         <v>186</v>
       </c>
       <c r="F40">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G40">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H40">
+        <v>1.29</v>
+      </c>
+      <c r="I40">
         <v>1.3</v>
       </c>
-      <c r="I40">
-        <v>1.31</v>
-      </c>
       <c r="J40">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K40">
         <v>7</v>
@@ -10415,10 +10415,10 @@
         <v>2.3</v>
       </c>
       <c r="V40">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="W40">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
         <v>46</v>
@@ -10445,7 +10445,7 @@
         <v>11.5</v>
       </c>
       <c r="AF40">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="AG40">
         <v>40</v>
@@ -10457,10 +10457,10 @@
         <v>27</v>
       </c>
       <c r="AJ40">
-        <v>390</v>
+        <v>490</v>
       </c>
       <c r="AK40">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="AL40">
         <v>95</v>
@@ -10469,13 +10469,13 @@
         <v>95</v>
       </c>
       <c r="AN40">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO40">
         <v>3.4</v>
       </c>
       <c r="AP40">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ40">
         <v>14</v>
@@ -10487,10 +10487,10 @@
         <v>10.5</v>
       </c>
       <c r="AT40">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AU40">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV40">
         <v>11</v>
@@ -10505,7 +10505,7 @@
         <v>34</v>
       </c>
       <c r="AZ40">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA40">
         <v>23</v>
@@ -10517,7 +10517,7 @@
         <v>44</v>
       </c>
       <c r="BD40">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BE40">
         <v>75</v>
@@ -10526,7 +10526,7 @@
         <v>42</v>
       </c>
       <c r="BG40">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BH40">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -625,7 +625,7 @@
     <t>Deportes Temuco</t>
   </si>
   <si>
-    <t>2026-09-14 01:45:40</t>
+    <t>2026-09-14 04:00:46</t>
   </si>
 </sst>
 </file>
@@ -1246,10 +1246,10 @@
         <v>2.84</v>
       </c>
       <c r="O2">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q2">
         <v>2.58</v>
@@ -1261,13 +1261,13 @@
         <v>5.3</v>
       </c>
       <c r="T2">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="U2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W2">
         <v>3</v>
@@ -1285,7 +1285,7 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
@@ -1294,7 +1294,7 @@
         <v>55</v>
       </c>
       <c r="AE2">
-        <v>640</v>
+        <v>550</v>
       </c>
       <c r="AF2">
         <v>6.6</v>
@@ -1303,13 +1303,13 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI2">
-        <v>630</v>
+        <v>540</v>
       </c>
       <c r="AJ2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK2">
         <v>24</v>
@@ -1318,7 +1318,7 @@
         <v>85</v>
       </c>
       <c r="AM2">
-        <v>630</v>
+        <v>540</v>
       </c>
       <c r="AN2">
         <v>12</v>
@@ -1336,7 +1336,7 @@
         <v>36</v>
       </c>
       <c r="AS2">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="AT2">
         <v>5</v>
@@ -1345,7 +1345,7 @@
         <v>9.4</v>
       </c>
       <c r="AV2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW2">
         <v>50</v>
@@ -1360,7 +1360,7 @@
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>11</v>
@@ -1372,7 +1372,7 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="BF2">
         <v>10.5</v>
@@ -1381,64 +1381,64 @@
         <v>60</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI2">
-        <v>1.35</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BK2">
-        <v>1.49</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BO2">
-        <v>1.49</v>
+        <v>3.2</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ2">
-        <v>1.49</v>
+        <v>5.6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BU2">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="s">
         <v>203</v>
@@ -1461,13 +1461,13 @@
         <v>160</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G3">
         <v>2.88</v>
       </c>
       <c r="H3">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -1476,7 +1476,7 @@
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
         <v>1.53</v>
@@ -1485,7 +1485,7 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>1.48</v>
@@ -1497,10 +1497,10 @@
         <v>2.46</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
         <v>2.04</v>
@@ -1608,7 +1608,7 @@
         <v>6.4</v>
       </c>
       <c r="BC3">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BD3">
         <v>6.6</v>
@@ -1623,64 +1623,64 @@
         <v>6.4</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI3">
-        <v>1.35</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>1.15</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.15</v>
+        <v>15</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>1.15</v>
+        <v>5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.15</v>
+        <v>12</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU3">
-        <v>1.83</v>
+        <v>5.2</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.15</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.15</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
         <v>203</v>
@@ -1703,7 +1703,7 @@
         <v>161</v>
       </c>
       <c r="F4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G4">
         <v>1.43</v>
@@ -1712,40 +1712,40 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P4">
         <v>2.02</v>
       </c>
       <c r="Q4">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U4">
         <v>1.72</v>
@@ -1754,7 +1754,7 @@
         <v>1.1</v>
       </c>
       <c r="W4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="X4">
         <v>19</v>
@@ -1766,19 +1766,19 @@
         <v>120</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AB4">
         <v>7.4</v>
       </c>
       <c r="AC4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD4">
         <v>40</v>
       </c>
       <c r="AE4">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AF4">
         <v>8.199999999999999</v>
@@ -1808,19 +1808,19 @@
         <v>7.4</v>
       </c>
       <c r="AO4">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AP4">
         <v>14.5</v>
       </c>
       <c r="AQ4">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
@@ -1829,10 +1829,10 @@
         <v>10</v>
       </c>
       <c r="AV4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4">
         <v>7</v>
@@ -1841,13 +1841,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC4">
         <v>14.5</v>
@@ -1856,19 +1856,19 @@
         <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4">
         <v>6.6</v>
       </c>
       <c r="BG4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH4">
         <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
         <v>14</v>
@@ -1922,7 +1922,7 @@
         <v>17.5</v>
       </c>
       <c r="CA4">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB4" t="s">
         <v>203</v>
@@ -1948,7 +1948,7 @@
         <v>1.97</v>
       </c>
       <c r="G5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -1978,7 +1978,7 @@
         <v>2.14</v>
       </c>
       <c r="Q5">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R5">
         <v>1.45</v>
@@ -1996,7 +1996,7 @@
         <v>1.31</v>
       </c>
       <c r="W5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X5">
         <v>17.5</v>
@@ -2005,10 +2005,10 @@
         <v>17</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB5">
         <v>10.5</v>
@@ -2029,25 +2029,25 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK5">
         <v>21</v>
       </c>
       <c r="AL5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO5">
         <v>55</v>
@@ -2059,22 +2059,22 @@
         <v>14.5</v>
       </c>
       <c r="AR5">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="AS5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT5">
         <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV5">
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
@@ -2086,7 +2086,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB5">
         <v>20</v>
@@ -2095,28 +2095,28 @@
         <v>17.5</v>
       </c>
       <c r="BD5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE5">
+        <v>12</v>
+      </c>
+      <c r="BF5">
+        <v>9</v>
+      </c>
+      <c r="BG5">
+        <v>11</v>
+      </c>
+      <c r="BH5">
+        <v>4.2</v>
+      </c>
+      <c r="BI5">
+        <v>3.4</v>
+      </c>
+      <c r="BJ5">
         <v>9.4</v>
       </c>
-      <c r="BE5">
-        <v>11.5</v>
-      </c>
-      <c r="BF5">
-        <v>11</v>
-      </c>
-      <c r="BG5">
-        <v>10</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>3.1</v>
-      </c>
-      <c r="BJ5">
-        <v>12.5</v>
-      </c>
       <c r="BK5">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2125,46 +2125,46 @@
         <v>21</v>
       </c>
       <c r="BN5">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
+        <v>14</v>
+      </c>
+      <c r="BQ5">
+        <v>11.5</v>
+      </c>
+      <c r="BR5">
+        <v>26</v>
+      </c>
+      <c r="BS5">
+        <v>22</v>
+      </c>
+      <c r="BT5">
+        <v>8.4</v>
+      </c>
+      <c r="BU5">
+        <v>6.6</v>
+      </c>
+      <c r="BV5">
+        <v>32</v>
+      </c>
+      <c r="BW5">
+        <v>27</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>34</v>
+      </c>
+      <c r="BZ5">
+        <v>21</v>
+      </c>
+      <c r="CA5">
         <v>18</v>
-      </c>
-      <c r="BQ5">
-        <v>10</v>
-      </c>
-      <c r="BR5">
-        <v>36</v>
-      </c>
-      <c r="BS5">
-        <v>16.5</v>
-      </c>
-      <c r="BT5">
-        <v>10</v>
-      </c>
-      <c r="BU5">
-        <v>6</v>
-      </c>
-      <c r="BV5">
-        <v>46</v>
-      </c>
-      <c r="BW5">
-        <v>20</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>21</v>
-      </c>
-      <c r="BZ5">
-        <v>29</v>
-      </c>
-      <c r="CA5">
-        <v>13.5</v>
       </c>
       <c r="CB5" t="s">
         <v>203</v>
@@ -2196,10 +2196,10 @@
         <v>2.08</v>
       </c>
       <c r="I6">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J6">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K6">
         <v>3.15</v>
@@ -2211,13 +2211,13 @@
         <v>1.16</v>
       </c>
       <c r="N6">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O6">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -2235,7 +2235,7 @@
         <v>1.63</v>
       </c>
       <c r="V6">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W6">
         <v>1.24</v>
@@ -2247,7 +2247,7 @@
         <v>6.2</v>
       </c>
       <c r="Z6">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA6">
         <v>36</v>
@@ -2259,7 +2259,7 @@
         <v>9</v>
       </c>
       <c r="AD6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE6">
         <v>36</v>
@@ -2268,7 +2268,7 @@
         <v>36</v>
       </c>
       <c r="AG6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH6">
         <v>32</v>
@@ -2298,28 +2298,28 @@
         <v>6.4</v>
       </c>
       <c r="AQ6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR6">
         <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT6">
         <v>9.800000000000001</v>
       </c>
       <c r="AU6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV6">
         <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY6">
         <v>17.5</v>
@@ -2328,25 +2328,25 @@
         <v>21</v>
       </c>
       <c r="BA6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG6">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH6">
         <v>2.82</v>
@@ -2429,22 +2429,22 @@
         <v>164</v>
       </c>
       <c r="F7">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G7">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H7">
         <v>3.95</v>
       </c>
       <c r="I7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
       <c r="K7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2453,10 +2453,10 @@
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O7">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P7">
         <v>1.52</v>
@@ -2474,7 +2474,7 @@
         <v>2.16</v>
       </c>
       <c r="U7">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V7">
         <v>1.29</v>
@@ -2486,13 +2486,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA7">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB7">
         <v>7.2</v>
@@ -2501,10 +2501,10 @@
         <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF7">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         <v>26</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ7">
         <v>34</v>
@@ -2531,13 +2531,13 @@
         <v>240</v>
       </c>
       <c r="AN7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO7">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7">
         <v>9.4</v>
@@ -2546,7 +2546,7 @@
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
@@ -2558,19 +2558,19 @@
         <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB7">
         <v>24</v>
@@ -2579,16 +2579,16 @@
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF7">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BG7">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2671,19 +2671,19 @@
         <v>165</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G8">
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2719,10 +2719,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2913,226 +2913,226 @@
         <v>166</v>
       </c>
       <c r="F9">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="G9">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J9">
         <v>3.75</v>
       </c>
       <c r="K9">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
+        <v>1.29</v>
+      </c>
+      <c r="P9">
+        <v>2.04</v>
+      </c>
+      <c r="Q9">
+        <v>1.86</v>
+      </c>
+      <c r="R9">
+        <v>1.4</v>
+      </c>
+      <c r="S9">
+        <v>3.2</v>
+      </c>
+      <c r="T9">
+        <v>1.77</v>
+      </c>
+      <c r="U9">
+        <v>2.14</v>
+      </c>
+      <c r="V9">
         <v>1.28</v>
-      </c>
-      <c r="P9">
-        <v>2</v>
-      </c>
-      <c r="Q9">
-        <v>1.77</v>
-      </c>
-      <c r="R9">
-        <v>1.36</v>
-      </c>
-      <c r="S9">
-        <v>3</v>
-      </c>
-      <c r="T9">
-        <v>1.75</v>
-      </c>
-      <c r="U9">
-        <v>2.04</v>
-      </c>
-      <c r="V9">
-        <v>1.27</v>
       </c>
       <c r="W9">
         <v>2.02</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB9">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF9">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN9">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH9">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BI9">
         <v>3.05</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK9">
-        <v>1.77</v>
+        <v>3.45</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.29</v>
+        <v>4.5</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO9">
-        <v>1.33</v>
+        <v>3.8</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ9">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS9">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU9">
-        <v>1.29</v>
+        <v>5.9</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW9">
-        <v>1.29</v>
+        <v>4.2</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.29</v>
+        <v>4.3</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA9">
-        <v>1.29</v>
+        <v>3.95</v>
       </c>
       <c r="CB9" t="s">
         <v>203</v>
@@ -3161,7 +3161,7 @@
         <v>4.5</v>
       </c>
       <c r="H10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="I10">
         <v>1.93</v>
@@ -3191,10 +3191,10 @@
         <v>1.5</v>
       </c>
       <c r="R10">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S10">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T10">
         <v>1.54</v>
@@ -3209,7 +3209,7 @@
         <v>1.28</v>
       </c>
       <c r="X10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y10">
         <v>15</v>
@@ -3236,19 +3236,19 @@
         <v>40</v>
       </c>
       <c r="AG10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH10">
         <v>16</v>
       </c>
       <c r="AI10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ10">
         <v>100</v>
       </c>
       <c r="AK10">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL10">
         <v>44</v>
@@ -3257,7 +3257,7 @@
         <v>65</v>
       </c>
       <c r="AN10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO10">
         <v>7.8</v>
@@ -3266,7 +3266,7 @@
         <v>20</v>
       </c>
       <c r="AQ10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR10">
         <v>13</v>
@@ -3320,61 +3320,61 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
+        <v>1.77</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.2</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.76</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.2</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.2</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
         <v>1.54</v>
       </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.72</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
-        <v>1.72</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
-        <v>1.72</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>1.72</v>
-      </c>
-      <c r="BT10">
-        <v>1000</v>
-      </c>
-      <c r="BU10">
-        <v>1.35</v>
-      </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="CB10" t="s">
         <v>203</v>
@@ -3397,16 +3397,16 @@
         <v>168</v>
       </c>
       <c r="F11">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I11">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3415,31 +3415,31 @@
         <v>4.4</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O11">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P11">
         <v>2.58</v>
       </c>
       <c r="Q11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R11">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S11">
         <v>2.44</v>
       </c>
       <c r="T11">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U11">
         <v>2.56</v>
@@ -3448,10 +3448,10 @@
         <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y11">
         <v>21</v>
@@ -3466,7 +3466,7 @@
         <v>14.5</v>
       </c>
       <c r="AC11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD11">
         <v>16.5</v>
@@ -3499,7 +3499,7 @@
         <v>70</v>
       </c>
       <c r="AN11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO11">
         <v>27</v>
@@ -3511,10 +3511,10 @@
         <v>17</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT11">
         <v>12</v>
@@ -3526,31 +3526,31 @@
         <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX11">
         <v>13.5</v>
       </c>
       <c r="AY11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
         <v>13.5</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB11">
         <v>19</v>
       </c>
       <c r="BC11">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD11">
         <v>20</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF11">
         <v>8.4</v>
@@ -3562,13 +3562,13 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3580,7 +3580,7 @@
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP11">
         <v>1000</v>
@@ -3598,7 +3598,7 @@
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -3639,40 +3639,40 @@
         <v>169</v>
       </c>
       <c r="F12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G12">
         <v>1.57</v>
       </c>
       <c r="H12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
         <v>4.5</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M12">
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O12">
         <v>1.27</v>
       </c>
       <c r="P12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R12">
         <v>1.44</v>
@@ -3681,34 +3681,34 @@
         <v>3.05</v>
       </c>
       <c r="T12">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U12">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W12">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X12">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z12">
-        <v>65</v>
+        <v>400</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
         <v>27</v>
@@ -3717,7 +3717,7 @@
         <v>130</v>
       </c>
       <c r="AF12">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
@@ -3729,13 +3729,13 @@
         <v>110</v>
       </c>
       <c r="AJ12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK12">
         <v>18</v>
       </c>
       <c r="AL12">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM12">
         <v>140</v>
@@ -3747,10 +3747,10 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR12">
         <v>29</v>
@@ -3762,10 +3762,10 @@
         <v>7.8</v>
       </c>
       <c r="AU12">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV12">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW12">
         <v>38</v>
@@ -3774,7 +3774,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12">
         <v>20</v>
@@ -3789,22 +3789,22 @@
         <v>13.5</v>
       </c>
       <c r="BD12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE12">
         <v>42</v>
       </c>
       <c r="BF12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG12">
         <v>42</v>
       </c>
       <c r="BH12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI12">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ12">
         <v>13</v>
@@ -3831,7 +3831,7 @@
         <v>3.4</v>
       </c>
       <c r="BR12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS12">
         <v>4.1</v>
@@ -3855,10 +3855,10 @@
         <v>4.5</v>
       </c>
       <c r="BZ12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA12">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CB12" t="s">
         <v>203</v>
@@ -3971,7 +3971,7 @@
         <v>55</v>
       </c>
       <c r="AJ13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK13">
         <v>25</v>
@@ -4004,7 +4004,7 @@
         <v>9</v>
       </c>
       <c r="AU13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV13">
         <v>13.5</v>
@@ -4058,7 +4058,7 @@
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>2.72</v>
+        <v>28</v>
       </c>
       <c r="BN13">
         <v>1000</v>
@@ -4076,7 +4076,7 @@
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>2.72</v>
+        <v>12.5</v>
       </c>
       <c r="BT13">
         <v>1000</v>
@@ -4088,19 +4088,19 @@
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>2.72</v>
+        <v>11.5</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>2.72</v>
+        <v>15.5</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>2.72</v>
+        <v>11</v>
       </c>
       <c r="CB13" t="s">
         <v>203</v>
@@ -4123,226 +4123,226 @@
         <v>171</v>
       </c>
       <c r="F14">
+        <v>2.66</v>
+      </c>
+      <c r="G14">
+        <v>2.8</v>
+      </c>
+      <c r="H14">
         <v>2.56</v>
       </c>
-      <c r="G14">
-        <v>3.1</v>
-      </c>
-      <c r="H14">
-        <v>2.4</v>
-      </c>
       <c r="I14">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K14">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M14">
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R14">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S14">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="T14">
         <v>1.59</v>
       </c>
       <c r="U14">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="V14">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W14">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC14">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14">
+        <v>12.5</v>
+      </c>
+      <c r="AE14">
+        <v>25</v>
+      </c>
+      <c r="AF14">
+        <v>21</v>
+      </c>
+      <c r="AG14">
+        <v>13</v>
+      </c>
+      <c r="AH14">
+        <v>15.5</v>
+      </c>
+      <c r="AI14">
+        <v>46</v>
+      </c>
+      <c r="AJ14">
+        <v>55</v>
+      </c>
+      <c r="AK14">
+        <v>27</v>
+      </c>
+      <c r="AL14">
         <v>34</v>
       </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>1000</v>
-      </c>
-      <c r="AG14">
+      <c r="AM14">
+        <v>85</v>
+      </c>
+      <c r="AN14">
+        <v>17.5</v>
+      </c>
+      <c r="AO14">
+        <v>16</v>
+      </c>
+      <c r="AP14">
+        <v>19</v>
+      </c>
+      <c r="AQ14">
+        <v>13</v>
+      </c>
+      <c r="AR14">
+        <v>17.5</v>
+      </c>
+      <c r="AS14">
+        <v>10.5</v>
+      </c>
+      <c r="AT14">
+        <v>13</v>
+      </c>
+      <c r="AU14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV14">
+        <v>11</v>
+      </c>
+      <c r="AW14">
+        <v>16.5</v>
+      </c>
+      <c r="AX14">
+        <v>18</v>
+      </c>
+      <c r="AY14">
+        <v>11</v>
+      </c>
+      <c r="AZ14">
+        <v>13.5</v>
+      </c>
+      <c r="BA14">
+        <v>10</v>
+      </c>
+      <c r="BB14">
+        <v>10.5</v>
+      </c>
+      <c r="BC14">
+        <v>16.5</v>
+      </c>
+      <c r="BD14">
+        <v>20</v>
+      </c>
+      <c r="BE14">
+        <v>11.5</v>
+      </c>
+      <c r="BF14">
+        <v>15</v>
+      </c>
+      <c r="BG14">
+        <v>14</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>3.35</v>
+      </c>
+      <c r="BJ14">
+        <v>11.5</v>
+      </c>
+      <c r="BK14">
+        <v>5.6</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>21</v>
+      </c>
+      <c r="BN14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO14">
+        <v>4.7</v>
+      </c>
+      <c r="BP14">
+        <v>26</v>
+      </c>
+      <c r="BQ14">
+        <v>12</v>
+      </c>
+      <c r="BR14">
         <v>38</v>
       </c>
-      <c r="AH14">
-        <v>1000</v>
-      </c>
-      <c r="AI14">
-        <v>1000</v>
-      </c>
-      <c r="AJ14">
-        <v>1000</v>
-      </c>
-      <c r="AK14">
-        <v>1000</v>
-      </c>
-      <c r="AL14">
-        <v>1000</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>1000</v>
-      </c>
-      <c r="AO14">
-        <v>48</v>
-      </c>
-      <c r="AP14">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14">
-        <v>1.01</v>
-      </c>
-      <c r="AR14">
-        <v>1.01</v>
-      </c>
-      <c r="AS14">
-        <v>1.01</v>
-      </c>
-      <c r="AT14">
-        <v>1.01</v>
-      </c>
-      <c r="AU14">
-        <v>1.01</v>
-      </c>
-      <c r="AV14">
-        <v>1.01</v>
-      </c>
-      <c r="AW14">
-        <v>1.01</v>
-      </c>
-      <c r="AX14">
-        <v>1.01</v>
-      </c>
-      <c r="AY14">
-        <v>1.01</v>
-      </c>
-      <c r="AZ14">
-        <v>1.01</v>
-      </c>
-      <c r="BA14">
-        <v>1.01</v>
-      </c>
-      <c r="BB14">
-        <v>1.01</v>
-      </c>
-      <c r="BC14">
-        <v>1.01</v>
-      </c>
-      <c r="BD14">
-        <v>1.01</v>
-      </c>
-      <c r="BE14">
-        <v>1.01</v>
-      </c>
-      <c r="BF14">
-        <v>1.01</v>
-      </c>
-      <c r="BG14">
-        <v>1.01</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.01</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.01</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.01</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.01</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.01</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB14" t="s">
         <v>203</v>
@@ -4368,19 +4368,19 @@
         <v>2.98</v>
       </c>
       <c r="G15">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H15">
         <v>2.24</v>
       </c>
       <c r="I15">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="J15">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4389,31 +4389,31 @@
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="O15">
         <v>1.19</v>
       </c>
       <c r="P15">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R15">
         <v>1.55</v>
       </c>
       <c r="S15">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T15">
         <v>1.47</v>
       </c>
       <c r="U15">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V15">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
         <v>1.41</v>
@@ -4437,7 +4437,7 @@
         <v>970</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE15">
         <v>1000</v>
@@ -4470,61 +4470,61 @@
         <v>1000</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP15">
+        <v>1.15</v>
+      </c>
+      <c r="AQ15">
+        <v>1.15</v>
+      </c>
+      <c r="AR15">
+        <v>1.15</v>
+      </c>
+      <c r="AS15">
+        <v>1.15</v>
+      </c>
+      <c r="AT15">
+        <v>1.15</v>
+      </c>
+      <c r="AU15">
         <v>1.06</v>
       </c>
-      <c r="AQ15">
-        <v>1.06</v>
-      </c>
-      <c r="AR15">
-        <v>1.06</v>
-      </c>
-      <c r="AS15">
-        <v>1.06</v>
-      </c>
-      <c r="AT15">
-        <v>1.06</v>
-      </c>
-      <c r="AU15">
-        <v>1.01</v>
-      </c>
       <c r="AV15">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AW15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AX15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AY15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AZ15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BA15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BB15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BC15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BD15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BE15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BF15">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BG15">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4607,7 +4607,7 @@
         <v>173</v>
       </c>
       <c r="F16">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G16">
         <v>2.92</v>
@@ -4622,7 +4622,7 @@
         <v>3.9</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4637,7 +4637,7 @@
         <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q16">
         <v>1.51</v>
@@ -4649,7 +4649,7 @@
         <v>2.26</v>
       </c>
       <c r="T16">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U16">
         <v>2.68</v>
@@ -4661,112 +4661,112 @@
         <v>1.52</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y16">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB16">
         <v>22</v>
       </c>
       <c r="AC16">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH16">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI16">
         <v>36</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL16">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN16">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP16">
-        <v>1.67</v>
+        <v>20</v>
       </c>
       <c r="AQ16">
-        <v>1.55</v>
+        <v>14.5</v>
       </c>
       <c r="AR16">
+        <v>17.5</v>
+      </c>
+      <c r="AS16">
+        <v>4.7</v>
+      </c>
+      <c r="AT16">
+        <v>15</v>
+      </c>
+      <c r="AU16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16">
+        <v>10.5</v>
+      </c>
+      <c r="AW16">
+        <v>19.5</v>
+      </c>
+      <c r="AX16">
         <v>16.5</v>
       </c>
-      <c r="AS16">
-        <v>1.67</v>
-      </c>
-      <c r="AT16">
-        <v>1.55</v>
-      </c>
-      <c r="AU16">
-        <v>7.2</v>
-      </c>
-      <c r="AV16">
-        <v>9</v>
-      </c>
-      <c r="AW16">
-        <v>16</v>
-      </c>
-      <c r="AX16">
-        <v>1.67</v>
-      </c>
       <c r="AY16">
-        <v>1.51</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BA16">
         <v>19</v>
       </c>
       <c r="BB16">
-        <v>1.67</v>
+        <v>4.7</v>
       </c>
       <c r="BC16">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BD16">
-        <v>1.6</v>
+        <v>20</v>
       </c>
       <c r="BE16">
-        <v>1.67</v>
+        <v>4.9</v>
       </c>
       <c r="BF16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG16">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4858,34 +4858,34 @@
         <v>17.5</v>
       </c>
       <c r="I17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J17">
         <v>6.4</v>
       </c>
       <c r="K17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P17">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q17">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R17">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S17">
         <v>2.82</v>
@@ -4897,7 +4897,7 @@
         <v>1.6</v>
       </c>
       <c r="V17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W17">
         <v>4.7</v>
@@ -4915,7 +4915,7 @@
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>16</v>
@@ -4939,7 +4939,7 @@
         <v>330</v>
       </c>
       <c r="AJ17">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AK17">
         <v>16.5</v>
@@ -4960,37 +4960,37 @@
         <v>18</v>
       </c>
       <c r="AQ17">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR17">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS17">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU17">
         <v>13</v>
       </c>
       <c r="AV17">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW17">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX17">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY17">
         <v>10.5</v>
       </c>
       <c r="AZ17">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA17">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB17">
         <v>7.6</v>
@@ -4999,70 +4999,70 @@
         <v>13.5</v>
       </c>
       <c r="BD17">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BE17">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG17">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH17">
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5091,19 +5091,19 @@
         <v>175</v>
       </c>
       <c r="F18">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G18">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I18">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K18">
         <v>3.35</v>
@@ -5112,145 +5112,145 @@
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N18">
         <v>2.58</v>
       </c>
       <c r="O18">
+        <v>1.56</v>
+      </c>
+      <c r="P18">
         <v>1.53</v>
       </c>
-      <c r="P18">
-        <v>1.55</v>
-      </c>
       <c r="Q18">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R18">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="S18">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="T18">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="U18">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="V18">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W18">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X18">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="Y18">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB18">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="AC18">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF18">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG18">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP18">
-        <v>1.52</v>
+        <v>7.4</v>
       </c>
       <c r="AQ18">
-        <v>1.64</v>
+        <v>10.5</v>
       </c>
       <c r="AR18">
-        <v>1.74</v>
+        <v>6.2</v>
       </c>
       <c r="AS18">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="AT18">
-        <v>1.46</v>
+        <v>5.9</v>
       </c>
       <c r="AU18">
-        <v>1.47</v>
+        <v>6.6</v>
       </c>
       <c r="AV18">
-        <v>1.74</v>
+        <v>17.5</v>
       </c>
       <c r="AW18">
-        <v>1.74</v>
+        <v>7</v>
       </c>
       <c r="AX18">
-        <v>1.59</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY18">
-        <v>1.62</v>
+        <v>10</v>
       </c>
       <c r="AZ18">
-        <v>1.74</v>
+        <v>20</v>
       </c>
       <c r="BA18">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="BB18">
-        <v>1.74</v>
+        <v>21</v>
       </c>
       <c r="BC18">
-        <v>1.74</v>
+        <v>21</v>
       </c>
       <c r="BD18">
-        <v>1.74</v>
+        <v>6.8</v>
       </c>
       <c r="BE18">
-        <v>1.74</v>
+        <v>7.4</v>
       </c>
       <c r="BF18">
-        <v>1.74</v>
+        <v>19.5</v>
       </c>
       <c r="BG18">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="BH18">
         <v>3.1</v>
@@ -5262,55 +5262,55 @@
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="CB18" t="s">
         <v>203</v>
@@ -5333,166 +5333,166 @@
         <v>176</v>
       </c>
       <c r="F19">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="G19">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="H19">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="I19">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K19">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="L19">
         <v>1.27</v>
       </c>
       <c r="M19">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N19">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P19">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q19">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R19">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S19">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T19">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="U19">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="V19">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W19">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN19">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5575,22 +5575,22 @@
         <v>177</v>
       </c>
       <c r="F20">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="G20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H20">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="I20">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="J20">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L20">
         <v>1.15</v>
@@ -5599,34 +5599,34 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O20">
         <v>1.08</v>
       </c>
       <c r="P20">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q20">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="R20">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="S20">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="T20">
         <v>1.8</v>
       </c>
       <c r="U20">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
         <v>1.06</v>
       </c>
       <c r="W20">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>80</v>
@@ -5638,28 +5638,28 @@
         <v>200</v>
       </c>
       <c r="AA20">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
         <v>23</v>
       </c>
       <c r="AC20">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AD20">
         <v>65</v>
       </c>
       <c r="AE20">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH20">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AI20">
         <v>140</v>
@@ -5677,34 +5677,34 @@
         <v>130</v>
       </c>
       <c r="AN20">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="AO20">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AQ20">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS20">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW20">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AX20">
         <v>11</v>
@@ -5716,85 +5716,85 @@
         <v>18.5</v>
       </c>
       <c r="BA20">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB20">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC20">
         <v>11.5</v>
       </c>
       <c r="BD20">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE20">
+        <v>9</v>
+      </c>
+      <c r="BF20">
+        <v>2.26</v>
+      </c>
+      <c r="BG20">
+        <v>10</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.65</v>
+      </c>
+      <c r="BJ20">
+        <v>17.5</v>
+      </c>
+      <c r="BK20">
+        <v>2.04</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>2.3</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>3.65</v>
+      </c>
+      <c r="BP20">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF20">
-        <v>2.42</v>
-      </c>
-      <c r="BG20">
-        <v>9</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.22</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.22</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.22</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.01</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
       <c r="BQ20">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS20">
-        <v>1.22</v>
+        <v>2.1</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BU20">
-        <v>1.22</v>
+        <v>2.12</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.22</v>
+        <v>2.3</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.22</v>
+        <v>2.26</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="CA20">
-        <v>1.22</v>
+        <v>3.55</v>
       </c>
       <c r="CB20" t="s">
         <v>203</v>
@@ -5817,10 +5817,10 @@
         <v>178</v>
       </c>
       <c r="F21">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G21">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H21">
         <v>5.1</v>
@@ -5829,7 +5829,7 @@
         <v>5.2</v>
       </c>
       <c r="J21">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21">
         <v>3.5</v>
@@ -5847,10 +5847,10 @@
         <v>1.44</v>
       </c>
       <c r="P21">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q21">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R21">
         <v>1.26</v>
@@ -5859,7 +5859,7 @@
         <v>4.5</v>
       </c>
       <c r="T21">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U21">
         <v>1.88</v>
@@ -5868,19 +5868,19 @@
         <v>1.23</v>
       </c>
       <c r="W21">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X21">
         <v>10.5</v>
       </c>
       <c r="Y21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z21">
         <v>36</v>
       </c>
       <c r="AA21">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB21">
         <v>7.4</v>
@@ -5889,10 +5889,10 @@
         <v>7.6</v>
       </c>
       <c r="AD21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE21">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF21">
         <v>10.5</v>
@@ -5904,7 +5904,7 @@
         <v>23</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ21">
         <v>22</v>
@@ -5913,7 +5913,7 @@
         <v>24</v>
       </c>
       <c r="AL21">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM21">
         <v>170</v>
@@ -5961,7 +5961,7 @@
         <v>70</v>
       </c>
       <c r="BB21">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC21">
         <v>21</v>
@@ -5970,73 +5970,73 @@
         <v>42</v>
       </c>
       <c r="BE21">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF21">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG21">
         <v>90</v>
       </c>
       <c r="BH21">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BI21">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK21">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2.82</v>
+        <v>32</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO21">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ21">
-        <v>2.82</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS21">
-        <v>2.82</v>
+        <v>11.5</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU21">
-        <v>2.26</v>
+        <v>7.2</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW21">
-        <v>2.82</v>
+        <v>13</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY21">
-        <v>2.82</v>
+        <v>14</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA21">
-        <v>2.82</v>
+        <v>11.5</v>
       </c>
       <c r="CB21" t="s">
         <v>203</v>
@@ -6059,22 +6059,22 @@
         <v>179</v>
       </c>
       <c r="F22">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G22">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H22">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I22">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J22">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6083,142 +6083,142 @@
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O22">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q22">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R22">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S22">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T22">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U22">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V22">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W22">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y22">
+        <v>15.5</v>
+      </c>
+      <c r="Z22">
+        <v>19.5</v>
+      </c>
+      <c r="AA22">
+        <v>42</v>
+      </c>
+      <c r="AB22">
+        <v>16</v>
+      </c>
+      <c r="AC22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD22">
+        <v>13</v>
+      </c>
+      <c r="AE22">
+        <v>30</v>
+      </c>
+      <c r="AF22">
+        <v>21</v>
+      </c>
+      <c r="AG22">
+        <v>13.5</v>
+      </c>
+      <c r="AH22">
+        <v>17</v>
+      </c>
+      <c r="AI22">
+        <v>40</v>
+      </c>
+      <c r="AJ22">
         <v>44</v>
       </c>
-      <c r="Z22">
-        <v>1000</v>
-      </c>
-      <c r="AA22">
-        <v>1000</v>
-      </c>
-      <c r="AB22">
+      <c r="AK22">
+        <v>30</v>
+      </c>
+      <c r="AL22">
         <v>40</v>
       </c>
-      <c r="AC22">
-        <v>970</v>
-      </c>
-      <c r="AD22">
+      <c r="AM22">
+        <v>80</v>
+      </c>
+      <c r="AN22">
+        <v>23</v>
+      </c>
+      <c r="AO22">
+        <v>22</v>
+      </c>
+      <c r="AP22">
+        <v>14.5</v>
+      </c>
+      <c r="AQ22">
+        <v>10.5</v>
+      </c>
+      <c r="AR22">
+        <v>16</v>
+      </c>
+      <c r="AS22">
+        <v>32</v>
+      </c>
+      <c r="AT22">
+        <v>11</v>
+      </c>
+      <c r="AU22">
+        <v>7.2</v>
+      </c>
+      <c r="AV22">
+        <v>10.5</v>
+      </c>
+      <c r="AW22">
+        <v>23</v>
+      </c>
+      <c r="AX22">
+        <v>16.5</v>
+      </c>
+      <c r="AY22">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22">
+        <v>13.5</v>
+      </c>
+      <c r="BA22">
+        <v>30</v>
+      </c>
+      <c r="BB22">
         <v>34</v>
       </c>
-      <c r="AE22">
-        <v>1000</v>
-      </c>
-      <c r="AF22">
-        <v>1000</v>
-      </c>
-      <c r="AG22">
-        <v>34</v>
-      </c>
-      <c r="AH22">
-        <v>1000</v>
-      </c>
-      <c r="AI22">
-        <v>1000</v>
-      </c>
-      <c r="AJ22">
-        <v>1000</v>
-      </c>
-      <c r="AK22">
-        <v>1000</v>
-      </c>
-      <c r="AL22">
-        <v>1000</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>1000</v>
-      </c>
-      <c r="AO22">
-        <v>1000</v>
-      </c>
-      <c r="AP22">
-        <v>1.01</v>
-      </c>
-      <c r="AQ22">
-        <v>1.01</v>
-      </c>
-      <c r="AR22">
-        <v>1.01</v>
-      </c>
-      <c r="AS22">
-        <v>1.01</v>
-      </c>
-      <c r="AT22">
-        <v>1.01</v>
-      </c>
-      <c r="AU22">
-        <v>5.8</v>
-      </c>
-      <c r="AV22">
-        <v>8.4</v>
-      </c>
-      <c r="AW22">
-        <v>1.01</v>
-      </c>
-      <c r="AX22">
-        <v>1.01</v>
-      </c>
-      <c r="AY22">
-        <v>1.01</v>
-      </c>
-      <c r="AZ22">
-        <v>1.01</v>
-      </c>
-      <c r="BA22">
-        <v>1.01</v>
-      </c>
-      <c r="BB22">
-        <v>1.01</v>
-      </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH22">
         <v>4.6</v>
@@ -6301,7 +6301,7 @@
         <v>180</v>
       </c>
       <c r="F23">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G23">
         <v>1.63</v>
@@ -6313,16 +6313,16 @@
         <v>6</v>
       </c>
       <c r="J23">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K23">
         <v>4.7</v>
       </c>
       <c r="L23">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N23">
         <v>5</v>
@@ -6334,16 +6334,16 @@
         <v>2.36</v>
       </c>
       <c r="Q23">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R23">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S23">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T23">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U23">
         <v>2.2</v>
@@ -6361,7 +6361,7 @@
         <v>25</v>
       </c>
       <c r="Z23">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA23">
         <v>160</v>
@@ -6415,7 +6415,7 @@
         <v>21</v>
       </c>
       <c r="AR23">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS23">
         <v>42</v>
@@ -6427,7 +6427,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV23">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW23">
         <v>50</v>
@@ -6442,7 +6442,7 @@
         <v>17.5</v>
       </c>
       <c r="BA23">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BB23">
         <v>14.5</v>
@@ -6454,73 +6454,73 @@
         <v>26</v>
       </c>
       <c r="BE23">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BF23">
         <v>6.8</v>
       </c>
       <c r="BG23">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI23">
-        <v>1.58</v>
+        <v>3.7</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK23">
-        <v>2.12</v>
+        <v>4.8</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>2.38</v>
+        <v>26</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO23">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ23">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS23">
-        <v>2.38</v>
+        <v>6.4</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU23">
-        <v>2.08</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW23">
-        <v>2.38</v>
+        <v>15.5</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY23">
-        <v>2.38</v>
+        <v>15.5</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA23">
-        <v>2.38</v>
+        <v>8</v>
       </c>
       <c r="CB23" t="s">
         <v>203</v>
@@ -6543,7 +6543,7 @@
         <v>181</v>
       </c>
       <c r="F24">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G24">
         <v>1.7</v>
@@ -6791,7 +6791,7 @@
         <v>1.3</v>
       </c>
       <c r="H25">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="I25">
         <v>990</v>
@@ -7027,7 +7027,7 @@
         <v>183</v>
       </c>
       <c r="F26">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="G26">
         <v>110</v>
@@ -7075,7 +7075,7 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W26">
         <v>1.01</v>
@@ -7269,19 +7269,19 @@
         <v>184</v>
       </c>
       <c r="F27">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G27">
         <v>2.64</v>
       </c>
       <c r="H27">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="I27">
         <v>990</v>
       </c>
       <c r="J27">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K27">
         <v>890</v>
@@ -7302,7 +7302,7 @@
         <v>1.25</v>
       </c>
       <c r="Q27">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="R27">
         <v>1.18</v>
@@ -7520,7 +7520,7 @@
         <v>1.04</v>
       </c>
       <c r="I28">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J28">
         <v>5.5</v>
@@ -7550,7 +7550,7 @@
         <v>1.57</v>
       </c>
       <c r="S28">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -7559,7 +7559,7 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W28">
         <v>3.05</v>
@@ -7756,7 +7756,7 @@
         <v>5.9</v>
       </c>
       <c r="G29">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>1.61</v>
@@ -7774,10 +7774,10 @@
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N29">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O29">
         <v>1.3</v>
@@ -7786,133 +7786,133 @@
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R29">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S29">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T29">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="U29">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="V29">
         <v>2.42</v>
       </c>
       <c r="W29">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X29">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y29">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC29">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD29">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE29">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG29">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH29">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI29">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AP29">
-        <v>1.43</v>
+        <v>14</v>
       </c>
       <c r="AQ29">
-        <v>1.39</v>
+        <v>7.4</v>
       </c>
       <c r="AR29">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29">
-        <v>1.43</v>
+        <v>14</v>
       </c>
       <c r="AT29">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU29">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="AV29">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW29">
-        <v>1.44</v>
+        <v>15</v>
       </c>
       <c r="AX29">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY29">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ29">
-        <v>1.55</v>
+        <v>16.5</v>
       </c>
       <c r="BA29">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB29">
-        <v>1.55</v>
+        <v>9</v>
       </c>
       <c r="BC29">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD29">
-        <v>1.55</v>
+        <v>8.6</v>
       </c>
       <c r="BE29">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG29">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7995,10 +7995,10 @@
         <v>187</v>
       </c>
       <c r="F30">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G30">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H30">
         <v>3.95</v>
@@ -8007,28 +8007,28 @@
         <v>4.2</v>
       </c>
       <c r="J30">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K30">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L30">
         <v>1.38</v>
       </c>
       <c r="M30">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N30">
         <v>3.95</v>
       </c>
       <c r="O30">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P30">
         <v>2.02</v>
       </c>
       <c r="Q30">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R30">
         <v>1.39</v>
@@ -8037,7 +8037,7 @@
         <v>3.3</v>
       </c>
       <c r="T30">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U30">
         <v>2.18</v>
@@ -8046,13 +8046,13 @@
         <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X30">
         <v>16</v>
       </c>
       <c r="Y30">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z30">
         <v>32</v>
@@ -8067,10 +8067,10 @@
         <v>8.4</v>
       </c>
       <c r="AD30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE30">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AF30">
         <v>13</v>
@@ -8079,10 +8079,10 @@
         <v>10.5</v>
       </c>
       <c r="AH30">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI30">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="AJ30">
         <v>25</v>
@@ -8091,7 +8091,7 @@
         <v>22</v>
       </c>
       <c r="AL30">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM30">
         <v>1000</v>
@@ -8100,7 +8100,7 @@
         <v>14</v>
       </c>
       <c r="AO30">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP30">
         <v>14</v>
@@ -8109,10 +8109,10 @@
         <v>13.5</v>
       </c>
       <c r="AR30">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS30">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AT30">
         <v>9</v>
@@ -8124,19 +8124,19 @@
         <v>14</v>
       </c>
       <c r="AW30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
       </c>
       <c r="AY30">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA30">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB30">
         <v>21</v>
@@ -8145,16 +8145,16 @@
         <v>17.5</v>
       </c>
       <c r="BD30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE30">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BF30">
         <v>12.5</v>
       </c>
       <c r="BG30">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8172,7 +8172,7 @@
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>2.4</v>
+        <v>27</v>
       </c>
       <c r="BN30">
         <v>5.8</v>
@@ -8190,7 +8190,7 @@
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="BT30">
         <v>1000</v>
@@ -8202,19 +8202,19 @@
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>2.4</v>
+        <v>12.5</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>2.4</v>
+        <v>15</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="CB30" t="s">
         <v>203</v>
@@ -8237,22 +8237,22 @@
         <v>188</v>
       </c>
       <c r="F31">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G31">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H31">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I31">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J31">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K31">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8261,7 +8261,7 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O31">
         <v>1.15</v>
@@ -8270,25 +8270,25 @@
         <v>2.58</v>
       </c>
       <c r="Q31">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R31">
         <v>1.64</v>
       </c>
       <c r="S31">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T31">
         <v>1.58</v>
       </c>
       <c r="U31">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V31">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W31">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8318,7 +8318,7 @@
         <v>1000</v>
       </c>
       <c r="AG31">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH31">
         <v>1000</v>
@@ -8345,58 +8345,58 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AQ31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AR31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AS31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AT31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AU31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AV31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AW31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AX31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AY31">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AZ31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BA31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BB31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BF31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG31">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8479,16 +8479,16 @@
         <v>189</v>
       </c>
       <c r="F32">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G32">
         <v>2.5</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I32">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J32">
         <v>3.6</v>
@@ -8497,7 +8497,7 @@
         <v>3.8</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M32">
         <v>1.06</v>
@@ -8512,10 +8512,10 @@
         <v>2.06</v>
       </c>
       <c r="Q32">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R32">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S32">
         <v>3.05</v>
@@ -8596,7 +8596,7 @@
         <v>17</v>
       </c>
       <c r="AS32">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT32">
         <v>10</v>
@@ -8608,7 +8608,7 @@
         <v>12</v>
       </c>
       <c r="AW32">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX32">
         <v>13.5</v>
@@ -8620,19 +8620,19 @@
         <v>13.5</v>
       </c>
       <c r="BA32">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB32">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC32">
         <v>17.5</v>
       </c>
       <c r="BD32">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE32">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF32">
         <v>14.5</v>
@@ -8641,64 +8641,64 @@
         <v>21</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI32">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK32">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL32">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ32">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU32">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW32">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA32">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="CB32" t="s">
         <v>203</v>
@@ -8727,7 +8727,7 @@
         <v>2.18</v>
       </c>
       <c r="H33">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I33">
         <v>3.6</v>
@@ -8739,7 +8739,7 @@
         <v>4.4</v>
       </c>
       <c r="L33">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M33">
         <v>1.01</v>
@@ -8751,16 +8751,16 @@
         <v>1.19</v>
       </c>
       <c r="P33">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
       </c>
       <c r="R33">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S33">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T33">
         <v>1.55</v>
@@ -8814,10 +8814,10 @@
         <v>32</v>
       </c>
       <c r="AK33">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM33">
         <v>70</v>
@@ -8838,7 +8838,7 @@
         <v>20</v>
       </c>
       <c r="AS33">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT33">
         <v>12</v>
@@ -8850,7 +8850,7 @@
         <v>12.5</v>
       </c>
       <c r="AW33">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX33">
         <v>14</v>
@@ -8862,7 +8862,7 @@
         <v>13</v>
       </c>
       <c r="BA33">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB33">
         <v>19</v>
@@ -8874,7 +8874,7 @@
         <v>19.5</v>
       </c>
       <c r="BE33">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF33">
         <v>8.800000000000001</v>
@@ -8883,64 +8883,64 @@
         <v>16</v>
       </c>
       <c r="BH33">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI33">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="BJ33">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BK33">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.97</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN33">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO33">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="BP33">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BQ33">
-        <v>1.82</v>
+        <v>10</v>
       </c>
       <c r="BR33">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BS33">
-        <v>1.89</v>
+        <v>6.8</v>
       </c>
       <c r="BT33">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BU33">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV33">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.89</v>
+        <v>7</v>
       </c>
       <c r="BX33">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.91</v>
+        <v>7.4</v>
       </c>
       <c r="BZ33">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="CA33">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="CB33" t="s">
         <v>203</v>
@@ -8963,166 +8963,166 @@
         <v>191</v>
       </c>
       <c r="F34">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G34">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H34">
         <v>3.65</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J34">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K34">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L34">
         <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N34">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O34">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P34">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q34">
         <v>1.92</v>
       </c>
       <c r="R34">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S34">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T34">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U34">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W34">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z34">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA34">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB34">
+        <v>10</v>
+      </c>
+      <c r="AC34">
+        <v>8.4</v>
+      </c>
+      <c r="AD34">
+        <v>16</v>
+      </c>
+      <c r="AE34">
+        <v>55</v>
+      </c>
+      <c r="AF34">
+        <v>16</v>
+      </c>
+      <c r="AG34">
+        <v>12.5</v>
+      </c>
+      <c r="AH34">
+        <v>18</v>
+      </c>
+      <c r="AI34">
+        <v>60</v>
+      </c>
+      <c r="AJ34">
+        <v>28</v>
+      </c>
+      <c r="AK34">
+        <v>27</v>
+      </c>
+      <c r="AL34">
+        <v>42</v>
+      </c>
+      <c r="AM34">
+        <v>110</v>
+      </c>
+      <c r="AN34">
+        <v>18.5</v>
+      </c>
+      <c r="AO34">
+        <v>55</v>
+      </c>
+      <c r="AP34">
+        <v>13</v>
+      </c>
+      <c r="AQ34">
+        <v>12.5</v>
+      </c>
+      <c r="AR34">
+        <v>6</v>
+      </c>
+      <c r="AS34">
+        <v>6.8</v>
+      </c>
+      <c r="AT34">
+        <v>8.6</v>
+      </c>
+      <c r="AU34">
+        <v>7.2</v>
+      </c>
+      <c r="AV34">
+        <v>13.5</v>
+      </c>
+      <c r="AW34">
+        <v>6.6</v>
+      </c>
+      <c r="AX34">
+        <v>12</v>
+      </c>
+      <c r="AY34">
+        <v>9.4</v>
+      </c>
+      <c r="AZ34">
+        <v>15</v>
+      </c>
+      <c r="BA34">
+        <v>6.6</v>
+      </c>
+      <c r="BB34">
         <v>20</v>
       </c>
-      <c r="AC34">
-        <v>970</v>
-      </c>
-      <c r="AD34">
-        <v>970</v>
-      </c>
-      <c r="AE34">
-        <v>1000</v>
-      </c>
-      <c r="AF34">
-        <v>1000</v>
-      </c>
-      <c r="AG34">
-        <v>1000</v>
-      </c>
-      <c r="AH34">
-        <v>21</v>
-      </c>
-      <c r="AI34">
-        <v>1000</v>
-      </c>
-      <c r="AJ34">
-        <v>34</v>
-      </c>
-      <c r="AK34">
-        <v>1000</v>
-      </c>
-      <c r="AL34">
-        <v>44</v>
-      </c>
-      <c r="AM34">
-        <v>1000</v>
-      </c>
-      <c r="AN34">
-        <v>970</v>
-      </c>
-      <c r="AO34">
-        <v>1000</v>
-      </c>
-      <c r="AP34">
-        <v>1.63</v>
-      </c>
-      <c r="AQ34">
-        <v>1.63</v>
-      </c>
-      <c r="AR34">
-        <v>19</v>
-      </c>
-      <c r="AS34">
-        <v>1.6</v>
-      </c>
-      <c r="AT34">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU34">
-        <v>1.43</v>
-      </c>
-      <c r="AV34">
-        <v>1.49</v>
-      </c>
-      <c r="AW34">
-        <v>1.63</v>
-      </c>
-      <c r="AX34">
-        <v>1.63</v>
-      </c>
-      <c r="AY34">
-        <v>1.63</v>
-      </c>
-      <c r="AZ34">
-        <v>1.51</v>
-      </c>
-      <c r="BA34">
-        <v>1.63</v>
-      </c>
-      <c r="BB34">
-        <v>19</v>
-      </c>
       <c r="BC34">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BD34">
-        <v>1.57</v>
+        <v>6.4</v>
       </c>
       <c r="BE34">
-        <v>1.63</v>
+        <v>7</v>
       </c>
       <c r="BF34">
-        <v>1.5</v>
+        <v>14</v>
       </c>
       <c r="BG34">
-        <v>1.63</v>
+        <v>6.8</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9205,22 +9205,22 @@
         <v>192</v>
       </c>
       <c r="F35">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="G35">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H35">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I35">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J35">
         <v>3.8</v>
       </c>
       <c r="K35">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9229,142 +9229,142 @@
         <v>1.04</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="O35">
         <v>1.2</v>
       </c>
       <c r="P35">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q35">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R35">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S35">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T35">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="U35">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V35">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W35">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X35">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y35">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Z35">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA35">
         <v>65</v>
       </c>
       <c r="AB35">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC35">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD35">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AE35">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF35">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AG35">
+        <v>13.5</v>
+      </c>
+      <c r="AH35">
         <v>16</v>
       </c>
-      <c r="AH35">
-        <v>20</v>
-      </c>
       <c r="AI35">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AJ35">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AK35">
+        <v>22</v>
+      </c>
+      <c r="AL35">
         <v>30</v>
       </c>
-      <c r="AL35">
-        <v>40</v>
-      </c>
       <c r="AM35">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN35">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AO35">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AP35">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ35">
+        <v>15</v>
+      </c>
+      <c r="AR35">
+        <v>21</v>
+      </c>
+      <c r="AS35">
+        <v>6.2</v>
+      </c>
+      <c r="AT35">
         <v>12</v>
       </c>
-      <c r="AR35">
-        <v>15.5</v>
-      </c>
-      <c r="AS35">
-        <v>1.01</v>
-      </c>
-      <c r="AT35">
-        <v>10.5</v>
-      </c>
       <c r="AU35">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV35">
+        <v>12</v>
+      </c>
+      <c r="AW35">
+        <v>6</v>
+      </c>
+      <c r="AX35">
+        <v>14.5</v>
+      </c>
+      <c r="AY35">
         <v>10</v>
       </c>
-      <c r="AW35">
-        <v>18.5</v>
-      </c>
-      <c r="AX35">
-        <v>12.5</v>
-      </c>
-      <c r="AY35">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA35">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB35">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="BC35">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BD35">
-        <v>18.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE35">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF35">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG35">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9447,19 +9447,19 @@
         <v>193</v>
       </c>
       <c r="F36">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G36">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H36">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I36">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="J36">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K36">
         <v>3.9</v>
@@ -9471,31 +9471,31 @@
         <v>1.02</v>
       </c>
       <c r="N36">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="O36">
         <v>1.26</v>
       </c>
       <c r="P36">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q36">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R36">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S36">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="T36">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U36">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V36">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
         <v>1.52</v>
@@ -9516,7 +9516,7 @@
         <v>17.5</v>
       </c>
       <c r="AC36">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD36">
         <v>15</v>
@@ -9555,16 +9555,16 @@
         <v>26</v>
       </c>
       <c r="AP36">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ36">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="AR36">
         <v>13</v>
       </c>
       <c r="AS36">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AT36">
         <v>10</v>
@@ -9588,22 +9588,22 @@
         <v>12</v>
       </c>
       <c r="BA36">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BB36">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BC36">
         <v>17.5</v>
       </c>
       <c r="BD36">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BE36">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BF36">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BG36">
         <v>13.5</v>
@@ -9692,7 +9692,7 @@
         <v>2.26</v>
       </c>
       <c r="G37">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H37">
         <v>2.9</v>
@@ -9713,7 +9713,7 @@
         <v>1.01</v>
       </c>
       <c r="N37">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O37">
         <v>1.22</v>
@@ -9731,7 +9731,7 @@
         <v>2.58</v>
       </c>
       <c r="T37">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U37">
         <v>2.4</v>
@@ -9740,7 +9740,7 @@
         <v>1.43</v>
       </c>
       <c r="W37">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9758,7 +9758,7 @@
         <v>1000</v>
       </c>
       <c r="AC37">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD37">
         <v>1000</v>
@@ -9797,58 +9797,58 @@
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU37">
         <v>1.01</v>
       </c>
       <c r="AV37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AX37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AY37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AZ37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BA37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BB37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BC37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BD37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BE37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BF37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG37">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9931,16 +9931,16 @@
         <v>195</v>
       </c>
       <c r="F38">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G38">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H38">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I38">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J38">
         <v>3.95</v>
@@ -9955,13 +9955,13 @@
         <v>1.02</v>
       </c>
       <c r="N38">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O38">
         <v>1.18</v>
       </c>
       <c r="P38">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q38">
         <v>1.53</v>
@@ -9970,19 +9970,19 @@
         <v>1.64</v>
       </c>
       <c r="S38">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T38">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U38">
         <v>2.56</v>
       </c>
       <c r="V38">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W38">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X38">
         <v>27</v>
@@ -10048,7 +10048,7 @@
         <v>20</v>
       </c>
       <c r="AS38">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT38">
         <v>12.5</v>
@@ -10060,7 +10060,7 @@
         <v>12.5</v>
       </c>
       <c r="AW38">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX38">
         <v>14.5</v>
@@ -10069,25 +10069,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ38">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA38">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB38">
         <v>19</v>
       </c>
       <c r="BC38">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BD38">
         <v>19</v>
       </c>
       <c r="BE38">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF38">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG38">
         <v>17.5</v>
@@ -10173,226 +10173,226 @@
         <v>196</v>
       </c>
       <c r="F39">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G39">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="H39">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I39">
+        <v>3.35</v>
+      </c>
+      <c r="J39">
         <v>3.5</v>
       </c>
-      <c r="J39">
-        <v>3.4</v>
-      </c>
       <c r="K39">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L39">
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N39">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O39">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P39">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="Q39">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="R39">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="S39">
-        <v>2.26</v>
+        <v>3.35</v>
       </c>
       <c r="T39">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V39">
         <v>1.42</v>
       </c>
       <c r="W39">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ39">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN39">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO39">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF39">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH39">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI39">
         <v>2.78</v>
       </c>
       <c r="BJ39">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK39">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="BN39">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO39">
-        <v>1.3</v>
+        <v>3.55</v>
       </c>
       <c r="BP39">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ39">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="BR39">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS39">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="BT39">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU39">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV39">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW39">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="BX39">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY39">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="BZ39">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA39">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="CB39" t="s">
         <v>203</v>
@@ -10415,7 +10415,7 @@
         <v>197</v>
       </c>
       <c r="F40">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G40">
         <v>13</v>
@@ -10457,7 +10457,7 @@
         <v>1.94</v>
       </c>
       <c r="T40">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U40">
         <v>2.3</v>
@@ -10472,7 +10472,7 @@
         <v>46</v>
       </c>
       <c r="Y40">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z40">
         <v>10.5</v>
@@ -10505,7 +10505,7 @@
         <v>27</v>
       </c>
       <c r="AJ40">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AK40">
         <v>1000</v>
@@ -10520,7 +10520,7 @@
         <v>160</v>
       </c>
       <c r="AO40">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AP40">
         <v>38</v>
@@ -10529,13 +10529,13 @@
         <v>14</v>
       </c>
       <c r="AR40">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS40">
         <v>10.5</v>
       </c>
       <c r="AT40">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AU40">
         <v>15</v>
@@ -10547,7 +10547,7 @@
         <v>10.5</v>
       </c>
       <c r="AX40">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AY40">
         <v>34</v>
@@ -10568,73 +10568,73 @@
         <v>75</v>
       </c>
       <c r="BE40">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BF40">
         <v>42</v>
       </c>
       <c r="BG40">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BH40">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI40">
+        <v>5.2</v>
+      </c>
+      <c r="BJ40">
+        <v>11</v>
+      </c>
+      <c r="BK40">
+        <v>9.6</v>
+      </c>
+      <c r="BL40">
+        <v>110</v>
+      </c>
+      <c r="BM40">
+        <v>10</v>
+      </c>
+      <c r="BN40">
+        <v>15</v>
+      </c>
+      <c r="BO40">
+        <v>12.5</v>
+      </c>
+      <c r="BP40">
+        <v>75</v>
+      </c>
+      <c r="BQ40">
+        <v>9.6</v>
+      </c>
+      <c r="BR40">
+        <v>70</v>
+      </c>
+      <c r="BS40">
+        <v>9.6</v>
+      </c>
+      <c r="BT40">
         <v>4.3</v>
       </c>
-      <c r="BJ40">
-        <v>1000</v>
-      </c>
-      <c r="BK40">
-        <v>1.96</v>
-      </c>
-      <c r="BL40">
-        <v>1000</v>
-      </c>
-      <c r="BM40">
-        <v>2.16</v>
-      </c>
-      <c r="BN40">
-        <v>1000</v>
-      </c>
-      <c r="BO40">
-        <v>2.08</v>
-      </c>
-      <c r="BP40">
-        <v>1000</v>
-      </c>
-      <c r="BQ40">
-        <v>4.7</v>
-      </c>
-      <c r="BR40">
-        <v>1000</v>
-      </c>
-      <c r="BS40">
-        <v>2.16</v>
-      </c>
-      <c r="BT40">
-        <v>4.9</v>
-      </c>
       <c r="BU40">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BV40">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BW40">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BX40">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY40">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ40">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="CA40">
-        <v>2.16</v>
+        <v>6.4</v>
       </c>
       <c r="CB40" t="s">
         <v>203</v>
@@ -10657,121 +10657,121 @@
         <v>198</v>
       </c>
       <c r="F41">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="G41">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="H41">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="I41">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="J41">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K41">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="L41">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M41">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N41">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O41">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P41">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q41">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="R41">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S41">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T41">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U41">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V41">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="X41">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y41">
         <v>14.5</v>
       </c>
       <c r="Z41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA41">
         <v>55</v>
       </c>
       <c r="AB41">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC41">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD41">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE41">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF41">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG41">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH41">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI41">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ41">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AK41">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL41">
         <v>36</v>
       </c>
       <c r="AM41">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN41">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO41">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AP41">
         <v>1.01</v>
       </c>
       <c r="AQ41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS41">
         <v>1.01</v>
@@ -10789,13 +10789,13 @@
         <v>1.01</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY41">
         <v>1.01</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA41">
         <v>1.01</v>
@@ -10813,70 +10813,70 @@
         <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH41">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI41">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BJ41">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK41">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL41">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM41">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN41">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO41">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP41">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ41">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR41">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS41">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT41">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU41">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV41">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW41">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BX41">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY41">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ41">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA41">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="CB41" t="s">
         <v>203</v>
@@ -10899,34 +10899,34 @@
         <v>199</v>
       </c>
       <c r="F42">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="G42">
         <v>2.92</v>
       </c>
       <c r="H42">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I42">
         <v>3.1</v>
       </c>
       <c r="J42">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K42">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L42">
         <v>1.47</v>
       </c>
       <c r="M42">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N42">
         <v>2.82</v>
       </c>
       <c r="O42">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P42">
         <v>1.61</v>
@@ -10935,16 +10935,16 @@
         <v>2.36</v>
       </c>
       <c r="R42">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S42">
         <v>4.5</v>
       </c>
       <c r="T42">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="U42">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="V42">
         <v>1.47</v>
@@ -10953,112 +10953,112 @@
         <v>1.52</v>
       </c>
       <c r="X42">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y42">
-        <v>16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z42">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA42">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB42">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="AC42">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD42">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE42">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF42">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG42">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH42">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI42">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ42">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK42">
         <v>48</v>
       </c>
       <c r="AL42">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM42">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN42">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO42">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP42">
-        <v>1.49</v>
+        <v>8.4</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR42">
-        <v>1.65</v>
+        <v>16</v>
       </c>
       <c r="AS42">
-        <v>1.65</v>
+        <v>34</v>
       </c>
       <c r="AT42">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU42">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV42">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW42">
-        <v>1.65</v>
+        <v>6.4</v>
       </c>
       <c r="AX42">
-        <v>1.53</v>
+        <v>15</v>
       </c>
       <c r="AY42">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ42">
-        <v>1.65</v>
+        <v>18</v>
       </c>
       <c r="BA42">
-        <v>1.65</v>
+        <v>40</v>
       </c>
       <c r="BB42">
-        <v>1.65</v>
+        <v>32</v>
       </c>
       <c r="BC42">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD42">
-        <v>1.65</v>
+        <v>38</v>
       </c>
       <c r="BE42">
-        <v>1.65</v>
+        <v>7.2</v>
       </c>
       <c r="BF42">
-        <v>1.65</v>
+        <v>6.4</v>
       </c>
       <c r="BG42">
-        <v>1.65</v>
+        <v>6.6</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11141,31 +11141,31 @@
         <v>200</v>
       </c>
       <c r="F43">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G43">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H43">
         <v>4.1</v>
       </c>
       <c r="I43">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J43">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K43">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L43">
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N43">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O43">
         <v>1.36</v>
@@ -11177,130 +11177,130 @@
         <v>1.98</v>
       </c>
       <c r="R43">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S43">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T43">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U43">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V43">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W43">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X43">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y43">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z43">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA43">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB43">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC43">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD43">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE43">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF43">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG43">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH43">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI43">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ43">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK43">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL43">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM43">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO43">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP43">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ43">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS43">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT43">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU43">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW43">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ43">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA43">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB43">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC43">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD43">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE43">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG43">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH43">
         <v>4</v>
@@ -11383,7 +11383,7 @@
         <v>201</v>
       </c>
       <c r="F44">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G44">
         <v>1.34</v>
@@ -11392,13 +11392,13 @@
         <v>12</v>
       </c>
       <c r="I44">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J44">
         <v>5.7</v>
       </c>
       <c r="K44">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L44">
         <v>1.32</v>
@@ -11410,10 +11410,10 @@
         <v>4.5</v>
       </c>
       <c r="O44">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P44">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q44">
         <v>1.69</v>
@@ -11422,13 +11422,13 @@
         <v>1.48</v>
       </c>
       <c r="S44">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="T44">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U44">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="V44">
         <v>1.08</v>
@@ -11452,7 +11452,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC44">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD44">
         <v>55</v>
@@ -11461,10 +11461,10 @@
         <v>280</v>
       </c>
       <c r="AF44">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG44">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH44">
         <v>36</v>
@@ -11491,118 +11491,118 @@
         <v>440</v>
       </c>
       <c r="AP44">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR44">
+        <v>10.5</v>
+      </c>
+      <c r="AS44">
         <v>11.5</v>
       </c>
-      <c r="AS44">
-        <v>12.5</v>
-      </c>
       <c r="AT44">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU44">
         <v>11.5</v>
       </c>
       <c r="AV44">
+        <v>10</v>
+      </c>
+      <c r="AW44">
         <v>11</v>
       </c>
-      <c r="AW44">
-        <v>12</v>
-      </c>
       <c r="AX44">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY44">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA44">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB44">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC44">
         <v>13.5</v>
       </c>
       <c r="BD44">
+        <v>10</v>
+      </c>
+      <c r="BE44">
         <v>11</v>
-      </c>
-      <c r="BE44">
-        <v>12</v>
       </c>
       <c r="BF44">
         <v>4.9</v>
       </c>
       <c r="BG44">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH44">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI44">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="BJ44">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK44">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BN44">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO44">
-        <v>1.29</v>
+        <v>3.2</v>
       </c>
       <c r="BP44">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BQ44">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BR44">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS44">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BT44">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BU44">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV44">
         <v>1000</v>
       </c>
       <c r="BW44">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX44">
         <v>1000</v>
       </c>
       <c r="BY44">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BZ44">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA44">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB44" t="s">
         <v>203</v>
@@ -11625,19 +11625,19 @@
         <v>202</v>
       </c>
       <c r="F45">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G45">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="H45">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="I45">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="J45">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="K45">
         <v>870</v>
@@ -11673,10 +11673,10 @@
         <v>1.01</v>
       </c>
       <c r="V45">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W45">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X45">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -625,7 +625,7 @@
     <t>Deportes Temuco</t>
   </si>
   <si>
-    <t>2026-09-14 04:00:46</t>
+    <t>2026-09-14 06:16:16</t>
   </si>
 </sst>
 </file>
@@ -1219,22 +1219,22 @@
         <v>159</v>
       </c>
       <c r="F2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H2">
         <v>10</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J2">
         <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.56</v>
@@ -1243,22 +1243,22 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q2">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="R2">
         <v>1.21</v>
       </c>
       <c r="S2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T2">
         <v>2.86</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="X2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y2">
         <v>22</v>
@@ -1294,7 +1294,7 @@
         <v>55</v>
       </c>
       <c r="AE2">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="AF2">
         <v>6.6</v>
@@ -1303,10 +1303,10 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="AI2">
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="AJ2">
         <v>13.5</v>
@@ -1315,22 +1315,22 @@
         <v>24</v>
       </c>
       <c r="AL2">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
         <v>540</v>
       </c>
       <c r="AN2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR2">
         <v>36</v>
@@ -1345,7 +1345,7 @@
         <v>9.4</v>
       </c>
       <c r="AV2">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AW2">
         <v>50</v>
@@ -1357,7 +1357,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BA2">
         <v>55</v>
@@ -1366,7 +1366,7 @@
         <v>11</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD2">
         <v>34</v>
@@ -1381,64 +1381,64 @@
         <v>60</v>
       </c>
       <c r="BH2">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.64</v>
+        <v>2.14</v>
       </c>
       <c r="BJ2">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>1.07</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>1.07</v>
       </c>
       <c r="BN2">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="BP2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>1.05</v>
       </c>
       <c r="BT2">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>6.4</v>
+        <v>1.07</v>
       </c>
       <c r="BV2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>1.06</v>
       </c>
       <c r="BX2">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>1.06</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>203</v>
@@ -1461,22 +1461,22 @@
         <v>160</v>
       </c>
       <c r="F3">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
         <v>2.88</v>
       </c>
       <c r="H3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J3">
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
         <v>1.53</v>
@@ -1497,7 +1497,7 @@
         <v>2.46</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
         <v>4.8</v>
@@ -1530,7 +1530,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
         <v>17</v>
@@ -1578,7 +1578,7 @@
         <v>16.5</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT3">
         <v>8.199999999999999</v>
@@ -1590,7 +1590,7 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX3">
         <v>15</v>
@@ -1602,10 +1602,10 @@
         <v>18</v>
       </c>
       <c r="BA3">
+        <v>6.8</v>
+      </c>
+      <c r="BB3">
         <v>6.6</v>
-      </c>
-      <c r="BB3">
-        <v>6.4</v>
       </c>
       <c r="BC3">
         <v>32</v>
@@ -1617,70 +1617,70 @@
         <v>7</v>
       </c>
       <c r="BF3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH3">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>203</v>
@@ -1706,7 +1706,7 @@
         <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -1718,10 +1718,10 @@
         <v>4.9</v>
       </c>
       <c r="K4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M4">
         <v>1.06</v>
@@ -1733,31 +1733,31 @@
         <v>1.31</v>
       </c>
       <c r="P4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R4">
         <v>1.39</v>
       </c>
       <c r="S4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
         <v>2.26</v>
       </c>
       <c r="U4">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V4">
         <v>1.1</v>
       </c>
       <c r="W4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="X4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y4">
         <v>29</v>
@@ -1766,61 +1766,61 @@
         <v>120</v>
       </c>
       <c r="AA4">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="AB4">
         <v>7.4</v>
       </c>
       <c r="AC4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD4">
         <v>40</v>
       </c>
       <c r="AE4">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AF4">
         <v>8.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH4">
         <v>32</v>
       </c>
       <c r="AI4">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AJ4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL4">
         <v>50</v>
       </c>
       <c r="AM4">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO4">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AP4">
         <v>14.5</v>
       </c>
       <c r="AQ4">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
@@ -1829,10 +1829,10 @@
         <v>10</v>
       </c>
       <c r="AV4">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW4">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX4">
         <v>7</v>
@@ -1841,10 +1841,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA4">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB4">
         <v>10</v>
@@ -1853,76 +1853,76 @@
         <v>14.5</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE4">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG4">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH4">
         <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BJ4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK4">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4">
         <v>3.75</v>
       </c>
       <c r="BO4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP4">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ4">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT4">
         <v>14.5</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="s">
         <v>203</v>
@@ -1948,7 +1948,7 @@
         <v>1.97</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -1996,7 +1996,7 @@
         <v>1.31</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X5">
         <v>17.5</v>
@@ -2032,10 +2032,10 @@
         <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK5">
         <v>21</v>
@@ -2062,7 +2062,7 @@
         <v>10</v>
       </c>
       <c r="AS5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT5">
         <v>9.6</v>
@@ -2095,13 +2095,13 @@
         <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE5">
         <v>12</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
         <v>11</v>
@@ -2116,13 +2116,13 @@
         <v>9.4</v>
       </c>
       <c r="BK5">
+        <v>4.7</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
         <v>8.4</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>21</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
@@ -2134,16 +2134,16 @@
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR5">
         <v>26</v>
       </c>
       <c r="BS5">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="BT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU5">
         <v>6.6</v>
@@ -2152,19 +2152,19 @@
         <v>32</v>
       </c>
       <c r="BW5">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5">
         <v>21</v>
       </c>
       <c r="CA5">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
         <v>203</v>
@@ -2205,7 +2205,7 @@
         <v>3.15</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
         <v>1.16</v>
@@ -2331,13 +2331,13 @@
         <v>6.4</v>
       </c>
       <c r="BB6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC6">
         <v>6.4</v>
       </c>
       <c r="BD6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE6">
         <v>6.6</v>
@@ -2349,58 +2349,58 @@
         <v>5.9</v>
       </c>
       <c r="BH6">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="BI6">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK6">
-        <v>1.56</v>
+        <v>4.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.56</v>
+        <v>6.4</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO6">
-        <v>1.56</v>
+        <v>3.9</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BQ6">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BS6">
-        <v>1.56</v>
+        <v>6.2</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU6">
-        <v>1.56</v>
+        <v>4.1</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW6">
-        <v>1.56</v>
+        <v>5.1</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY6">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>164</v>
       </c>
       <c r="F7">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G7">
         <v>2.34</v>
@@ -2438,25 +2438,25 @@
         <v>3.95</v>
       </c>
       <c r="I7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
       <c r="K7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M7">
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P7">
         <v>1.52</v>
@@ -2489,10 +2489,10 @@
         <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB7">
         <v>7.2</v>
@@ -2501,10 +2501,10 @@
         <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF7">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         <v>26</v>
       </c>
       <c r="AI7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ7">
         <v>34</v>
@@ -2528,13 +2528,13 @@
         <v>75</v>
       </c>
       <c r="AM7">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN7">
         <v>38</v>
       </c>
       <c r="AO7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP7">
         <v>7.2</v>
@@ -2546,7 +2546,7 @@
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
@@ -2558,19 +2558,19 @@
         <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7">
         <v>24</v>
@@ -2579,76 +2579,76 @@
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE7">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7">
         <v>26</v>
       </c>
       <c r="BG7">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI7">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK7">
-        <v>1.18</v>
+        <v>9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.18</v>
+        <v>6.8</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO7">
-        <v>1.57</v>
+        <v>4.3</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ7">
-        <v>1.18</v>
+        <v>5.3</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS7">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU7">
-        <v>1.22</v>
+        <v>6</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW7">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY7">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA7">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="s">
         <v>203</v>
@@ -2671,112 +2671,112 @@
         <v>165</v>
       </c>
       <c r="F8">
+        <v>7.6</v>
+      </c>
+      <c r="G8">
+        <v>12.5</v>
+      </c>
+      <c r="H8">
+        <v>1.29</v>
+      </c>
+      <c r="I8">
+        <v>1.36</v>
+      </c>
+      <c r="J8">
+        <v>5.5</v>
+      </c>
+      <c r="K8">
+        <v>7.4</v>
+      </c>
+      <c r="L8">
+        <v>1.19</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>4.8</v>
+      </c>
+      <c r="O8">
         <v>1.12</v>
       </c>
-      <c r="G8">
-        <v>990</v>
-      </c>
-      <c r="H8">
-        <v>1.12</v>
-      </c>
-      <c r="I8">
-        <v>990</v>
-      </c>
-      <c r="J8">
-        <v>1.23</v>
-      </c>
-      <c r="K8">
-        <v>950</v>
-      </c>
-      <c r="L8">
-        <v>1.01</v>
-      </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
-      <c r="N8">
-        <v>1.1</v>
-      </c>
-      <c r="O8">
-        <v>1.15</v>
-      </c>
       <c r="P8">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="Q8">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="R8">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="S8">
-        <v>1.16</v>
+        <v>1.83</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V8">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="W8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="AP8">
         <v>1.03</v>
@@ -2830,19 +2830,19 @@
         <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2851,10 +2851,10 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BP8">
         <v>1000</v>
@@ -2869,28 +2869,28 @@
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="s">
         <v>203</v>
@@ -2913,10 +2913,10 @@
         <v>166</v>
       </c>
       <c r="F9">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G9">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H9">
         <v>4.3</v>
@@ -2925,13 +2925,13 @@
         <v>4.6</v>
       </c>
       <c r="J9">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K9">
         <v>4</v>
       </c>
       <c r="L9">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M9">
         <v>1.06</v>
@@ -2940,25 +2940,25 @@
         <v>4.1</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P9">
         <v>2.04</v>
       </c>
       <c r="Q9">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S9">
         <v>3.2</v>
       </c>
       <c r="T9">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U9">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.28</v>
@@ -2967,7 +2967,7 @@
         <v>2.02</v>
       </c>
       <c r="X9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y9">
         <v>17.5</v>
@@ -3075,64 +3075,64 @@
         <v>9.4</v>
       </c>
       <c r="BH9">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BI9">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BJ9">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BN9">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9">
-        <v>3.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BT9">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BV9">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="CA9">
-        <v>3.95</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="s">
         <v>203</v>
@@ -3164,16 +3164,16 @@
         <v>1.85</v>
       </c>
       <c r="I10">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="J10">
         <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M10">
         <v>1.01</v>
@@ -3182,7 +3182,7 @@
         <v>6</v>
       </c>
       <c r="O10">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P10">
         <v>2.68</v>
@@ -3191,10 +3191,10 @@
         <v>1.5</v>
       </c>
       <c r="R10">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S10">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T10">
         <v>1.54</v>
@@ -3206,10 +3206,10 @@
         <v>2.06</v>
       </c>
       <c r="W10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y10">
         <v>15</v>
@@ -3236,31 +3236,31 @@
         <v>40</v>
       </c>
       <c r="AG10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH10">
         <v>16</v>
       </c>
       <c r="AI10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ10">
         <v>100</v>
       </c>
       <c r="AK10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL10">
         <v>44</v>
       </c>
       <c r="AM10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP10">
         <v>20</v>
@@ -3287,7 +3287,7 @@
         <v>14.5</v>
       </c>
       <c r="AX10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY10">
         <v>15</v>
@@ -3299,82 +3299,82 @@
         <v>21</v>
       </c>
       <c r="BB10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC10">
+        <v>9</v>
+      </c>
+      <c r="BD10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE10">
         <v>9.4</v>
       </c>
-      <c r="BC10">
-        <v>8.6</v>
-      </c>
-      <c r="BD10">
-        <v>8.6</v>
-      </c>
-      <c r="BE10">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG10">
         <v>6.8</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI10">
-        <v>1.49</v>
+        <v>4.1</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>1.77</v>
+        <v>7.6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.2</v>
+        <v>10.5</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO10">
-        <v>1.76</v>
+        <v>7</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ10">
-        <v>1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU10">
-        <v>1.54</v>
+        <v>4.6</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW10">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY10">
-        <v>2.06</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA10">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="s">
         <v>203</v>
@@ -3415,7 +3415,7 @@
         <v>4.4</v>
       </c>
       <c r="L11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M11">
         <v>1.04</v>
@@ -3430,7 +3430,7 @@
         <v>2.58</v>
       </c>
       <c r="Q11">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R11">
         <v>1.62</v>
@@ -3511,7 +3511,7 @@
         <v>17</v>
       </c>
       <c r="AR11">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="AS11">
         <v>8.4</v>
@@ -3538,7 +3538,7 @@
         <v>13.5</v>
       </c>
       <c r="BA11">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BB11">
         <v>19</v>
@@ -3559,64 +3559,64 @@
         <v>19</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI11">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK11">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO11">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU11">
         <v>4.8</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB11" t="s">
         <v>203</v>
@@ -3639,10 +3639,10 @@
         <v>169</v>
       </c>
       <c r="F12">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G12">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H12">
         <v>6.8</v>
@@ -3651,13 +3651,13 @@
         <v>7.6</v>
       </c>
       <c r="J12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M12">
         <v>1.06</v>
@@ -3669,13 +3669,13 @@
         <v>1.27</v>
       </c>
       <c r="P12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q12">
         <v>1.8</v>
       </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S12">
         <v>3.05</v>
@@ -3690,7 +3690,7 @@
         <v>1.15</v>
       </c>
       <c r="W12">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="X12">
         <v>18.5</v>
@@ -3747,7 +3747,7 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12">
         <v>20</v>
@@ -3759,13 +3759,13 @@
         <v>48</v>
       </c>
       <c r="AT12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12">
         <v>9</v>
       </c>
       <c r="AV12">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AW12">
         <v>38</v>
@@ -3777,19 +3777,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB12">
         <v>12</v>
       </c>
       <c r="BC12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE12">
         <v>42</v>
@@ -3881,7 +3881,7 @@
         <v>170</v>
       </c>
       <c r="F13">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G13">
         <v>2.3</v>
@@ -3971,7 +3971,7 @@
         <v>55</v>
       </c>
       <c r="AJ13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK13">
         <v>25</v>
@@ -4034,7 +4034,7 @@
         <v>34</v>
       </c>
       <c r="BE13">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BF13">
         <v>17</v>
@@ -4094,13 +4094,13 @@
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB13" t="s">
         <v>203</v>
@@ -4141,7 +4141,7 @@
         <v>4.1</v>
       </c>
       <c r="L14">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M14">
         <v>1.04</v>
@@ -4285,61 +4285,61 @@
         <v>14</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI14">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BJ14">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BK14">
         <v>5.6</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM14">
         <v>21</v>
       </c>
       <c r="BN14">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BO14">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BP14">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BQ14">
         <v>12</v>
       </c>
       <c r="BR14">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BS14">
         <v>16.5</v>
       </c>
       <c r="BT14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU14">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="BV14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BW14">
         <v>11.5</v>
       </c>
       <c r="BX14">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BY14">
         <v>16.5</v>
       </c>
       <c r="BZ14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="CA14">
         <v>11.5</v>
@@ -4365,25 +4365,25 @@
         <v>172</v>
       </c>
       <c r="F15">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H15">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="I15">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M15">
         <v>1.02</v>
@@ -4392,199 +4392,199 @@
         <v>5.1</v>
       </c>
       <c r="O15">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q15">
+        <v>1.62</v>
+      </c>
+      <c r="R15">
         <v>1.57</v>
       </c>
-      <c r="R15">
-        <v>1.55</v>
-      </c>
       <c r="S15">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="T15">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="U15">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="W15">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC15">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
+        <v>14.5</v>
+      </c>
+      <c r="AE15">
+        <v>27</v>
+      </c>
+      <c r="AF15">
+        <v>30</v>
+      </c>
+      <c r="AG15">
+        <v>17</v>
+      </c>
+      <c r="AH15">
+        <v>18.5</v>
+      </c>
+      <c r="AI15">
+        <v>36</v>
+      </c>
+      <c r="AJ15">
+        <v>60</v>
+      </c>
+      <c r="AK15">
+        <v>38</v>
+      </c>
+      <c r="AL15">
+        <v>42</v>
+      </c>
+      <c r="AM15">
+        <v>75</v>
+      </c>
+      <c r="AN15">
+        <v>25</v>
+      </c>
+      <c r="AO15">
+        <v>15.5</v>
+      </c>
+      <c r="AP15">
+        <v>16.5</v>
+      </c>
+      <c r="AQ15">
+        <v>12.5</v>
+      </c>
+      <c r="AR15">
+        <v>15.5</v>
+      </c>
+      <c r="AS15">
+        <v>4</v>
+      </c>
+      <c r="AT15">
+        <v>14.5</v>
+      </c>
+      <c r="AU15">
+        <v>8.4</v>
+      </c>
+      <c r="AV15">
+        <v>10</v>
+      </c>
+      <c r="AW15">
+        <v>16</v>
+      </c>
+      <c r="AX15">
+        <v>17.5</v>
+      </c>
+      <c r="AY15">
+        <v>12</v>
+      </c>
+      <c r="AZ15">
+        <v>13</v>
+      </c>
+      <c r="BA15">
+        <v>21</v>
+      </c>
+      <c r="BB15">
+        <v>4.2</v>
+      </c>
+      <c r="BC15">
+        <v>21</v>
+      </c>
+      <c r="BD15">
+        <v>4</v>
+      </c>
+      <c r="BE15">
+        <v>4.2</v>
+      </c>
+      <c r="BF15">
+        <v>17.5</v>
+      </c>
+      <c r="BG15">
+        <v>11</v>
+      </c>
+      <c r="BH15">
+        <v>5</v>
+      </c>
+      <c r="BI15">
+        <v>3.3</v>
+      </c>
+      <c r="BJ15">
+        <v>10.5</v>
+      </c>
+      <c r="BK15">
+        <v>6.4</v>
+      </c>
+      <c r="BL15">
+        <v>95</v>
+      </c>
+      <c r="BM15">
+        <v>50</v>
+      </c>
+      <c r="BN15">
+        <v>8</v>
+      </c>
+      <c r="BO15">
+        <v>5</v>
+      </c>
+      <c r="BP15">
+        <v>26</v>
+      </c>
+      <c r="BQ15">
+        <v>15</v>
+      </c>
+      <c r="BR15">
         <v>34</v>
       </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>30</v>
-      </c>
-      <c r="AP15">
-        <v>1.15</v>
-      </c>
-      <c r="AQ15">
-        <v>1.15</v>
-      </c>
-      <c r="AR15">
-        <v>1.15</v>
-      </c>
-      <c r="AS15">
-        <v>1.15</v>
-      </c>
-      <c r="AT15">
-        <v>1.15</v>
-      </c>
-      <c r="AU15">
-        <v>1.06</v>
-      </c>
-      <c r="AV15">
-        <v>1.12</v>
-      </c>
-      <c r="AW15">
-        <v>1.15</v>
-      </c>
-      <c r="AX15">
-        <v>1.15</v>
-      </c>
-      <c r="AY15">
-        <v>1.15</v>
-      </c>
-      <c r="AZ15">
-        <v>1.15</v>
-      </c>
-      <c r="BA15">
-        <v>1.15</v>
-      </c>
-      <c r="BB15">
-        <v>1.15</v>
-      </c>
-      <c r="BC15">
-        <v>1.15</v>
-      </c>
-      <c r="BD15">
-        <v>1.15</v>
-      </c>
-      <c r="BE15">
-        <v>1.15</v>
-      </c>
-      <c r="BF15">
-        <v>1.15</v>
-      </c>
-      <c r="BG15">
-        <v>1.11</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.01</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.01</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.01</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>1.01</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.01</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB15" t="s">
         <v>203</v>
@@ -4607,16 +4607,16 @@
         <v>173</v>
       </c>
       <c r="F16">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G16">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H16">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I16">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J16">
         <v>3.9</v>
@@ -4625,7 +4625,7 @@
         <v>4.4</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M16">
         <v>1.03</v>
@@ -4634,16 +4634,16 @@
         <v>5.7</v>
       </c>
       <c r="O16">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P16">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q16">
         <v>1.51</v>
       </c>
       <c r="R16">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="S16">
         <v>2.26</v>
@@ -4655,10 +4655,10 @@
         <v>2.68</v>
       </c>
       <c r="V16">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W16">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X16">
         <v>34</v>
@@ -4670,10 +4670,10 @@
         <v>26</v>
       </c>
       <c r="AA16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC16">
         <v>11</v>
@@ -4682,28 +4682,28 @@
         <v>15.5</v>
       </c>
       <c r="AE16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF16">
         <v>28</v>
       </c>
       <c r="AG16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH16">
         <v>15.5</v>
       </c>
       <c r="AI16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ16">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK16">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL16">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM16">
         <v>65</v>
@@ -4718,7 +4718,7 @@
         <v>20</v>
       </c>
       <c r="AQ16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR16">
         <v>17.5</v>
@@ -4733,13 +4733,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW16">
         <v>19.5</v>
       </c>
       <c r="AX16">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY16">
         <v>11</v>
@@ -4754,7 +4754,7 @@
         <v>4.7</v>
       </c>
       <c r="BC16">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BD16">
         <v>20</v>
@@ -4763,70 +4763,70 @@
         <v>4.9</v>
       </c>
       <c r="BF16">
+        <v>11</v>
+      </c>
+      <c r="BG16">
+        <v>11</v>
+      </c>
+      <c r="BH16">
+        <v>5.4</v>
+      </c>
+      <c r="BI16">
+        <v>3.55</v>
+      </c>
+      <c r="BJ16">
+        <v>10</v>
+      </c>
+      <c r="BK16">
+        <v>6.2</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>46</v>
+      </c>
+      <c r="BN16">
+        <v>7.6</v>
+      </c>
+      <c r="BO16">
+        <v>4.8</v>
+      </c>
+      <c r="BP16">
+        <v>22</v>
+      </c>
+      <c r="BQ16">
+        <v>13</v>
+      </c>
+      <c r="BR16">
+        <v>29</v>
+      </c>
+      <c r="BS16">
+        <v>17</v>
+      </c>
+      <c r="BT16">
+        <v>7.4</v>
+      </c>
+      <c r="BU16">
+        <v>4.6</v>
+      </c>
+      <c r="BV16">
+        <v>21</v>
+      </c>
+      <c r="BW16">
         <v>12</v>
       </c>
-      <c r="BG16">
+      <c r="BX16">
+        <v>28</v>
+      </c>
+      <c r="BY16">
+        <v>16.5</v>
+      </c>
+      <c r="BZ16">
+        <v>17.5</v>
+      </c>
+      <c r="CA16">
         <v>10.5</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.01</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.01</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.01</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.01</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.01</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.01</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.01</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>1.01</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>1.01</v>
-      </c>
-      <c r="BZ16">
-        <v>1000</v>
-      </c>
-      <c r="CA16">
-        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
         <v>203</v>
@@ -4867,34 +4867,34 @@
         <v>7.2</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M17">
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O17">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P17">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q17">
         <v>1.71</v>
       </c>
       <c r="R17">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S17">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T17">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U17">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V17">
         <v>1.05</v>
@@ -4978,10 +4978,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW17">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY17">
         <v>10.5</v>
@@ -4990,7 +4990,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BA17">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB17">
         <v>7.6</v>
@@ -5002,7 +5002,7 @@
         <v>8</v>
       </c>
       <c r="BE17">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17">
         <v>4.4</v>
@@ -5011,58 +5011,58 @@
         <v>8.6</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI17">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="BJ17">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BK17">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.38</v>
+        <v>5.3</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO17">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="BP17">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BQ17">
-        <v>1.57</v>
+        <v>5.7</v>
       </c>
       <c r="BR17">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BS17">
-        <v>1.79</v>
+        <v>4.6</v>
       </c>
       <c r="BT17">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BU17">
-        <v>1.76</v>
+        <v>4.6</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.38</v>
+        <v>5.3</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.38</v>
+        <v>5.3</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5100,7 +5100,7 @@
         <v>4.7</v>
       </c>
       <c r="I18">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18">
         <v>3.1</v>
@@ -5109,7 +5109,7 @@
         <v>3.35</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M18">
         <v>1.13</v>
@@ -5145,7 +5145,7 @@
         <v>1.91</v>
       </c>
       <c r="X18">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y18">
         <v>15</v>
@@ -5199,16 +5199,16 @@
         <v>180</v>
       </c>
       <c r="AP18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18">
         <v>10.5</v>
       </c>
       <c r="AR18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT18">
         <v>5.9</v>
@@ -5220,7 +5220,7 @@
         <v>17.5</v>
       </c>
       <c r="AW18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX18">
         <v>9.800000000000001</v>
@@ -5232,7 +5232,7 @@
         <v>20</v>
       </c>
       <c r="BA18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB18">
         <v>21</v>
@@ -5241,76 +5241,76 @@
         <v>21</v>
       </c>
       <c r="BD18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF18">
         <v>19.5</v>
       </c>
       <c r="BG18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH18">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="BI18">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK18">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO18">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ18">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CB18" t="s">
         <v>203</v>
@@ -5333,10 +5333,10 @@
         <v>176</v>
       </c>
       <c r="F19">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G19">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H19">
         <v>5.9</v>
@@ -5348,10 +5348,10 @@
         <v>4.1</v>
       </c>
       <c r="K19">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L19">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="M19">
         <v>1.06</v>
@@ -5360,7 +5360,7 @@
         <v>4</v>
       </c>
       <c r="O19">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P19">
         <v>2.04</v>
@@ -5375,7 +5375,7 @@
         <v>3</v>
       </c>
       <c r="T19">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U19">
         <v>1.98</v>
@@ -5384,19 +5384,19 @@
         <v>1.17</v>
       </c>
       <c r="W19">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X19">
         <v>20</v>
       </c>
       <c r="Y19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z19">
         <v>65</v>
       </c>
       <c r="AA19">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB19">
         <v>9.199999999999999</v>
@@ -5423,7 +5423,7 @@
         <v>95</v>
       </c>
       <c r="AJ19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK19">
         <v>19.5</v>
@@ -5447,7 +5447,7 @@
         <v>18.5</v>
       </c>
       <c r="AR19">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AS19">
         <v>6.8</v>
@@ -5492,19 +5492,19 @@
         <v>7.6</v>
       </c>
       <c r="BG19">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI19">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5513,46 +5513,46 @@
         <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB19" t="s">
         <v>203</v>
@@ -5578,22 +5578,22 @@
         <v>1.18</v>
       </c>
       <c r="G20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H20">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="I20">
         <v>19.5</v>
       </c>
       <c r="J20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="K20">
         <v>10.5</v>
       </c>
       <c r="L20">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="M20">
         <v>1.01</v>
@@ -5617,13 +5617,13 @@
         <v>1.64</v>
       </c>
       <c r="T20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U20">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V20">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -5644,16 +5644,16 @@
         <v>23</v>
       </c>
       <c r="AC20">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AD20">
         <v>65</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF20">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG20">
         <v>14.5</v>
@@ -5668,43 +5668,43 @@
         <v>11</v>
       </c>
       <c r="AK20">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL20">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM20">
         <v>130</v>
       </c>
       <c r="AN20">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP20">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ20">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR20">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT20">
         <v>18</v>
       </c>
       <c r="AU20">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AV20">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AW20">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX20">
         <v>11</v>
@@ -5713,10 +5713,10 @@
         <v>12</v>
       </c>
       <c r="AZ20">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB20">
         <v>9.6</v>
@@ -5725,76 +5725,76 @@
         <v>11.5</v>
       </c>
       <c r="BD20">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF20">
         <v>2.26</v>
       </c>
       <c r="BG20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BI20">
-        <v>1.65</v>
+        <v>6.2</v>
       </c>
       <c r="BJ20">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK20">
-        <v>2.04</v>
+        <v>7.4</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO20">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP20">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BQ20">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="BR20">
         <v>24</v>
       </c>
       <c r="BS20">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="BT20">
         <v>26</v>
       </c>
       <c r="BU20">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>2.26</v>
+        <v>6.2</v>
       </c>
       <c r="BZ20">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="CA20">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="CB20" t="s">
         <v>203</v>
@@ -5820,16 +5820,16 @@
         <v>1.92</v>
       </c>
       <c r="G21">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H21">
         <v>5.1</v>
       </c>
       <c r="I21">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J21">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K21">
         <v>3.5</v>
@@ -5862,7 +5862,7 @@
         <v>2.06</v>
       </c>
       <c r="U21">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V21">
         <v>1.23</v>
@@ -5886,7 +5886,7 @@
         <v>7.4</v>
       </c>
       <c r="AC21">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD21">
         <v>21</v>
@@ -5943,13 +5943,13 @@
         <v>7.2</v>
       </c>
       <c r="AV21">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW21">
         <v>65</v>
       </c>
       <c r="AX21">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY21">
         <v>9.6</v>
@@ -5970,7 +5970,7 @@
         <v>42</v>
       </c>
       <c r="BE21">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF21">
         <v>16</v>
@@ -6059,7 +6059,7 @@
         <v>179</v>
       </c>
       <c r="F22">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G22">
         <v>2.86</v>
@@ -6068,7 +6068,7 @@
         <v>2.62</v>
       </c>
       <c r="I22">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J22">
         <v>3.55</v>
@@ -6077,7 +6077,7 @@
         <v>3.85</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M22">
         <v>1.05</v>
@@ -6092,7 +6092,7 @@
         <v>2.1</v>
       </c>
       <c r="Q22">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R22">
         <v>1.42</v>
@@ -6101,7 +6101,7 @@
         <v>3.05</v>
       </c>
       <c r="T22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U22">
         <v>2.32</v>
@@ -6128,7 +6128,7 @@
         <v>16</v>
       </c>
       <c r="AC22">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD22">
         <v>13</v>
@@ -6161,58 +6161,58 @@
         <v>80</v>
       </c>
       <c r="AN22">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR22">
         <v>16</v>
       </c>
       <c r="AS22">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="AT22">
+        <v>11.5</v>
+      </c>
+      <c r="AU22">
+        <v>7.6</v>
+      </c>
+      <c r="AV22">
         <v>11</v>
       </c>
-      <c r="AU22">
-        <v>7.2</v>
-      </c>
-      <c r="AV22">
-        <v>10.5</v>
-      </c>
       <c r="AW22">
-        <v>23</v>
+        <v>6.4</v>
       </c>
       <c r="AX22">
         <v>16.5</v>
       </c>
       <c r="AY22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA22">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="BB22">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="BC22">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="BD22">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="BE22">
-        <v>60</v>
+        <v>7.4</v>
       </c>
       <c r="BF22">
         <v>18</v>
@@ -6221,7 +6221,7 @@
         <v>17.5</v>
       </c>
       <c r="BH22">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
         <v>3.1</v>
@@ -6230,55 +6230,55 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>203</v>
@@ -6301,16 +6301,16 @@
         <v>180</v>
       </c>
       <c r="F23">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G23">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H23">
+        <v>5.6</v>
+      </c>
+      <c r="I23">
         <v>5.8</v>
-      </c>
-      <c r="I23">
-        <v>6</v>
       </c>
       <c r="J23">
         <v>4.5</v>
@@ -6319,7 +6319,7 @@
         <v>4.7</v>
       </c>
       <c r="L23">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M23">
         <v>1.04</v>
@@ -6337,7 +6337,7 @@
         <v>1.67</v>
       </c>
       <c r="R23">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S23">
         <v>2.68</v>
@@ -6352,13 +6352,13 @@
         <v>1.2</v>
       </c>
       <c r="W23">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X23">
         <v>21</v>
       </c>
       <c r="Y23">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z23">
         <v>48</v>
@@ -6370,7 +6370,7 @@
         <v>10.5</v>
       </c>
       <c r="AC23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD23">
         <v>22</v>
@@ -6388,7 +6388,7 @@
         <v>19.5</v>
       </c>
       <c r="AI23">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
         <v>16.5</v>
@@ -6409,13 +6409,13 @@
         <v>70</v>
       </c>
       <c r="AP23">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ23">
         <v>21</v>
       </c>
       <c r="AR23">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AS23">
         <v>42</v>
@@ -6424,13 +6424,13 @@
         <v>9.4</v>
       </c>
       <c r="AU23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV23">
         <v>19.5</v>
       </c>
       <c r="AW23">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AX23">
         <v>9.800000000000001</v>
@@ -6439,13 +6439,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA23">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB23">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC23">
         <v>14</v>
@@ -6454,49 +6454,49 @@
         <v>26</v>
       </c>
       <c r="BE23">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="BF23">
         <v>6.8</v>
       </c>
       <c r="BG23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH23">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI23">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ23">
         <v>11.5</v>
       </c>
       <c r="BK23">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM23">
         <v>26</v>
       </c>
       <c r="BN23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO23">
         <v>3.95</v>
       </c>
       <c r="BP23">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ23">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BR23">
         <v>26</v>
       </c>
       <c r="BS23">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT23">
         <v>11</v>
@@ -6505,7 +6505,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BV23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW23">
         <v>15.5</v>
@@ -6517,7 +6517,7 @@
         <v>15.5</v>
       </c>
       <c r="BZ23">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA23">
         <v>8</v>
@@ -6543,7 +6543,7 @@
         <v>181</v>
       </c>
       <c r="F24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G24">
         <v>1.7</v>
@@ -6558,7 +6558,7 @@
         <v>1.1</v>
       </c>
       <c r="K24">
-        <v>880</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6591,7 +6591,7 @@
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W24">
         <v>1.01</v>
@@ -6651,52 +6651,52 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -6788,19 +6788,19 @@
         <v>1.05</v>
       </c>
       <c r="G25">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H25">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="I25">
         <v>990</v>
       </c>
       <c r="J25">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="K25">
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6809,7 +6809,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O25">
         <v>1.2</v>
@@ -6893,52 +6893,52 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -7027,13 +7027,13 @@
         <v>183</v>
       </c>
       <c r="F26">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G26">
-        <v>110</v>
+        <v>1.8</v>
       </c>
       <c r="H26">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="I26">
         <v>110</v>
@@ -7042,7 +7042,7 @@
         <v>3.5</v>
       </c>
       <c r="K26">
-        <v>880</v>
+        <v>950</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7075,10 +7075,10 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7135,52 +7135,52 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF26">
         <v>1.01</v>
@@ -7269,22 +7269,22 @@
         <v>184</v>
       </c>
       <c r="F27">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G27">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="H27">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="I27">
         <v>990</v>
       </c>
       <c r="J27">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K27">
-        <v>890</v>
+        <v>950</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7317,10 +7317,10 @@
         <v>1.11</v>
       </c>
       <c r="V27">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W27">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7377,52 +7377,52 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF27">
         <v>1.01</v>
@@ -7514,10 +7514,10 @@
         <v>1.31</v>
       </c>
       <c r="G28">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H28">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I28">
         <v>18</v>
@@ -7526,7 +7526,7 @@
         <v>5.5</v>
       </c>
       <c r="K28">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7535,139 +7535,139 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>2.52</v>
+        <v>4.4</v>
       </c>
       <c r="O28">
         <v>1.02</v>
       </c>
       <c r="P28">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="Q28">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="R28">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S28">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W28">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG28">
         <v>1.01</v>
@@ -7756,10 +7756,10 @@
         <v>5.9</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H29">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="I29">
         <v>1.7</v>
@@ -7768,7 +7768,7 @@
         <v>4</v>
       </c>
       <c r="K29">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7786,7 +7786,7 @@
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="R29">
         <v>1.39</v>
@@ -7795,7 +7795,7 @@
         <v>3.2</v>
       </c>
       <c r="T29">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U29">
         <v>1.97</v>
@@ -7995,10 +7995,10 @@
         <v>187</v>
       </c>
       <c r="F30">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G30">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H30">
         <v>3.95</v>
@@ -8007,16 +8007,16 @@
         <v>4.2</v>
       </c>
       <c r="J30">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K30">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L30">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N30">
         <v>3.95</v>
@@ -8028,7 +8028,7 @@
         <v>2.02</v>
       </c>
       <c r="Q30">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R30">
         <v>1.39</v>
@@ -8040,25 +8040,25 @@
         <v>1.78</v>
       </c>
       <c r="U30">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V30">
         <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X30">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y30">
         <v>16</v>
       </c>
       <c r="Z30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB30">
         <v>9.800000000000001</v>
@@ -8070,7 +8070,7 @@
         <v>16.5</v>
       </c>
       <c r="AE30">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF30">
         <v>13</v>
@@ -8079,58 +8079,58 @@
         <v>10.5</v>
       </c>
       <c r="AH30">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI30">
-        <v>370</v>
+        <v>55</v>
       </c>
       <c r="AJ30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL30">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN30">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO30">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP30">
         <v>14</v>
       </c>
       <c r="AQ30">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR30">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AS30">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AT30">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU30">
         <v>7.6</v>
       </c>
       <c r="AV30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW30">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
       </c>
       <c r="AY30">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30">
         <v>15.5</v>
@@ -8139,34 +8139,34 @@
         <v>32</v>
       </c>
       <c r="BB30">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC30">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD30">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BE30">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BF30">
         <v>12.5</v>
       </c>
       <c r="BG30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI30">
-        <v>1.49</v>
+        <v>3.25</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK30">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8175,46 +8175,46 @@
         <v>27</v>
       </c>
       <c r="BN30">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO30">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ30">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS30">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU30">
-        <v>1.96</v>
+        <v>6.6</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW30">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY30">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CB30" t="s">
         <v>203</v>
@@ -8237,22 +8237,22 @@
         <v>188</v>
       </c>
       <c r="F31">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="G31">
         <v>1.65</v>
       </c>
       <c r="H31">
+        <v>5</v>
+      </c>
+      <c r="I31">
+        <v>5.9</v>
+      </c>
+      <c r="J31">
         <v>4.5</v>
       </c>
-      <c r="I31">
-        <v>6.8</v>
-      </c>
-      <c r="J31">
-        <v>4.1</v>
-      </c>
       <c r="K31">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8261,142 +8261,142 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>1.15</v>
       </c>
       <c r="P31">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q31">
         <v>1.46</v>
       </c>
       <c r="R31">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S31">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T31">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U31">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="V31">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W31">
         <v>2.52</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB31">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC31">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF31">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG31">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN31">
-        <v>970</v>
+        <v>6.2</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP31">
-        <v>1.21</v>
+        <v>20</v>
       </c>
       <c r="AQ31">
-        <v>1.21</v>
+        <v>19.5</v>
       </c>
       <c r="AR31">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="AS31">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="AT31">
-        <v>1.21</v>
+        <v>11.5</v>
       </c>
       <c r="AU31">
-        <v>1.21</v>
+        <v>10</v>
       </c>
       <c r="AV31">
-        <v>1.21</v>
+        <v>18.5</v>
       </c>
       <c r="AW31">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="AX31">
-        <v>1.21</v>
+        <v>11</v>
       </c>
       <c r="AY31">
-        <v>1.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31">
-        <v>1.21</v>
+        <v>15</v>
       </c>
       <c r="BA31">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="BB31">
-        <v>1.21</v>
+        <v>14.5</v>
       </c>
       <c r="BC31">
-        <v>1.21</v>
+        <v>13</v>
       </c>
       <c r="BD31">
-        <v>1.21</v>
+        <v>18.5</v>
       </c>
       <c r="BE31">
-        <v>1.21</v>
+        <v>6.2</v>
       </c>
       <c r="BF31">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BG31">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8479,22 +8479,22 @@
         <v>189</v>
       </c>
       <c r="F32">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G32">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H32">
         <v>3.05</v>
       </c>
       <c r="I32">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K32">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L32">
         <v>1.32</v>
@@ -8503,16 +8503,16 @@
         <v>1.06</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O32">
         <v>1.28</v>
       </c>
       <c r="P32">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q32">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="R32">
         <v>1.39</v>
@@ -8521,7 +8521,7 @@
         <v>3.05</v>
       </c>
       <c r="T32">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U32">
         <v>2.28</v>
@@ -8530,13 +8530,13 @@
         <v>1.43</v>
       </c>
       <c r="W32">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X32">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y32">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z32">
         <v>25</v>
@@ -8551,13 +8551,13 @@
         <v>10.5</v>
       </c>
       <c r="AD32">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AE32">
         <v>38</v>
       </c>
       <c r="AF32">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AG32">
         <v>12</v>
@@ -8566,7 +8566,7 @@
         <v>17</v>
       </c>
       <c r="AI32">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ32">
         <v>34</v>
@@ -8581,13 +8581,13 @@
         <v>95</v>
       </c>
       <c r="AN32">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO32">
         <v>32</v>
       </c>
       <c r="AP32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ32">
         <v>12</v>
@@ -8596,7 +8596,7 @@
         <v>17</v>
       </c>
       <c r="AS32">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT32">
         <v>10</v>
@@ -8608,34 +8608,34 @@
         <v>12</v>
       </c>
       <c r="AW32">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AX32">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY32">
         <v>10</v>
       </c>
       <c r="AZ32">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA32">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB32">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BC32">
         <v>17.5</v>
       </c>
       <c r="BD32">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BE32">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF32">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG32">
         <v>21</v>
@@ -8644,7 +8644,7 @@
         <v>4.3</v>
       </c>
       <c r="BI32">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ32">
         <v>11</v>
@@ -8689,7 +8689,7 @@
         <v>17</v>
       </c>
       <c r="BX32">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY32">
         <v>24</v>
@@ -8698,7 +8698,7 @@
         <v>28</v>
       </c>
       <c r="CA32">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CB32" t="s">
         <v>203</v>
@@ -8724,10 +8724,10 @@
         <v>2.06</v>
       </c>
       <c r="G33">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H33">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I33">
         <v>3.6</v>
@@ -8736,13 +8736,13 @@
         <v>4</v>
       </c>
       <c r="K33">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L33">
         <v>1.24</v>
       </c>
       <c r="M33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N33">
         <v>5.3</v>
@@ -8751,7 +8751,7 @@
         <v>1.19</v>
       </c>
       <c r="P33">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -8760,19 +8760,19 @@
         <v>1.62</v>
       </c>
       <c r="S33">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T33">
         <v>1.55</v>
       </c>
       <c r="U33">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X33">
         <v>30</v>
@@ -8796,7 +8796,7 @@
         <v>15.5</v>
       </c>
       <c r="AE33">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF33">
         <v>17</v>
@@ -8805,10 +8805,10 @@
         <v>12</v>
       </c>
       <c r="AH33">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI33">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ33">
         <v>32</v>
@@ -8826,7 +8826,7 @@
         <v>10.5</v>
       </c>
       <c r="AO33">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP33">
         <v>18.5</v>
@@ -8838,7 +8838,7 @@
         <v>20</v>
       </c>
       <c r="AS33">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT33">
         <v>12</v>
@@ -8850,7 +8850,7 @@
         <v>12.5</v>
       </c>
       <c r="AW33">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX33">
         <v>14</v>
@@ -8862,7 +8862,7 @@
         <v>13</v>
       </c>
       <c r="BA33">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB33">
         <v>19</v>
@@ -8874,10 +8874,10 @@
         <v>19.5</v>
       </c>
       <c r="BE33">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF33">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG33">
         <v>16</v>
@@ -8910,7 +8910,7 @@
         <v>15</v>
       </c>
       <c r="BQ33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BR33">
         <v>23</v>
@@ -8922,7 +8922,7 @@
         <v>7.4</v>
       </c>
       <c r="BU33">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV33">
         <v>1000</v>
@@ -8963,16 +8963,16 @@
         <v>191</v>
       </c>
       <c r="F34">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G34">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H34">
         <v>3.65</v>
       </c>
       <c r="I34">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J34">
         <v>3.5</v>
@@ -8981,52 +8981,52 @@
         <v>3.7</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M34">
         <v>1.07</v>
       </c>
       <c r="N34">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O34">
         <v>1.32</v>
       </c>
       <c r="P34">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q34">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R34">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S34">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T34">
         <v>1.76</v>
       </c>
       <c r="U34">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V34">
         <v>1.34</v>
       </c>
       <c r="W34">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X34">
         <v>15.5</v>
       </c>
       <c r="Y34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z34">
         <v>28</v>
       </c>
       <c r="AA34">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB34">
         <v>10</v>
@@ -9059,7 +9059,7 @@
         <v>27</v>
       </c>
       <c r="AL34">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM34">
         <v>110</v>
@@ -9077,13 +9077,13 @@
         <v>12.5</v>
       </c>
       <c r="AR34">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS34">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT34">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU34">
         <v>7.2</v>
@@ -9092,46 +9092,46 @@
         <v>13.5</v>
       </c>
       <c r="AW34">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX34">
         <v>12</v>
       </c>
       <c r="AY34">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ34">
         <v>15</v>
       </c>
       <c r="BA34">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB34">
         <v>20</v>
       </c>
       <c r="BC34">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD34">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE34">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF34">
         <v>14</v>
       </c>
       <c r="BG34">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH34">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI34">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK34">
         <v>1.04</v>
@@ -9143,13 +9143,13 @@
         <v>1.04</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO34">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ34">
         <v>1.04</v>
@@ -9161,10 +9161,10 @@
         <v>1.04</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU34">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV34">
         <v>1000</v>
@@ -9205,25 +9205,25 @@
         <v>192</v>
       </c>
       <c r="F35">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G35">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H35">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I35">
         <v>3.4</v>
       </c>
       <c r="J35">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K35">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L35">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M35">
         <v>1.04</v>
@@ -9235,13 +9235,13 @@
         <v>1.2</v>
       </c>
       <c r="P35">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q35">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R35">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S35">
         <v>2.46</v>
@@ -9250,13 +9250,13 @@
         <v>1.55</v>
       </c>
       <c r="U35">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V35">
         <v>1.41</v>
       </c>
       <c r="W35">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X35">
         <v>27</v>
@@ -9277,13 +9277,13 @@
         <v>11</v>
       </c>
       <c r="AD35">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE35">
         <v>34</v>
       </c>
       <c r="AF35">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG35">
         <v>13.5</v>
@@ -9322,7 +9322,7 @@
         <v>21</v>
       </c>
       <c r="AS35">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT35">
         <v>12</v>
@@ -9334,7 +9334,7 @@
         <v>12</v>
       </c>
       <c r="AW35">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AX35">
         <v>14.5</v>
@@ -9346,19 +9346,19 @@
         <v>13</v>
       </c>
       <c r="BA35">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BB35">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC35">
         <v>17.5</v>
       </c>
       <c r="BD35">
+        <v>5.6</v>
+      </c>
+      <c r="BE35">
         <v>5.9</v>
-      </c>
-      <c r="BE35">
-        <v>6.2</v>
       </c>
       <c r="BF35">
         <v>10</v>
@@ -9367,13 +9367,13 @@
         <v>18</v>
       </c>
       <c r="BH35">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI35">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BJ35">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK35">
         <v>1.04</v>
@@ -9385,43 +9385,43 @@
         <v>1.04</v>
       </c>
       <c r="BN35">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO35">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP35">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ35">
         <v>1.04</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS35">
         <v>1.04</v>
       </c>
       <c r="BT35">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU35">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV35">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW35">
         <v>1.04</v>
       </c>
       <c r="BX35">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY35">
         <v>1.04</v>
       </c>
       <c r="BZ35">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA35">
         <v>1.04</v>
@@ -9450,16 +9450,16 @@
         <v>2.72</v>
       </c>
       <c r="G36">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H36">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I36">
         <v>2.76</v>
       </c>
       <c r="J36">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K36">
         <v>3.9</v>
@@ -9468,16 +9468,16 @@
         <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N36">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O36">
         <v>1.26</v>
       </c>
       <c r="P36">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q36">
         <v>1.75</v>
@@ -9486,187 +9486,187 @@
         <v>1.44</v>
       </c>
       <c r="S36">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T36">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U36">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V36">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W36">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X36">
+        <v>18.5</v>
+      </c>
+      <c r="Y36">
+        <v>13.5</v>
+      </c>
+      <c r="Z36">
+        <v>19</v>
+      </c>
+      <c r="AA36">
+        <v>38</v>
+      </c>
+      <c r="AB36">
+        <v>14</v>
+      </c>
+      <c r="AC36">
+        <v>9</v>
+      </c>
+      <c r="AD36">
+        <v>12.5</v>
+      </c>
+      <c r="AE36">
+        <v>28</v>
+      </c>
+      <c r="AF36">
         <v>22</v>
       </c>
-      <c r="Y36">
+      <c r="AG36">
+        <v>13.5</v>
+      </c>
+      <c r="AH36">
+        <v>16.5</v>
+      </c>
+      <c r="AI36">
+        <v>36</v>
+      </c>
+      <c r="AJ36">
+        <v>46</v>
+      </c>
+      <c r="AK36">
+        <v>32</v>
+      </c>
+      <c r="AL36">
+        <v>40</v>
+      </c>
+      <c r="AM36">
+        <v>75</v>
+      </c>
+      <c r="AN36">
+        <v>24</v>
+      </c>
+      <c r="AO36">
+        <v>19.5</v>
+      </c>
+      <c r="AP36">
+        <v>15</v>
+      </c>
+      <c r="AQ36">
+        <v>11</v>
+      </c>
+      <c r="AR36">
+        <v>15.5</v>
+      </c>
+      <c r="AS36">
+        <v>7.8</v>
+      </c>
+      <c r="AT36">
+        <v>11.5</v>
+      </c>
+      <c r="AU36">
+        <v>7.4</v>
+      </c>
+      <c r="AV36">
+        <v>10.5</v>
+      </c>
+      <c r="AW36">
+        <v>7.2</v>
+      </c>
+      <c r="AX36">
+        <v>17.5</v>
+      </c>
+      <c r="AY36">
+        <v>11</v>
+      </c>
+      <c r="AZ36">
+        <v>13.5</v>
+      </c>
+      <c r="BA36">
+        <v>7.8</v>
+      </c>
+      <c r="BB36">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC36">
+        <v>7.6</v>
+      </c>
+      <c r="BD36">
+        <v>8</v>
+      </c>
+      <c r="BE36">
+        <v>8.6</v>
+      </c>
+      <c r="BF36">
+        <v>19</v>
+      </c>
+      <c r="BG36">
         <v>16</v>
       </c>
-      <c r="Z36">
-        <v>28</v>
-      </c>
-      <c r="AA36">
-        <v>55</v>
-      </c>
-      <c r="AB36">
-        <v>17.5</v>
-      </c>
-      <c r="AC36">
-        <v>970</v>
-      </c>
-      <c r="AD36">
-        <v>15</v>
-      </c>
-      <c r="AE36">
-        <v>38</v>
-      </c>
-      <c r="AF36">
-        <v>30</v>
-      </c>
-      <c r="AG36">
-        <v>18</v>
-      </c>
-      <c r="AH36">
-        <v>22</v>
-      </c>
-      <c r="AI36">
-        <v>50</v>
-      </c>
-      <c r="AJ36">
-        <v>65</v>
-      </c>
-      <c r="AK36">
-        <v>44</v>
-      </c>
-      <c r="AL36">
-        <v>55</v>
-      </c>
-      <c r="AM36">
-        <v>100</v>
-      </c>
-      <c r="AN36">
-        <v>30</v>
-      </c>
-      <c r="AO36">
-        <v>26</v>
-      </c>
-      <c r="AP36">
-        <v>11.5</v>
-      </c>
-      <c r="AQ36">
-        <v>2.8</v>
-      </c>
-      <c r="AR36">
-        <v>13</v>
-      </c>
-      <c r="AS36">
-        <v>3.2</v>
-      </c>
-      <c r="AT36">
-        <v>10</v>
-      </c>
-      <c r="AU36">
-        <v>6.2</v>
-      </c>
-      <c r="AV36">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW36">
-        <v>16</v>
-      </c>
-      <c r="AX36">
-        <v>14.5</v>
-      </c>
-      <c r="AY36">
-        <v>10</v>
-      </c>
-      <c r="AZ36">
-        <v>12</v>
-      </c>
-      <c r="BA36">
-        <v>3.2</v>
-      </c>
-      <c r="BB36">
-        <v>3.25</v>
-      </c>
-      <c r="BC36">
-        <v>17.5</v>
-      </c>
-      <c r="BD36">
-        <v>3.2</v>
-      </c>
-      <c r="BE36">
-        <v>3.3</v>
-      </c>
-      <c r="BF36">
-        <v>3.05</v>
-      </c>
-      <c r="BG36">
-        <v>13.5</v>
-      </c>
       <c r="BH36">
         <v>1000</v>
       </c>
       <c r="BI36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ36">
         <v>1000</v>
       </c>
       <c r="BK36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN36">
         <v>1000</v>
       </c>
       <c r="BO36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP36">
         <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT36">
         <v>1000</v>
       </c>
       <c r="BU36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB36" t="s">
         <v>203</v>
@@ -9689,22 +9689,22 @@
         <v>194</v>
       </c>
       <c r="F37">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="G37">
         <v>2.52</v>
       </c>
       <c r="H37">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I37">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J37">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K37">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9725,19 +9725,19 @@
         <v>1.64</v>
       </c>
       <c r="R37">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S37">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T37">
         <v>1.53</v>
       </c>
       <c r="U37">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V37">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
         <v>1.65</v>
@@ -9931,10 +9931,10 @@
         <v>195</v>
       </c>
       <c r="F38">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G38">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H38">
         <v>3.2</v>
@@ -9946,43 +9946,43 @@
         <v>3.95</v>
       </c>
       <c r="K38">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L38">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N38">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O38">
         <v>1.18</v>
       </c>
       <c r="P38">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="Q38">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R38">
         <v>1.64</v>
       </c>
       <c r="S38">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="T38">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U38">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V38">
         <v>1.38</v>
       </c>
       <c r="W38">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X38">
         <v>27</v>
@@ -10042,13 +10042,13 @@
         <v>19</v>
       </c>
       <c r="AQ38">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR38">
         <v>20</v>
       </c>
       <c r="AS38">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT38">
         <v>12.5</v>
@@ -10060,7 +10060,7 @@
         <v>12.5</v>
       </c>
       <c r="AW38">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX38">
         <v>14.5</v>
@@ -10072,19 +10072,19 @@
         <v>13</v>
       </c>
       <c r="BA38">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB38">
         <v>19</v>
       </c>
       <c r="BC38">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD38">
         <v>19</v>
       </c>
       <c r="BE38">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF38">
         <v>8.6</v>
@@ -10093,64 +10093,64 @@
         <v>17.5</v>
       </c>
       <c r="BH38">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI38">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ38">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK38">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN38">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO38">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP38">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ38">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR38">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS38">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BT38">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU38">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV38">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW38">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX38">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY38">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BZ38">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA38">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB38" t="s">
         <v>203</v>
@@ -10173,16 +10173,16 @@
         <v>196</v>
       </c>
       <c r="F39">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G39">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H39">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I39">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J39">
         <v>3.5</v>
@@ -10194,7 +10194,7 @@
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N39">
         <v>3.85</v>
@@ -10212,28 +10212,28 @@
         <v>1.38</v>
       </c>
       <c r="S39">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T39">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U39">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V39">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W39">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X39">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y39">
         <v>16</v>
       </c>
       <c r="Z39">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA39">
         <v>70</v>
@@ -10260,7 +10260,7 @@
         <v>21</v>
       </c>
       <c r="AI39">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ39">
         <v>40</v>
@@ -10275,19 +10275,19 @@
         <v>110</v>
       </c>
       <c r="AN39">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO39">
         <v>42</v>
       </c>
       <c r="AP39">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ39">
         <v>11.5</v>
       </c>
       <c r="AR39">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS39">
         <v>1.03</v>
@@ -10305,7 +10305,7 @@
         <v>1.03</v>
       </c>
       <c r="AX39">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AY39">
         <v>10</v>
@@ -10320,7 +10320,7 @@
         <v>1.03</v>
       </c>
       <c r="BC39">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD39">
         <v>1.03</v>
@@ -10329,7 +10329,7 @@
         <v>1.03</v>
       </c>
       <c r="BF39">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG39">
         <v>24</v>
@@ -10344,13 +10344,13 @@
         <v>13.5</v>
       </c>
       <c r="BK39">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="BN39">
         <v>7.6</v>
@@ -10359,40 +10359,40 @@
         <v>3.55</v>
       </c>
       <c r="BP39">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ39">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="BR39">
         <v>44</v>
       </c>
       <c r="BS39">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="BT39">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU39">
         <v>4.2</v>
       </c>
       <c r="BV39">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW39">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="BX39">
         <v>50</v>
       </c>
       <c r="BY39">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BZ39">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA39">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CB39" t="s">
         <v>203</v>
@@ -10415,22 +10415,22 @@
         <v>197</v>
       </c>
       <c r="F40">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G40">
         <v>13</v>
       </c>
       <c r="H40">
+        <v>1.28</v>
+      </c>
+      <c r="I40">
         <v>1.29</v>
       </c>
-      <c r="I40">
-        <v>1.3</v>
-      </c>
       <c r="J40">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L40">
         <v>1.21</v>
@@ -10442,28 +10442,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O40">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P40">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q40">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R40">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S40">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="T40">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U40">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V40">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="W40">
         <v>1.08</v>
@@ -10484,7 +10484,7 @@
         <v>55</v>
       </c>
       <c r="AC40">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD40">
         <v>12</v>
@@ -10496,10 +10496,10 @@
         <v>170</v>
       </c>
       <c r="AG40">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AH40">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI40">
         <v>27</v>
@@ -10508,19 +10508,19 @@
         <v>480</v>
       </c>
       <c r="AK40">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL40">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AM40">
         <v>95</v>
       </c>
       <c r="AN40">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AO40">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AP40">
         <v>38</v>
@@ -10565,7 +10565,7 @@
         <v>44</v>
       </c>
       <c r="BD40">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BE40">
         <v>65</v>
@@ -10574,13 +10574,13 @@
         <v>42</v>
       </c>
       <c r="BG40">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BH40">
         <v>5.7</v>
       </c>
       <c r="BI40">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BJ40">
         <v>11</v>
@@ -10604,13 +10604,13 @@
         <v>75</v>
       </c>
       <c r="BQ40">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR40">
         <v>70</v>
       </c>
       <c r="BS40">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT40">
         <v>4.3</v>
@@ -10619,7 +10619,7 @@
         <v>3.95</v>
       </c>
       <c r="BV40">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BW40">
         <v>6</v>
@@ -10631,7 +10631,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BZ40">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA40">
         <v>6.4</v>
@@ -10899,13 +10899,13 @@
         <v>199</v>
       </c>
       <c r="F42">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G42">
         <v>2.92</v>
       </c>
       <c r="H42">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I42">
         <v>3.1</v>
@@ -10914,10 +10914,10 @@
         <v>3.1</v>
       </c>
       <c r="K42">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L42">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M42">
         <v>1.12</v>
@@ -10929,7 +10929,7 @@
         <v>1.47</v>
       </c>
       <c r="P42">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q42">
         <v>2.36</v>
@@ -10938,13 +10938,13 @@
         <v>1.23</v>
       </c>
       <c r="S42">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T42">
         <v>1.99</v>
       </c>
       <c r="U42">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V42">
         <v>1.47</v>
@@ -11061,13 +11061,13 @@
         <v>6.6</v>
       </c>
       <c r="BH42">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI42">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="BJ42">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BK42">
         <v>6.4</v>
@@ -11076,49 +11076,49 @@
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BN42">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO42">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP42">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BQ42">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="BR42">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS42">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BT42">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BU42">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV42">
         <v>38</v>
       </c>
       <c r="BW42">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX42">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY42">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BZ42">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA42">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB42" t="s">
         <v>203</v>
@@ -11141,7 +11141,7 @@
         <v>200</v>
       </c>
       <c r="F43">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G43">
         <v>2.08</v>
@@ -11150,19 +11150,19 @@
         <v>4.1</v>
       </c>
       <c r="I43">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J43">
         <v>3.45</v>
       </c>
       <c r="K43">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L43">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M43">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N43">
         <v>3.45</v>
@@ -11174,7 +11174,7 @@
         <v>1.86</v>
       </c>
       <c r="Q43">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R43">
         <v>1.31</v>
@@ -11183,22 +11183,22 @@
         <v>3.6</v>
       </c>
       <c r="T43">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U43">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V43">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W43">
         <v>1.92</v>
       </c>
       <c r="X43">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y43">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z43">
         <v>40</v>
@@ -11216,7 +11216,7 @@
         <v>22</v>
       </c>
       <c r="AE43">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF43">
         <v>15</v>
@@ -11255,10 +11255,10 @@
         <v>12.5</v>
       </c>
       <c r="AR43">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS43">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT43">
         <v>7.4</v>
@@ -11270,7 +11270,7 @@
         <v>15</v>
       </c>
       <c r="AW43">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX43">
         <v>10</v>
@@ -11282,7 +11282,7 @@
         <v>16.5</v>
       </c>
       <c r="BA43">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB43">
         <v>20</v>
@@ -11291,76 +11291,76 @@
         <v>18.5</v>
       </c>
       <c r="BD43">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE43">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF43">
         <v>11.5</v>
       </c>
       <c r="BG43">
+        <v>4.4</v>
+      </c>
+      <c r="BH43">
+        <v>3.4</v>
+      </c>
+      <c r="BI43">
+        <v>2.92</v>
+      </c>
+      <c r="BJ43">
+        <v>12</v>
+      </c>
+      <c r="BK43">
+        <v>3.9</v>
+      </c>
+      <c r="BL43">
+        <v>1000</v>
+      </c>
+      <c r="BM43">
+        <v>5.6</v>
+      </c>
+      <c r="BN43">
+        <v>5.5</v>
+      </c>
+      <c r="BO43">
+        <v>3.6</v>
+      </c>
+      <c r="BP43">
+        <v>17.5</v>
+      </c>
+      <c r="BQ43">
         <v>4.3</v>
       </c>
-      <c r="BH43">
-        <v>4</v>
-      </c>
-      <c r="BI43">
-        <v>2.64</v>
-      </c>
-      <c r="BJ43">
-        <v>1000</v>
-      </c>
-      <c r="BK43">
-        <v>1.34</v>
-      </c>
-      <c r="BL43">
-        <v>1000</v>
-      </c>
-      <c r="BM43">
-        <v>1.34</v>
-      </c>
-      <c r="BN43">
-        <v>1000</v>
-      </c>
-      <c r="BO43">
-        <v>1.34</v>
-      </c>
-      <c r="BP43">
-        <v>1000</v>
-      </c>
-      <c r="BQ43">
-        <v>1.34</v>
-      </c>
       <c r="BR43">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS43">
-        <v>1.34</v>
+        <v>5</v>
       </c>
       <c r="BT43">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU43">
-        <v>1.34</v>
+        <v>5.6</v>
       </c>
       <c r="BV43">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW43">
-        <v>1.34</v>
+        <v>5.1</v>
       </c>
       <c r="BX43">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY43">
-        <v>1.34</v>
+        <v>5.3</v>
       </c>
       <c r="BZ43">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA43">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="CB43" t="s">
         <v>203</v>
@@ -11383,7 +11383,7 @@
         <v>201</v>
       </c>
       <c r="F44">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G44">
         <v>1.34</v>
@@ -11392,13 +11392,13 @@
         <v>12</v>
       </c>
       <c r="I44">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J44">
         <v>5.7</v>
       </c>
       <c r="K44">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L44">
         <v>1.32</v>
@@ -11413,22 +11413,22 @@
         <v>1.25</v>
       </c>
       <c r="P44">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q44">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R44">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S44">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T44">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U44">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V44">
         <v>1.08</v>
@@ -11452,7 +11452,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC44">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD44">
         <v>55</v>
@@ -11464,7 +11464,7 @@
         <v>7.6</v>
       </c>
       <c r="AG44">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH44">
         <v>36</v>
@@ -11494,64 +11494,64 @@
         <v>17.5</v>
       </c>
       <c r="AQ44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR44">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS44">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT44">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU44">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV44">
+        <v>11</v>
+      </c>
+      <c r="AW44">
+        <v>12</v>
+      </c>
+      <c r="AX44">
+        <v>6.6</v>
+      </c>
+      <c r="AY44">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ44">
         <v>10</v>
       </c>
-      <c r="AW44">
-        <v>11</v>
-      </c>
-      <c r="AX44">
-        <v>6.4</v>
-      </c>
-      <c r="AY44">
-        <v>9.6</v>
-      </c>
-      <c r="AZ44">
-        <v>9</v>
-      </c>
       <c r="BA44">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB44">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC44">
         <v>13.5</v>
       </c>
       <c r="BD44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE44">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF44">
         <v>4.9</v>
       </c>
       <c r="BG44">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH44">
         <v>4.5</v>
       </c>
       <c r="BI44">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ44">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BK44">
         <v>4.2</v>
@@ -11563,16 +11563,16 @@
         <v>5.7</v>
       </c>
       <c r="BN44">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO44">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BP44">
         <v>8.4</v>
       </c>
       <c r="BQ44">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR44">
         <v>30</v>
@@ -11581,7 +11581,7 @@
         <v>4.9</v>
       </c>
       <c r="BT44">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU44">
         <v>4.4</v>
@@ -11602,7 +11602,7 @@
         <v>14.5</v>
       </c>
       <c r="CA44">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CB44" t="s">
         <v>203</v>
@@ -11625,19 +11625,19 @@
         <v>202</v>
       </c>
       <c r="F45">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G45">
-        <v>180</v>
+        <v>990</v>
       </c>
       <c r="H45">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="I45">
-        <v>130</v>
+        <v>990</v>
       </c>
       <c r="J45">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="K45">
         <v>870</v>
@@ -11649,34 +11649,34 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O45">
         <v>1.21</v>
       </c>
       <c r="P45">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q45">
         <v>1.21</v>
       </c>
       <c r="R45">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S45">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W45">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X45">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-15.xlsx
@@ -766,7 +766,7 @@
     <t>Academia Anzoategui FC</t>
   </si>
   <si>
-    <t>2026-09-14 19:56:13</t>
+    <t>2026-09-14 22:11:53</t>
   </si>
 </sst>
 </file>
@@ -1360,226 +1360,226 @@
         <v>189</v>
       </c>
       <c r="F2">
-        <v>1.47</v>
+        <v>2.02</v>
       </c>
       <c r="G2">
-        <v>1.49</v>
+        <v>2.04</v>
       </c>
       <c r="H2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>2.46</v>
       </c>
       <c r="L2">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="N2">
-        <v>2.54</v>
+        <v>1.45</v>
       </c>
       <c r="O2">
-        <v>1.63</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="Q2">
-        <v>2.92</v>
+        <v>9.6</v>
       </c>
       <c r="R2">
+        <v>1.02</v>
+      </c>
+      <c r="S2">
+        <v>36</v>
+      </c>
+      <c r="T2">
+        <v>6.2</v>
+      </c>
+      <c r="U2">
         <v>1.17</v>
       </c>
-      <c r="S2">
-        <v>6.6</v>
-      </c>
-      <c r="T2">
-        <v>3.3</v>
-      </c>
-      <c r="U2">
-        <v>1.41</v>
-      </c>
       <c r="V2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W2">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="X2">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="Y2">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
         <v>130</v>
       </c>
       <c r="AA2">
-        <v>940</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="AC2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD2">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AE2">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="AH2">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AI2">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
+        <v>40</v>
+      </c>
+      <c r="AK2">
+        <v>140</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>150</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>3.1</v>
+      </c>
+      <c r="AQ2">
         <v>12</v>
       </c>
-      <c r="AK2">
-        <v>25</v>
-      </c>
-      <c r="AL2">
-        <v>120</v>
-      </c>
-      <c r="AM2">
-        <v>790</v>
-      </c>
-      <c r="AN2">
-        <v>14.5</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>7.8</v>
-      </c>
-      <c r="AQ2">
-        <v>19.5</v>
-      </c>
       <c r="AR2">
+        <v>90</v>
+      </c>
+      <c r="AS2">
+        <v>340</v>
+      </c>
+      <c r="AT2">
+        <v>3.35</v>
+      </c>
+      <c r="AU2">
+        <v>11.5</v>
+      </c>
+      <c r="AV2">
+        <v>90</v>
+      </c>
+      <c r="AW2">
+        <v>17.5</v>
+      </c>
+      <c r="AX2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY2">
+        <v>26</v>
+      </c>
+      <c r="AZ2">
+        <v>130</v>
+      </c>
+      <c r="BA2">
+        <v>16</v>
+      </c>
+      <c r="BB2">
+        <v>30</v>
+      </c>
+      <c r="BC2">
         <v>100</v>
       </c>
-      <c r="AS2">
-        <v>65</v>
-      </c>
-      <c r="AT2">
-        <v>4.5</v>
-      </c>
-      <c r="AU2">
-        <v>10</v>
-      </c>
-      <c r="AV2">
-        <v>50</v>
-      </c>
-      <c r="AW2">
-        <v>70</v>
-      </c>
-      <c r="AX2">
-        <v>5.8</v>
-      </c>
-      <c r="AY2">
-        <v>12</v>
-      </c>
-      <c r="AZ2">
-        <v>46</v>
-      </c>
-      <c r="BA2">
-        <v>75</v>
-      </c>
-      <c r="BB2">
-        <v>11</v>
-      </c>
-      <c r="BC2">
-        <v>23</v>
-      </c>
       <c r="BD2">
-        <v>46</v>
+        <v>300</v>
       </c>
       <c r="BE2">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>85</v>
       </c>
       <c r="BG2">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="BH2">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>250</v>
@@ -1602,226 +1602,226 @@
         <v>190</v>
       </c>
       <c r="F3">
-        <v>2.82</v>
+        <v>6.4</v>
       </c>
       <c r="G3">
-        <v>2.86</v>
+        <v>9.6</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="I3">
-        <v>3.05</v>
+        <v>1.73</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
+        <v>4.1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>4.5</v>
+      </c>
+      <c r="O3">
+        <v>1.23</v>
+      </c>
+      <c r="P3">
+        <v>1.78</v>
+      </c>
+      <c r="Q3">
+        <v>2.08</v>
+      </c>
+      <c r="R3">
+        <v>1.23</v>
+      </c>
+      <c r="S3">
+        <v>5.1</v>
+      </c>
+      <c r="T3">
+        <v>1.67</v>
+      </c>
+      <c r="U3">
+        <v>2.36</v>
+      </c>
+      <c r="V3">
+        <v>2.62</v>
+      </c>
+      <c r="W3">
+        <v>1.13</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>5.6</v>
+      </c>
+      <c r="Z3">
+        <v>9</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>990</v>
+      </c>
+      <c r="AD3">
+        <v>990</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>990</v>
+      </c>
+      <c r="AH3">
+        <v>28</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>10.5</v>
+      </c>
+      <c r="AQ3">
+        <v>1.17</v>
+      </c>
+      <c r="AR3">
+        <v>1.28</v>
+      </c>
+      <c r="AS3">
+        <v>1.49</v>
+      </c>
+      <c r="AT3">
+        <v>10.5</v>
+      </c>
+      <c r="AU3">
+        <v>1.49</v>
+      </c>
+      <c r="AV3">
+        <v>1.49</v>
+      </c>
+      <c r="AW3">
+        <v>1.49</v>
+      </c>
+      <c r="AX3">
+        <v>10.5</v>
+      </c>
+      <c r="AY3">
+        <v>1.49</v>
+      </c>
+      <c r="AZ3">
+        <v>1.42</v>
+      </c>
+      <c r="BA3">
+        <v>1.49</v>
+      </c>
+      <c r="BB3">
+        <v>10.5</v>
+      </c>
+      <c r="BC3">
+        <v>1.49</v>
+      </c>
+      <c r="BD3">
+        <v>1.49</v>
+      </c>
+      <c r="BE3">
+        <v>2</v>
+      </c>
+      <c r="BF3">
+        <v>1.49</v>
+      </c>
+      <c r="BG3">
+        <v>1.49</v>
+      </c>
+      <c r="BH3">
         <v>3.2</v>
       </c>
-      <c r="L3">
-        <v>1.57</v>
-      </c>
-      <c r="M3">
-        <v>1.12</v>
-      </c>
-      <c r="N3">
-        <v>2.78</v>
-      </c>
-      <c r="O3">
-        <v>1.53</v>
-      </c>
-      <c r="P3">
-        <v>1.59</v>
-      </c>
-      <c r="Q3">
-        <v>2.66</v>
-      </c>
-      <c r="R3">
-        <v>1.2</v>
-      </c>
-      <c r="S3">
-        <v>5.5</v>
-      </c>
-      <c r="T3">
-        <v>2.12</v>
-      </c>
-      <c r="U3">
-        <v>1.84</v>
-      </c>
-      <c r="V3">
-        <v>1.48</v>
-      </c>
-      <c r="W3">
-        <v>1.53</v>
-      </c>
-      <c r="X3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Y3">
-        <v>9</v>
-      </c>
-      <c r="Z3">
-        <v>19</v>
-      </c>
-      <c r="AA3">
-        <v>55</v>
-      </c>
-      <c r="AB3">
-        <v>8.6</v>
-      </c>
-      <c r="AC3">
-        <v>7.2</v>
-      </c>
-      <c r="AD3">
-        <v>14</v>
-      </c>
-      <c r="AE3">
-        <v>55</v>
-      </c>
-      <c r="AF3">
-        <v>17</v>
-      </c>
-      <c r="AG3">
-        <v>13.5</v>
-      </c>
-      <c r="AH3">
-        <v>23</v>
-      </c>
-      <c r="AI3">
-        <v>80</v>
-      </c>
-      <c r="AJ3">
-        <v>50</v>
-      </c>
-      <c r="AK3">
-        <v>48</v>
-      </c>
-      <c r="AL3">
-        <v>70</v>
-      </c>
-      <c r="AM3">
-        <v>170</v>
-      </c>
-      <c r="AN3">
-        <v>50</v>
-      </c>
-      <c r="AO3">
-        <v>55</v>
-      </c>
-      <c r="AP3">
-        <v>8</v>
-      </c>
-      <c r="AQ3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR3">
-        <v>16.5</v>
-      </c>
-      <c r="AS3">
-        <v>32</v>
-      </c>
-      <c r="AT3">
-        <v>7.8</v>
-      </c>
-      <c r="AU3">
-        <v>6.6</v>
-      </c>
-      <c r="AV3">
-        <v>12.5</v>
-      </c>
-      <c r="AW3">
-        <v>38</v>
-      </c>
-      <c r="AX3">
-        <v>15.5</v>
-      </c>
-      <c r="AY3">
-        <v>12</v>
-      </c>
-      <c r="AZ3">
-        <v>20</v>
-      </c>
-      <c r="BA3">
-        <v>46</v>
-      </c>
-      <c r="BB3">
-        <v>42</v>
-      </c>
-      <c r="BC3">
-        <v>36</v>
-      </c>
-      <c r="BD3">
-        <v>46</v>
-      </c>
-      <c r="BE3">
-        <v>130</v>
-      </c>
-      <c r="BF3">
-        <v>40</v>
-      </c>
-      <c r="BG3">
-        <v>38</v>
-      </c>
-      <c r="BH3">
-        <v>2.74</v>
-      </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>1.45</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>30</v>
+        <v>1.45</v>
       </c>
       <c r="BN3">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>1.45</v>
       </c>
       <c r="BP3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>1.45</v>
       </c>
       <c r="BR3">
-        <v>46</v>
+        <v>910</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>1.45</v>
       </c>
       <c r="BT3">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>5.2</v>
+        <v>1.45</v>
       </c>
       <c r="BV3">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>1.45</v>
       </c>
       <c r="BX3">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>1.45</v>
       </c>
       <c r="BZ3">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13</v>
+        <v>1.45</v>
       </c>
       <c r="CB3" t="s">
         <v>250</v>
@@ -1844,226 +1844,226 @@
         <v>191</v>
       </c>
       <c r="F4">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="G4">
+        <v>1.33</v>
+      </c>
+      <c r="H4">
+        <v>13.5</v>
+      </c>
+      <c r="I4">
+        <v>14.5</v>
+      </c>
+      <c r="J4">
+        <v>5.7</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
+      </c>
+      <c r="L4">
         <v>1.38</v>
-      </c>
-      <c r="H4">
-        <v>11</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>5.3</v>
-      </c>
-      <c r="K4">
-        <v>5.6</v>
-      </c>
-      <c r="L4">
-        <v>1.34</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R4">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T4">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="V4">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W4">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="X4">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y4">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Z4">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AA4">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
         <v>13</v>
       </c>
       <c r="AD4">
+        <v>65</v>
+      </c>
+      <c r="AE4">
+        <v>360</v>
+      </c>
+      <c r="AF4">
+        <v>7</v>
+      </c>
+      <c r="AG4">
+        <v>11.5</v>
+      </c>
+      <c r="AH4">
+        <v>40</v>
+      </c>
+      <c r="AI4">
+        <v>230</v>
+      </c>
+      <c r="AJ4">
+        <v>9.6</v>
+      </c>
+      <c r="AK4">
+        <v>16</v>
+      </c>
+      <c r="AL4">
+        <v>55</v>
+      </c>
+      <c r="AM4">
+        <v>250</v>
+      </c>
+      <c r="AN4">
+        <v>5.5</v>
+      </c>
+      <c r="AO4">
+        <v>570</v>
+      </c>
+      <c r="AP4">
+        <v>16</v>
+      </c>
+      <c r="AQ4">
+        <v>32</v>
+      </c>
+      <c r="AR4">
+        <v>100</v>
+      </c>
+      <c r="AS4">
+        <v>14.5</v>
+      </c>
+      <c r="AT4">
+        <v>7</v>
+      </c>
+      <c r="AU4">
+        <v>11.5</v>
+      </c>
+      <c r="AV4">
         <v>44</v>
       </c>
-      <c r="AE4">
-        <v>200</v>
-      </c>
-      <c r="AF4">
-        <v>7.8</v>
-      </c>
-      <c r="AG4">
-        <v>11</v>
-      </c>
-      <c r="AH4">
+      <c r="AW4">
+        <v>180</v>
+      </c>
+      <c r="AX4">
+        <v>6.4</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
         <v>32</v>
       </c>
-      <c r="AI4">
-        <v>180</v>
-      </c>
-      <c r="AJ4">
-        <v>10.5</v>
-      </c>
-      <c r="AK4">
-        <v>15</v>
-      </c>
-      <c r="AL4">
-        <v>42</v>
-      </c>
-      <c r="AM4">
-        <v>190</v>
-      </c>
-      <c r="AN4">
-        <v>6.2</v>
-      </c>
-      <c r="AO4">
-        <v>290</v>
-      </c>
-      <c r="AP4">
-        <v>17.5</v>
-      </c>
-      <c r="AQ4">
-        <v>30</v>
-      </c>
-      <c r="AR4">
-        <v>14.5</v>
-      </c>
-      <c r="AS4">
-        <v>13</v>
-      </c>
-      <c r="AT4">
-        <v>7.8</v>
-      </c>
-      <c r="AU4">
-        <v>11</v>
-      </c>
-      <c r="AV4">
-        <v>36</v>
-      </c>
-      <c r="AW4">
-        <v>12.5</v>
-      </c>
-      <c r="AX4">
-        <v>7</v>
-      </c>
-      <c r="AY4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ4">
-        <v>15.5</v>
-      </c>
       <c r="BA4">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="BB4">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC4">
         <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="BE4">
+        <v>17</v>
+      </c>
+      <c r="BF4">
+        <v>5</v>
+      </c>
+      <c r="BG4">
+        <v>220</v>
+      </c>
+      <c r="BH4">
+        <v>3.65</v>
+      </c>
+      <c r="BI4">
+        <v>3.3</v>
+      </c>
+      <c r="BJ4">
+        <v>15</v>
+      </c>
+      <c r="BK4">
+        <v>12.5</v>
+      </c>
+      <c r="BL4">
+        <v>300</v>
+      </c>
+      <c r="BM4">
+        <v>11</v>
+      </c>
+      <c r="BN4">
+        <v>3.6</v>
+      </c>
+      <c r="BO4">
+        <v>3.2</v>
+      </c>
+      <c r="BP4">
+        <v>7.6</v>
+      </c>
+      <c r="BQ4">
+        <v>6.6</v>
+      </c>
+      <c r="BR4">
+        <v>36</v>
+      </c>
+      <c r="BS4">
+        <v>26</v>
+      </c>
+      <c r="BT4">
+        <v>16.5</v>
+      </c>
+      <c r="BU4">
+        <v>14</v>
+      </c>
+      <c r="BV4">
+        <v>170</v>
+      </c>
+      <c r="BW4">
+        <v>11.5</v>
+      </c>
+      <c r="BX4">
+        <v>160</v>
+      </c>
+      <c r="BY4">
+        <v>11.5</v>
+      </c>
+      <c r="BZ4">
+        <v>15.5</v>
+      </c>
+      <c r="CA4">
         <v>13</v>
-      </c>
-      <c r="BF4">
-        <v>5.5</v>
-      </c>
-      <c r="BG4">
-        <v>12.5</v>
-      </c>
-      <c r="BH4">
-        <v>3.9</v>
-      </c>
-      <c r="BI4">
-        <v>3.55</v>
-      </c>
-      <c r="BJ4">
-        <v>13</v>
-      </c>
-      <c r="BK4">
-        <v>7</v>
-      </c>
-      <c r="BL4">
-        <v>200</v>
-      </c>
-      <c r="BM4">
-        <v>14.5</v>
-      </c>
-      <c r="BN4">
-        <v>3.65</v>
-      </c>
-      <c r="BO4">
-        <v>3.35</v>
-      </c>
-      <c r="BP4">
-        <v>8</v>
-      </c>
-      <c r="BQ4">
-        <v>5.3</v>
-      </c>
-      <c r="BR4">
-        <v>26</v>
-      </c>
-      <c r="BS4">
-        <v>9.6</v>
-      </c>
-      <c r="BT4">
-        <v>14.5</v>
-      </c>
-      <c r="BU4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BV4">
-        <v>120</v>
-      </c>
-      <c r="BW4">
-        <v>13.5</v>
-      </c>
-      <c r="BX4">
-        <v>110</v>
-      </c>
-      <c r="BY4">
-        <v>13.5</v>
-      </c>
-      <c r="BZ4">
-        <v>13.5</v>
-      </c>
-      <c r="CA4">
-        <v>8.6</v>
       </c>
       <c r="CB4" t="s">
         <v>250</v>
@@ -2086,85 +2086,85 @@
         <v>192</v>
       </c>
       <c r="F5">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="G5">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="H5">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R5">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T5">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y5">
         <v>18</v>
       </c>
       <c r="Z5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -2179,31 +2179,31 @@
         <v>23</v>
       </c>
       <c r="AK5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM5">
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AR5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -2212,49 +2212,49 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AX5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BB5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC5">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD5">
         <v>27</v>
       </c>
       <c r="BE5">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BF5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BH5">
         <v>3.85</v>
       </c>
       <c r="BI5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK5">
         <v>8.199999999999999</v>
@@ -2263,49 +2263,49 @@
         <v>110</v>
       </c>
       <c r="BM5">
+        <v>75</v>
+      </c>
+      <c r="BN5">
+        <v>5</v>
+      </c>
+      <c r="BO5">
+        <v>4.5</v>
+      </c>
+      <c r="BP5">
+        <v>13.5</v>
+      </c>
+      <c r="BQ5">
         <v>11.5</v>
       </c>
-      <c r="BN5">
-        <v>4.8</v>
-      </c>
-      <c r="BO5">
-        <v>4.4</v>
-      </c>
-      <c r="BP5">
-        <v>13</v>
-      </c>
-      <c r="BQ5">
-        <v>11</v>
-      </c>
       <c r="BR5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS5">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="BT5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BV5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW5">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="BX5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BZ5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CA5">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="CB5" t="s">
         <v>250</v>
@@ -2331,13 +2331,13 @@
         <v>4.8</v>
       </c>
       <c r="G6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H6">
         <v>2.08</v>
       </c>
       <c r="I6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J6">
         <v>2.98</v>
@@ -2358,7 +2358,7 @@
         <v>1.68</v>
       </c>
       <c r="P6">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q6">
         <v>3.05</v>
@@ -2418,19 +2418,19 @@
         <v>95</v>
       </c>
       <c r="AJ6">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AK6">
         <v>140</v>
       </c>
       <c r="AL6">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AM6">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="AN6">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AO6">
         <v>42</v>
@@ -2445,7 +2445,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT6">
         <v>10</v>
@@ -2457,37 +2457,37 @@
         <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6">
         <v>19.5</v>
       </c>
       <c r="AZ6">
+        <v>7.8</v>
+      </c>
+      <c r="BA6">
+        <v>9</v>
+      </c>
+      <c r="BB6">
+        <v>9.6</v>
+      </c>
+      <c r="BC6">
+        <v>9.6</v>
+      </c>
+      <c r="BD6">
+        <v>9.6</v>
+      </c>
+      <c r="BE6">
+        <v>10</v>
+      </c>
+      <c r="BF6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG6">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BA6">
-        <v>9.4</v>
-      </c>
-      <c r="BB6">
-        <v>10</v>
-      </c>
-      <c r="BC6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD6">
-        <v>10.5</v>
-      </c>
-      <c r="BE6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG6">
-        <v>8.800000000000001</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2570,7 +2570,7 @@
         <v>194</v>
       </c>
       <c r="F7">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G7">
         <v>2.32</v>
@@ -2579,22 +2579,22 @@
         <v>4.1</v>
       </c>
       <c r="I7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
       <c r="K7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L7">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M7">
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
         <v>1.57</v>
@@ -2609,7 +2609,7 @@
         <v>1.19</v>
       </c>
       <c r="S7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T7">
         <v>2.18</v>
@@ -2618,10 +2618,10 @@
         <v>1.74</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X7">
         <v>8.6</v>
@@ -2648,7 +2648,7 @@
         <v>85</v>
       </c>
       <c r="AF7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
@@ -2687,7 +2687,7 @@
         <v>22</v>
       </c>
       <c r="AS7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
@@ -2699,7 +2699,7 @@
         <v>16</v>
       </c>
       <c r="AW7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2711,37 +2711,37 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB7">
         <v>27</v>
       </c>
       <c r="BC7">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BD7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE7">
         <v>10</v>
       </c>
       <c r="BF7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH7">
         <v>2.94</v>
       </c>
       <c r="BI7">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7">
         <v>13.5</v>
       </c>
       <c r="BK7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2750,13 +2750,13 @@
         <v>6</v>
       </c>
       <c r="BN7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ7">
         <v>4.8</v>
@@ -2768,10 +2768,10 @@
         <v>5.5</v>
       </c>
       <c r="BT7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV7">
         <v>50</v>
@@ -2780,10 +2780,10 @@
         <v>5.5</v>
       </c>
       <c r="BX7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BZ7">
         <v>60</v>
@@ -2830,7 +2830,7 @@
         <v>3.75</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
         <v>1.02</v>
@@ -2866,112 +2866,112 @@
         <v>1.8</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC8">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AQ8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AR8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AS8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AT8">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AV8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AX8">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="AY8">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AZ8">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="BA8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="BB8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="BC8">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="BD8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="BE8">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="BF8">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BG8">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3060,13 +3060,13 @@
         <v>2.08</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I9">
         <v>4.4</v>
       </c>
       <c r="J9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K9">
         <v>3.9</v>
@@ -3105,7 +3105,7 @@
         <v>1.29</v>
       </c>
       <c r="W9">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X9">
         <v>18</v>
@@ -3156,64 +3156,64 @@
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO9">
         <v>60</v>
       </c>
       <c r="AP9">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="AR9">
+        <v>4.9</v>
+      </c>
+      <c r="AS9">
+        <v>5.4</v>
+      </c>
+      <c r="AT9">
+        <v>8.4</v>
+      </c>
+      <c r="AU9">
+        <v>7.4</v>
+      </c>
+      <c r="AV9">
+        <v>14.5</v>
+      </c>
+      <c r="AW9">
+        <v>5.2</v>
+      </c>
+      <c r="AX9">
+        <v>11</v>
+      </c>
+      <c r="AY9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9">
+        <v>15.5</v>
+      </c>
+      <c r="BA9">
+        <v>5.2</v>
+      </c>
+      <c r="BB9">
         <v>4.7</v>
       </c>
-      <c r="AS9">
-        <v>5.1</v>
-      </c>
-      <c r="AT9">
-        <v>3.8</v>
-      </c>
-      <c r="AU9">
-        <v>3.45</v>
-      </c>
-      <c r="AV9">
-        <v>4.4</v>
-      </c>
-      <c r="AW9">
+      <c r="BC9">
+        <v>18</v>
+      </c>
+      <c r="BD9">
         <v>5</v>
       </c>
-      <c r="AX9">
-        <v>4.1</v>
-      </c>
-      <c r="AY9">
-        <v>3.9</v>
-      </c>
-      <c r="AZ9">
-        <v>4.5</v>
-      </c>
-      <c r="BA9">
-        <v>5</v>
-      </c>
-      <c r="BB9">
-        <v>4.5</v>
-      </c>
-      <c r="BC9">
-        <v>4.4</v>
-      </c>
-      <c r="BD9">
-        <v>4.8</v>
-      </c>
       <c r="BE9">
+        <v>5.4</v>
+      </c>
+      <c r="BF9">
+        <v>12</v>
+      </c>
+      <c r="BG9">
         <v>5.2</v>
-      </c>
-      <c r="BF9">
-        <v>4.2</v>
-      </c>
-      <c r="BG9">
-        <v>5</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3296,7 +3296,7 @@
         <v>197</v>
       </c>
       <c r="F10">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G10">
         <v>1.97</v>
@@ -3314,7 +3314,7 @@
         <v>3.95</v>
       </c>
       <c r="L10">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M10">
         <v>1.06</v>
@@ -3341,7 +3341,7 @@
         <v>1.79</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V10">
         <v>1.28</v>
@@ -3350,7 +3350,7 @@
         <v>2.02</v>
       </c>
       <c r="X10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y10">
         <v>17.5</v>
@@ -3368,10 +3368,10 @@
         <v>8.6</v>
       </c>
       <c r="AD10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE10">
-        <v>320</v>
+        <v>130</v>
       </c>
       <c r="AF10">
         <v>13.5</v>
@@ -3380,7 +3380,7 @@
         <v>11</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10">
         <v>250</v>
@@ -3395,7 +3395,7 @@
         <v>70</v>
       </c>
       <c r="AM10">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN10">
         <v>12.5</v>
@@ -3413,7 +3413,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT10">
         <v>8.800000000000001</v>
@@ -3425,7 +3425,7 @@
         <v>15</v>
       </c>
       <c r="AW10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX10">
         <v>10.5</v>
@@ -3437,10 +3437,10 @@
         <v>15.5</v>
       </c>
       <c r="BA10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BC10">
         <v>17</v>
@@ -3449,7 +3449,7 @@
         <v>16</v>
       </c>
       <c r="BE10">
-        <v>9.4</v>
+        <v>22</v>
       </c>
       <c r="BF10">
         <v>10.5</v>
@@ -3562,7 +3562,7 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O11">
         <v>1.12</v>
@@ -3577,13 +3577,13 @@
         <v>1.95</v>
       </c>
       <c r="S11">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="T11">
         <v>1.84</v>
       </c>
       <c r="U11">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="V11">
         <v>4.1</v>
@@ -3619,13 +3619,13 @@
         <v>540</v>
       </c>
       <c r="AG11">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH11">
         <v>28</v>
       </c>
       <c r="AI11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
         <v>400</v>
@@ -3643,22 +3643,22 @@
         <v>500</v>
       </c>
       <c r="AO11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AP11">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AQ11">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="AR11">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS11">
         <v>6.4</v>
       </c>
       <c r="AT11">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AU11">
         <v>14.5</v>
@@ -3667,37 +3667,37 @@
         <v>6.4</v>
       </c>
       <c r="AW11">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX11">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AZ11">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BA11">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="BB11">
+        <v>11</v>
+      </c>
+      <c r="BC11">
+        <v>10.5</v>
+      </c>
+      <c r="BD11">
+        <v>10.5</v>
+      </c>
+      <c r="BE11">
         <v>10</v>
       </c>
-      <c r="BC11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD11">
-        <v>9.6</v>
-      </c>
-      <c r="BE11">
-        <v>9.6</v>
-      </c>
       <c r="BF11">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG11">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BH11">
         <v>5.9</v>
@@ -3786,7 +3786,7 @@
         <v>1.78</v>
       </c>
       <c r="H12">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I12">
         <v>7.8</v>
@@ -3810,7 +3810,7 @@
         <v>1.35</v>
       </c>
       <c r="P12">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q12">
         <v>2.04</v>
@@ -3834,58 +3834,58 @@
         <v>2.28</v>
       </c>
       <c r="X12">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Y12">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Z12">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB12">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="AC12">
         <v>14.5</v>
       </c>
       <c r="AD12">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AE12">
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="AF12">
-        <v>19.5</v>
+        <v>40</v>
       </c>
       <c r="AG12">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AH12">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AI12">
-        <v>440</v>
+        <v>700</v>
       </c>
       <c r="AJ12">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK12">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AL12">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP12">
         <v>6.2</v>
@@ -3894,10 +3894,10 @@
         <v>9</v>
       </c>
       <c r="AR12">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AS12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AT12">
         <v>4.4</v>
@@ -3906,40 +3906,40 @@
         <v>5.1</v>
       </c>
       <c r="AV12">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AW12">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AX12">
         <v>4.9</v>
       </c>
       <c r="AY12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AZ12">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="BA12">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="BB12">
         <v>7.6</v>
       </c>
       <c r="BC12">
-        <v>1.93</v>
+        <v>10.5</v>
       </c>
       <c r="BD12">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BE12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BF12">
         <v>3.8</v>
       </c>
       <c r="BG12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -4046,13 +4046,13 @@
         <v>1.09</v>
       </c>
       <c r="N13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O13">
         <v>1.42</v>
       </c>
       <c r="P13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q13">
         <v>2.22</v>
@@ -4079,7 +4079,7 @@
         <v>11.5</v>
       </c>
       <c r="Y13">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z13">
         <v>18.5</v>
@@ -4091,7 +4091,7 @@
         <v>13</v>
       </c>
       <c r="AC13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD13">
         <v>12.5</v>
@@ -4100,13 +4100,13 @@
         <v>110</v>
       </c>
       <c r="AF13">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="AG13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH13">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AI13">
         <v>60</v>
@@ -4121,7 +4121,7 @@
         <v>70</v>
       </c>
       <c r="AM13">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN13">
         <v>55</v>
@@ -4133,13 +4133,13 @@
         <v>10</v>
       </c>
       <c r="AQ13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS13">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AT13">
         <v>9.6</v>
@@ -4151,10 +4151,10 @@
         <v>10.5</v>
       </c>
       <c r="AW13">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY13">
         <v>12</v>
@@ -4163,19 +4163,19 @@
         <v>16.5</v>
       </c>
       <c r="BA13">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB13">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC13">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BD13">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE13">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF13">
         <v>7.2</v>
@@ -4264,19 +4264,19 @@
         <v>201</v>
       </c>
       <c r="F14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G14">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H14">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I14">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K14">
         <v>4.3</v>
@@ -4288,28 +4288,28 @@
         <v>1.03</v>
       </c>
       <c r="N14">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O14">
         <v>1.16</v>
       </c>
       <c r="P14">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q14">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R14">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S14">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T14">
         <v>1.54</v>
       </c>
       <c r="U14">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V14">
         <v>2.12</v>
@@ -4342,7 +4342,7 @@
         <v>17</v>
       </c>
       <c r="AF14">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AG14">
         <v>18.5</v>
@@ -4369,7 +4369,7 @@
         <v>30</v>
       </c>
       <c r="AO14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP14">
         <v>24</v>
@@ -4506,7 +4506,7 @@
         <v>202</v>
       </c>
       <c r="F15">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G15">
         <v>2.04</v>
@@ -4524,7 +4524,7 @@
         <v>4.3</v>
       </c>
       <c r="L15">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M15">
         <v>1.04</v>
@@ -4539,10 +4539,10 @@
         <v>2.58</v>
       </c>
       <c r="Q15">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R15">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S15">
         <v>2.46</v>
@@ -4581,10 +4581,10 @@
         <v>16.5</v>
       </c>
       <c r="AE15">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
@@ -4593,7 +4593,7 @@
         <v>16.5</v>
       </c>
       <c r="AI15">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ15">
         <v>25</v>
@@ -4620,10 +4620,10 @@
         <v>17.5</v>
       </c>
       <c r="AR15">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS15">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15">
         <v>12</v>
@@ -4635,7 +4635,7 @@
         <v>14</v>
       </c>
       <c r="AW15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15">
         <v>13.5</v>
@@ -4659,13 +4659,13 @@
         <v>20</v>
       </c>
       <c r="BE15">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG15">
-        <v>19.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4763,10 +4763,10 @@
         <v>4.7</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M16">
         <v>1.05</v>
@@ -4835,7 +4835,7 @@
         <v>26</v>
       </c>
       <c r="AI16">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="AJ16">
         <v>13</v>
@@ -4883,7 +4883,7 @@
         <v>7.8</v>
       </c>
       <c r="AY16">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16">
         <v>21</v>
@@ -4910,7 +4910,7 @@
         <v>42</v>
       </c>
       <c r="BH16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI16">
         <v>3.45</v>
@@ -4919,13 +4919,13 @@
         <v>13.5</v>
       </c>
       <c r="BK16">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BL16">
         <v>180</v>
       </c>
       <c r="BM16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN16">
         <v>4.6</v>
@@ -4937,37 +4937,37 @@
         <v>11</v>
       </c>
       <c r="BQ16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BR16">
         <v>30</v>
       </c>
       <c r="BS16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT16">
         <v>14</v>
       </c>
       <c r="BU16">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV16">
         <v>90</v>
       </c>
       <c r="BW16">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BX16">
         <v>85</v>
       </c>
       <c r="BY16">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BZ16">
         <v>18.5</v>
       </c>
       <c r="CA16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="CB16" t="s">
         <v>250</v>
@@ -4990,16 +4990,16 @@
         <v>204</v>
       </c>
       <c r="F17">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G17">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H17">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="I17">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="J17">
         <v>3.8</v>
@@ -5023,7 +5023,7 @@
         <v>2.38</v>
       </c>
       <c r="Q17">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R17">
         <v>1.56</v>
@@ -5032,16 +5032,16 @@
         <v>2.62</v>
       </c>
       <c r="T17">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U17">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V17">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W17">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X17">
         <v>22</v>
@@ -5050,13 +5050,13 @@
         <v>15</v>
       </c>
       <c r="Z17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA17">
         <v>38</v>
       </c>
       <c r="AB17">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC17">
         <v>9.199999999999999</v>
@@ -5065,7 +5065,7 @@
         <v>12.5</v>
       </c>
       <c r="AE17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF17">
         <v>21</v>
@@ -5074,28 +5074,28 @@
         <v>13</v>
       </c>
       <c r="AH17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI17">
         <v>32</v>
       </c>
       <c r="AJ17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL17">
         <v>32</v>
       </c>
       <c r="AM17">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AN17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP17">
         <v>19</v>
@@ -5107,7 +5107,7 @@
         <v>17.5</v>
       </c>
       <c r="AS17">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AT17">
         <v>13.5</v>
@@ -5143,7 +5143,7 @@
         <v>24</v>
       </c>
       <c r="BE17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF17">
         <v>14.5</v>
@@ -5232,7 +5232,7 @@
         <v>205</v>
       </c>
       <c r="F18">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G18">
         <v>2.38</v>
@@ -5262,13 +5262,13 @@
         <v>1.33</v>
       </c>
       <c r="P18">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R18">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S18">
         <v>3.55</v>
@@ -5292,7 +5292,7 @@
         <v>13</v>
       </c>
       <c r="Z18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA18">
         <v>65</v>
@@ -5307,7 +5307,7 @@
         <v>13.5</v>
       </c>
       <c r="AE18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF18">
         <v>14.5</v>
@@ -5334,7 +5334,7 @@
         <v>90</v>
       </c>
       <c r="AN18">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO18">
         <v>40</v>
@@ -5474,13 +5474,13 @@
         <v>206</v>
       </c>
       <c r="F19">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G19">
         <v>1.7</v>
       </c>
       <c r="H19">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I19">
         <v>6.4</v>
@@ -5489,40 +5489,40 @@
         <v>4.2</v>
       </c>
       <c r="K19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M19">
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O19">
         <v>1.27</v>
       </c>
       <c r="P19">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q19">
         <v>1.79</v>
       </c>
       <c r="R19">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S19">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="T19">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U19">
         <v>2.02</v>
       </c>
       <c r="V19">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W19">
         <v>2.42</v>
@@ -5582,13 +5582,13 @@
         <v>110</v>
       </c>
       <c r="AP19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ19">
         <v>17.5</v>
       </c>
       <c r="AR19">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS19">
         <v>10.5</v>
@@ -5630,70 +5630,70 @@
         <v>10</v>
       </c>
       <c r="BF19">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG19">
         <v>10</v>
       </c>
       <c r="BH19">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
         <v>250</v>
@@ -5725,7 +5725,7 @@
         <v>2.28</v>
       </c>
       <c r="I20">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J20">
         <v>3.85</v>
@@ -5752,7 +5752,7 @@
         <v>1.62</v>
       </c>
       <c r="R20">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S20">
         <v>2.56</v>
@@ -5764,10 +5764,10 @@
         <v>2.56</v>
       </c>
       <c r="V20">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W20">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X20">
         <v>28</v>
@@ -5833,7 +5833,7 @@
         <v>15.5</v>
       </c>
       <c r="AS20">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AT20">
         <v>14.5</v>
@@ -5866,7 +5866,7 @@
         <v>21</v>
       </c>
       <c r="BD20">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BE20">
         <v>4.3</v>
@@ -5958,13 +5958,13 @@
         <v>208</v>
       </c>
       <c r="F21">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G21">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H21">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I21">
         <v>3.1</v>
@@ -5985,7 +5985,7 @@
         <v>7</v>
       </c>
       <c r="O21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P21">
         <v>3</v>
@@ -5997,7 +5997,7 @@
         <v>1.82</v>
       </c>
       <c r="S21">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="T21">
         <v>1.44</v>
@@ -6009,7 +6009,7 @@
         <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X21">
         <v>44</v>
@@ -6063,7 +6063,7 @@
         <v>11</v>
       </c>
       <c r="AO21">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP21">
         <v>14.5</v>
@@ -6075,7 +6075,7 @@
         <v>20</v>
       </c>
       <c r="AS21">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT21">
         <v>16.5</v>
@@ -6111,7 +6111,7 @@
         <v>17.5</v>
       </c>
       <c r="BE21">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF21">
         <v>7.8</v>
@@ -6200,16 +6200,16 @@
         <v>209</v>
       </c>
       <c r="F22">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G22">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <v>2.36</v>
       </c>
       <c r="I22">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="J22">
         <v>4.1</v>
@@ -6230,13 +6230,13 @@
         <v>1.17</v>
       </c>
       <c r="P22">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R22">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S22">
         <v>2.26</v>
@@ -6245,13 +6245,13 @@
         <v>1.5</v>
       </c>
       <c r="U22">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V22">
         <v>1.7</v>
       </c>
       <c r="W22">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X22">
         <v>34</v>
@@ -6305,7 +6305,7 @@
         <v>16</v>
       </c>
       <c r="AO22">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP22">
         <v>19.5</v>
@@ -6442,7 +6442,7 @@
         <v>210</v>
       </c>
       <c r="F23">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G23">
         <v>4.2</v>
@@ -6457,7 +6457,7 @@
         <v>3.85</v>
       </c>
       <c r="K23">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6487,7 +6487,7 @@
         <v>1.54</v>
       </c>
       <c r="U23">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
         <v>1.84</v>
@@ -6496,73 +6496,73 @@
         <v>1.32</v>
       </c>
       <c r="X23">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="Z23">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB23">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
         <v>42</v>
       </c>
       <c r="AD23">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="AE23">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AF23">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN23">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AO23">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="AQ23">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR23">
         <v>8.4</v>
       </c>
       <c r="AS23">
-        <v>2.06</v>
+        <v>1.41</v>
       </c>
       <c r="AT23">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="AU23">
         <v>4.9</v>
@@ -6571,34 +6571,34 @@
         <v>6.2</v>
       </c>
       <c r="AW23">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="AX23">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="AY23">
-        <v>8.4</v>
+        <v>1.41</v>
       </c>
       <c r="AZ23">
         <v>8.4</v>
       </c>
       <c r="BA23">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="BB23">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="BC23">
-        <v>2.06</v>
+        <v>1.42</v>
       </c>
       <c r="BD23">
-        <v>2.06</v>
+        <v>1.42</v>
       </c>
       <c r="BE23">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="BF23">
-        <v>4.3</v>
+        <v>1.55</v>
       </c>
       <c r="BG23">
         <v>2.68</v>
@@ -6702,7 +6702,7 @@
         <v>6.6</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M24">
         <v>1.02</v>
@@ -6756,7 +6756,7 @@
         <v>16.5</v>
       </c>
       <c r="AD24">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AE24">
         <v>130</v>
@@ -6795,13 +6795,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ24">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR24">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS24">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT24">
         <v>11</v>
@@ -6810,10 +6810,10 @@
         <v>12</v>
       </c>
       <c r="AV24">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AW24">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX24">
         <v>9.199999999999999</v>
@@ -6825,7 +6825,7 @@
         <v>20</v>
       </c>
       <c r="BA24">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB24">
         <v>10.5</v>
@@ -6837,7 +6837,7 @@
         <v>14.5</v>
       </c>
       <c r="BE24">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF24">
         <v>3.75</v>
@@ -6846,13 +6846,13 @@
         <v>10.5</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK24">
         <v>1.04</v>
@@ -6864,43 +6864,43 @@
         <v>1.04</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS24">
         <v>1.04</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU24">
         <v>1.04</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW24">
         <v>1.04</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY24">
         <v>1.04</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA24">
         <v>1.04</v>
@@ -6935,7 +6935,7 @@
         <v>17.5</v>
       </c>
       <c r="I25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J25">
         <v>6.4</v>
@@ -6956,7 +6956,7 @@
         <v>1.25</v>
       </c>
       <c r="P25">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q25">
         <v>1.73</v>
@@ -6977,7 +6977,7 @@
         <v>1.05</v>
       </c>
       <c r="W25">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X25">
         <v>25</v>
@@ -7016,7 +7016,7 @@
         <v>330</v>
       </c>
       <c r="AJ25">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AK25">
         <v>16.5</v>
@@ -7189,7 +7189,7 @@
         <v>1.55</v>
       </c>
       <c r="M26">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N26">
         <v>2.58</v>
@@ -7210,7 +7210,7 @@
         <v>5.5</v>
       </c>
       <c r="T26">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U26">
         <v>1.72</v>
@@ -7413,13 +7413,13 @@
         <v>1.15</v>
       </c>
       <c r="G27">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="H27">
         <v>20</v>
       </c>
       <c r="I27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J27">
         <v>10.5</v>
@@ -7440,19 +7440,19 @@
         <v>1.07</v>
       </c>
       <c r="P27">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Q27">
         <v>1.23</v>
       </c>
       <c r="R27">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="S27">
         <v>1.59</v>
       </c>
       <c r="T27">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U27">
         <v>2.08</v>
@@ -7470,7 +7470,7 @@
         <v>130</v>
       </c>
       <c r="Z27">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AA27">
         <v>1000</v>
@@ -7485,7 +7485,7 @@
         <v>90</v>
       </c>
       <c r="AE27">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AF27">
         <v>15.5</v>
@@ -7494,13 +7494,13 @@
         <v>15</v>
       </c>
       <c r="AH27">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI27">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK27">
         <v>14</v>
@@ -7515,16 +7515,16 @@
         <v>2.28</v>
       </c>
       <c r="AO27">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AP27">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="AQ27">
         <v>29</v>
       </c>
       <c r="AR27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS27">
         <v>10.5</v>
@@ -7539,7 +7539,7 @@
         <v>42</v>
       </c>
       <c r="AW27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX27">
         <v>11.5</v>
@@ -7548,7 +7548,7 @@
         <v>13</v>
       </c>
       <c r="AZ27">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BA27">
         <v>10.5</v>
@@ -7563,13 +7563,13 @@
         <v>20</v>
       </c>
       <c r="BE27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF27">
         <v>2.14</v>
       </c>
       <c r="BG27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7629,7 +7629,7 @@
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
         <v>250</v>
@@ -7652,10 +7652,10 @@
         <v>215</v>
       </c>
       <c r="F28">
+        <v>1.89</v>
+      </c>
+      <c r="G28">
         <v>1.91</v>
-      </c>
-      <c r="G28">
-        <v>1.92</v>
       </c>
       <c r="H28">
         <v>5.3</v>
@@ -7769,10 +7769,10 @@
         <v>34</v>
       </c>
       <c r="AS28">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU28">
         <v>7.2</v>
@@ -7817,7 +7817,7 @@
         <v>2.98</v>
       </c>
       <c r="BI28">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ28">
         <v>11</v>
@@ -7841,7 +7841,7 @@
         <v>14</v>
       </c>
       <c r="BQ28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BR28">
         <v>34</v>
@@ -7897,19 +7897,19 @@
         <v>2.72</v>
       </c>
       <c r="G29">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H29">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I29">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J29">
         <v>3.5</v>
       </c>
       <c r="K29">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L29">
         <v>1.32</v>
@@ -7918,7 +7918,7 @@
         <v>1.06</v>
       </c>
       <c r="N29">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O29">
         <v>1.28</v>
@@ -7927,7 +7927,7 @@
         <v>2.08</v>
       </c>
       <c r="Q29">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R29">
         <v>1.43</v>
@@ -7939,13 +7939,13 @@
         <v>1.69</v>
       </c>
       <c r="U29">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V29">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W29">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X29">
         <v>16.5</v>
@@ -7993,10 +7993,10 @@
         <v>38</v>
       </c>
       <c r="AM29">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO29">
         <v>22</v>
@@ -8011,7 +8011,7 @@
         <v>16.5</v>
       </c>
       <c r="AS29">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT29">
         <v>11.5</v>
@@ -8023,7 +8023,7 @@
         <v>11</v>
       </c>
       <c r="AW29">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AX29">
         <v>17</v>
@@ -8041,7 +8041,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC29">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="BD29">
         <v>9</v>
@@ -8065,7 +8065,7 @@
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BL29">
         <v>1000</v>
@@ -8077,7 +8077,7 @@
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="BP29">
         <v>1000</v>
@@ -8095,7 +8095,7 @@
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BV29">
         <v>1000</v>
@@ -8142,7 +8142,7 @@
         <v>1.48</v>
       </c>
       <c r="H30">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="I30">
         <v>23</v>
@@ -8151,7 +8151,7 @@
         <v>5.5</v>
       </c>
       <c r="K30">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8190,10 +8190,10 @@
         <v>3.1</v>
       </c>
       <c r="X30">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="Y30">
-        <v>140</v>
+        <v>950</v>
       </c>
       <c r="Z30">
         <v>540</v>
@@ -8202,13 +8202,13 @@
         <v>1000</v>
       </c>
       <c r="AB30">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="AC30">
-        <v>18</v>
+        <v>950</v>
       </c>
       <c r="AD30">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AE30">
         <v>1000</v>
@@ -8217,10 +8217,10 @@
         <v>18.5</v>
       </c>
       <c r="AG30">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="AH30">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI30">
         <v>470</v>
@@ -8244,7 +8244,7 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="AQ30">
         <v>4.2</v>
@@ -8256,10 +8256,10 @@
         <v>2.5</v>
       </c>
       <c r="AT30">
-        <v>6.4</v>
+        <v>1.64</v>
       </c>
       <c r="AU30">
-        <v>7</v>
+        <v>1.63</v>
       </c>
       <c r="AV30">
         <v>4.2</v>
@@ -8268,31 +8268,31 @@
         <v>2.5</v>
       </c>
       <c r="AX30">
-        <v>5.1</v>
+        <v>1.63</v>
       </c>
       <c r="AY30">
-        <v>6.2</v>
+        <v>1.61</v>
       </c>
       <c r="AZ30">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="BA30">
         <v>4.2</v>
       </c>
       <c r="BB30">
-        <v>6.2</v>
+        <v>1.69</v>
       </c>
       <c r="BC30">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="BD30">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="BE30">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BF30">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="BG30">
         <v>3.4</v>
@@ -8384,10 +8384,10 @@
         <v>1.92</v>
       </c>
       <c r="H31">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I31">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J31">
         <v>3.9</v>
@@ -8408,16 +8408,16 @@
         <v>1.26</v>
       </c>
       <c r="P31">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q31">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R31">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S31">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T31">
         <v>1.71</v>
@@ -8456,7 +8456,7 @@
         <v>55</v>
       </c>
       <c r="AF31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG31">
         <v>11</v>
@@ -8468,34 +8468,34 @@
         <v>55</v>
       </c>
       <c r="AJ31">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK31">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM31">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN31">
         <v>11</v>
       </c>
       <c r="AO31">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="AP31">
         <v>16.5</v>
       </c>
       <c r="AQ31">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR31">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AS31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT31">
         <v>9.6</v>
@@ -8504,10 +8504,10 @@
         <v>8</v>
       </c>
       <c r="AV31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW31">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX31">
         <v>11</v>
@@ -8519,7 +8519,7 @@
         <v>15.5</v>
       </c>
       <c r="BA31">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB31">
         <v>18</v>
@@ -8528,16 +8528,16 @@
         <v>16</v>
       </c>
       <c r="BD31">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="BE31">
+        <v>11</v>
+      </c>
+      <c r="BF31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG31">
         <v>10</v>
-      </c>
-      <c r="BF31">
-        <v>9.4</v>
-      </c>
-      <c r="BG31">
-        <v>9.199999999999999</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8629,7 +8629,7 @@
         <v>1.93</v>
       </c>
       <c r="I32">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J32">
         <v>3.8</v>
@@ -8653,7 +8653,7 @@
         <v>2.18</v>
       </c>
       <c r="Q32">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R32">
         <v>1.46</v>
@@ -8674,7 +8674,7 @@
         <v>1.28</v>
       </c>
       <c r="X32">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y32">
         <v>10.5</v>
@@ -8686,7 +8686,7 @@
         <v>22</v>
       </c>
       <c r="AB32">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC32">
         <v>8.800000000000001</v>
@@ -8695,7 +8695,7 @@
         <v>10.5</v>
       </c>
       <c r="AE32">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AF32">
         <v>34</v>
@@ -8740,7 +8740,7 @@
         <v>20</v>
       </c>
       <c r="AT32">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU32">
         <v>8</v>
@@ -8749,7 +8749,7 @@
         <v>9.4</v>
       </c>
       <c r="AW32">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX32">
         <v>30</v>
@@ -8764,7 +8764,7 @@
         <v>28</v>
       </c>
       <c r="BB32">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC32">
         <v>44</v>
@@ -8773,7 +8773,7 @@
         <v>46</v>
       </c>
       <c r="BE32">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BF32">
         <v>32</v>
@@ -8865,13 +8865,13 @@
         <v>1.52</v>
       </c>
       <c r="G33">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H33">
         <v>6.2</v>
       </c>
       <c r="I33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>4.8</v>
@@ -8892,13 +8892,13 @@
         <v>1.18</v>
       </c>
       <c r="P33">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q33">
         <v>1.55</v>
       </c>
       <c r="R33">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S33">
         <v>2.36</v>
@@ -8913,7 +8913,7 @@
         <v>1.17</v>
       </c>
       <c r="W33">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X33">
         <v>34</v>
@@ -8973,7 +8973,7 @@
         <v>23</v>
       </c>
       <c r="AQ33">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AR33">
         <v>10</v>
@@ -9012,13 +9012,13 @@
         <v>13</v>
       </c>
       <c r="BD33">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BE33">
         <v>19</v>
       </c>
       <c r="BF33">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG33">
         <v>10</v>
@@ -9833,25 +9833,25 @@
         <v>4.8</v>
       </c>
       <c r="G37">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H37">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="I37">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J37">
         <v>3.95</v>
       </c>
       <c r="K37">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L37">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M37">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N37">
         <v>3.85</v>
@@ -9860,10 +9860,10 @@
         <v>1.32</v>
       </c>
       <c r="P37">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q37">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R37">
         <v>1.38</v>
@@ -9884,7 +9884,7 @@
         <v>1.23</v>
       </c>
       <c r="X37">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -9896,10 +9896,10 @@
         <v>21</v>
       </c>
       <c r="AB37">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC37">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD37">
         <v>10.5</v>
@@ -9911,28 +9911,28 @@
         <v>40</v>
       </c>
       <c r="AG37">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH37">
         <v>21</v>
       </c>
       <c r="AI37">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AJ37">
         <v>130</v>
       </c>
       <c r="AK37">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL37">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM37">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN37">
-        <v>530</v>
+        <v>80</v>
       </c>
       <c r="AO37">
         <v>11.5</v>
@@ -9941,13 +9941,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ37">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR37">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS37">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AT37">
         <v>14.5</v>
@@ -9959,10 +9959,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW37">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AX37">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AY37">
         <v>16.5</v>
@@ -9974,22 +9974,22 @@
         <v>18</v>
       </c>
       <c r="BB37">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC37">
+        <v>55</v>
+      </c>
+      <c r="BD37">
+        <v>55</v>
+      </c>
+      <c r="BE37">
+        <v>30</v>
+      </c>
+      <c r="BF37">
+        <v>46</v>
+      </c>
+      <c r="BG37">
         <v>10</v>
-      </c>
-      <c r="BD37">
-        <v>10</v>
-      </c>
-      <c r="BE37">
-        <v>10.5</v>
-      </c>
-      <c r="BF37">
-        <v>10</v>
-      </c>
-      <c r="BG37">
-        <v>8.6</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -10084,13 +10084,13 @@
         <v>32</v>
       </c>
       <c r="J38">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="K38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="L38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M38">
         <v>1.01</v>
@@ -10123,7 +10123,7 @@
         <v>1.03</v>
       </c>
       <c r="W38">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="X38">
         <v>950</v>
@@ -10132,7 +10132,7 @@
         <v>950</v>
       </c>
       <c r="Z38">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AA38">
         <v>1000</v>
@@ -10147,7 +10147,7 @@
         <v>950</v>
       </c>
       <c r="AE38">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="AF38">
         <v>11</v>
@@ -10192,7 +10192,7 @@
         <v>6</v>
       </c>
       <c r="AT38">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU38">
         <v>18</v>
@@ -10201,13 +10201,13 @@
         <v>5.7</v>
       </c>
       <c r="AW38">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX38">
         <v>7.6</v>
       </c>
       <c r="AY38">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AZ38">
         <v>5.4</v>
@@ -10243,13 +10243,13 @@
         <v>15.5</v>
       </c>
       <c r="BK38">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN38">
         <v>4.1</v>
@@ -10267,31 +10267,31 @@
         <v>22</v>
       </c>
       <c r="BS38">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT38">
         <v>23</v>
       </c>
       <c r="BU38">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ38">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CA38">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB38" t="s">
         <v>250</v>
@@ -10338,7 +10338,7 @@
         <v>1.04</v>
       </c>
       <c r="N39">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O39">
         <v>1.22</v>
@@ -10389,7 +10389,7 @@
         <v>22</v>
       </c>
       <c r="AE39">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AF39">
         <v>10.5</v>
@@ -10425,13 +10425,13 @@
         <v>19</v>
       </c>
       <c r="AQ39">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR39">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AS39">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AT39">
         <v>9.800000000000001</v>
@@ -10556,64 +10556,64 @@
         <v>227</v>
       </c>
       <c r="F40">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G40">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H40">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I40">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J40">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K40">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L40">
         <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N40">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O40">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P40">
         <v>2.26</v>
       </c>
       <c r="Q40">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="R40">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S40">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T40">
         <v>1.54</v>
       </c>
       <c r="U40">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V40">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W40">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X40">
         <v>1000</v>
       </c>
       <c r="Y40">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z40">
         <v>150</v>
@@ -10622,25 +10622,25 @@
         <v>900</v>
       </c>
       <c r="AB40">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC40">
         <v>14</v>
       </c>
       <c r="AD40">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE40">
         <v>160</v>
       </c>
       <c r="AF40">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG40">
         <v>13</v>
       </c>
       <c r="AH40">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI40">
         <v>210</v>
@@ -10649,10 +10649,10 @@
         <v>900</v>
       </c>
       <c r="AK40">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL40">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AM40">
         <v>580</v>
@@ -10664,55 +10664,55 @@
         <v>48</v>
       </c>
       <c r="AP40">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AQ40">
-        <v>12</v>
+        <v>1.54</v>
       </c>
       <c r="AR40">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AS40">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AT40">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AU40">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV40">
         <v>9</v>
       </c>
       <c r="AW40">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="AX40">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AY40">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AZ40">
         <v>12</v>
       </c>
       <c r="BA40">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="BB40">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="BC40">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="BD40">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="BE40">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="BF40">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="BG40">
         <v>3.9</v>
@@ -10798,7 +10798,7 @@
         <v>228</v>
       </c>
       <c r="F41">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G41">
         <v>2.48</v>
@@ -10807,7 +10807,7 @@
         <v>3.1</v>
       </c>
       <c r="I41">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J41">
         <v>3.6</v>
@@ -10846,7 +10846,7 @@
         <v>2.24</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
         <v>1.68</v>
@@ -11040,25 +11040,25 @@
         <v>229</v>
       </c>
       <c r="F42">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G42">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H42">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I42">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J42">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K42">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L42">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M42">
         <v>1.06</v>
@@ -11070,10 +11070,10 @@
         <v>1.28</v>
       </c>
       <c r="P42">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q42">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R42">
         <v>1.39</v>
@@ -11091,7 +11091,7 @@
         <v>1.42</v>
       </c>
       <c r="W42">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X42">
         <v>21</v>
@@ -11106,7 +11106,7 @@
         <v>65</v>
       </c>
       <c r="AB42">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC42">
         <v>8.6</v>
@@ -11115,7 +11115,7 @@
         <v>16</v>
       </c>
       <c r="AE42">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF42">
         <v>20</v>
@@ -11124,28 +11124,28 @@
         <v>13.5</v>
       </c>
       <c r="AH42">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI42">
         <v>55</v>
       </c>
       <c r="AJ42">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK42">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL42">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM42">
         <v>95</v>
       </c>
       <c r="AN42">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO42">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AP42">
         <v>14.5</v>
@@ -11157,7 +11157,7 @@
         <v>17</v>
       </c>
       <c r="AS42">
-        <v>5.5</v>
+        <v>38</v>
       </c>
       <c r="AT42">
         <v>10</v>
@@ -11169,7 +11169,7 @@
         <v>12</v>
       </c>
       <c r="AW42">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AX42">
         <v>14</v>
@@ -11193,13 +11193,13 @@
         <v>16</v>
       </c>
       <c r="BE42">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF42">
         <v>15</v>
       </c>
       <c r="BG42">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BH42">
         <v>4.3</v>
@@ -11241,7 +11241,7 @@
         <v>7.8</v>
       </c>
       <c r="BU42">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="BV42">
         <v>29</v>
@@ -11282,28 +11282,28 @@
         <v>230</v>
       </c>
       <c r="F43">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G43">
         <v>2.1</v>
       </c>
       <c r="H43">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I43">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J43">
         <v>4.1</v>
       </c>
       <c r="K43">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L43">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N43">
         <v>5.5</v>
@@ -11312,10 +11312,10 @@
         <v>1.19</v>
       </c>
       <c r="P43">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q43">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R43">
         <v>1.63</v>
@@ -11336,7 +11336,7 @@
         <v>1.9</v>
       </c>
       <c r="X43">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="Y43">
         <v>21</v>
@@ -11390,7 +11390,7 @@
         <v>24</v>
       </c>
       <c r="AP43">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AQ43">
         <v>16.5</v>
@@ -11423,7 +11423,7 @@
         <v>13.5</v>
       </c>
       <c r="BA43">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB43">
         <v>22</v>
@@ -11435,7 +11435,7 @@
         <v>19</v>
       </c>
       <c r="BE43">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF43">
         <v>8.6</v>
@@ -11447,7 +11447,7 @@
         <v>4.6</v>
       </c>
       <c r="BI43">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ43">
         <v>9</v>
@@ -11530,10 +11530,10 @@
         <v>2.22</v>
       </c>
       <c r="H44">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I44">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J44">
         <v>3.5</v>
@@ -11542,7 +11542,7 @@
         <v>3.65</v>
       </c>
       <c r="L44">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M44">
         <v>1.07</v>
@@ -11554,28 +11554,28 @@
         <v>1.32</v>
       </c>
       <c r="P44">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q44">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R44">
         <v>1.38</v>
       </c>
       <c r="S44">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T44">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U44">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V44">
         <v>1.34</v>
       </c>
       <c r="W44">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X44">
         <v>15</v>
@@ -11593,7 +11593,7 @@
         <v>11.5</v>
       </c>
       <c r="AC44">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD44">
         <v>16</v>
@@ -11602,7 +11602,7 @@
         <v>55</v>
       </c>
       <c r="AF44">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG44">
         <v>11</v>
@@ -11620,7 +11620,7 @@
         <v>24</v>
       </c>
       <c r="AL44">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AM44">
         <v>380</v>
@@ -11641,7 +11641,7 @@
         <v>13</v>
       </c>
       <c r="AS44">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT44">
         <v>8.800000000000001</v>
@@ -11653,7 +11653,7 @@
         <v>13.5</v>
       </c>
       <c r="AW44">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX44">
         <v>12</v>
@@ -11665,7 +11665,7 @@
         <v>15</v>
       </c>
       <c r="BA44">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB44">
         <v>11.5</v>
@@ -11674,22 +11674,22 @@
         <v>10.5</v>
       </c>
       <c r="BD44">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BE44">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF44">
         <v>14</v>
       </c>
       <c r="BG44">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH44">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI44">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="BJ44">
         <v>9.6</v>
@@ -11701,25 +11701,25 @@
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN44">
         <v>5</v>
       </c>
       <c r="BO44">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP44">
         <v>15.5</v>
       </c>
       <c r="BQ44">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR44">
         <v>1000</v>
       </c>
       <c r="BS44">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT44">
         <v>7</v>
@@ -11731,19 +11731,19 @@
         <v>1000</v>
       </c>
       <c r="BW44">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX44">
         <v>1000</v>
       </c>
       <c r="BY44">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ44">
         <v>1000</v>
       </c>
       <c r="CA44">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB44" t="s">
         <v>250</v>
@@ -11847,7 +11847,7 @@
         <v>20</v>
       </c>
       <c r="AG45">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH45">
         <v>16</v>
@@ -11910,7 +11910,7 @@
         <v>29</v>
       </c>
       <c r="BB45">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BC45">
         <v>18</v>
@@ -12008,58 +12008,58 @@
         <v>233</v>
       </c>
       <c r="F46">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G46">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H46">
         <v>2.48</v>
       </c>
       <c r="I46">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="J46">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L46">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M46">
         <v>1.04</v>
       </c>
       <c r="N46">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O46">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P46">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q46">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R46">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S46">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="T46">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U46">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V46">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W46">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X46">
         <v>22</v>
@@ -12071,13 +12071,13 @@
         <v>23</v>
       </c>
       <c r="AA46">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AB46">
         <v>16</v>
       </c>
       <c r="AC46">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD46">
         <v>14</v>
@@ -12095,37 +12095,37 @@
         <v>19.5</v>
       </c>
       <c r="AI46">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AJ46">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK46">
         <v>30</v>
       </c>
       <c r="AL46">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM46">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN46">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO46">
         <v>22</v>
       </c>
       <c r="AP46">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ46">
         <v>11</v>
       </c>
       <c r="AR46">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS46">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT46">
         <v>12</v>
@@ -12137,10 +12137,10 @@
         <v>10.5</v>
       </c>
       <c r="AW46">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="AX46">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY46">
         <v>11</v>
@@ -12149,22 +12149,22 @@
         <v>13.5</v>
       </c>
       <c r="BA46">
-        <v>16</v>
+        <v>5.2</v>
       </c>
       <c r="BB46">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC46">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BD46">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE46">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF46">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG46">
         <v>15.5</v>
@@ -12253,7 +12253,7 @@
         <v>2.04</v>
       </c>
       <c r="G47">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -12265,16 +12265,16 @@
         <v>3.7</v>
       </c>
       <c r="K47">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L47">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M47">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O47">
         <v>1.31</v>
@@ -12283,7 +12283,7 @@
         <v>2.02</v>
       </c>
       <c r="Q47">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R47">
         <v>1.39</v>
@@ -12295,34 +12295,34 @@
         <v>1.79</v>
       </c>
       <c r="U47">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V47">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W47">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X47">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y47">
         <v>15.5</v>
       </c>
       <c r="Z47">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA47">
         <v>85</v>
       </c>
       <c r="AB47">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC47">
         <v>8.199999999999999</v>
       </c>
       <c r="AD47">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE47">
         <v>48</v>
@@ -12331,7 +12331,7 @@
         <v>13</v>
       </c>
       <c r="AG47">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH47">
         <v>17.5</v>
@@ -12361,13 +12361,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ47">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR47">
         <v>26</v>
       </c>
       <c r="AS47">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AT47">
         <v>9.199999999999999</v>
@@ -12385,13 +12385,13 @@
         <v>11.5</v>
       </c>
       <c r="AY47">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ47">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA47">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB47">
         <v>21</v>
@@ -12400,13 +12400,13 @@
         <v>19</v>
       </c>
       <c r="BD47">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE47">
         <v>60</v>
       </c>
       <c r="BF47">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG47">
         <v>40</v>
@@ -12492,16 +12492,16 @@
         <v>235</v>
       </c>
       <c r="F48">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G48">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H48">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I48">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J48">
         <v>4</v>
@@ -12510,7 +12510,7 @@
         <v>4.3</v>
       </c>
       <c r="L48">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M48">
         <v>1.03</v>
@@ -12519,7 +12519,7 @@
         <v>5.5</v>
       </c>
       <c r="O48">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P48">
         <v>2.56</v>
@@ -12528,19 +12528,19 @@
         <v>1.53</v>
       </c>
       <c r="R48">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S48">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="T48">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U48">
         <v>2.74</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W48">
         <v>1.84</v>
@@ -12552,7 +12552,7 @@
         <v>21</v>
       </c>
       <c r="Z48">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AA48">
         <v>70</v>
@@ -12564,22 +12564,22 @@
         <v>11</v>
       </c>
       <c r="AD48">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE48">
         <v>40</v>
       </c>
       <c r="AF48">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG48">
         <v>12</v>
       </c>
       <c r="AH48">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI48">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AJ48">
         <v>32</v>
@@ -12591,28 +12591,28 @@
         <v>38</v>
       </c>
       <c r="AM48">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN48">
         <v>10.5</v>
       </c>
       <c r="AO48">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP48">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ48">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR48">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS48">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="AT48">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU48">
         <v>8.800000000000001</v>
@@ -12621,19 +12621,19 @@
         <v>12.5</v>
       </c>
       <c r="AW48">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AX48">
         <v>14.5</v>
       </c>
       <c r="AY48">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ48">
         <v>13</v>
       </c>
       <c r="BA48">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="BB48">
         <v>20</v>
@@ -12645,10 +12645,10 @@
         <v>20</v>
       </c>
       <c r="BE48">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BF48">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG48">
         <v>18</v>
@@ -12737,7 +12737,7 @@
         <v>1.57</v>
       </c>
       <c r="G49">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H49">
         <v>5.2</v>
@@ -12749,43 +12749,43 @@
         <v>4.6</v>
       </c>
       <c r="K49">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L49">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M49">
         <v>1.03</v>
       </c>
       <c r="N49">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O49">
         <v>1.15</v>
       </c>
       <c r="P49">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q49">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R49">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S49">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T49">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U49">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V49">
         <v>1.2</v>
       </c>
       <c r="W49">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="X49">
         <v>38</v>
@@ -12803,7 +12803,7 @@
         <v>16.5</v>
       </c>
       <c r="AC49">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD49">
         <v>26</v>
@@ -12812,7 +12812,7 @@
         <v>70</v>
       </c>
       <c r="AF49">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG49">
         <v>13</v>
@@ -12851,7 +12851,7 @@
         <v>23</v>
       </c>
       <c r="AS49">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT49">
         <v>11.5</v>
@@ -12863,7 +12863,7 @@
         <v>19</v>
       </c>
       <c r="AW49">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AX49">
         <v>11</v>
@@ -12887,10 +12887,10 @@
         <v>18</v>
       </c>
       <c r="BE49">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF49">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG49">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>1.95</v>
       </c>
       <c r="G50">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H50">
         <v>2.24</v>
@@ -12991,7 +12991,7 @@
         <v>3.2</v>
       </c>
       <c r="K50">
-        <v>470</v>
+        <v>10</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -13000,16 +13000,16 @@
         <v>1.02</v>
       </c>
       <c r="N50">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="O50">
         <v>1.14</v>
       </c>
       <c r="P50">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="Q50">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="R50">
         <v>1.57</v>
@@ -13027,109 +13027,109 @@
         <v>1.47</v>
       </c>
       <c r="W50">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X50">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Y50">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Z50">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA50">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB50">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AC50">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD50">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AE50">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF50">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AG50">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="AH50">
         <v>130</v>
       </c>
       <c r="AI50">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ50">
         <v>900</v>
       </c>
       <c r="AK50">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL50">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM50">
         <v>580</v>
       </c>
       <c r="AN50">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO50">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AP50">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="AQ50">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="AR50">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="AS50">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AT50">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AU50">
         <v>5.1</v>
       </c>
       <c r="AV50">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="AW50">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="AX50">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="AY50">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AZ50">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="BA50">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="BB50">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="BC50">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="BD50">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="BE50">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BF50">
         <v>3.25</v>
@@ -13218,7 +13218,7 @@
         <v>238</v>
       </c>
       <c r="F51">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G51">
         <v>1.77</v>
@@ -13230,13 +13230,13 @@
         <v>4.6</v>
       </c>
       <c r="J51">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K51">
         <v>5.7</v>
       </c>
       <c r="L51">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M51">
         <v>1.01</v>
@@ -13245,10 +13245,10 @@
         <v>12</v>
       </c>
       <c r="O51">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P51">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q51">
         <v>1.23</v>
@@ -13266,19 +13266,19 @@
         <v>3.65</v>
       </c>
       <c r="V51">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W51">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X51">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="Y51">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="Z51">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA51">
         <v>120</v>
@@ -13299,10 +13299,10 @@
         <v>25</v>
       </c>
       <c r="AG51">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH51">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI51">
         <v>36</v>
@@ -13326,19 +13326,19 @@
         <v>16.5</v>
       </c>
       <c r="AP51">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AQ51">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR51">
+        <v>8</v>
+      </c>
+      <c r="AS51">
+        <v>7.8</v>
+      </c>
+      <c r="AT51">
         <v>7</v>
-      </c>
-      <c r="AS51">
-        <v>7.2</v>
-      </c>
-      <c r="AT51">
-        <v>6.4</v>
       </c>
       <c r="AU51">
         <v>14.5</v>
@@ -13347,7 +13347,7 @@
         <v>18.5</v>
       </c>
       <c r="AW51">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX51">
         <v>20</v>
@@ -13359,7 +13359,7 @@
         <v>13</v>
       </c>
       <c r="BA51">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="BB51">
         <v>19.5</v>
@@ -13371,7 +13371,7 @@
         <v>16</v>
       </c>
       <c r="BE51">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BF51">
         <v>3.7</v>
@@ -13460,10 +13460,10 @@
         <v>239</v>
       </c>
       <c r="F52">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G52">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H52">
         <v>1.24</v>
@@ -13472,10 +13472,10 @@
         <v>1.25</v>
       </c>
       <c r="J52">
+        <v>7.6</v>
+      </c>
+      <c r="K52">
         <v>7.8</v>
-      </c>
-      <c r="K52">
-        <v>8</v>
       </c>
       <c r="L52">
         <v>1.2</v>
@@ -13502,16 +13502,16 @@
         <v>1.88</v>
       </c>
       <c r="T52">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U52">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V52">
         <v>5</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
         <v>55</v>
@@ -13541,7 +13541,7 @@
         <v>160</v>
       </c>
       <c r="AG52">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AH52">
         <v>28</v>
@@ -13553,19 +13553,19 @@
         <v>530</v>
       </c>
       <c r="AK52">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AL52">
+        <v>120</v>
+      </c>
+      <c r="AM52">
         <v>110</v>
-      </c>
-      <c r="AM52">
-        <v>130</v>
       </c>
       <c r="AN52">
         <v>170</v>
       </c>
       <c r="AO52">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AP52">
         <v>44</v>
@@ -13583,7 +13583,7 @@
         <v>50</v>
       </c>
       <c r="AU52">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AV52">
         <v>11</v>
@@ -13592,7 +13592,7 @@
         <v>11</v>
       </c>
       <c r="AX52">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AY52">
         <v>42</v>
@@ -13604,10 +13604,10 @@
         <v>25</v>
       </c>
       <c r="BB52">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BC52">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BD52">
         <v>95</v>
@@ -13619,7 +13619,7 @@
         <v>120</v>
       </c>
       <c r="BG52">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH52">
         <v>6</v>
@@ -13631,10 +13631,10 @@
         <v>11.5</v>
       </c>
       <c r="BK52">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BL52">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BM52">
         <v>12</v>
@@ -13643,13 +13643,13 @@
         <v>15.5</v>
       </c>
       <c r="BO52">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BP52">
         <v>90</v>
       </c>
       <c r="BQ52">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR52">
         <v>60</v>
@@ -13667,7 +13667,7 @@
         <v>6.8</v>
       </c>
       <c r="BW52">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BX52">
         <v>18</v>
@@ -13714,10 +13714,10 @@
         <v>3.3</v>
       </c>
       <c r="J53">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K53">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L53">
         <v>1.35</v>
@@ -13726,7 +13726,7 @@
         <v>1.05</v>
       </c>
       <c r="N53">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O53">
         <v>1.26</v>
@@ -13738,10 +13738,10 @@
         <v>1.76</v>
       </c>
       <c r="R53">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S53">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T53">
         <v>1.64</v>
@@ -13810,64 +13810,64 @@
         <v>32</v>
       </c>
       <c r="AP53">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="AQ53">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AR53">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="AS53">
         <v>6.6</v>
       </c>
       <c r="AT53">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AU53">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AV53">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW53">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX53">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY53">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AZ53">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="BA53">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BB53">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BC53">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="BD53">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BE53">
         <v>6.8</v>
       </c>
       <c r="BF53">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BG53">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH53">
         <v>4.4</v>
       </c>
       <c r="BI53">
-        <v>2.26</v>
+        <v>2.98</v>
       </c>
       <c r="BJ53">
         <v>11</v>
@@ -13885,7 +13885,7 @@
         <v>6.6</v>
       </c>
       <c r="BO53">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP53">
         <v>21</v>
@@ -13903,7 +13903,7 @@
         <v>7.6</v>
       </c>
       <c r="BU53">
-        <v>2.88</v>
+        <v>5.6</v>
       </c>
       <c r="BV53">
         <v>28</v>
@@ -13947,19 +13947,19 @@
         <v>3.75</v>
       </c>
       <c r="G54">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="H54">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="I54">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="J54">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="K54">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="L54">
         <v>1.01</v>
@@ -13968,13 +13968,13 @@
         <v>1.01</v>
       </c>
       <c r="N54">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O54">
         <v>1.14</v>
       </c>
       <c r="P54">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q54">
         <v>1.14</v>
@@ -13992,49 +13992,49 @@
         <v>1.11</v>
       </c>
       <c r="V54">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="W54">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="X54">
         <v>1000</v>
       </c>
       <c r="Y54">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z54">
         <v>500</v>
       </c>
       <c r="AA54">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB54">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC54">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD54">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE54">
         <v>500</v>
       </c>
       <c r="AF54">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AG54">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH54">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI54">
         <v>500</v>
       </c>
       <c r="AJ54">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK54">
         <v>1000</v>
@@ -14046,64 +14046,64 @@
         <v>1000</v>
       </c>
       <c r="AN54">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AO54">
         <v>500</v>
       </c>
       <c r="AP54">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AQ54">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AR54">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AS54">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AT54">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AU54">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AV54">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AW54">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AX54">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AY54">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AZ54">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BA54">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BB54">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BC54">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BD54">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BE54">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BF54">
         <v>1.55</v>
       </c>
       <c r="BG54">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BH54">
         <v>1000</v>
@@ -14186,13 +14186,13 @@
         <v>242</v>
       </c>
       <c r="F55">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G55">
+        <v>2.9</v>
+      </c>
+      <c r="H55">
         <v>2.92</v>
-      </c>
-      <c r="H55">
-        <v>2.9</v>
       </c>
       <c r="I55">
         <v>3.05</v>
@@ -14201,7 +14201,7 @@
         <v>3.15</v>
       </c>
       <c r="K55">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L55">
         <v>1.5</v>
@@ -14213,43 +14213,43 @@
         <v>2.62</v>
       </c>
       <c r="O55">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P55">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q55">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R55">
         <v>1.19</v>
       </c>
       <c r="S55">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T55">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U55">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V55">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W55">
         <v>1.52</v>
       </c>
       <c r="X55">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y55">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z55">
         <v>18</v>
       </c>
       <c r="AA55">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB55">
         <v>8.199999999999999</v>
@@ -14267,13 +14267,13 @@
         <v>17.5</v>
       </c>
       <c r="AG55">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH55">
         <v>26</v>
       </c>
       <c r="AI55">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ55">
         <v>900</v>
@@ -14282,28 +14282,28 @@
         <v>95</v>
       </c>
       <c r="AL55">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM55">
         <v>580</v>
       </c>
       <c r="AN55">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO55">
         <v>70</v>
       </c>
       <c r="AP55">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ55">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR55">
         <v>15.5</v>
       </c>
       <c r="AS55">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT55">
         <v>7.4</v>
@@ -14312,10 +14312,10 @@
         <v>6.4</v>
       </c>
       <c r="AV55">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW55">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX55">
         <v>14.5</v>
@@ -14324,28 +14324,28 @@
         <v>12</v>
       </c>
       <c r="AZ55">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA55">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB55">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC55">
         <v>38</v>
       </c>
       <c r="BD55">
+        <v>10.5</v>
+      </c>
+      <c r="BE55">
+        <v>11.5</v>
+      </c>
+      <c r="BF55">
         <v>10</v>
       </c>
-      <c r="BE55">
-        <v>11</v>
-      </c>
-      <c r="BF55">
-        <v>32</v>
-      </c>
       <c r="BG55">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -14363,7 +14363,7 @@
         <v>1000</v>
       </c>
       <c r="BM55">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BN55">
         <v>1000</v>
@@ -14381,7 +14381,7 @@
         <v>1000</v>
       </c>
       <c r="BS55">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT55">
         <v>1000</v>
@@ -14399,13 +14399,13 @@
         <v>1000</v>
       </c>
       <c r="BY55">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ55">
         <v>1000</v>
       </c>
       <c r="CA55">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB55" t="s">
         <v>250</v>
@@ -14428,22 +14428,22 @@
         <v>243</v>
       </c>
       <c r="F56">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="G56">
         <v>3.35</v>
       </c>
       <c r="H56">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="I56">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="K56">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -14455,7 +14455,7 @@
         <v>3.05</v>
       </c>
       <c r="O56">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P56">
         <v>1.63</v>
@@ -14467,7 +14467,7 @@
         <v>1.22</v>
       </c>
       <c r="S56">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T56">
         <v>1.84</v>
@@ -14476,31 +14476,31 @@
         <v>1.87</v>
       </c>
       <c r="V56">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W56">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X56">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y56">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z56">
         <v>500</v>
       </c>
       <c r="AA56">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB56">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC56">
         <v>500</v>
       </c>
       <c r="AD56">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE56">
         <v>500</v>
@@ -14509,10 +14509,10 @@
         <v>500</v>
       </c>
       <c r="AG56">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH56">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI56">
         <v>500</v>
@@ -14536,58 +14536,58 @@
         <v>500</v>
       </c>
       <c r="AP56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AQ56">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="AR56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AS56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AT56">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AU56">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AV56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AW56">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AX56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AY56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AZ56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="BA56">
-        <v>24</v>
+        <v>1.25</v>
       </c>
       <c r="BB56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="BC56">
         <v>16</v>
       </c>
       <c r="BD56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="BE56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="BF56">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="BG56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="BH56">
         <v>1000</v>
@@ -14679,10 +14679,10 @@
         <v>2.1</v>
       </c>
       <c r="I57">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J57">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="K57">
         <v>950</v>
@@ -14694,13 +14694,13 @@
         <v>1.01</v>
       </c>
       <c r="N57">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O57">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="P57">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q57">
         <v>1.41</v>
@@ -14709,7 +14709,7 @@
         <v>1.18</v>
       </c>
       <c r="S57">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T57">
         <v>1.11</v>
@@ -14718,10 +14718,10 @@
         <v>1.11</v>
       </c>
       <c r="V57">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W57">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
         <v>1000</v>
@@ -14736,7 +14736,7 @@
         <v>1000</v>
       </c>
       <c r="AB57">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC57">
         <v>1000</v>
@@ -14751,7 +14751,7 @@
         <v>500</v>
       </c>
       <c r="AG57">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH57">
         <v>1000</v>
@@ -14778,58 +14778,58 @@
         <v>1000</v>
       </c>
       <c r="AP57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF57">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BG57">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH57">
         <v>1000</v>
@@ -14915,10 +14915,10 @@
         <v>1.32</v>
       </c>
       <c r="G58">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H58">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I58">
         <v>13.5</v>
@@ -14942,7 +14942,7 @@
         <v>1.25</v>
       </c>
       <c r="P58">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q58">
         <v>1.74</v>
@@ -14954,16 +14954,16 @@
         <v>2.92</v>
       </c>
       <c r="T58">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U58">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V58">
         <v>1.08</v>
       </c>
       <c r="W58">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X58">
         <v>21</v>
@@ -14984,7 +14984,7 @@
         <v>14</v>
       </c>
       <c r="AD58">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AE58">
         <v>250</v>
@@ -14996,10 +14996,10 @@
         <v>11</v>
       </c>
       <c r="AH58">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI58">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ58">
         <v>10.5</v>
@@ -15017,7 +15017,7 @@
         <v>5.6</v>
       </c>
       <c r="AO58">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="AP58">
         <v>18</v>
@@ -15026,10 +15026,10 @@
         <v>26</v>
       </c>
       <c r="AR58">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS58">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT58">
         <v>7.4</v>
@@ -15038,10 +15038,10 @@
         <v>12</v>
       </c>
       <c r="AV58">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AW58">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX58">
         <v>6.8</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="BA58">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB58">
         <v>9</v>
@@ -15062,16 +15062,16 @@
         <v>13.5</v>
       </c>
       <c r="BD58">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BE58">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF58">
         <v>5.1</v>
       </c>
       <c r="BG58">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH58">
         <v>1000</v>
@@ -15187,16 +15187,16 @@
         <v>1.89</v>
       </c>
       <c r="Q59">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R59">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S59">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T59">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U59">
         <v>2.04</v>
@@ -15211,13 +15211,13 @@
         <v>16</v>
       </c>
       <c r="Y59">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z59">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AA59">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB59">
         <v>8.6</v>
@@ -15226,7 +15226,7 @@
         <v>8.4</v>
       </c>
       <c r="AD59">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE59">
         <v>160</v>
@@ -15256,46 +15256,46 @@
         <v>580</v>
       </c>
       <c r="AN59">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO59">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP59">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ59">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR59">
         <v>14.5</v>
       </c>
       <c r="AS59">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT59">
         <v>7.8</v>
       </c>
       <c r="AU59">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV59">
         <v>15.5</v>
       </c>
       <c r="AW59">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX59">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY59">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ59">
         <v>17</v>
       </c>
       <c r="BA59">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB59">
         <v>20</v>
@@ -15307,13 +15307,13 @@
         <v>32</v>
       </c>
       <c r="BE59">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF59">
         <v>13.5</v>
       </c>
       <c r="BG59">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH59">
         <v>1000</v>
@@ -15408,7 +15408,7 @@
         <v>990</v>
       </c>
       <c r="J60">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K60">
         <v>950</v>
@@ -15420,7 +15420,7 @@
         <v>1.01</v>
       </c>
       <c r="N60">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O60">
         <v>1.4</v>
@@ -15435,7 +15435,7 @@
         <v>1.18</v>
       </c>
       <c r="S60">
-        <v>2.46</v>
+        <v>3.35</v>
       </c>
       <c r="T60">
         <v>1.11</v>
@@ -15444,10 +15444,10 @@
         <v>1.11</v>
       </c>
       <c r="V60">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W60">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -15462,7 +15462,7 @@
         <v>1000</v>
       </c>
       <c r="AB60">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC60">
         <v>1000</v>
@@ -15477,7 +15477,7 @@
         <v>500</v>
       </c>
       <c r="AG60">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH60">
         <v>1000</v>
@@ -15504,55 +15504,55 @@
         <v>1000</v>
       </c>
       <c r="AP60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF60">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BG60">
         <v>1.55</v>
@@ -15638,28 +15638,28 @@
         <v>248</v>
       </c>
       <c r="F61">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G61">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H61">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="I61">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J61">
         <v>3.25</v>
       </c>
       <c r="K61">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="L61">
         <v>1.01</v>
       </c>
       <c r="M61">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N61">
         <v>3.55</v>
@@ -15668,25 +15668,25 @@
         <v>1.31</v>
       </c>
       <c r="P61">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q61">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R61">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S61">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="T61">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U61">
         <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W61">
         <v>1.67</v>
@@ -15707,7 +15707,7 @@
         <v>1000</v>
       </c>
       <c r="AC61">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD61">
         <v>1000</v>
@@ -15746,58 +15746,58 @@
         <v>1000</v>
       </c>
       <c r="AP61">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AQ61">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR61">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS61">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AT61">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU61">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV61">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW61">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AX61">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AY61">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AZ61">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA61">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB61">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC61">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD61">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BE61">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF61">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG61">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH61">
         <v>3.8</v>
@@ -15889,7 +15889,7 @@
         <v>2.2</v>
       </c>
       <c r="I62">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J62">
         <v>3.4</v>
@@ -15904,13 +15904,13 @@
         <v>1.01</v>
       </c>
       <c r="N62">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O62">
         <v>1.21</v>
       </c>
       <c r="P62">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q62">
         <v>1.2</v>
@@ -15928,10 +15928,10 @@
         <v>1.11</v>
       </c>
       <c r="V62">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W62">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X62">
         <v>1000</v>
@@ -15988,52 +15988,52 @@
         <v>1000</v>
       </c>
       <c r="AP62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF62">
         <v>1.01</v>
